--- a/reports/scenario_comparison_dec_options.xlsx
+++ b/reports/scenario_comparison_dec_options.xlsx
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -97,8 +97,37 @@
       <color rgb="000F4C81"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="000F4C81"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001A2332"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="001B7A41"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="000F4C81"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001B7A41"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -113,6 +142,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9F2E2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8EFF9"/>
       </patternFill>
     </fill>
   </fills>
@@ -142,7 +176,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -180,6 +214,43 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -988,15 +1059,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J57"/>
+  <dimension ref="A1:H133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1009,12 +1082,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Option 1: park surplus trucks (fewer DT, same target met). Option 2: same trucks re-dispatched to the LONG STOCK routes KR→FENI KM0 and TF→FENI KM0 — kilnable stock built at the plants, fleet 100% used, sales lines still exactly met. Cuts come only from rows above their own target or from untargeted split flows; no targeted route drops below its line.</t>
+          <t>Option 1: park the surplus trucks. Option 2: re-dispatch the SAME trucks to the long stock routes KR→FENI KM0 and TF→FENI KM0 — kilnable stock at the plants, fleet 100% used, sales lines exactly met. Each scenario shows the full re-dispatched December plan (every route, new DT) and the material totals.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t>Scenario 3.0.1 — December</t>
         </is>
@@ -1042,6 +1115,7 @@
           <t>Fleet DT</t>
         </is>
       </c>
+      <c r="F5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
@@ -1072,7 +1146,7 @@
         <v>5131386</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>5132333</v>
+        <v>5132370</v>
       </c>
       <c r="D7" s="7" t="n">
         <v>1</v>
@@ -1091,7 +1165,7 @@
         <v>5131386</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>5132333</v>
+        <v>5132370</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>1</v>
@@ -1105,623 +1179,1008 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Cut from route</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Cut: TF&gt;HUAFEI (RIM, LD): −26 DT  →  re-dispatched to KR&gt;FENI KM0 (13 DT) + TF&gt;FENI KM0 (13 DT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>OPTION 2 — full December plan (re-dispatched)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Route</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Contractor</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>DT removed</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>t/day per DT</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>DT before</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>DT after</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Δ DT</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>t/day</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>t/month</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>TF&gt;HUAFEI</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>RIM</t>
         </is>
       </c>
-      <c r="C11" s="14" t="n">
-        <v>26</v>
-      </c>
-      <c r="D11" s="14" t="n">
-        <v>104.7</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Option 2 stock route</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>DT added</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>trips/DT/day</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>t/day</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>t/month (Dec)</t>
-        </is>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="n">
+        <v>437</v>
+      </c>
+      <c r="E13" s="19" t="n">
+        <v>411</v>
+      </c>
+      <c r="F13" s="19" t="n">
+        <v>-26</v>
+      </c>
+      <c r="G13" s="15" t="n">
+        <v>43013</v>
+      </c>
+      <c r="H13" s="15" t="n">
+        <v>1333403</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>KR&gt;FENI KM0</t>
-        </is>
-      </c>
-      <c r="B14" s="14" t="n">
-        <v>13</v>
-      </c>
-      <c r="C14" s="14" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="D14" s="15" t="n">
-        <v>1765</v>
-      </c>
-      <c r="E14" s="15" t="n">
-        <v>54712</v>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="n">
+        <v>150</v>
+      </c>
+      <c r="E14" s="14" t="n">
+        <v>150</v>
+      </c>
+      <c r="F14" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="15" t="n">
+        <v>15675</v>
+      </c>
+      <c r="H14" s="15" t="n">
+        <v>485925</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
+          <t>BLB&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="n">
+        <v>95</v>
+      </c>
+      <c r="E15" s="14" t="n">
+        <v>95</v>
+      </c>
+      <c r="F15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="15" t="n">
+        <v>23250</v>
+      </c>
+      <c r="H15" s="15" t="n">
+        <v>720750</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="n">
+        <v>62</v>
+      </c>
+      <c r="E16" s="14" t="n">
+        <v>62</v>
+      </c>
+      <c r="F16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="15" t="n">
+        <v>6489</v>
+      </c>
+      <c r="H16" s="15" t="n">
+        <v>201159</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>KR&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="n">
+        <v>19</v>
+      </c>
+      <c r="E17" s="14" t="n">
+        <v>19</v>
+      </c>
+      <c r="F17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="15" t="n">
+        <v>2563</v>
+      </c>
+      <c r="H17" s="15" t="n">
+        <v>79453</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>BLB&gt;FENI KM0</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="n">
+        <v>202</v>
+      </c>
+      <c r="E18" s="14" t="n">
+        <v>202</v>
+      </c>
+      <c r="F18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="15" t="n">
+        <v>45786</v>
+      </c>
+      <c r="H18" s="15" t="n">
+        <v>1419366</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>TF&gt;FENI KM15</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="n">
+        <v>140</v>
+      </c>
+      <c r="E19" s="14" t="n">
+        <v>140</v>
+      </c>
+      <c r="F19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="15" t="n">
+        <v>14736</v>
+      </c>
+      <c r="H19" s="15" t="n">
+        <v>456816</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>KR&gt;FENI KM15</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="E20" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="F20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="15" t="n">
+        <v>7958</v>
+      </c>
+      <c r="H20" s="15" t="n">
+        <v>246698</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>BLB&gt;POS 14</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="E21" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="F21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="15" t="n">
+        <v>2044</v>
+      </c>
+      <c r="H21" s="15" t="n">
+        <v>63364</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>TF&gt;POS 12</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="E22" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="F22" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="15" t="n">
+        <v>2039</v>
+      </c>
+      <c r="H22" s="15" t="n">
+        <v>63209</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>KR&gt;POS 12</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F23" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="15" t="n">
+        <v>2009</v>
+      </c>
+      <c r="H23" s="15" t="n">
+        <v>62279</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="20" t="inlineStr">
+        <is>
+          <t>KR&gt;FENI KM0</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>reallocated</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>STOCK (kilnable, FeNi KM0)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E24" s="28" t="n">
+        <v>13</v>
+      </c>
+      <c r="F24" s="28" t="n">
+        <v>13</v>
+      </c>
+      <c r="G24" s="29" t="n">
+        <v>1765</v>
+      </c>
+      <c r="H24" s="29" t="n">
+        <v>54712</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="20" t="inlineStr">
+        <is>
           <t>TF&gt;FENI KM0</t>
         </is>
       </c>
-      <c r="B15" s="14" t="n">
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>reallocated</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>STOCK (kilnable, FeNi KM0)</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E25" s="28" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="D15" s="15" t="n">
+      <c r="F25" s="28" t="n">
+        <v>13</v>
+      </c>
+      <c r="G25" s="29" t="n">
         <v>1432</v>
       </c>
-      <c r="E15" s="15" t="n">
+      <c r="H25" s="29" t="n">
         <v>44408</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="n"/>
+      <c r="C26" s="24" t="n"/>
+      <c r="D26" s="25" t="n">
+        <v>1190</v>
+      </c>
+      <c r="E26" s="25" t="n">
+        <v>1190</v>
+      </c>
+      <c r="F26" s="24" t="n"/>
+      <c r="G26" s="24" t="n"/>
+      <c r="H26" s="25" t="n">
+        <v>5231542</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>OPTION 2 — tonnage by material (December)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>t/month (new plan)</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>December sales share</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="14" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>2311732</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>2311213</v>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>1.000224557407734</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>1001362</v>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>996084</v>
+      </c>
+      <c r="D31" s="7" t="n">
+        <v>1.005298749904626</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="14" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>1819328</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>1719964</v>
+      </c>
+      <c r="D32" s="7" t="n">
+        <v>1.057770976601836</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="26" t="inlineStr">
+        <is>
+          <t>STOCK (kilnable, FeNi KM0)</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>99120</v>
+      </c>
+      <c r="C33" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D33" s="26" t="inlineStr">
+        <is>
+          <t>on top of the met sales lines</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="18" t="inlineStr">
         <is>
           <t>Scenario 3.0.2 — December</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr"/>
-      <c r="B19" s="3" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr"/>
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>Target t</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>Predicted t</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>Coverage</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="E37" s="3" t="inlineStr">
         <is>
           <t>Fleet DT</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="F37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
         <is>
           <t>As frozen</t>
         </is>
       </c>
-      <c r="B20" s="5" t="n">
+      <c r="B38" s="5" t="n">
         <v>5131386</v>
       </c>
-      <c r="C20" s="5" t="n">
+      <c r="C38" s="5" t="n">
         <v>5343787</v>
       </c>
-      <c r="D20" s="7" t="n">
+      <c r="D38" s="7" t="n">
         <v>1.041392520461333</v>
       </c>
-      <c r="E20" s="5" t="n">
+      <c r="E38" s="5" t="n">
         <v>1190</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="12" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="12" t="inlineStr">
         <is>
           <t>OPTION 1 · park 54 DT</t>
         </is>
       </c>
-      <c r="B21" s="5" t="n">
+      <c r="B39" s="5" t="n">
         <v>5131386</v>
       </c>
-      <c r="C21" s="5" t="n">
-        <v>5131189</v>
-      </c>
-      <c r="D21" s="7" t="n">
+      <c r="C39" s="5" t="n">
+        <v>5131167</v>
+      </c>
+      <c r="D39" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E21" s="5" t="n">
+      <c r="E39" s="5" t="n">
         <v>1136</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="13" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="13" t="inlineStr">
         <is>
           <t>OPTION 2 · re-dispatch 54 DT to stock</t>
         </is>
       </c>
-      <c r="B22" s="5" t="n">
+      <c r="B40" s="5" t="n">
         <v>5131386</v>
       </c>
-      <c r="C22" s="5" t="n">
-        <v>5131189</v>
-      </c>
-      <c r="D22" s="7" t="n">
+      <c r="C40" s="5" t="n">
+        <v>5131167</v>
+      </c>
+      <c r="D40" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E22" s="5" t="n">
+      <c r="E40" s="5" t="n">
         <v>1190</v>
       </c>
-      <c r="F22" s="13" t="inlineStr">
+      <c r="F40" s="13" t="inlineStr">
         <is>
           <t>+ 205,542 t stock to FeNi KM0</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>Cut from route</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Cut: TF&gt;POS 6 (RIM, LD): −54 DT  →  re-dispatched to KR&gt;FENI KM0 (27 DT) + TF&gt;FENI KM0 (27 DT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="16" t="inlineStr">
+        <is>
+          <t>OPTION 2 — full December plan (re-dispatched)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Route</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>Contractor</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>DT removed</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>t/day per DT</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="14" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>DT before</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>DT after</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Δ DT</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>t/day</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>t/month</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="14" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B45" s="14" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C45" s="14" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D45" s="14" t="n">
+        <v>288</v>
+      </c>
+      <c r="E45" s="14" t="n">
+        <v>288</v>
+      </c>
+      <c r="F45" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="15" t="n">
+        <v>30085</v>
+      </c>
+      <c r="H45" s="15" t="n">
+        <v>932635</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="14" t="inlineStr">
         <is>
           <t>TF&gt;POS 6</t>
         </is>
       </c>
-      <c r="B25" s="14" t="inlineStr">
+      <c r="B46" s="14" t="inlineStr">
         <is>
           <t>RIM</t>
         </is>
       </c>
-      <c r="C25" s="14" t="n">
-        <v>54</v>
-      </c>
-      <c r="D25" s="14" t="n">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>Option 2 stock route</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>DT added</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>trips/DT/day</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>t/day</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>t/month (Dec)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="14" t="inlineStr">
-        <is>
-          <t>KR&gt;FENI KM0</t>
-        </is>
-      </c>
-      <c r="B28" s="14" t="n">
-        <v>27</v>
-      </c>
-      <c r="C28" s="14" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="D28" s="15" t="n">
-        <v>3661</v>
-      </c>
-      <c r="E28" s="15" t="n">
-        <v>113497</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="14" t="inlineStr">
-        <is>
-          <t>TF&gt;FENI KM0</t>
-        </is>
-      </c>
-      <c r="B29" s="14" t="n">
-        <v>27</v>
-      </c>
-      <c r="C29" s="14" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="D29" s="15" t="n">
-        <v>2969</v>
-      </c>
-      <c r="E29" s="15" t="n">
-        <v>92045</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="8" t="inlineStr">
-        <is>
-          <t>Scenario 3.1.1 — December</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr"/>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>Target t</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>Predicted t</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>Coverage</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>Fleet DT</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="11" t="inlineStr">
-        <is>
-          <t>As frozen</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="n">
-        <v>4810381</v>
-      </c>
-      <c r="C34" s="5" t="n">
-        <v>4971401</v>
-      </c>
-      <c r="D34" s="7" t="n">
-        <v>1.033473440045601</v>
-      </c>
-      <c r="E34" s="5" t="n">
-        <v>1052</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="12" t="inlineStr">
-        <is>
-          <t>OPTION 1 · park 49 DT</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="n">
-        <v>4810381</v>
-      </c>
-      <c r="C35" s="5" t="n">
-        <v>4811602</v>
-      </c>
-      <c r="D35" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E35" s="5" t="n">
-        <v>1003</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="13" t="inlineStr">
-        <is>
-          <t>OPTION 2 · re-dispatch 49 DT to stock</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="n">
-        <v>4810381</v>
-      </c>
-      <c r="C36" s="5" t="n">
-        <v>4811602</v>
-      </c>
-      <c r="D36" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E36" s="5" t="n">
-        <v>1052</v>
-      </c>
-      <c r="F36" s="13" t="inlineStr">
-        <is>
-          <t>+ 182,767 t stock to FeNi KM0</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>Cut from route</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>Contractor</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>DT removed</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>t/day per DT</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="14" t="inlineStr">
+      <c r="C46" s="14" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D46" s="14" t="n">
+        <v>149</v>
+      </c>
+      <c r="E46" s="19" t="n">
+        <v>95</v>
+      </c>
+      <c r="F46" s="19" t="n">
+        <v>-54</v>
+      </c>
+      <c r="G46" s="15" t="n">
+        <v>12066</v>
+      </c>
+      <c r="H46" s="15" t="n">
+        <v>374055</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="14" t="inlineStr">
+        <is>
+          <t>TF&gt;POS 6</t>
+        </is>
+      </c>
+      <c r="B47" s="14" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C47" s="14" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D47" s="14" t="n">
+        <v>75</v>
+      </c>
+      <c r="E47" s="14" t="n">
+        <v>75</v>
+      </c>
+      <c r="F47" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="15" t="n">
+        <v>8701</v>
+      </c>
+      <c r="H47" s="15" t="n">
+        <v>269731</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="14" t="inlineStr">
         <is>
           <t>TF&gt;HUAFEI</t>
         </is>
       </c>
-      <c r="B39" s="14" t="inlineStr">
+      <c r="B48" s="14" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C48" s="14" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D48" s="14" t="n">
+        <v>75</v>
+      </c>
+      <c r="E48" s="14" t="n">
+        <v>75</v>
+      </c>
+      <c r="F48" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="15" t="n">
+        <v>7822</v>
+      </c>
+      <c r="H48" s="15" t="n">
+        <v>242482</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="14" t="inlineStr">
+        <is>
+          <t>BLB&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B49" s="14" t="inlineStr">
         <is>
           <t>RIM</t>
         </is>
       </c>
-      <c r="C39" s="14" t="n">
-        <v>49</v>
-      </c>
-      <c r="D39" s="14" t="n">
-        <v>105.2</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>Option 2 stock route</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>DT added</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>trips/DT/day</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>t/day</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>t/month (Dec)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="14" t="inlineStr">
-        <is>
-          <t>KR&gt;FENI KM0</t>
-        </is>
-      </c>
-      <c r="B42" s="14" t="n">
-        <v>24</v>
-      </c>
-      <c r="C42" s="14" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="D42" s="15" t="n">
-        <v>3255</v>
-      </c>
-      <c r="E42" s="15" t="n">
-        <v>100911</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="14" t="inlineStr">
-        <is>
-          <t>TF&gt;FENI KM0</t>
-        </is>
-      </c>
-      <c r="B43" s="14" t="n">
-        <v>24</v>
-      </c>
-      <c r="C43" s="14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="D43" s="15" t="n">
-        <v>2640</v>
-      </c>
-      <c r="E43" s="15" t="n">
-        <v>81856</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="8" t="inlineStr">
-        <is>
-          <t>Scenario 3.1.2 — December</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr"/>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>Target t</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>Predicted t</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>Coverage</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="inlineStr">
-        <is>
-          <t>Fleet DT</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="11" t="inlineStr">
-        <is>
-          <t>As frozen</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="n">
-        <v>4810381</v>
-      </c>
-      <c r="C48" s="5" t="n">
-        <v>5045234</v>
-      </c>
-      <c r="D48" s="7" t="n">
-        <v>1.048822120326852</v>
-      </c>
-      <c r="E48" s="5" t="n">
-        <v>1052</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="12" t="inlineStr">
-        <is>
-          <t>OPTION 1 · park 59 DT</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="n">
-        <v>4810381</v>
-      </c>
-      <c r="C49" s="5" t="n">
-        <v>4811671</v>
-      </c>
-      <c r="D49" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E49" s="5" t="n">
-        <v>993</v>
+      <c r="C49" s="14" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D49" s="14" t="n">
+        <v>95</v>
+      </c>
+      <c r="E49" s="14" t="n">
+        <v>95</v>
+      </c>
+      <c r="F49" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="15" t="n">
+        <v>23250</v>
+      </c>
+      <c r="H49" s="15" t="n">
+        <v>720750</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="13" t="inlineStr">
-        <is>
-          <t>OPTION 2 · re-dispatch 59 DT to stock</t>
-        </is>
-      </c>
-      <c r="B50" s="5" t="n">
-        <v>4810381</v>
-      </c>
-      <c r="C50" s="5" t="n">
-        <v>4811671</v>
-      </c>
-      <c r="D50" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E50" s="5" t="n">
-        <v>1052</v>
-      </c>
-      <c r="F50" s="13" t="inlineStr">
-        <is>
-          <t>+ 228,303 t stock to FeNi KM0</t>
-        </is>
+      <c r="A50" s="14" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B50" s="14" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C50" s="14" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D50" s="14" t="n">
+        <v>62</v>
+      </c>
+      <c r="E50" s="14" t="n">
+        <v>62</v>
+      </c>
+      <c r="F50" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="15" t="n">
+        <v>6477</v>
+      </c>
+      <c r="H50" s="15" t="n">
+        <v>200787</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="14" t="inlineStr">
+        <is>
+          <t>KR&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B51" s="14" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C51" s="14" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D51" s="14" t="n">
+        <v>19</v>
+      </c>
+      <c r="E51" s="14" t="n">
+        <v>19</v>
+      </c>
+      <c r="F51" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="15" t="n">
+        <v>2549</v>
+      </c>
+      <c r="H51" s="15" t="n">
+        <v>79019</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>Cut from route</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>Contractor</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t>DT removed</t>
-        </is>
-      </c>
-      <c r="D52" s="3" t="inlineStr">
-        <is>
-          <t>t/day per DT</t>
-        </is>
+      <c r="A52" s="14" t="inlineStr">
+        <is>
+          <t>BLB&gt;FENI KM0</t>
+        </is>
+      </c>
+      <c r="B52" s="14" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C52" s="14" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D52" s="14" t="n">
+        <v>202</v>
+      </c>
+      <c r="E52" s="14" t="n">
+        <v>202</v>
+      </c>
+      <c r="F52" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="15" t="n">
+        <v>45786</v>
+      </c>
+      <c r="H52" s="15" t="n">
+        <v>1419366</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="14" t="inlineStr">
         <is>
-          <t>TF&gt;POS 6</t>
+          <t>TF&gt;FENI KM15</t>
         </is>
       </c>
       <c r="B53" s="14" t="inlineStr">
@@ -1729,81 +2188,1783 @@
           <t>RIM</t>
         </is>
       </c>
-      <c r="C53" s="14" t="n">
-        <v>59</v>
+      <c r="C53" s="14" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
       </c>
       <c r="D53" s="14" t="n">
-        <v>127.7</v>
+        <v>140</v>
+      </c>
+      <c r="E53" s="14" t="n">
+        <v>140</v>
+      </c>
+      <c r="F53" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="15" t="n">
+        <v>14736</v>
+      </c>
+      <c r="H53" s="15" t="n">
+        <v>456816</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="14" t="inlineStr">
+        <is>
+          <t>KR&gt;FENI KM15</t>
+        </is>
+      </c>
+      <c r="B54" s="14" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C54" s="14" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D54" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="E54" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="F54" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="15" t="n">
+        <v>7958</v>
+      </c>
+      <c r="H54" s="15" t="n">
+        <v>246698</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>Option 2 stock route</t>
-        </is>
-      </c>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>DT added</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>trips/DT/day</t>
-        </is>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>t/day</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="inlineStr">
-        <is>
-          <t>t/month (Dec)</t>
-        </is>
+      <c r="A55" s="14" t="inlineStr">
+        <is>
+          <t>BLB&gt;POS 14</t>
+        </is>
+      </c>
+      <c r="B55" s="14" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C55" s="14" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D55" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="E55" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="F55" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="15" t="n">
+        <v>2044</v>
+      </c>
+      <c r="H55" s="15" t="n">
+        <v>63364</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="14" t="inlineStr">
         <is>
-          <t>KR&gt;FENI KM0</t>
-        </is>
-      </c>
-      <c r="B56" s="14" t="n">
-        <v>30</v>
-      </c>
-      <c r="C56" s="14" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="D56" s="15" t="n">
-        <v>4067</v>
-      </c>
-      <c r="E56" s="15" t="n">
-        <v>126074</v>
+          <t>TF&gt;POS 12</t>
+        </is>
+      </c>
+      <c r="B56" s="14" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C56" s="14" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D56" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="E56" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="F56" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="15" t="n">
+        <v>2039</v>
+      </c>
+      <c r="H56" s="15" t="n">
+        <v>63209</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="14" t="inlineStr">
         <is>
+          <t>KR&gt;POS 12</t>
+        </is>
+      </c>
+      <c r="B57" s="14" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C57" s="14" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D57" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E57" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F57" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="15" t="n">
+        <v>2009</v>
+      </c>
+      <c r="H57" s="15" t="n">
+        <v>62279</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="20" t="inlineStr">
+        <is>
+          <t>KR&gt;FENI KM0</t>
+        </is>
+      </c>
+      <c r="B58" s="20" t="inlineStr">
+        <is>
+          <t>reallocated</t>
+        </is>
+      </c>
+      <c r="C58" s="20" t="inlineStr">
+        <is>
+          <t>STOCK (kilnable, FeNi KM0)</t>
+        </is>
+      </c>
+      <c r="D58" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E58" s="28" t="n">
+        <v>27</v>
+      </c>
+      <c r="F58" s="28" t="n">
+        <v>27</v>
+      </c>
+      <c r="G58" s="29" t="n">
+        <v>3661</v>
+      </c>
+      <c r="H58" s="29" t="n">
+        <v>113497</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="20" t="inlineStr">
+        <is>
           <t>TF&gt;FENI KM0</t>
         </is>
       </c>
-      <c r="B57" s="14" t="n">
+      <c r="B59" s="20" t="inlineStr">
+        <is>
+          <t>reallocated</t>
+        </is>
+      </c>
+      <c r="C59" s="20" t="inlineStr">
+        <is>
+          <t>STOCK (kilnable, FeNi KM0)</t>
+        </is>
+      </c>
+      <c r="D59" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E59" s="28" t="n">
+        <v>27</v>
+      </c>
+      <c r="F59" s="28" t="n">
+        <v>27</v>
+      </c>
+      <c r="G59" s="29" t="n">
+        <v>2969</v>
+      </c>
+      <c r="H59" s="29" t="n">
+        <v>92045</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="24" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B60" s="24" t="n"/>
+      <c r="C60" s="24" t="n"/>
+      <c r="D60" s="25" t="n">
+        <v>1190</v>
+      </c>
+      <c r="E60" s="25" t="n">
+        <v>1190</v>
+      </c>
+      <c r="F60" s="24" t="n"/>
+      <c r="G60" s="24" t="n"/>
+      <c r="H60" s="25" t="n">
+        <v>5336733</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="16" t="inlineStr">
+        <is>
+          <t>OPTION 2 — tonnage by material (December)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>t/month (new plan)</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>December sales share</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="14" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="n">
+        <v>2311732</v>
+      </c>
+      <c r="C64" s="5" t="n">
+        <v>2311213</v>
+      </c>
+      <c r="D64" s="7" t="n">
+        <v>1.000224557407734</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="14" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="n">
+        <v>1000556</v>
+      </c>
+      <c r="C65" s="5" t="n">
+        <v>996084</v>
+      </c>
+      <c r="D65" s="7" t="n">
+        <v>1.004489581199979</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="14" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="n">
+        <v>1818903</v>
+      </c>
+      <c r="C66" s="5" t="n">
+        <v>1719964</v>
+      </c>
+      <c r="D66" s="7" t="n">
+        <v>1.057523878406757</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="26" t="inlineStr">
+        <is>
+          <t>STOCK (kilnable, FeNi KM0)</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="n">
+        <v>205542</v>
+      </c>
+      <c r="C67" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D67" s="26" t="inlineStr">
+        <is>
+          <t>on top of the met sales lines</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="18" t="inlineStr">
+        <is>
+          <t>Scenario 3.1.1 — December</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr"/>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>Target t</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>Predicted t</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>Fleet DT</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="11" t="inlineStr">
+        <is>
+          <t>As frozen</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="n">
+        <v>4810381</v>
+      </c>
+      <c r="C72" s="5" t="n">
+        <v>4971401</v>
+      </c>
+      <c r="D72" s="7" t="n">
+        <v>1.033473440045601</v>
+      </c>
+      <c r="E72" s="5" t="n">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="12" t="inlineStr">
+        <is>
+          <t>OPTION 1 · park 49 DT</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="n">
+        <v>4810381</v>
+      </c>
+      <c r="C73" s="5" t="n">
+        <v>4811620</v>
+      </c>
+      <c r="D73" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" s="5" t="n">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="13" t="inlineStr">
+        <is>
+          <t>OPTION 2 · re-dispatch 49 DT to stock</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="n">
+        <v>4810381</v>
+      </c>
+      <c r="C74" s="5" t="n">
+        <v>4811620</v>
+      </c>
+      <c r="D74" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" s="5" t="n">
+        <v>1052</v>
+      </c>
+      <c r="F74" s="13" t="inlineStr">
+        <is>
+          <t>+ 182,767 t stock to FeNi KM0</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Cut: TF&gt;HUAFEI (RIM, LD): −49 DT  →  re-dispatched to KR&gt;FENI KM0 (24 DT) + TF&gt;FENI KM0 (24 DT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="16" t="inlineStr">
+        <is>
+          <t>OPTION 2 — full December plan (re-dispatched)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>Route</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>Contractor</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>DT before</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>DT after</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>Δ DT</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="inlineStr">
+        <is>
+          <t>t/day</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>t/month</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="14" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B79" s="14" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C79" s="14" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D79" s="14" t="n">
+        <v>319</v>
+      </c>
+      <c r="E79" s="19" t="n">
+        <v>270</v>
+      </c>
+      <c r="F79" s="19" t="n">
+        <v>-49</v>
+      </c>
+      <c r="G79" s="15" t="n">
+        <v>28401</v>
+      </c>
+      <c r="H79" s="15" t="n">
+        <v>880424</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="14" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B80" s="14" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C80" s="14" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D80" s="14" t="n">
+        <v>87</v>
+      </c>
+      <c r="E80" s="14" t="n">
+        <v>87</v>
+      </c>
+      <c r="F80" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" s="15" t="n">
+        <v>9142</v>
+      </c>
+      <c r="H80" s="15" t="n">
+        <v>283402</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="14" t="inlineStr">
+        <is>
+          <t>BLB&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B81" s="14" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C81" s="14" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D81" s="14" t="n">
+        <v>139</v>
+      </c>
+      <c r="E81" s="14" t="n">
+        <v>139</v>
+      </c>
+      <c r="F81" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" s="15" t="n">
+        <v>33859</v>
+      </c>
+      <c r="H81" s="15" t="n">
+        <v>1049629</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="14" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B82" s="14" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C82" s="14" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D82" s="14" t="n">
+        <v>62</v>
+      </c>
+      <c r="E82" s="14" t="n">
+        <v>62</v>
+      </c>
+      <c r="F82" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" s="15" t="n">
+        <v>6522</v>
+      </c>
+      <c r="H82" s="15" t="n">
+        <v>202182</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="14" t="inlineStr">
+        <is>
+          <t>KR&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B83" s="14" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C83" s="14" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D83" s="14" t="n">
+        <v>19</v>
+      </c>
+      <c r="E83" s="14" t="n">
+        <v>19</v>
+      </c>
+      <c r="F83" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" s="15" t="n">
+        <v>2597</v>
+      </c>
+      <c r="H83" s="15" t="n">
+        <v>80507</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="14" t="inlineStr">
+        <is>
+          <t>BLB&gt;FENI KM0</t>
+        </is>
+      </c>
+      <c r="B84" s="14" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C84" s="14" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D84" s="14" t="n">
+        <v>202</v>
+      </c>
+      <c r="E84" s="14" t="n">
+        <v>202</v>
+      </c>
+      <c r="F84" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" s="15" t="n">
+        <v>45786</v>
+      </c>
+      <c r="H84" s="15" t="n">
+        <v>1419366</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="14" t="inlineStr">
+        <is>
+          <t>TF&gt;FENI KM15</t>
+        </is>
+      </c>
+      <c r="B85" s="14" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C85" s="14" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D85" s="14" t="n">
+        <v>140</v>
+      </c>
+      <c r="E85" s="14" t="n">
+        <v>140</v>
+      </c>
+      <c r="F85" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" s="15" t="n">
+        <v>14847</v>
+      </c>
+      <c r="H85" s="15" t="n">
+        <v>460257</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="14" t="inlineStr">
+        <is>
+          <t>KR&gt;FENI KM15</t>
+        </is>
+      </c>
+      <c r="B86" s="14" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C86" s="14" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D86" s="14" t="n">
+        <v>49</v>
+      </c>
+      <c r="E86" s="14" t="n">
+        <v>49</v>
+      </c>
+      <c r="F86" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="15" t="n">
+        <v>7929</v>
+      </c>
+      <c r="H86" s="15" t="n">
+        <v>245799</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="14" t="inlineStr">
+        <is>
+          <t>TF&gt;POS 12</t>
+        </is>
+      </c>
+      <c r="B87" s="14" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C87" s="14" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D87" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="E87" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="F87" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="15" t="n">
+        <v>2045</v>
+      </c>
+      <c r="H87" s="15" t="n">
+        <v>63395</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="14" t="inlineStr">
+        <is>
+          <t>BLB&gt;POS 14</t>
+        </is>
+      </c>
+      <c r="B88" s="14" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C88" s="14" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D88" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="E88" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="F88" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="15" t="n">
+        <v>2044</v>
+      </c>
+      <c r="H88" s="15" t="n">
+        <v>63364</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="14" t="inlineStr">
+        <is>
+          <t>KR&gt;POS 12</t>
+        </is>
+      </c>
+      <c r="B89" s="14" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C89" s="14" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D89" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E89" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F89" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" s="15" t="n">
+        <v>2042</v>
+      </c>
+      <c r="H89" s="15" t="n">
+        <v>63302</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="20" t="inlineStr">
+        <is>
+          <t>KR&gt;FENI KM0</t>
+        </is>
+      </c>
+      <c r="B90" s="20" t="inlineStr">
+        <is>
+          <t>reallocated</t>
+        </is>
+      </c>
+      <c r="C90" s="20" t="inlineStr">
+        <is>
+          <t>STOCK (kilnable, FeNi KM0)</t>
+        </is>
+      </c>
+      <c r="D90" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E90" s="28" t="n">
+        <v>24</v>
+      </c>
+      <c r="F90" s="28" t="n">
+        <v>24</v>
+      </c>
+      <c r="G90" s="29" t="n">
+        <v>3255</v>
+      </c>
+      <c r="H90" s="29" t="n">
+        <v>100911</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="20" t="inlineStr">
+        <is>
+          <t>TF&gt;FENI KM0</t>
+        </is>
+      </c>
+      <c r="B91" s="20" t="inlineStr">
+        <is>
+          <t>reallocated</t>
+        </is>
+      </c>
+      <c r="C91" s="20" t="inlineStr">
+        <is>
+          <t>STOCK (kilnable, FeNi KM0)</t>
+        </is>
+      </c>
+      <c r="D91" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E91" s="28" t="n">
+        <v>24</v>
+      </c>
+      <c r="F91" s="28" t="n">
+        <v>24</v>
+      </c>
+      <c r="G91" s="29" t="n">
+        <v>2640</v>
+      </c>
+      <c r="H91" s="29" t="n">
+        <v>81856</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="24" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B92" s="24" t="n"/>
+      <c r="C92" s="24" t="n"/>
+      <c r="D92" s="25" t="n">
+        <v>1052</v>
+      </c>
+      <c r="E92" s="25" t="n">
+        <v>1051</v>
+      </c>
+      <c r="F92" s="24" t="n"/>
+      <c r="G92" s="24" t="n"/>
+      <c r="H92" s="25" t="n">
+        <v>4994394</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="16" t="inlineStr">
+        <is>
+          <t>OPTION 2 — tonnage by material (December)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>t/month (new plan)</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>December sales share</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="14" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="n">
+        <v>2315483</v>
+      </c>
+      <c r="C96" s="5" t="n">
+        <v>2311213</v>
+      </c>
+      <c r="D96" s="7" t="n">
+        <v>1.001847514703318</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="14" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="n">
+        <v>1332318</v>
+      </c>
+      <c r="C97" s="5" t="n">
+        <v>1326082</v>
+      </c>
+      <c r="D97" s="7" t="n">
+        <v>1.004702574953887</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="14" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="B98" s="5" t="n">
+        <v>1163826</v>
+      </c>
+      <c r="C98" s="5" t="n">
+        <v>992213</v>
+      </c>
+      <c r="D98" s="7" t="n">
+        <v>1.172959838260535</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="26" t="inlineStr">
+        <is>
+          <t>STOCK (kilnable, FeNi KM0)</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="n">
+        <v>182767</v>
+      </c>
+      <c r="C99" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D99" s="26" t="inlineStr">
+        <is>
+          <t>on top of the met sales lines</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="18" t="inlineStr">
+        <is>
+          <t>Scenario 3.1.2 — December</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr"/>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>Target t</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>Predicted t</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>Fleet DT</t>
+        </is>
+      </c>
+      <c r="F103" s="3" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="11" t="inlineStr">
+        <is>
+          <t>As frozen</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="n">
+        <v>4810381</v>
+      </c>
+      <c r="C104" s="5" t="n">
+        <v>5045234</v>
+      </c>
+      <c r="D104" s="7" t="n">
+        <v>1.048822120326852</v>
+      </c>
+      <c r="E104" s="5" t="n">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="12" t="inlineStr">
+        <is>
+          <t>OPTION 1 · park 59 DT</t>
+        </is>
+      </c>
+      <c r="B105" s="5" t="n">
+        <v>4810381</v>
+      </c>
+      <c r="C105" s="5" t="n">
+        <v>4811739</v>
+      </c>
+      <c r="D105" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E105" s="5" t="n">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="13" t="inlineStr">
+        <is>
+          <t>OPTION 2 · re-dispatch 59 DT to stock</t>
+        </is>
+      </c>
+      <c r="B106" s="5" t="n">
+        <v>4810381</v>
+      </c>
+      <c r="C106" s="5" t="n">
+        <v>4811739</v>
+      </c>
+      <c r="D106" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E106" s="5" t="n">
+        <v>1052</v>
+      </c>
+      <c r="F106" s="13" t="inlineStr">
+        <is>
+          <t>+ 228,303 t stock to FeNi KM0</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>Cut: TF&gt;POS 6 (RIM, LD): −59 DT  →  re-dispatched to KR&gt;FENI KM0 (30 DT) + TF&gt;FENI KM0 (30 DT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="16" t="inlineStr">
+        <is>
+          <t>OPTION 2 — full December plan (re-dispatched)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="inlineStr">
+        <is>
+          <t>Route</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>Contractor</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>DT before</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>DT after</t>
+        </is>
+      </c>
+      <c r="F110" s="3" t="inlineStr">
+        <is>
+          <t>Δ DT</t>
+        </is>
+      </c>
+      <c r="G110" s="3" t="inlineStr">
+        <is>
+          <t>t/day</t>
+        </is>
+      </c>
+      <c r="H110" s="3" t="inlineStr">
+        <is>
+          <t>t/month</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="14" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B111" s="14" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C111" s="14" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D111" s="14" t="n">
+        <v>233</v>
+      </c>
+      <c r="E111" s="14" t="n">
+        <v>233</v>
+      </c>
+      <c r="F111" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G111" s="15" t="n">
+        <v>24482</v>
+      </c>
+      <c r="H111" s="15" t="n">
+        <v>758942</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="14" t="inlineStr">
+        <is>
+          <t>TF&gt;POS 6</t>
+        </is>
+      </c>
+      <c r="B112" s="14" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C112" s="14" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D112" s="14" t="n">
+        <v>43</v>
+      </c>
+      <c r="E112" s="14" t="n">
+        <v>43</v>
+      </c>
+      <c r="F112" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" s="15" t="n">
+        <v>5014</v>
+      </c>
+      <c r="H112" s="15" t="n">
+        <v>155434</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="14" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B113" s="14" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C113" s="14" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D113" s="14" t="n">
+        <v>44</v>
+      </c>
+      <c r="E113" s="14" t="n">
+        <v>44</v>
+      </c>
+      <c r="F113" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G113" s="15" t="n">
+        <v>4618</v>
+      </c>
+      <c r="H113" s="15" t="n">
+        <v>143158</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="14" t="inlineStr">
+        <is>
+          <t>TF&gt;POS 6</t>
+        </is>
+      </c>
+      <c r="B114" s="14" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C114" s="14" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D114" s="14" t="n">
+        <v>86</v>
+      </c>
+      <c r="E114" s="19" t="n">
+        <v>27</v>
+      </c>
+      <c r="F114" s="19" t="n">
+        <v>-59</v>
+      </c>
+      <c r="G114" s="15" t="n">
+        <v>3447</v>
+      </c>
+      <c r="H114" s="15" t="n">
+        <v>106854</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="14" t="inlineStr">
+        <is>
+          <t>BLB&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B115" s="14" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C115" s="14" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D115" s="14" t="n">
+        <v>139</v>
+      </c>
+      <c r="E115" s="14" t="n">
+        <v>139</v>
+      </c>
+      <c r="F115" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G115" s="15" t="n">
+        <v>33859</v>
+      </c>
+      <c r="H115" s="15" t="n">
+        <v>1049629</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="14" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B116" s="14" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C116" s="14" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D116" s="14" t="n">
+        <v>62</v>
+      </c>
+      <c r="E116" s="14" t="n">
+        <v>62</v>
+      </c>
+      <c r="F116" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G116" s="15" t="n">
+        <v>6514</v>
+      </c>
+      <c r="H116" s="15" t="n">
+        <v>201934</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="14" t="inlineStr">
+        <is>
+          <t>KR&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B117" s="14" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C117" s="14" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D117" s="14" t="n">
+        <v>19</v>
+      </c>
+      <c r="E117" s="14" t="n">
+        <v>19</v>
+      </c>
+      <c r="F117" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G117" s="15" t="n">
+        <v>2590</v>
+      </c>
+      <c r="H117" s="15" t="n">
+        <v>80290</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="14" t="inlineStr">
+        <is>
+          <t>BLB&gt;FENI KM0</t>
+        </is>
+      </c>
+      <c r="B118" s="14" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C118" s="14" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D118" s="14" t="n">
+        <v>202</v>
+      </c>
+      <c r="E118" s="14" t="n">
+        <v>202</v>
+      </c>
+      <c r="F118" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G118" s="15" t="n">
+        <v>45786</v>
+      </c>
+      <c r="H118" s="15" t="n">
+        <v>1419366</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="14" t="inlineStr">
+        <is>
+          <t>TF&gt;FENI KM15</t>
+        </is>
+      </c>
+      <c r="B119" s="14" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C119" s="14" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D119" s="14" t="n">
+        <v>140</v>
+      </c>
+      <c r="E119" s="14" t="n">
+        <v>140</v>
+      </c>
+      <c r="F119" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G119" s="15" t="n">
+        <v>14847</v>
+      </c>
+      <c r="H119" s="15" t="n">
+        <v>460257</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="14" t="inlineStr">
+        <is>
+          <t>KR&gt;FENI KM15</t>
+        </is>
+      </c>
+      <c r="B120" s="14" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C120" s="14" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D120" s="14" t="n">
+        <v>49</v>
+      </c>
+      <c r="E120" s="14" t="n">
+        <v>49</v>
+      </c>
+      <c r="F120" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G120" s="15" t="n">
+        <v>7929</v>
+      </c>
+      <c r="H120" s="15" t="n">
+        <v>245799</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="14" t="inlineStr">
+        <is>
+          <t>TF&gt;POS 12</t>
+        </is>
+      </c>
+      <c r="B121" s="14" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C121" s="14" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D121" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="E121" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="F121" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G121" s="15" t="n">
+        <v>2045</v>
+      </c>
+      <c r="H121" s="15" t="n">
+        <v>63395</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="14" t="inlineStr">
+        <is>
+          <t>BLB&gt;POS 14</t>
+        </is>
+      </c>
+      <c r="B122" s="14" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C122" s="14" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D122" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="E122" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="F122" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G122" s="15" t="n">
+        <v>2044</v>
+      </c>
+      <c r="H122" s="15" t="n">
+        <v>63364</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="14" t="inlineStr">
+        <is>
+          <t>KR&gt;POS 12</t>
+        </is>
+      </c>
+      <c r="B123" s="14" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C123" s="14" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D123" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E123" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F123" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G123" s="15" t="n">
+        <v>2042</v>
+      </c>
+      <c r="H123" s="15" t="n">
+        <v>63302</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="20" t="inlineStr">
+        <is>
+          <t>KR&gt;FENI KM0</t>
+        </is>
+      </c>
+      <c r="B124" s="20" t="inlineStr">
+        <is>
+          <t>reallocated</t>
+        </is>
+      </c>
+      <c r="C124" s="20" t="inlineStr">
+        <is>
+          <t>STOCK (kilnable, FeNi KM0)</t>
+        </is>
+      </c>
+      <c r="D124" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E124" s="28" t="n">
         <v>30</v>
       </c>
-      <c r="C57" s="14" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="D57" s="15" t="n">
+      <c r="F124" s="28" t="n">
+        <v>30</v>
+      </c>
+      <c r="G124" s="29" t="n">
+        <v>4067</v>
+      </c>
+      <c r="H124" s="29" t="n">
+        <v>126074</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="20" t="inlineStr">
+        <is>
+          <t>TF&gt;FENI KM0</t>
+        </is>
+      </c>
+      <c r="B125" s="20" t="inlineStr">
+        <is>
+          <t>reallocated</t>
+        </is>
+      </c>
+      <c r="C125" s="20" t="inlineStr">
+        <is>
+          <t>STOCK (kilnable, FeNi KM0)</t>
+        </is>
+      </c>
+      <c r="D125" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E125" s="28" t="n">
+        <v>30</v>
+      </c>
+      <c r="F125" s="28" t="n">
+        <v>30</v>
+      </c>
+      <c r="G125" s="29" t="n">
         <v>3298</v>
       </c>
-      <c r="E57" s="15" t="n">
+      <c r="H125" s="29" t="n">
         <v>102229</v>
       </c>
     </row>
+    <row r="126">
+      <c r="A126" s="24" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B126" s="24" t="n"/>
+      <c r="C126" s="24" t="n"/>
+      <c r="D126" s="25" t="n">
+        <v>1052</v>
+      </c>
+      <c r="E126" s="25" t="n">
+        <v>1053</v>
+      </c>
+      <c r="F126" s="24" t="n"/>
+      <c r="G126" s="24" t="n"/>
+      <c r="H126" s="25" t="n">
+        <v>5040027</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="16" t="inlineStr">
+        <is>
+          <t>OPTION 2 — tonnage by material (December)</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>t/month (new plan)</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t>December sales share</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="14" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B130" s="5" t="n">
+        <v>2315483</v>
+      </c>
+      <c r="C130" s="5" t="n">
+        <v>2311213</v>
+      </c>
+      <c r="D130" s="7" t="n">
+        <v>1.001847514703318</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="14" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="B131" s="5" t="n">
+        <v>1331853</v>
+      </c>
+      <c r="C131" s="5" t="n">
+        <v>1326082</v>
+      </c>
+      <c r="D131" s="7" t="n">
+        <v>1.004351917905529</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="14" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="B132" s="5" t="n">
+        <v>1164388</v>
+      </c>
+      <c r="C132" s="5" t="n">
+        <v>992213</v>
+      </c>
+      <c r="D132" s="7" t="n">
+        <v>1.173526248900186</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="26" t="inlineStr">
+        <is>
+          <t>STOCK (kilnable, FeNi KM0)</t>
+        </is>
+      </c>
+      <c r="B133" s="5" t="n">
+        <v>228303</v>
+      </c>
+      <c r="C133" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D133" s="26" t="inlineStr">
+        <is>
+          <t>on top of the met sales lines</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:J2"/>
+  <mergeCells count="5">
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A107:H107"/>
+    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="A75:H75"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/scenario_comparison_dec_options.xlsx
+++ b/reports/scenario_comparison_dec_options.xlsx
@@ -18,10 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="+0.0%;-0.0%"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -126,6 +127,24 @@
       <color rgb="001B7A41"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00A52929"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001B7A41"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="000F4C81"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -150,7 +169,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -172,11 +191,12 @@
         <color rgb="00DBE4EE"/>
       </bottom>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -250,6 +270,28 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1059,16 +1101,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H133"/>
+  <dimension ref="A1:H135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -1086,6 +1128,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="18" t="inlineStr">
         <is>
@@ -1186,6 +1229,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="16" t="inlineStr">
         <is>
@@ -1675,6 +1719,7 @@
         <v>5231542</v>
       </c>
     </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" s="16" t="inlineStr">
         <is>
@@ -1690,19 +1735,35 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>t/month (new plan)</t>
+          <t>BEFORE re-dispatch t/mo</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>December sales share</t>
+          <t>AFTER re-dispatch t/mo</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Coverage</t>
-        </is>
-      </c>
+          <t>Δ t/mo</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Change %</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Dec sales share</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>Coverage after</t>
+        </is>
+      </c>
+      <c r="H29" s="31" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="14" t="inlineStr">
@@ -1710,15 +1771,25 @@
           <t>SAP</t>
         </is>
       </c>
-      <c r="B30" s="5" t="n">
+      <c r="B30" s="15" t="n">
         <v>2311732</v>
       </c>
-      <c r="C30" s="5" t="n">
+      <c r="C30" s="32" t="n">
+        <v>2311732</v>
+      </c>
+      <c r="D30" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="15" t="n">
         <v>2311213</v>
       </c>
-      <c r="D30" s="7" t="n">
+      <c r="G30" s="34" t="n">
         <v>1.000224557407734</v>
       </c>
+      <c r="H30" s="31" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
@@ -1726,15 +1797,25 @@
           <t>LIM-TOS</t>
         </is>
       </c>
-      <c r="B31" s="5" t="n">
+      <c r="B31" s="15" t="n">
         <v>1001362</v>
       </c>
-      <c r="C31" s="5" t="n">
+      <c r="C31" s="32" t="n">
+        <v>1001362</v>
+      </c>
+      <c r="D31" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="15" t="n">
         <v>996084</v>
       </c>
-      <c r="D31" s="7" t="n">
+      <c r="G31" s="34" t="n">
         <v>1.005298749904626</v>
       </c>
+      <c r="H31" s="31" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="14" t="inlineStr">
@@ -1742,35 +1823,87 @@
           <t>LIM-LD</t>
         </is>
       </c>
-      <c r="B32" s="5" t="n">
+      <c r="B32" s="15" t="n">
+        <v>1903679</v>
+      </c>
+      <c r="C32" s="32" t="n">
         <v>1819328</v>
       </c>
-      <c r="C32" s="5" t="n">
+      <c r="D32" s="35" t="n">
+        <v>-84351</v>
+      </c>
+      <c r="E32" s="36" t="n">
+        <v>-0.04430946603917992</v>
+      </c>
+      <c r="F32" s="15" t="n">
         <v>1719964</v>
       </c>
-      <c r="D32" s="7" t="n">
+      <c r="G32" s="34" t="n">
         <v>1.057770976601836</v>
       </c>
+      <c r="H32" s="31" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="26" t="inlineStr">
+      <c r="A33" s="28" t="inlineStr">
         <is>
           <t>STOCK (kilnable, FeNi KM0)</t>
         </is>
       </c>
-      <c r="B33" s="5" t="n">
+      <c r="B33" s="15" t="n"/>
+      <c r="C33" s="32" t="n">
         <v>99120</v>
       </c>
-      <c r="C33" s="30" t="inlineStr">
+      <c r="D33" s="27" t="n">
+        <v>99120</v>
+      </c>
+      <c r="E33" s="26" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F33" s="30" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D33" s="26" t="inlineStr">
+      <c r="G33" s="37" t="inlineStr">
         <is>
           <t>on top of the met sales lines</t>
         </is>
       </c>
+      <c r="H33" s="31" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="38" t="inlineStr">
+        <is>
+          <t>TOTAL moved</t>
+        </is>
+      </c>
+      <c r="B34" s="32" t="n">
+        <v>5216773</v>
+      </c>
+      <c r="C34" s="32" t="n">
+        <v>5231542</v>
+      </c>
+      <c r="D34" s="27" t="n">
+        <v>14769</v>
+      </c>
+      <c r="E34" s="33" t="n">
+        <v>0.002831060504261926</v>
+      </c>
+      <c r="F34" s="31" t="n"/>
+      <c r="G34" s="31" t="n"/>
+      <c r="H34" s="31" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="31" t="n"/>
+      <c r="B35" s="31" t="n"/>
+      <c r="C35" s="31" t="n"/>
+      <c r="D35" s="31" t="n"/>
+      <c r="E35" s="31" t="n"/>
+      <c r="F35" s="31" t="n"/>
+      <c r="G35" s="31" t="n"/>
+      <c r="H35" s="31" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="18" t="inlineStr">
@@ -1872,6 +2005,7 @@
         </is>
       </c>
     </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" s="16" t="inlineStr">
         <is>
@@ -2425,6 +2559,7 @@
         <v>5336733</v>
       </c>
     </row>
+    <row r="61"/>
     <row r="62">
       <c r="A62" s="16" t="inlineStr">
         <is>
@@ -2440,19 +2575,35 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>t/month (new plan)</t>
+          <t>BEFORE re-dispatch t/mo</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>December sales share</t>
+          <t>AFTER re-dispatch t/mo</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>Coverage</t>
-        </is>
-      </c>
+          <t>Δ t/mo</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>Change %</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>Dec sales share</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>Coverage after</t>
+        </is>
+      </c>
+      <c r="H63" s="31" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="14" t="inlineStr">
@@ -2460,15 +2611,25 @@
           <t>SAP</t>
         </is>
       </c>
-      <c r="B64" s="5" t="n">
+      <c r="B64" s="15" t="n">
         <v>2311732</v>
       </c>
-      <c r="C64" s="5" t="n">
+      <c r="C64" s="32" t="n">
+        <v>2311732</v>
+      </c>
+      <c r="D64" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="15" t="n">
         <v>2311213</v>
       </c>
-      <c r="D64" s="7" t="n">
+      <c r="G64" s="34" t="n">
         <v>1.000224557407734</v>
       </c>
+      <c r="H64" s="31" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="14" t="inlineStr">
@@ -2476,15 +2637,25 @@
           <t>LIM-TOS</t>
         </is>
       </c>
-      <c r="B65" s="5" t="n">
+      <c r="B65" s="15" t="n">
         <v>1000556</v>
       </c>
-      <c r="C65" s="5" t="n">
+      <c r="C65" s="32" t="n">
+        <v>1000556</v>
+      </c>
+      <c r="D65" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="15" t="n">
         <v>996084</v>
       </c>
-      <c r="D65" s="7" t="n">
+      <c r="G65" s="34" t="n">
         <v>1.004489581199979</v>
       </c>
+      <c r="H65" s="31" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="14" t="inlineStr">
@@ -2492,35 +2663,87 @@
           <t>LIM-LD</t>
         </is>
       </c>
-      <c r="B66" s="5" t="n">
+      <c r="B66" s="15" t="n">
+        <v>2031523</v>
+      </c>
+      <c r="C66" s="32" t="n">
         <v>1818903</v>
       </c>
-      <c r="C66" s="5" t="n">
+      <c r="D66" s="35" t="n">
+        <v>-212620</v>
+      </c>
+      <c r="E66" s="36" t="n">
+        <v>-0.1046603951813492</v>
+      </c>
+      <c r="F66" s="15" t="n">
         <v>1719964</v>
       </c>
-      <c r="D66" s="7" t="n">
+      <c r="G66" s="34" t="n">
         <v>1.057523878406757</v>
       </c>
+      <c r="H66" s="31" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="26" t="inlineStr">
+      <c r="A67" s="28" t="inlineStr">
         <is>
           <t>STOCK (kilnable, FeNi KM0)</t>
         </is>
       </c>
-      <c r="B67" s="5" t="n">
+      <c r="B67" s="15" t="n"/>
+      <c r="C67" s="32" t="n">
         <v>205542</v>
       </c>
-      <c r="C67" s="30" t="inlineStr">
+      <c r="D67" s="27" t="n">
+        <v>205542</v>
+      </c>
+      <c r="E67" s="26" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F67" s="30" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D67" s="26" t="inlineStr">
+      <c r="G67" s="37" t="inlineStr">
         <is>
           <t>on top of the met sales lines</t>
         </is>
       </c>
+      <c r="H67" s="31" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="38" t="inlineStr">
+        <is>
+          <t>TOTAL moved</t>
+        </is>
+      </c>
+      <c r="B68" s="32" t="n">
+        <v>5343811</v>
+      </c>
+      <c r="C68" s="32" t="n">
+        <v>5336733</v>
+      </c>
+      <c r="D68" s="35" t="n">
+        <v>-7078</v>
+      </c>
+      <c r="E68" s="36" t="n">
+        <v>-0.001324522891995993</v>
+      </c>
+      <c r="F68" s="31" t="n"/>
+      <c r="G68" s="31" t="n"/>
+      <c r="H68" s="31" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="31" t="n"/>
+      <c r="B69" s="31" t="n"/>
+      <c r="C69" s="31" t="n"/>
+      <c r="D69" s="31" t="n"/>
+      <c r="E69" s="31" t="n"/>
+      <c r="F69" s="31" t="n"/>
+      <c r="G69" s="31" t="n"/>
+      <c r="H69" s="31" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="18" t="inlineStr">
@@ -2622,6 +2845,7 @@
         </is>
       </c>
     </row>
+    <row r="76"/>
     <row r="77">
       <c r="A77" s="16" t="inlineStr">
         <is>
@@ -3111,6 +3335,7 @@
         <v>4994394</v>
       </c>
     </row>
+    <row r="93"/>
     <row r="94">
       <c r="A94" s="16" t="inlineStr">
         <is>
@@ -3126,19 +3351,35 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>t/month (new plan)</t>
+          <t>BEFORE re-dispatch t/mo</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>December sales share</t>
+          <t>AFTER re-dispatch t/mo</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>Coverage</t>
-        </is>
-      </c>
+          <t>Δ t/mo</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>Change %</t>
+        </is>
+      </c>
+      <c r="F95" s="3" t="inlineStr">
+        <is>
+          <t>Dec sales share</t>
+        </is>
+      </c>
+      <c r="G95" s="3" t="inlineStr">
+        <is>
+          <t>Coverage after</t>
+        </is>
+      </c>
+      <c r="H95" s="31" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="14" t="inlineStr">
@@ -3146,15 +3387,25 @@
           <t>SAP</t>
         </is>
       </c>
-      <c r="B96" s="5" t="n">
+      <c r="B96" s="15" t="n">
         <v>2315483</v>
       </c>
-      <c r="C96" s="5" t="n">
+      <c r="C96" s="32" t="n">
+        <v>2315483</v>
+      </c>
+      <c r="D96" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" s="15" t="n">
         <v>2311213</v>
       </c>
-      <c r="D96" s="7" t="n">
+      <c r="G96" s="34" t="n">
         <v>1.001847514703318</v>
       </c>
+      <c r="H96" s="31" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="14" t="inlineStr">
@@ -3162,15 +3413,25 @@
           <t>LIM-TOS</t>
         </is>
       </c>
-      <c r="B97" s="5" t="n">
+      <c r="B97" s="15" t="n">
         <v>1332318</v>
       </c>
-      <c r="C97" s="5" t="n">
+      <c r="C97" s="32" t="n">
+        <v>1332318</v>
+      </c>
+      <c r="D97" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" s="15" t="n">
         <v>1326082</v>
       </c>
-      <c r="D97" s="7" t="n">
+      <c r="G97" s="34" t="n">
         <v>1.004702574953887</v>
       </c>
+      <c r="H97" s="31" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="14" t="inlineStr">
@@ -3178,35 +3439,87 @@
           <t>LIM-LD</t>
         </is>
       </c>
-      <c r="B98" s="5" t="n">
+      <c r="B98" s="15" t="n">
+        <v>1323607</v>
+      </c>
+      <c r="C98" s="32" t="n">
         <v>1163826</v>
       </c>
-      <c r="C98" s="5" t="n">
+      <c r="D98" s="35" t="n">
+        <v>-159781</v>
+      </c>
+      <c r="E98" s="36" t="n">
+        <v>-0.1207163455617868</v>
+      </c>
+      <c r="F98" s="15" t="n">
         <v>992213</v>
       </c>
-      <c r="D98" s="7" t="n">
+      <c r="G98" s="34" t="n">
         <v>1.172959838260535</v>
       </c>
+      <c r="H98" s="31" t="n"/>
     </row>
     <row r="99">
-      <c r="A99" s="26" t="inlineStr">
+      <c r="A99" s="28" t="inlineStr">
         <is>
           <t>STOCK (kilnable, FeNi KM0)</t>
         </is>
       </c>
-      <c r="B99" s="5" t="n">
+      <c r="B99" s="15" t="n"/>
+      <c r="C99" s="32" t="n">
         <v>182767</v>
       </c>
-      <c r="C99" s="30" t="inlineStr">
+      <c r="D99" s="27" t="n">
+        <v>182767</v>
+      </c>
+      <c r="E99" s="26" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F99" s="30" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D99" s="26" t="inlineStr">
+      <c r="G99" s="37" t="inlineStr">
         <is>
           <t>on top of the met sales lines</t>
         </is>
       </c>
+      <c r="H99" s="31" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="38" t="inlineStr">
+        <is>
+          <t>TOTAL moved</t>
+        </is>
+      </c>
+      <c r="B100" s="32" t="n">
+        <v>4971408</v>
+      </c>
+      <c r="C100" s="32" t="n">
+        <v>4994394</v>
+      </c>
+      <c r="D100" s="27" t="n">
+        <v>22986</v>
+      </c>
+      <c r="E100" s="33" t="n">
+        <v>0.004623639821957884</v>
+      </c>
+      <c r="F100" s="31" t="n"/>
+      <c r="G100" s="31" t="n"/>
+      <c r="H100" s="31" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="31" t="n"/>
+      <c r="B101" s="31" t="n"/>
+      <c r="C101" s="31" t="n"/>
+      <c r="D101" s="31" t="n"/>
+      <c r="E101" s="31" t="n"/>
+      <c r="F101" s="31" t="n"/>
+      <c r="G101" s="31" t="n"/>
+      <c r="H101" s="31" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="18" t="inlineStr">
@@ -3308,6 +3621,7 @@
         </is>
       </c>
     </row>
+    <row r="108"/>
     <row r="109">
       <c r="A109" s="16" t="inlineStr">
         <is>
@@ -3861,6 +4175,7 @@
         <v>5040027</v>
       </c>
     </row>
+    <row r="127"/>
     <row r="128">
       <c r="A128" s="16" t="inlineStr">
         <is>
@@ -3876,19 +4191,35 @@
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>t/month (new plan)</t>
+          <t>BEFORE re-dispatch t/mo</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>December sales share</t>
+          <t>AFTER re-dispatch t/mo</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>Coverage</t>
-        </is>
-      </c>
+          <t>Δ t/mo</t>
+        </is>
+      </c>
+      <c r="E129" s="3" t="inlineStr">
+        <is>
+          <t>Change %</t>
+        </is>
+      </c>
+      <c r="F129" s="3" t="inlineStr">
+        <is>
+          <t>Dec sales share</t>
+        </is>
+      </c>
+      <c r="G129" s="3" t="inlineStr">
+        <is>
+          <t>Coverage after</t>
+        </is>
+      </c>
+      <c r="H129" s="31" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="14" t="inlineStr">
@@ -3896,15 +4227,25 @@
           <t>SAP</t>
         </is>
       </c>
-      <c r="B130" s="5" t="n">
+      <c r="B130" s="15" t="n">
         <v>2315483</v>
       </c>
-      <c r="C130" s="5" t="n">
+      <c r="C130" s="32" t="n">
+        <v>2315483</v>
+      </c>
+      <c r="D130" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E130" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F130" s="15" t="n">
         <v>2311213</v>
       </c>
-      <c r="D130" s="7" t="n">
+      <c r="G130" s="34" t="n">
         <v>1.001847514703318</v>
       </c>
+      <c r="H130" s="31" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="14" t="inlineStr">
@@ -3912,15 +4253,25 @@
           <t>LIM-TOS</t>
         </is>
       </c>
-      <c r="B131" s="5" t="n">
+      <c r="B131" s="15" t="n">
         <v>1331853</v>
       </c>
-      <c r="C131" s="5" t="n">
+      <c r="C131" s="32" t="n">
+        <v>1331853</v>
+      </c>
+      <c r="D131" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" s="15" t="n">
         <v>1326082</v>
       </c>
-      <c r="D131" s="7" t="n">
+      <c r="G131" s="34" t="n">
         <v>1.004351917905529</v>
       </c>
+      <c r="H131" s="31" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="14" t="inlineStr">
@@ -3928,35 +4279,87 @@
           <t>LIM-LD</t>
         </is>
       </c>
-      <c r="B132" s="5" t="n">
+      <c r="B132" s="15" t="n">
+        <v>1397883</v>
+      </c>
+      <c r="C132" s="32" t="n">
         <v>1164388</v>
       </c>
-      <c r="C132" s="5" t="n">
+      <c r="D132" s="35" t="n">
+        <v>-233495</v>
+      </c>
+      <c r="E132" s="36" t="n">
+        <v>-0.167034723220756</v>
+      </c>
+      <c r="F132" s="15" t="n">
         <v>992213</v>
       </c>
-      <c r="D132" s="7" t="n">
+      <c r="G132" s="34" t="n">
         <v>1.173526248900186</v>
       </c>
+      <c r="H132" s="31" t="n"/>
     </row>
     <row r="133">
-      <c r="A133" s="26" t="inlineStr">
+      <c r="A133" s="28" t="inlineStr">
         <is>
           <t>STOCK (kilnable, FeNi KM0)</t>
         </is>
       </c>
-      <c r="B133" s="5" t="n">
+      <c r="B133" s="15" t="n"/>
+      <c r="C133" s="32" t="n">
         <v>228303</v>
       </c>
-      <c r="C133" s="30" t="inlineStr">
+      <c r="D133" s="27" t="n">
+        <v>228303</v>
+      </c>
+      <c r="E133" s="26" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F133" s="30" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D133" s="26" t="inlineStr">
+      <c r="G133" s="37" t="inlineStr">
         <is>
           <t>on top of the met sales lines</t>
         </is>
       </c>
+      <c r="H133" s="31" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="38" t="inlineStr">
+        <is>
+          <t>TOTAL moved</t>
+        </is>
+      </c>
+      <c r="B134" s="32" t="n">
+        <v>5045219</v>
+      </c>
+      <c r="C134" s="32" t="n">
+        <v>5040027</v>
+      </c>
+      <c r="D134" s="35" t="n">
+        <v>-5192</v>
+      </c>
+      <c r="E134" s="36" t="n">
+        <v>-0.001029093087931366</v>
+      </c>
+      <c r="F134" s="31" t="n"/>
+      <c r="G134" s="31" t="n"/>
+      <c r="H134" s="31" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="31" t="n"/>
+      <c r="B135" s="31" t="n"/>
+      <c r="C135" s="31" t="n"/>
+      <c r="D135" s="31" t="n"/>
+      <c r="E135" s="31" t="n"/>
+      <c r="F135" s="31" t="n"/>
+      <c r="G135" s="31" t="n"/>
+      <c r="H135" s="31" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/reports/scenario_comparison_dec_options.xlsx
+++ b/reports/scenario_comparison_dec_options.xlsx
@@ -18,11 +18,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="+0.0%;-0.0%"/>
+    <numFmt numFmtId="166" formatCode="+0.0%;-0.0%;0%"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="23">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -145,6 +146,17 @@
       <color rgb="000F4C81"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="005B6B7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="001B7A41"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -196,7 +208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -294,6 +306,26 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="21" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="21" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1101,7 +1133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H135"/>
+  <dimension ref="A1:H136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1644,7 +1676,7 @@
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>STOCK (kilnable, FeNi KM0)</t>
+          <t>SAP (stock at FeNi KM0)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -1678,7 +1710,7 @@
       </c>
       <c r="C25" s="20" t="inlineStr">
         <is>
-          <t>STOCK (kilnable, FeNi KM0)</t>
+          <t>SAP (stock at FeNi KM0)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -1766,7 +1798,7 @@
       <c r="H29" s="31" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="14" t="inlineStr">
+      <c r="A30" s="19" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
@@ -1775,19 +1807,19 @@
         <v>2311732</v>
       </c>
       <c r="C30" s="32" t="n">
-        <v>2311732</v>
+        <v>2410852</v>
       </c>
       <c r="D30" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" s="33" t="n">
-        <v>0</v>
+        <v>99120</v>
+      </c>
+      <c r="E30" s="39" t="n">
+        <v>0.04287694248295218</v>
       </c>
       <c r="F30" s="15" t="n">
         <v>2311213</v>
       </c>
       <c r="G30" s="34" t="n">
-        <v>1.000224557407734</v>
+        <v>1.043111128225741</v>
       </c>
       <c r="H30" s="31" t="n"/>
     </row>
@@ -1803,10 +1835,10 @@
       <c r="C31" s="32" t="n">
         <v>1001362</v>
       </c>
-      <c r="D31" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="33" t="n">
+      <c r="D31" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="41" t="n">
         <v>0</v>
       </c>
       <c r="F31" s="15" t="n">
@@ -1832,7 +1864,7 @@
       <c r="D32" s="35" t="n">
         <v>-84351</v>
       </c>
-      <c r="E32" s="36" t="n">
+      <c r="E32" s="42" t="n">
         <v>-0.04430946603917992</v>
       </c>
       <c r="F32" s="15" t="n">
@@ -1844,33 +1876,25 @@
       <c r="H32" s="31" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="28" t="inlineStr">
-        <is>
-          <t>STOCK (kilnable, FeNi KM0)</t>
-        </is>
-      </c>
-      <c r="B33" s="15" t="n"/>
-      <c r="C33" s="32" t="n">
+      <c r="A33" s="43" t="inlineStr">
+        <is>
+          <t>of which reallocated to FeNi KM0 stockpile (KR/TF&gt;FENI KM0)</t>
+        </is>
+      </c>
+      <c r="B33" s="44" t="n"/>
+      <c r="C33" s="27" t="n">
         <v>99120</v>
       </c>
       <c r="D33" s="27" t="n">
         <v>99120</v>
       </c>
-      <c r="E33" s="26" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="F33" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G33" s="37" t="inlineStr">
-        <is>
-          <t>on top of the met sales lines</t>
-        </is>
-      </c>
+      <c r="E33" s="45" t="inlineStr">
+        <is>
+          <t>in SAP row</t>
+        </is>
+      </c>
+      <c r="F33" s="30" t="n"/>
+      <c r="G33" s="37" t="n"/>
       <c r="H33" s="31" t="n"/>
     </row>
     <row r="34">
@@ -1888,7 +1912,7 @@
       <c r="D34" s="27" t="n">
         <v>14769</v>
       </c>
-      <c r="E34" s="33" t="n">
+      <c r="E34" s="39" t="n">
         <v>0.002831060504261926</v>
       </c>
       <c r="F34" s="31" t="n"/>
@@ -1906,11 +1930,14 @@
       <c r="H35" s="31" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="18" t="inlineStr">
-        <is>
-          <t>Scenario 3.0.2 — December</t>
-        </is>
-      </c>
+      <c r="A36" s="46" t="n"/>
+      <c r="B36" s="31" t="n"/>
+      <c r="C36" s="31" t="n"/>
+      <c r="D36" s="31" t="n"/>
+      <c r="E36" s="31" t="n"/>
+      <c r="F36" s="31" t="n"/>
+      <c r="G36" s="31" t="n"/>
+      <c r="H36" s="31" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr"/>
@@ -2484,7 +2511,7 @@
       </c>
       <c r="C58" s="20" t="inlineStr">
         <is>
-          <t>STOCK (kilnable, FeNi KM0)</t>
+          <t>SAP (stock at FeNi KM0)</t>
         </is>
       </c>
       <c r="D58" s="20" t="inlineStr">
@@ -2518,7 +2545,7 @@
       </c>
       <c r="C59" s="20" t="inlineStr">
         <is>
-          <t>STOCK (kilnable, FeNi KM0)</t>
+          <t>SAP (stock at FeNi KM0)</t>
         </is>
       </c>
       <c r="D59" s="20" t="inlineStr">
@@ -2606,7 +2633,7 @@
       <c r="H63" s="31" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="14" t="inlineStr">
+      <c r="A64" s="19" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
@@ -2615,19 +2642,19 @@
         <v>2311732</v>
       </c>
       <c r="C64" s="32" t="n">
-        <v>2311732</v>
+        <v>2517274</v>
       </c>
       <c r="D64" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E64" s="33" t="n">
-        <v>0</v>
+        <v>205542</v>
+      </c>
+      <c r="E64" s="39" t="n">
+        <v>0.08891255560765694</v>
       </c>
       <c r="F64" s="15" t="n">
         <v>2311213</v>
       </c>
       <c r="G64" s="34" t="n">
-        <v>1.000224557407734</v>
+        <v>1.089157078988393</v>
       </c>
       <c r="H64" s="31" t="n"/>
     </row>
@@ -2643,10 +2670,10 @@
       <c r="C65" s="32" t="n">
         <v>1000556</v>
       </c>
-      <c r="D65" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E65" s="33" t="n">
+      <c r="D65" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="41" t="n">
         <v>0</v>
       </c>
       <c r="F65" s="15" t="n">
@@ -2672,7 +2699,7 @@
       <c r="D66" s="35" t="n">
         <v>-212620</v>
       </c>
-      <c r="E66" s="36" t="n">
+      <c r="E66" s="42" t="n">
         <v>-0.1046603951813492</v>
       </c>
       <c r="F66" s="15" t="n">
@@ -2684,33 +2711,25 @@
       <c r="H66" s="31" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="28" t="inlineStr">
-        <is>
-          <t>STOCK (kilnable, FeNi KM0)</t>
-        </is>
-      </c>
-      <c r="B67" s="15" t="n"/>
-      <c r="C67" s="32" t="n">
+      <c r="A67" s="43" t="inlineStr">
+        <is>
+          <t>of which reallocated to FeNi KM0 stockpile (KR/TF&gt;FENI KM0)</t>
+        </is>
+      </c>
+      <c r="B67" s="44" t="n"/>
+      <c r="C67" s="27" t="n">
         <v>205542</v>
       </c>
       <c r="D67" s="27" t="n">
         <v>205542</v>
       </c>
-      <c r="E67" s="26" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="F67" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G67" s="37" t="inlineStr">
-        <is>
-          <t>on top of the met sales lines</t>
-        </is>
-      </c>
+      <c r="E67" s="45" t="inlineStr">
+        <is>
+          <t>in SAP row</t>
+        </is>
+      </c>
+      <c r="F67" s="30" t="n"/>
+      <c r="G67" s="37" t="n"/>
       <c r="H67" s="31" t="n"/>
     </row>
     <row r="68">
@@ -2728,7 +2747,7 @@
       <c r="D68" s="35" t="n">
         <v>-7078</v>
       </c>
-      <c r="E68" s="36" t="n">
+      <c r="E68" s="42" t="n">
         <v>-0.001324522891995993</v>
       </c>
       <c r="F68" s="31" t="n"/>
@@ -2746,11 +2765,14 @@
       <c r="H69" s="31" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="18" t="inlineStr">
-        <is>
-          <t>Scenario 3.1.1 — December</t>
-        </is>
-      </c>
+      <c r="A70" s="46" t="n"/>
+      <c r="B70" s="31" t="n"/>
+      <c r="C70" s="31" t="n"/>
+      <c r="D70" s="31" t="n"/>
+      <c r="E70" s="31" t="n"/>
+      <c r="F70" s="31" t="n"/>
+      <c r="G70" s="31" t="n"/>
+      <c r="H70" s="31" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr"/>
@@ -3260,7 +3282,7 @@
       </c>
       <c r="C90" s="20" t="inlineStr">
         <is>
-          <t>STOCK (kilnable, FeNi KM0)</t>
+          <t>SAP (stock at FeNi KM0)</t>
         </is>
       </c>
       <c r="D90" s="20" t="inlineStr">
@@ -3294,7 +3316,7 @@
       </c>
       <c r="C91" s="20" t="inlineStr">
         <is>
-          <t>STOCK (kilnable, FeNi KM0)</t>
+          <t>SAP (stock at FeNi KM0)</t>
         </is>
       </c>
       <c r="D91" s="20" t="inlineStr">
@@ -3382,7 +3404,7 @@
       <c r="H95" s="31" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" s="14" t="inlineStr">
+      <c r="A96" s="19" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
@@ -3391,19 +3413,19 @@
         <v>2315483</v>
       </c>
       <c r="C96" s="32" t="n">
-        <v>2315483</v>
+        <v>2498250</v>
       </c>
       <c r="D96" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E96" s="33" t="n">
-        <v>0</v>
+        <v>182767</v>
+      </c>
+      <c r="E96" s="39" t="n">
+        <v>0.07893255964306367</v>
       </c>
       <c r="F96" s="15" t="n">
         <v>2311213</v>
       </c>
       <c r="G96" s="34" t="n">
-        <v>1.001847514703318</v>
+        <v>1.080925903410893</v>
       </c>
       <c r="H96" s="31" t="n"/>
     </row>
@@ -3419,10 +3441,10 @@
       <c r="C97" s="32" t="n">
         <v>1332318</v>
       </c>
-      <c r="D97" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E97" s="33" t="n">
+      <c r="D97" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" s="41" t="n">
         <v>0</v>
       </c>
       <c r="F97" s="15" t="n">
@@ -3448,7 +3470,7 @@
       <c r="D98" s="35" t="n">
         <v>-159781</v>
       </c>
-      <c r="E98" s="36" t="n">
+      <c r="E98" s="42" t="n">
         <v>-0.1207163455617868</v>
       </c>
       <c r="F98" s="15" t="n">
@@ -3460,33 +3482,25 @@
       <c r="H98" s="31" t="n"/>
     </row>
     <row r="99">
-      <c r="A99" s="28" t="inlineStr">
-        <is>
-          <t>STOCK (kilnable, FeNi KM0)</t>
-        </is>
-      </c>
-      <c r="B99" s="15" t="n"/>
-      <c r="C99" s="32" t="n">
+      <c r="A99" s="43" t="inlineStr">
+        <is>
+          <t>of which reallocated to FeNi KM0 stockpile (KR/TF&gt;FENI KM0)</t>
+        </is>
+      </c>
+      <c r="B99" s="44" t="n"/>
+      <c r="C99" s="27" t="n">
         <v>182767</v>
       </c>
       <c r="D99" s="27" t="n">
         <v>182767</v>
       </c>
-      <c r="E99" s="26" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="F99" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G99" s="37" t="inlineStr">
-        <is>
-          <t>on top of the met sales lines</t>
-        </is>
-      </c>
+      <c r="E99" s="45" t="inlineStr">
+        <is>
+          <t>in SAP row</t>
+        </is>
+      </c>
+      <c r="F99" s="30" t="n"/>
+      <c r="G99" s="37" t="n"/>
       <c r="H99" s="31" t="n"/>
     </row>
     <row r="100">
@@ -3504,7 +3518,7 @@
       <c r="D100" s="27" t="n">
         <v>22986</v>
       </c>
-      <c r="E100" s="33" t="n">
+      <c r="E100" s="39" t="n">
         <v>0.004623639821957884</v>
       </c>
       <c r="F100" s="31" t="n"/>
@@ -3522,11 +3536,14 @@
       <c r="H101" s="31" t="n"/>
     </row>
     <row r="102">
-      <c r="A102" s="18" t="inlineStr">
-        <is>
-          <t>Scenario 3.1.2 — December</t>
-        </is>
-      </c>
+      <c r="A102" s="46" t="n"/>
+      <c r="B102" s="31" t="n"/>
+      <c r="C102" s="31" t="n"/>
+      <c r="D102" s="31" t="n"/>
+      <c r="E102" s="31" t="n"/>
+      <c r="F102" s="31" t="n"/>
+      <c r="G102" s="31" t="n"/>
+      <c r="H102" s="31" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr"/>
@@ -4100,7 +4117,7 @@
       </c>
       <c r="C124" s="20" t="inlineStr">
         <is>
-          <t>STOCK (kilnable, FeNi KM0)</t>
+          <t>SAP (stock at FeNi KM0)</t>
         </is>
       </c>
       <c r="D124" s="20" t="inlineStr">
@@ -4134,7 +4151,7 @@
       </c>
       <c r="C125" s="20" t="inlineStr">
         <is>
-          <t>STOCK (kilnable, FeNi KM0)</t>
+          <t>SAP (stock at FeNi KM0)</t>
         </is>
       </c>
       <c r="D125" s="20" t="inlineStr">
@@ -4222,7 +4239,7 @@
       <c r="H129" s="31" t="n"/>
     </row>
     <row r="130">
-      <c r="A130" s="14" t="inlineStr">
+      <c r="A130" s="19" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
@@ -4231,19 +4248,19 @@
         <v>2315483</v>
       </c>
       <c r="C130" s="32" t="n">
-        <v>2315483</v>
+        <v>2543786</v>
       </c>
       <c r="D130" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E130" s="33" t="n">
-        <v>0</v>
+        <v>228303</v>
+      </c>
+      <c r="E130" s="39" t="n">
+        <v>0.09859843497015526</v>
       </c>
       <c r="F130" s="15" t="n">
         <v>2311213</v>
       </c>
       <c r="G130" s="34" t="n">
-        <v>1.001847514703318</v>
+        <v>1.100628111731805</v>
       </c>
       <c r="H130" s="31" t="n"/>
     </row>
@@ -4259,10 +4276,10 @@
       <c r="C131" s="32" t="n">
         <v>1331853</v>
       </c>
-      <c r="D131" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E131" s="33" t="n">
+      <c r="D131" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" s="41" t="n">
         <v>0</v>
       </c>
       <c r="F131" s="15" t="n">
@@ -4288,7 +4305,7 @@
       <c r="D132" s="35" t="n">
         <v>-233495</v>
       </c>
-      <c r="E132" s="36" t="n">
+      <c r="E132" s="42" t="n">
         <v>-0.167034723220756</v>
       </c>
       <c r="F132" s="15" t="n">
@@ -4300,33 +4317,25 @@
       <c r="H132" s="31" t="n"/>
     </row>
     <row r="133">
-      <c r="A133" s="28" t="inlineStr">
-        <is>
-          <t>STOCK (kilnable, FeNi KM0)</t>
-        </is>
-      </c>
-      <c r="B133" s="15" t="n"/>
-      <c r="C133" s="32" t="n">
+      <c r="A133" s="43" t="inlineStr">
+        <is>
+          <t>of which reallocated to FeNi KM0 stockpile (KR/TF&gt;FENI KM0)</t>
+        </is>
+      </c>
+      <c r="B133" s="44" t="n"/>
+      <c r="C133" s="27" t="n">
         <v>228303</v>
       </c>
       <c r="D133" s="27" t="n">
         <v>228303</v>
       </c>
-      <c r="E133" s="26" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="F133" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G133" s="37" t="inlineStr">
-        <is>
-          <t>on top of the met sales lines</t>
-        </is>
-      </c>
+      <c r="E133" s="45" t="inlineStr">
+        <is>
+          <t>in SAP row</t>
+        </is>
+      </c>
+      <c r="F133" s="30" t="n"/>
+      <c r="G133" s="37" t="n"/>
       <c r="H133" s="31" t="n"/>
     </row>
     <row r="134">
@@ -4344,7 +4353,7 @@
       <c r="D134" s="35" t="n">
         <v>-5192</v>
       </c>
-      <c r="E134" s="36" t="n">
+      <c r="E134" s="42" t="n">
         <v>-0.001029093087931366</v>
       </c>
       <c r="F134" s="31" t="n"/>
@@ -4361,13 +4370,27 @@
       <c r="G135" s="31" t="n"/>
       <c r="H135" s="31" t="n"/>
     </row>
+    <row r="136">
+      <c r="A136" s="31" t="n"/>
+      <c r="B136" s="31" t="n"/>
+      <c r="C136" s="31" t="n"/>
+      <c r="D136" s="31" t="n"/>
+      <c r="E136" s="31" t="n"/>
+      <c r="F136" s="31" t="n"/>
+      <c r="G136" s="31" t="n"/>
+      <c r="H136" s="31" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="9">
     <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A33:B33"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A107:H107"/>
+    <mergeCell ref="A99:B99"/>
+    <mergeCell ref="A133:B133"/>
     <mergeCell ref="A41:H41"/>
     <mergeCell ref="A75:H75"/>
+    <mergeCell ref="A67:B67"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/scenario_comparison_dec_options.xlsx
+++ b/reports/scenario_comparison_dec_options.xlsx
@@ -23,7 +23,7 @@
     <numFmt numFmtId="165" formatCode="+0.0%;-0.0%"/>
     <numFmt numFmtId="166" formatCode="+0.0%;-0.0%;0%"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -157,6 +157,12 @@
       <color rgb="001B7A41"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="000F4C81"/>
+      <sz val="12"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -181,7 +187,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -204,11 +210,44 @@
       </bottom>
     </border>
     <border/>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00DBE4EE"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00DBE4EE"/>
+      </right>
+      <top style="thin">
+        <color rgb="00DBE4EE"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00DBE4EE"/>
+      </right>
+      <top style="thin">
+        <color rgb="00DBE4EE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00DBE4EE"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -326,6 +365,30 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1133,36 +1196,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H136"/>
+  <dimension ref="A1:H137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>December runs over target — two ways to land it at exactly 100%</t>
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>December runs over target in every scenario — two ways to spend the surplus</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Option 1: park the surplus trucks. Option 2: re-dispatch the SAME trucks to the long stock routes KR→FENI KM0 and TF→FENI KM0 — kilnable stock at the plants, fleet 100% used, sales lines exactly met. Each scenario shows the full re-dispatched December plan (every route, new DT) and the material totals.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" s="47" t="inlineStr">
+        <is>
+          <t>Option 1: park the surplus DT (total month lands at 100.0%). Option 2: cut LIM-LD to exactly its December line and re-dispatch every freed DT to KR&gt;FENI KM0 + TF&gt;FENI KM0 — the hauled material is kilnable SAP feed stocked at the plant.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="A4" s="48" t="inlineStr">
         <is>
           <t>Scenario 3.0.1 — December</t>
         </is>
@@ -1193,75 +1255,74 @@
       <c r="F5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>As frozen</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="15" t="n">
         <v>5131386</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="15" t="n">
         <v>5216721</v>
       </c>
-      <c r="D6" s="7" t="n">
+      <c r="D6" s="49" t="n">
         <v>1.016630009903757</v>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="E6" s="15" t="n">
         <v>1190</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>OPTION 1 · park 26 DT</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>OPTION 1 · park 26 DT (total month → 100.0%)</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="n">
         <v>5131386</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="15" t="n">
         <v>5132370</v>
       </c>
-      <c r="D7" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="5" t="n">
+      <c r="D7" s="34" t="n">
+        <v>1.00019176105637</v>
+      </c>
+      <c r="E7" s="15" t="n">
         <v>1164</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t>OPTION 2 · re-dispatch 26 DT to stock</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>OPTION 2 · re-dispatch 56 DT (LIM-LD → 100.0%)</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="n">
         <v>5131386</v>
       </c>
-      <c r="C8" s="5" t="n">
-        <v>5132370</v>
-      </c>
-      <c r="D8" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="5" t="n">
+      <c r="C8" s="15" t="n">
+        <v>5248586</v>
+      </c>
+      <c r="D8" s="50" t="n">
+        <v>1.0228398331367</v>
+      </c>
+      <c r="E8" s="15" t="n">
         <v>1190</v>
       </c>
-      <c r="F8" s="13" t="inlineStr">
-        <is>
-          <t>+ 99,120 t stock to FeNi KM0</t>
+      <c r="F8" s="51" t="inlineStr">
+        <is>
+          <t>+ 213,461 t SAP stocked at FeNi KM0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Cut: TF&gt;HUAFEI (RIM, LD): −26 DT  →  re-dispatched to KR&gt;FENI KM0 (13 DT) + TF&gt;FENI KM0 (13 DT)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
+          <t>Option 2 cut (sized so LIM-LD lands exactly on its line): TF&gt;HUAFEI (RIM, LD): −56 DT @ 104.7 t/day/DT</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" s="16" t="inlineStr">
         <is>
@@ -1327,20 +1388,20 @@
           <t>LIM-LD</t>
         </is>
       </c>
-      <c r="D13" s="14" t="n">
+      <c r="D13" s="15" t="n">
         <v>437</v>
       </c>
-      <c r="E13" s="19" t="n">
-        <v>411</v>
-      </c>
-      <c r="F13" s="19" t="n">
-        <v>-26</v>
+      <c r="E13" s="32" t="n">
+        <v>381</v>
+      </c>
+      <c r="F13" s="35" t="n">
+        <v>-56</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>43013</v>
+        <v>39874</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>1333403</v>
+        <v>1236106</v>
       </c>
     </row>
     <row r="14">
@@ -1359,13 +1420,13 @@
           <t>LIM-LD</t>
         </is>
       </c>
-      <c r="D14" s="14" t="n">
+      <c r="D14" s="15" t="n">
         <v>150</v>
       </c>
-      <c r="E14" s="14" t="n">
+      <c r="E14" s="15" t="n">
         <v>150</v>
       </c>
-      <c r="F14" s="14" t="n">
+      <c r="F14" s="52" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="15" t="n">
@@ -1391,13 +1452,13 @@
           <t>LIM-TOS</t>
         </is>
       </c>
-      <c r="D15" s="14" t="n">
+      <c r="D15" s="15" t="n">
         <v>95</v>
       </c>
-      <c r="E15" s="14" t="n">
+      <c r="E15" s="15" t="n">
         <v>95</v>
       </c>
-      <c r="F15" s="14" t="n">
+      <c r="F15" s="52" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="15" t="n">
@@ -1423,13 +1484,13 @@
           <t>LIM-TOS</t>
         </is>
       </c>
-      <c r="D16" s="14" t="n">
+      <c r="D16" s="15" t="n">
         <v>62</v>
       </c>
-      <c r="E16" s="14" t="n">
+      <c r="E16" s="15" t="n">
         <v>62</v>
       </c>
-      <c r="F16" s="14" t="n">
+      <c r="F16" s="52" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="15" t="n">
@@ -1455,13 +1516,13 @@
           <t>LIM-TOS</t>
         </is>
       </c>
-      <c r="D17" s="14" t="n">
+      <c r="D17" s="15" t="n">
         <v>19</v>
       </c>
-      <c r="E17" s="14" t="n">
+      <c r="E17" s="15" t="n">
         <v>19</v>
       </c>
-      <c r="F17" s="14" t="n">
+      <c r="F17" s="52" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="15" t="n">
@@ -1487,13 +1548,13 @@
           <t>SAP</t>
         </is>
       </c>
-      <c r="D18" s="14" t="n">
+      <c r="D18" s="15" t="n">
         <v>202</v>
       </c>
-      <c r="E18" s="14" t="n">
+      <c r="E18" s="15" t="n">
         <v>202</v>
       </c>
-      <c r="F18" s="14" t="n">
+      <c r="F18" s="52" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="15" t="n">
@@ -1519,13 +1580,13 @@
           <t>SAP</t>
         </is>
       </c>
-      <c r="D19" s="14" t="n">
+      <c r="D19" s="15" t="n">
         <v>140</v>
       </c>
-      <c r="E19" s="14" t="n">
+      <c r="E19" s="15" t="n">
         <v>140</v>
       </c>
-      <c r="F19" s="14" t="n">
+      <c r="F19" s="52" t="n">
         <v>0</v>
       </c>
       <c r="G19" s="15" t="n">
@@ -1551,13 +1612,13 @@
           <t>SAP</t>
         </is>
       </c>
-      <c r="D20" s="14" t="n">
+      <c r="D20" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="E20" s="14" t="n">
+      <c r="E20" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="F20" s="14" t="n">
+      <c r="F20" s="52" t="n">
         <v>0</v>
       </c>
       <c r="G20" s="15" t="n">
@@ -1583,13 +1644,13 @@
           <t>SAP</t>
         </is>
       </c>
-      <c r="D21" s="14" t="n">
+      <c r="D21" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="E21" s="14" t="n">
+      <c r="E21" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="F21" s="14" t="n">
+      <c r="F21" s="52" t="n">
         <v>0</v>
       </c>
       <c r="G21" s="15" t="n">
@@ -1615,13 +1676,13 @@
           <t>SAP</t>
         </is>
       </c>
-      <c r="D22" s="14" t="n">
+      <c r="D22" s="15" t="n">
         <v>18</v>
       </c>
-      <c r="E22" s="14" t="n">
+      <c r="E22" s="15" t="n">
         <v>18</v>
       </c>
-      <c r="F22" s="14" t="n">
+      <c r="F22" s="52" t="n">
         <v>0</v>
       </c>
       <c r="G22" s="15" t="n">
@@ -1647,13 +1708,13 @@
           <t>SAP</t>
         </is>
       </c>
-      <c r="D23" s="14" t="n">
+      <c r="D23" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="E23" s="14" t="n">
+      <c r="E23" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="F23" s="14" t="n">
+      <c r="F23" s="52" t="n">
         <v>0</v>
       </c>
       <c r="G23" s="15" t="n">
@@ -1664,94 +1725,89 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="20" t="inlineStr">
+      <c r="A24" s="28" t="inlineStr">
         <is>
           <t>KR&gt;FENI KM0</t>
         </is>
       </c>
-      <c r="B24" s="20" t="inlineStr">
+      <c r="B24" s="28" t="inlineStr">
         <is>
           <t>reallocated</t>
         </is>
       </c>
-      <c r="C24" s="20" t="inlineStr">
+      <c r="C24" s="28" t="inlineStr">
         <is>
           <t>SAP (stock at FeNi KM0)</t>
         </is>
       </c>
-      <c r="D24" s="20" t="inlineStr">
+      <c r="D24" s="53" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E24" s="28" t="n">
-        <v>13</v>
-      </c>
-      <c r="F24" s="28" t="n">
-        <v>13</v>
-      </c>
-      <c r="G24" s="29" t="n">
-        <v>1765</v>
-      </c>
-      <c r="H24" s="29" t="n">
-        <v>54712</v>
+      <c r="E24" s="54" t="n">
+        <v>28</v>
+      </c>
+      <c r="F24" s="54" t="n">
+        <v>28</v>
+      </c>
+      <c r="G24" s="54" t="n">
+        <v>3802</v>
+      </c>
+      <c r="H24" s="54" t="n">
+        <v>117848</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="20" t="inlineStr">
+      <c r="A25" s="28" t="inlineStr">
         <is>
           <t>TF&gt;FENI KM0</t>
         </is>
       </c>
-      <c r="B25" s="20" t="inlineStr">
+      <c r="B25" s="28" t="inlineStr">
         <is>
           <t>reallocated</t>
         </is>
       </c>
-      <c r="C25" s="20" t="inlineStr">
+      <c r="C25" s="28" t="inlineStr">
         <is>
           <t>SAP (stock at FeNi KM0)</t>
         </is>
       </c>
-      <c r="D25" s="20" t="inlineStr">
+      <c r="D25" s="53" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E25" s="28" t="n">
-        <v>13</v>
-      </c>
-      <c r="F25" s="28" t="n">
-        <v>13</v>
-      </c>
-      <c r="G25" s="29" t="n">
-        <v>1432</v>
-      </c>
-      <c r="H25" s="29" t="n">
-        <v>44408</v>
+      <c r="E25" s="54" t="n">
+        <v>28</v>
+      </c>
+      <c r="F25" s="54" t="n">
+        <v>28</v>
+      </c>
+      <c r="G25" s="54" t="n">
+        <v>3084</v>
+      </c>
+      <c r="H25" s="54" t="n">
+        <v>95614</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="24" t="inlineStr">
+      <c r="A26" s="38" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B26" s="24" t="n"/>
-      <c r="C26" s="24" t="n"/>
-      <c r="D26" s="25" t="n">
+      <c r="D26" s="32" t="n">
         <v>1190</v>
       </c>
-      <c r="E26" s="25" t="n">
+      <c r="E26" s="32" t="n">
         <v>1190</v>
       </c>
-      <c r="F26" s="24" t="n"/>
-      <c r="G26" s="24" t="n"/>
-      <c r="H26" s="25" t="n">
-        <v>5231542</v>
-      </c>
-    </row>
-    <row r="27"/>
+      <c r="H26" s="32" t="n">
+        <v>5248587</v>
+      </c>
+    </row>
     <row r="28">
       <c r="A28" s="16" t="inlineStr">
         <is>
@@ -1787,7 +1843,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>Dec sales share</t>
+          <t>December TARGET t</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
@@ -1795,7 +1851,6 @@
           <t>Coverage after</t>
         </is>
       </c>
-      <c r="H29" s="31" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="19" t="inlineStr">
@@ -1807,21 +1862,20 @@
         <v>2311732</v>
       </c>
       <c r="C30" s="32" t="n">
-        <v>2410852</v>
+        <v>2525193</v>
       </c>
       <c r="D30" s="27" t="n">
-        <v>99120</v>
+        <v>213461</v>
       </c>
       <c r="E30" s="39" t="n">
-        <v>0.04287694248295218</v>
+        <v>0.09233812569969184</v>
       </c>
       <c r="F30" s="15" t="n">
         <v>2311213</v>
       </c>
       <c r="G30" s="34" t="n">
-        <v>1.043111128225741</v>
-      </c>
-      <c r="H30" s="31" t="n"/>
+        <v>1.092583418317567</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
@@ -1835,10 +1889,10 @@
       <c r="C31" s="32" t="n">
         <v>1001362</v>
       </c>
-      <c r="D31" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="41" t="n">
+      <c r="D31" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="55" t="n">
         <v>0</v>
       </c>
       <c r="F31" s="15" t="n">
@@ -1847,7 +1901,6 @@
       <c r="G31" s="34" t="n">
         <v>1.005298749904626</v>
       </c>
-      <c r="H31" s="31" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="14" t="inlineStr">
@@ -1856,46 +1909,42 @@
         </is>
       </c>
       <c r="B32" s="15" t="n">
-        <v>1903679</v>
+        <v>1903716</v>
       </c>
       <c r="C32" s="32" t="n">
-        <v>1819328</v>
+        <v>1722031</v>
       </c>
       <c r="D32" s="35" t="n">
-        <v>-84351</v>
+        <v>-181685</v>
       </c>
       <c r="E32" s="42" t="n">
-        <v>-0.04430946603917992</v>
+        <v>-0.09543702947288356</v>
       </c>
       <c r="F32" s="15" t="n">
         <v>1719964</v>
       </c>
       <c r="G32" s="34" t="n">
-        <v>1.057770976601836</v>
-      </c>
-      <c r="H32" s="31" t="n"/>
+        <v>1.001201769339358</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="43" t="inlineStr">
         <is>
-          <t>of which reallocated to FeNi KM0 stockpile (KR/TF&gt;FENI KM0)</t>
-        </is>
-      </c>
-      <c r="B33" s="44" t="n"/>
+          <t>of which SAP stocked at FeNi KM0 (KR 28 DT + TF 28 DT reallocated)</t>
+        </is>
+      </c>
+      <c r="B33" s="56" t="n"/>
       <c r="C33" s="27" t="n">
-        <v>99120</v>
+        <v>213461</v>
       </c>
       <c r="D33" s="27" t="n">
-        <v>99120</v>
+        <v>213461</v>
       </c>
       <c r="E33" s="45" t="inlineStr">
         <is>
-          <t>in SAP row</t>
-        </is>
-      </c>
-      <c r="F33" s="30" t="n"/>
-      <c r="G33" s="37" t="n"/>
-      <c r="H33" s="31" t="n"/>
+          <t>inside the SAP row</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="38" t="inlineStr">
@@ -1904,220 +1953,171 @@
         </is>
       </c>
       <c r="B34" s="32" t="n">
-        <v>5216773</v>
+        <v>5216810</v>
       </c>
       <c r="C34" s="32" t="n">
-        <v>5231542</v>
+        <v>5248586</v>
       </c>
       <c r="D34" s="27" t="n">
-        <v>14769</v>
+        <v>31776</v>
       </c>
       <c r="E34" s="39" t="n">
-        <v>0.002831060504261926</v>
-      </c>
-      <c r="F34" s="31" t="n"/>
-      <c r="G34" s="31" t="n"/>
-      <c r="H34" s="31" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="31" t="n"/>
-      <c r="B35" s="31" t="n"/>
-      <c r="C35" s="31" t="n"/>
-      <c r="D35" s="31" t="n"/>
-      <c r="E35" s="31" t="n"/>
-      <c r="F35" s="31" t="n"/>
-      <c r="G35" s="31" t="n"/>
-      <c r="H35" s="31" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="46" t="n"/>
-      <c r="B36" s="31" t="n"/>
-      <c r="C36" s="31" t="n"/>
-      <c r="D36" s="31" t="n"/>
-      <c r="E36" s="31" t="n"/>
-      <c r="F36" s="31" t="n"/>
-      <c r="G36" s="31" t="n"/>
-      <c r="H36" s="31" t="n"/>
+        <v>0.006091078647679329</v>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr"/>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="A37" s="48" t="inlineStr">
+        <is>
+          <t>Scenario 3.0.2 — December</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr"/>
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>Target t</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>Predicted t</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="D38" s="3" t="inlineStr">
         <is>
           <t>Coverage</t>
         </is>
       </c>
-      <c r="E37" s="3" t="inlineStr">
+      <c r="E38" s="3" t="inlineStr">
         <is>
           <t>Fleet DT</t>
         </is>
       </c>
-      <c r="F37" s="3" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="11" t="inlineStr">
+      <c r="F38" s="3" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="19" t="inlineStr">
         <is>
           <t>As frozen</t>
         </is>
       </c>
-      <c r="B38" s="5" t="n">
+      <c r="B39" s="15" t="n">
         <v>5131386</v>
       </c>
-      <c r="C38" s="5" t="n">
+      <c r="C39" s="15" t="n">
         <v>5343787</v>
       </c>
-      <c r="D38" s="7" t="n">
+      <c r="D39" s="49" t="n">
         <v>1.041392520461333</v>
       </c>
-      <c r="E38" s="5" t="n">
+      <c r="E39" s="15" t="n">
         <v>1190</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="12" t="inlineStr">
-        <is>
-          <t>OPTION 1 · park 54 DT</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="n">
+    <row r="40">
+      <c r="A40" s="19" t="inlineStr">
+        <is>
+          <t>OPTION 1 · park 54 DT (total month → 100.0%)</t>
+        </is>
+      </c>
+      <c r="B40" s="15" t="n">
         <v>5131386</v>
       </c>
-      <c r="C39" s="5" t="n">
+      <c r="C40" s="15" t="n">
         <v>5131167</v>
       </c>
-      <c r="D39" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E39" s="5" t="n">
+      <c r="D40" s="34" t="n">
+        <v>0.9999573214722104</v>
+      </c>
+      <c r="E40" s="15" t="n">
         <v>1136</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="13" t="inlineStr">
-        <is>
-          <t>OPTION 2 · re-dispatch 54 DT to stock</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="n">
+    <row r="41">
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>OPTION 2 · re-dispatch 79 DT (LIM-LD → 100.0%)</t>
+        </is>
+      </c>
+      <c r="B41" s="15" t="n">
         <v>5131386</v>
       </c>
-      <c r="C40" s="5" t="n">
-        <v>5131167</v>
-      </c>
-      <c r="D40" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E40" s="5" t="n">
+      <c r="C41" s="15" t="n">
+        <v>5333821</v>
+      </c>
+      <c r="D41" s="50" t="n">
+        <v>1.039450355128225</v>
+      </c>
+      <c r="E41" s="15" t="n">
         <v>1190</v>
       </c>
-      <c r="F40" s="13" t="inlineStr">
-        <is>
-          <t>+ 205,542 t stock to FeNi KM0</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>Cut: TF&gt;POS 6 (RIM, LD): −54 DT  →  re-dispatched to KR&gt;FENI KM0 (27 DT) + TF&gt;FENI KM0 (27 DT)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42"/>
-    <row r="43">
-      <c r="A43" s="16" t="inlineStr">
+      <c r="F41" s="51" t="inlineStr">
+        <is>
+          <t>+ 301,080 t SAP stocked at FeNi KM0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Option 2 cut (sized so LIM-LD lands exactly on its line): TF&gt;POS 6 (RIM, LD): −79 DT @ 127.0 t/day/DT</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="16" t="inlineStr">
         <is>
           <t>OPTION 2 — full December plan (re-dispatched)</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>Contractor</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="D44" s="3" t="inlineStr">
+      <c r="D45" s="3" t="inlineStr">
         <is>
           <t>DT before</t>
         </is>
       </c>
-      <c r="E44" s="3" t="inlineStr">
+      <c r="E45" s="3" t="inlineStr">
         <is>
           <t>DT after</t>
         </is>
       </c>
-      <c r="F44" s="3" t="inlineStr">
+      <c r="F45" s="3" t="inlineStr">
         <is>
           <t>Δ DT</t>
         </is>
       </c>
-      <c r="G44" s="3" t="inlineStr">
+      <c r="G45" s="3" t="inlineStr">
         <is>
           <t>t/day</t>
         </is>
       </c>
-      <c r="H44" s="3" t="inlineStr">
+      <c r="H45" s="3" t="inlineStr">
         <is>
           <t>t/month</t>
         </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="14" t="inlineStr">
-        <is>
-          <t>TF&gt;HUAFEI</t>
-        </is>
-      </c>
-      <c r="B45" s="14" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C45" s="14" t="inlineStr">
-        <is>
-          <t>LIM-LD</t>
-        </is>
-      </c>
-      <c r="D45" s="14" t="n">
-        <v>288</v>
-      </c>
-      <c r="E45" s="14" t="n">
-        <v>288</v>
-      </c>
-      <c r="F45" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" s="15" t="n">
-        <v>30085</v>
-      </c>
-      <c r="H45" s="15" t="n">
-        <v>932635</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="14" t="inlineStr">
         <is>
-          <t>TF&gt;POS 6</t>
+          <t>TF&gt;HUAFEI</t>
         </is>
       </c>
       <c r="B46" s="14" t="inlineStr">
@@ -2130,20 +2130,20 @@
           <t>LIM-LD</t>
         </is>
       </c>
-      <c r="D46" s="14" t="n">
-        <v>149</v>
-      </c>
-      <c r="E46" s="19" t="n">
-        <v>95</v>
-      </c>
-      <c r="F46" s="19" t="n">
-        <v>-54</v>
+      <c r="D46" s="15" t="n">
+        <v>288</v>
+      </c>
+      <c r="E46" s="15" t="n">
+        <v>288</v>
+      </c>
+      <c r="F46" s="52" t="n">
+        <v>0</v>
       </c>
       <c r="G46" s="15" t="n">
-        <v>12066</v>
+        <v>30085</v>
       </c>
       <c r="H46" s="15" t="n">
-        <v>374055</v>
+        <v>932635</v>
       </c>
     </row>
     <row r="47">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>SMA</t>
+          <t>RIM</t>
         </is>
       </c>
       <c r="C47" s="14" t="inlineStr">
@@ -2162,26 +2162,26 @@
           <t>LIM-LD</t>
         </is>
       </c>
-      <c r="D47" s="14" t="n">
-        <v>75</v>
-      </c>
-      <c r="E47" s="14" t="n">
-        <v>75</v>
-      </c>
-      <c r="F47" s="14" t="n">
-        <v>0</v>
+      <c r="D47" s="15" t="n">
+        <v>149</v>
+      </c>
+      <c r="E47" s="32" t="n">
+        <v>70</v>
+      </c>
+      <c r="F47" s="35" t="n">
+        <v>-79</v>
       </c>
       <c r="G47" s="15" t="n">
-        <v>8701</v>
+        <v>8890</v>
       </c>
       <c r="H47" s="15" t="n">
-        <v>269731</v>
+        <v>275605</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="14" t="inlineStr">
         <is>
-          <t>TF&gt;HUAFEI</t>
+          <t>TF&gt;POS 6</t>
         </is>
       </c>
       <c r="B48" s="14" t="inlineStr">
@@ -2194,58 +2194,58 @@
           <t>LIM-LD</t>
         </is>
       </c>
-      <c r="D48" s="14" t="n">
+      <c r="D48" s="15" t="n">
         <v>75</v>
       </c>
-      <c r="E48" s="14" t="n">
+      <c r="E48" s="15" t="n">
         <v>75</v>
       </c>
-      <c r="F48" s="14" t="n">
+      <c r="F48" s="52" t="n">
         <v>0</v>
       </c>
       <c r="G48" s="15" t="n">
-        <v>7822</v>
+        <v>8701</v>
       </c>
       <c r="H48" s="15" t="n">
-        <v>242482</v>
+        <v>269731</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="14" t="inlineStr">
         <is>
-          <t>BLB&gt;HUAFEI</t>
+          <t>TF&gt;HUAFEI</t>
         </is>
       </c>
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>RIM</t>
+          <t>SMA</t>
         </is>
       </c>
       <c r="C49" s="14" t="inlineStr">
         <is>
-          <t>LIM-TOS</t>
-        </is>
-      </c>
-      <c r="D49" s="14" t="n">
-        <v>95</v>
-      </c>
-      <c r="E49" s="14" t="n">
-        <v>95</v>
-      </c>
-      <c r="F49" s="14" t="n">
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D49" s="15" t="n">
+        <v>75</v>
+      </c>
+      <c r="E49" s="15" t="n">
+        <v>75</v>
+      </c>
+      <c r="F49" s="52" t="n">
         <v>0</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>23250</v>
+        <v>7822</v>
       </c>
       <c r="H49" s="15" t="n">
-        <v>720750</v>
+        <v>242482</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="14" t="inlineStr">
         <is>
-          <t>TF&gt;HUAFEI</t>
+          <t>BLB&gt;HUAFEI</t>
         </is>
       </c>
       <c r="B50" s="14" t="inlineStr">
@@ -2258,31 +2258,31 @@
           <t>LIM-TOS</t>
         </is>
       </c>
-      <c r="D50" s="14" t="n">
-        <v>62</v>
-      </c>
-      <c r="E50" s="14" t="n">
-        <v>62</v>
-      </c>
-      <c r="F50" s="14" t="n">
+      <c r="D50" s="15" t="n">
+        <v>95</v>
+      </c>
+      <c r="E50" s="15" t="n">
+        <v>95</v>
+      </c>
+      <c r="F50" s="52" t="n">
         <v>0</v>
       </c>
       <c r="G50" s="15" t="n">
-        <v>6477</v>
+        <v>23250</v>
       </c>
       <c r="H50" s="15" t="n">
-        <v>200787</v>
+        <v>720750</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="14" t="inlineStr">
         <is>
-          <t>KR&gt;HUAFEI</t>
+          <t>TF&gt;HUAFEI</t>
         </is>
       </c>
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>SMA</t>
+          <t>RIM</t>
         </is>
       </c>
       <c r="C51" s="14" t="inlineStr">
@@ -2290,58 +2290,58 @@
           <t>LIM-TOS</t>
         </is>
       </c>
-      <c r="D51" s="14" t="n">
-        <v>19</v>
-      </c>
-      <c r="E51" s="14" t="n">
-        <v>19</v>
-      </c>
-      <c r="F51" s="14" t="n">
+      <c r="D51" s="15" t="n">
+        <v>62</v>
+      </c>
+      <c r="E51" s="15" t="n">
+        <v>62</v>
+      </c>
+      <c r="F51" s="52" t="n">
         <v>0</v>
       </c>
       <c r="G51" s="15" t="n">
-        <v>2549</v>
+        <v>6477</v>
       </c>
       <c r="H51" s="15" t="n">
-        <v>79019</v>
+        <v>200787</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="14" t="inlineStr">
         <is>
-          <t>BLB&gt;FENI KM0</t>
+          <t>KR&gt;HUAFEI</t>
         </is>
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>RIM</t>
+          <t>SMA</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
         <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="D52" s="14" t="n">
-        <v>202</v>
-      </c>
-      <c r="E52" s="14" t="n">
-        <v>202</v>
-      </c>
-      <c r="F52" s="14" t="n">
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D52" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="E52" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="F52" s="52" t="n">
         <v>0</v>
       </c>
       <c r="G52" s="15" t="n">
-        <v>45786</v>
+        <v>2549</v>
       </c>
       <c r="H52" s="15" t="n">
-        <v>1419366</v>
+        <v>79019</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="14" t="inlineStr">
         <is>
-          <t>TF&gt;FENI KM15</t>
+          <t>BLB&gt;FENI KM0</t>
         </is>
       </c>
       <c r="B53" s="14" t="inlineStr">
@@ -2354,31 +2354,31 @@
           <t>SAP</t>
         </is>
       </c>
-      <c r="D53" s="14" t="n">
-        <v>140</v>
-      </c>
-      <c r="E53" s="14" t="n">
-        <v>140</v>
-      </c>
-      <c r="F53" s="14" t="n">
+      <c r="D53" s="15" t="n">
+        <v>202</v>
+      </c>
+      <c r="E53" s="15" t="n">
+        <v>202</v>
+      </c>
+      <c r="F53" s="52" t="n">
         <v>0</v>
       </c>
       <c r="G53" s="15" t="n">
-        <v>14736</v>
+        <v>45786</v>
       </c>
       <c r="H53" s="15" t="n">
-        <v>456816</v>
+        <v>1419366</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="14" t="inlineStr">
         <is>
-          <t>KR&gt;FENI KM15</t>
+          <t>TF&gt;FENI KM15</t>
         </is>
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t>SMA</t>
+          <t>RIM</t>
         </is>
       </c>
       <c r="C54" s="14" t="inlineStr">
@@ -2386,31 +2386,31 @@
           <t>SAP</t>
         </is>
       </c>
-      <c r="D54" s="14" t="n">
-        <v>50</v>
-      </c>
-      <c r="E54" s="14" t="n">
-        <v>50</v>
-      </c>
-      <c r="F54" s="14" t="n">
+      <c r="D54" s="15" t="n">
+        <v>140</v>
+      </c>
+      <c r="E54" s="15" t="n">
+        <v>140</v>
+      </c>
+      <c r="F54" s="52" t="n">
         <v>0</v>
       </c>
       <c r="G54" s="15" t="n">
-        <v>7958</v>
+        <v>14736</v>
       </c>
       <c r="H54" s="15" t="n">
-        <v>246698</v>
+        <v>456816</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="14" t="inlineStr">
         <is>
-          <t>BLB&gt;POS 14</t>
+          <t>KR&gt;FENI KM15</t>
         </is>
       </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>RIM</t>
+          <t>SMA</t>
         </is>
       </c>
       <c r="C55" s="14" t="inlineStr">
@@ -2418,26 +2418,26 @@
           <t>SAP</t>
         </is>
       </c>
-      <c r="D55" s="14" t="n">
-        <v>7</v>
-      </c>
-      <c r="E55" s="14" t="n">
-        <v>7</v>
-      </c>
-      <c r="F55" s="14" t="n">
+      <c r="D55" s="15" t="n">
+        <v>50</v>
+      </c>
+      <c r="E55" s="15" t="n">
+        <v>50</v>
+      </c>
+      <c r="F55" s="52" t="n">
         <v>0</v>
       </c>
       <c r="G55" s="15" t="n">
-        <v>2044</v>
+        <v>7958</v>
       </c>
       <c r="H55" s="15" t="n">
-        <v>63364</v>
+        <v>246698</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="14" t="inlineStr">
         <is>
-          <t>TF&gt;POS 12</t>
+          <t>BLB&gt;POS 14</t>
         </is>
       </c>
       <c r="B56" s="14" t="inlineStr">
@@ -2450,541 +2450,480 @@
           <t>SAP</t>
         </is>
       </c>
-      <c r="D56" s="14" t="n">
-        <v>18</v>
-      </c>
-      <c r="E56" s="14" t="n">
-        <v>18</v>
-      </c>
-      <c r="F56" s="14" t="n">
+      <c r="D56" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="E56" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="F56" s="52" t="n">
         <v>0</v>
       </c>
       <c r="G56" s="15" t="n">
-        <v>2039</v>
+        <v>2044</v>
       </c>
       <c r="H56" s="15" t="n">
-        <v>63209</v>
+        <v>63364</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="14" t="inlineStr">
         <is>
+          <t>TF&gt;POS 12</t>
+        </is>
+      </c>
+      <c r="B57" s="14" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C57" s="14" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D57" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="E57" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="F57" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="15" t="n">
+        <v>2039</v>
+      </c>
+      <c r="H57" s="15" t="n">
+        <v>63209</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="14" t="inlineStr">
+        <is>
           <t>KR&gt;POS 12</t>
         </is>
       </c>
-      <c r="B57" s="14" t="inlineStr">
+      <c r="B58" s="14" t="inlineStr">
         <is>
           <t>SMA</t>
         </is>
       </c>
-      <c r="C57" s="14" t="inlineStr">
+      <c r="C58" s="14" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="D57" s="14" t="n">
+      <c r="D58" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="E57" s="14" t="n">
+      <c r="E58" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="F57" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G57" s="15" t="n">
+      <c r="F58" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="15" t="n">
         <v>2009</v>
       </c>
-      <c r="H57" s="15" t="n">
+      <c r="H58" s="15" t="n">
         <v>62279</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="20" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="28" t="inlineStr">
         <is>
           <t>KR&gt;FENI KM0</t>
         </is>
       </c>
-      <c r="B58" s="20" t="inlineStr">
+      <c r="B59" s="28" t="inlineStr">
         <is>
           <t>reallocated</t>
         </is>
       </c>
-      <c r="C58" s="20" t="inlineStr">
+      <c r="C59" s="28" t="inlineStr">
         <is>
           <t>SAP (stock at FeNi KM0)</t>
         </is>
       </c>
-      <c r="D58" s="20" t="inlineStr">
+      <c r="D59" s="53" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E58" s="28" t="n">
-        <v>27</v>
-      </c>
-      <c r="F58" s="28" t="n">
-        <v>27</v>
-      </c>
-      <c r="G58" s="29" t="n">
-        <v>3661</v>
-      </c>
-      <c r="H58" s="29" t="n">
-        <v>113497</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="20" t="inlineStr">
+      <c r="E59" s="54" t="n">
+        <v>40</v>
+      </c>
+      <c r="F59" s="54" t="n">
+        <v>40</v>
+      </c>
+      <c r="G59" s="54" t="n">
+        <v>5424</v>
+      </c>
+      <c r="H59" s="54" t="n">
+        <v>168135</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="28" t="inlineStr">
         <is>
           <t>TF&gt;FENI KM0</t>
         </is>
       </c>
-      <c r="B59" s="20" t="inlineStr">
+      <c r="B60" s="28" t="inlineStr">
         <is>
           <t>reallocated</t>
         </is>
       </c>
-      <c r="C59" s="20" t="inlineStr">
+      <c r="C60" s="28" t="inlineStr">
         <is>
           <t>SAP (stock at FeNi KM0)</t>
         </is>
       </c>
-      <c r="D59" s="20" t="inlineStr">
+      <c r="D60" s="53" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E59" s="28" t="n">
-        <v>27</v>
-      </c>
-      <c r="F59" s="28" t="n">
-        <v>27</v>
-      </c>
-      <c r="G59" s="29" t="n">
-        <v>2969</v>
-      </c>
-      <c r="H59" s="29" t="n">
-        <v>92045</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="24" t="inlineStr">
+      <c r="E60" s="54" t="n">
+        <v>39</v>
+      </c>
+      <c r="F60" s="54" t="n">
+        <v>39</v>
+      </c>
+      <c r="G60" s="54" t="n">
+        <v>4289</v>
+      </c>
+      <c r="H60" s="54" t="n">
+        <v>132945</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="38" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B60" s="24" t="n"/>
-      <c r="C60" s="24" t="n"/>
-      <c r="D60" s="25" t="n">
+      <c r="D61" s="32" t="n">
         <v>1190</v>
       </c>
-      <c r="E60" s="25" t="n">
+      <c r="E61" s="32" t="n">
         <v>1190</v>
       </c>
-      <c r="F60" s="24" t="n"/>
-      <c r="G60" s="24" t="n"/>
-      <c r="H60" s="25" t="n">
-        <v>5336733</v>
-      </c>
-    </row>
-    <row r="61"/>
-    <row r="62">
-      <c r="A62" s="16" t="inlineStr">
+      <c r="H61" s="32" t="n">
+        <v>5333821</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="16" t="inlineStr">
         <is>
           <t>OPTION 2 — tonnage by material (December)</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="3" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="B63" s="3" t="inlineStr">
+      <c r="B64" s="3" t="inlineStr">
         <is>
           <t>BEFORE re-dispatch t/mo</t>
         </is>
       </c>
-      <c r="C63" s="3" t="inlineStr">
+      <c r="C64" s="3" t="inlineStr">
         <is>
           <t>AFTER re-dispatch t/mo</t>
         </is>
       </c>
-      <c r="D63" s="3" t="inlineStr">
+      <c r="D64" s="3" t="inlineStr">
         <is>
           <t>Δ t/mo</t>
         </is>
       </c>
-      <c r="E63" s="3" t="inlineStr">
+      <c r="E64" s="3" t="inlineStr">
         <is>
           <t>Change %</t>
         </is>
       </c>
-      <c r="F63" s="3" t="inlineStr">
-        <is>
-          <t>Dec sales share</t>
-        </is>
-      </c>
-      <c r="G63" s="3" t="inlineStr">
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>December TARGET t</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
         <is>
           <t>Coverage after</t>
         </is>
       </c>
-      <c r="H63" s="31" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="19" t="inlineStr">
+    </row>
+    <row r="65">
+      <c r="A65" s="19" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="B64" s="15" t="n">
+      <c r="B65" s="15" t="n">
         <v>2311732</v>
       </c>
-      <c r="C64" s="32" t="n">
-        <v>2517274</v>
-      </c>
-      <c r="D64" s="27" t="n">
-        <v>205542</v>
-      </c>
-      <c r="E64" s="39" t="n">
-        <v>0.08891255560765694</v>
-      </c>
-      <c r="F64" s="15" t="n">
+      <c r="C65" s="32" t="n">
+        <v>2612812</v>
+      </c>
+      <c r="D65" s="27" t="n">
+        <v>301080</v>
+      </c>
+      <c r="E65" s="39" t="n">
+        <v>0.1302400105202506</v>
+      </c>
+      <c r="F65" s="15" t="n">
         <v>2311213</v>
       </c>
-      <c r="G64" s="34" t="n">
-        <v>1.089157078988393</v>
-      </c>
-      <c r="H64" s="31" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="14" t="inlineStr">
-        <is>
-          <t>LIM-TOS</t>
-        </is>
-      </c>
-      <c r="B65" s="15" t="n">
-        <v>1000556</v>
-      </c>
-      <c r="C65" s="32" t="n">
-        <v>1000556</v>
-      </c>
-      <c r="D65" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="E65" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="F65" s="15" t="n">
-        <v>996084</v>
-      </c>
       <c r="G65" s="34" t="n">
-        <v>1.004489581199979</v>
-      </c>
-      <c r="H65" s="31" t="n"/>
+        <v>1.13049381428713</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="14" t="inlineStr">
         <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="B66" s="15" t="n">
+        <v>1000556</v>
+      </c>
+      <c r="C66" s="32" t="n">
+        <v>1000556</v>
+      </c>
+      <c r="D66" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" s="15" t="n">
+        <v>996084</v>
+      </c>
+      <c r="G66" s="34" t="n">
+        <v>1.004489581199979</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="14" t="inlineStr">
+        <is>
           <t>LIM-LD</t>
         </is>
       </c>
-      <c r="B66" s="15" t="n">
-        <v>2031523</v>
-      </c>
-      <c r="C66" s="32" t="n">
-        <v>1818903</v>
-      </c>
-      <c r="D66" s="35" t="n">
-        <v>-212620</v>
-      </c>
-      <c r="E66" s="42" t="n">
-        <v>-0.1046603951813492</v>
-      </c>
-      <c r="F66" s="15" t="n">
+      <c r="B67" s="15" t="n">
+        <v>2031492</v>
+      </c>
+      <c r="C67" s="32" t="n">
+        <v>1720453</v>
+      </c>
+      <c r="D67" s="35" t="n">
+        <v>-311039</v>
+      </c>
+      <c r="E67" s="42" t="n">
+        <v>-0.1531086511785427</v>
+      </c>
+      <c r="F67" s="15" t="n">
         <v>1719964</v>
       </c>
-      <c r="G66" s="34" t="n">
-        <v>1.057523878406757</v>
-      </c>
-      <c r="H66" s="31" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="43" t="inlineStr">
-        <is>
-          <t>of which reallocated to FeNi KM0 stockpile (KR/TF&gt;FENI KM0)</t>
-        </is>
-      </c>
-      <c r="B67" s="44" t="n"/>
-      <c r="C67" s="27" t="n">
-        <v>205542</v>
-      </c>
-      <c r="D67" s="27" t="n">
-        <v>205542</v>
-      </c>
-      <c r="E67" s="45" t="inlineStr">
-        <is>
-          <t>in SAP row</t>
-        </is>
-      </c>
-      <c r="F67" s="30" t="n"/>
-      <c r="G67" s="37" t="n"/>
-      <c r="H67" s="31" t="n"/>
+      <c r="G67" s="34" t="n">
+        <v>1.00028430827622</v>
+      </c>
     </row>
     <row r="68">
-      <c r="A68" s="38" t="inlineStr">
+      <c r="A68" s="43" t="inlineStr">
+        <is>
+          <t>of which SAP stocked at FeNi KM0 (KR 40 DT + TF 39 DT reallocated)</t>
+        </is>
+      </c>
+      <c r="B68" s="56" t="n"/>
+      <c r="C68" s="27" t="n">
+        <v>301080</v>
+      </c>
+      <c r="D68" s="27" t="n">
+        <v>301080</v>
+      </c>
+      <c r="E68" s="45" t="inlineStr">
+        <is>
+          <t>inside the SAP row</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="38" t="inlineStr">
         <is>
           <t>TOTAL moved</t>
         </is>
       </c>
-      <c r="B68" s="32" t="n">
-        <v>5343811</v>
-      </c>
-      <c r="C68" s="32" t="n">
-        <v>5336733</v>
-      </c>
-      <c r="D68" s="35" t="n">
-        <v>-7078</v>
-      </c>
-      <c r="E68" s="42" t="n">
-        <v>-0.001324522891995993</v>
-      </c>
-      <c r="F68" s="31" t="n"/>
-      <c r="G68" s="31" t="n"/>
-      <c r="H68" s="31" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="31" t="n"/>
-      <c r="B69" s="31" t="n"/>
-      <c r="C69" s="31" t="n"/>
-      <c r="D69" s="31" t="n"/>
-      <c r="E69" s="31" t="n"/>
-      <c r="F69" s="31" t="n"/>
-      <c r="G69" s="31" t="n"/>
-      <c r="H69" s="31" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="46" t="n"/>
-      <c r="B70" s="31" t="n"/>
-      <c r="C70" s="31" t="n"/>
-      <c r="D70" s="31" t="n"/>
-      <c r="E70" s="31" t="n"/>
-      <c r="F70" s="31" t="n"/>
-      <c r="G70" s="31" t="n"/>
-      <c r="H70" s="31" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="3" t="inlineStr"/>
-      <c r="B71" s="3" t="inlineStr">
+      <c r="B69" s="32" t="n">
+        <v>5343780</v>
+      </c>
+      <c r="C69" s="32" t="n">
+        <v>5333821</v>
+      </c>
+      <c r="D69" s="35" t="n">
+        <v>-9959</v>
+      </c>
+      <c r="E69" s="42" t="n">
+        <v>-0.001863662051955732</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="48" t="inlineStr">
+        <is>
+          <t>Scenario 3.1.1 — December</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr"/>
+      <c r="B73" s="3" t="inlineStr">
         <is>
           <t>Target t</t>
         </is>
       </c>
-      <c r="C71" s="3" t="inlineStr">
+      <c r="C73" s="3" t="inlineStr">
         <is>
           <t>Predicted t</t>
         </is>
       </c>
-      <c r="D71" s="3" t="inlineStr">
+      <c r="D73" s="3" t="inlineStr">
         <is>
           <t>Coverage</t>
         </is>
       </c>
-      <c r="E71" s="3" t="inlineStr">
+      <c r="E73" s="3" t="inlineStr">
         <is>
           <t>Fleet DT</t>
         </is>
       </c>
-      <c r="F71" s="3" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="11" t="inlineStr">
+      <c r="F73" s="3" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="19" t="inlineStr">
         <is>
           <t>As frozen</t>
         </is>
       </c>
-      <c r="B72" s="5" t="n">
+      <c r="B74" s="15" t="n">
         <v>4810381</v>
       </c>
-      <c r="C72" s="5" t="n">
+      <c r="C74" s="15" t="n">
         <v>4971401</v>
       </c>
-      <c r="D72" s="7" t="n">
+      <c r="D74" s="49" t="n">
         <v>1.033473440045601</v>
       </c>
-      <c r="E72" s="5" t="n">
+      <c r="E74" s="15" t="n">
         <v>1052</v>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="12" t="inlineStr">
-        <is>
-          <t>OPTION 1 · park 49 DT</t>
-        </is>
-      </c>
-      <c r="B73" s="5" t="n">
+    <row r="75">
+      <c r="A75" s="19" t="inlineStr">
+        <is>
+          <t>OPTION 1 · park 49 DT (total month → 100.0%)</t>
+        </is>
+      </c>
+      <c r="B75" s="15" t="n">
         <v>4810381</v>
       </c>
-      <c r="C73" s="5" t="n">
+      <c r="C75" s="15" t="n">
         <v>4811620</v>
       </c>
-      <c r="D73" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E73" s="5" t="n">
+      <c r="D75" s="34" t="n">
+        <v>1.000257567955636</v>
+      </c>
+      <c r="E75" s="15" t="n">
         <v>1003</v>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="13" t="inlineStr">
-        <is>
-          <t>OPTION 2 · re-dispatch 49 DT to stock</t>
-        </is>
-      </c>
-      <c r="B74" s="5" t="n">
+    <row r="76">
+      <c r="A76" s="19" t="inlineStr">
+        <is>
+          <t>OPTION 2 · re-dispatch 101 DT (LIM-LD → 100.0%)</t>
+        </is>
+      </c>
+      <c r="B76" s="15" t="n">
         <v>4810381</v>
       </c>
-      <c r="C74" s="5" t="n">
-        <v>4811620</v>
-      </c>
-      <c r="D74" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E74" s="5" t="n">
+      <c r="C76" s="15" t="n">
+        <v>5027004</v>
+      </c>
+      <c r="D76" s="50" t="n">
+        <v>1.045032399720521</v>
+      </c>
+      <c r="E76" s="15" t="n">
         <v>1052</v>
       </c>
-      <c r="F74" s="13" t="inlineStr">
-        <is>
-          <t>+ 182,767 t stock to FeNi KM0</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>Cut: TF&gt;HUAFEI (RIM, LD): −49 DT  →  re-dispatched to KR&gt;FENI KM0 (24 DT) + TF&gt;FENI KM0 (24 DT)</t>
-        </is>
-      </c>
-    </row>
-    <row r="76"/>
+      <c r="F76" s="51" t="inlineStr">
+        <is>
+          <t>+ 384,923 t SAP stocked at FeNi KM0</t>
+        </is>
+      </c>
+    </row>
     <row r="77">
-      <c r="A77" s="16" t="inlineStr">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Option 2 cut (sized so LIM-LD lands exactly on its line): TF&gt;HUAFEI (RIM, LD): −101 DT @ 105.2 t/day/DT</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="16" t="inlineStr">
         <is>
           <t>OPTION 2 — full December plan (re-dispatched)</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="3" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="B78" s="3" t="inlineStr">
+      <c r="B80" s="3" t="inlineStr">
         <is>
           <t>Contractor</t>
         </is>
       </c>
-      <c r="C78" s="3" t="inlineStr">
+      <c r="C80" s="3" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="D78" s="3" t="inlineStr">
+      <c r="D80" s="3" t="inlineStr">
         <is>
           <t>DT before</t>
         </is>
       </c>
-      <c r="E78" s="3" t="inlineStr">
+      <c r="E80" s="3" t="inlineStr">
         <is>
           <t>DT after</t>
         </is>
       </c>
-      <c r="F78" s="3" t="inlineStr">
+      <c r="F80" s="3" t="inlineStr">
         <is>
           <t>Δ DT</t>
         </is>
       </c>
-      <c r="G78" s="3" t="inlineStr">
+      <c r="G80" s="3" t="inlineStr">
         <is>
           <t>t/day</t>
         </is>
       </c>
-      <c r="H78" s="3" t="inlineStr">
+      <c r="H80" s="3" t="inlineStr">
         <is>
           <t>t/month</t>
         </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="14" t="inlineStr">
-        <is>
-          <t>TF&gt;HUAFEI</t>
-        </is>
-      </c>
-      <c r="B79" s="14" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C79" s="14" t="inlineStr">
-        <is>
-          <t>LIM-LD</t>
-        </is>
-      </c>
-      <c r="D79" s="14" t="n">
-        <v>319</v>
-      </c>
-      <c r="E79" s="19" t="n">
-        <v>270</v>
-      </c>
-      <c r="F79" s="19" t="n">
-        <v>-49</v>
-      </c>
-      <c r="G79" s="15" t="n">
-        <v>28401</v>
-      </c>
-      <c r="H79" s="15" t="n">
-        <v>880424</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="14" t="inlineStr">
-        <is>
-          <t>TF&gt;HUAFEI</t>
-        </is>
-      </c>
-      <c r="B80" s="14" t="inlineStr">
-        <is>
-          <t>SMA</t>
-        </is>
-      </c>
-      <c r="C80" s="14" t="inlineStr">
-        <is>
-          <t>LIM-LD</t>
-        </is>
-      </c>
-      <c r="D80" s="14" t="n">
-        <v>87</v>
-      </c>
-      <c r="E80" s="14" t="n">
-        <v>87</v>
-      </c>
-      <c r="F80" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G80" s="15" t="n">
-        <v>9142</v>
-      </c>
-      <c r="H80" s="15" t="n">
-        <v>283402</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="14" t="inlineStr">
         <is>
-          <t>BLB&gt;HUAFEI</t>
+          <t>TF&gt;HUAFEI</t>
         </is>
       </c>
       <c r="B81" s="14" t="inlineStr">
@@ -2994,23 +2933,23 @@
       </c>
       <c r="C81" s="14" t="inlineStr">
         <is>
-          <t>LIM-TOS</t>
-        </is>
-      </c>
-      <c r="D81" s="14" t="n">
-        <v>139</v>
-      </c>
-      <c r="E81" s="14" t="n">
-        <v>139</v>
-      </c>
-      <c r="F81" s="14" t="n">
-        <v>0</v>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D81" s="15" t="n">
+        <v>319</v>
+      </c>
+      <c r="E81" s="32" t="n">
+        <v>218</v>
+      </c>
+      <c r="F81" s="35" t="n">
+        <v>-101</v>
       </c>
       <c r="G81" s="15" t="n">
-        <v>33859</v>
+        <v>22932</v>
       </c>
       <c r="H81" s="15" t="n">
-        <v>1049629</v>
+        <v>710878</v>
       </c>
     </row>
     <row r="82">
@@ -3021,39 +2960,39 @@
       </c>
       <c r="B82" s="14" t="inlineStr">
         <is>
-          <t>RIM</t>
+          <t>SMA</t>
         </is>
       </c>
       <c r="C82" s="14" t="inlineStr">
         <is>
-          <t>LIM-TOS</t>
-        </is>
-      </c>
-      <c r="D82" s="14" t="n">
-        <v>62</v>
-      </c>
-      <c r="E82" s="14" t="n">
-        <v>62</v>
-      </c>
-      <c r="F82" s="14" t="n">
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D82" s="15" t="n">
+        <v>87</v>
+      </c>
+      <c r="E82" s="15" t="n">
+        <v>87</v>
+      </c>
+      <c r="F82" s="52" t="n">
         <v>0</v>
       </c>
       <c r="G82" s="15" t="n">
-        <v>6522</v>
+        <v>9142</v>
       </c>
       <c r="H82" s="15" t="n">
-        <v>202182</v>
+        <v>283402</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="14" t="inlineStr">
         <is>
-          <t>KR&gt;HUAFEI</t>
+          <t>BLB&gt;HUAFEI</t>
         </is>
       </c>
       <c r="B83" s="14" t="inlineStr">
         <is>
-          <t>SMA</t>
+          <t>RIM</t>
         </is>
       </c>
       <c r="C83" s="14" t="inlineStr">
@@ -3061,26 +3000,26 @@
           <t>LIM-TOS</t>
         </is>
       </c>
-      <c r="D83" s="14" t="n">
-        <v>19</v>
-      </c>
-      <c r="E83" s="14" t="n">
-        <v>19</v>
-      </c>
-      <c r="F83" s="14" t="n">
+      <c r="D83" s="15" t="n">
+        <v>139</v>
+      </c>
+      <c r="E83" s="15" t="n">
+        <v>139</v>
+      </c>
+      <c r="F83" s="52" t="n">
         <v>0</v>
       </c>
       <c r="G83" s="15" t="n">
-        <v>2597</v>
+        <v>33859</v>
       </c>
       <c r="H83" s="15" t="n">
-        <v>80507</v>
+        <v>1049629</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="14" t="inlineStr">
         <is>
-          <t>BLB&gt;FENI KM0</t>
+          <t>TF&gt;HUAFEI</t>
         </is>
       </c>
       <c r="B84" s="14" t="inlineStr">
@@ -3090,66 +3029,66 @@
       </c>
       <c r="C84" s="14" t="inlineStr">
         <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="D84" s="14" t="n">
-        <v>202</v>
-      </c>
-      <c r="E84" s="14" t="n">
-        <v>202</v>
-      </c>
-      <c r="F84" s="14" t="n">
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D84" s="15" t="n">
+        <v>62</v>
+      </c>
+      <c r="E84" s="15" t="n">
+        <v>62</v>
+      </c>
+      <c r="F84" s="52" t="n">
         <v>0</v>
       </c>
       <c r="G84" s="15" t="n">
-        <v>45786</v>
+        <v>6522</v>
       </c>
       <c r="H84" s="15" t="n">
-        <v>1419366</v>
+        <v>202182</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="14" t="inlineStr">
         <is>
-          <t>TF&gt;FENI KM15</t>
+          <t>KR&gt;HUAFEI</t>
         </is>
       </c>
       <c r="B85" s="14" t="inlineStr">
         <is>
-          <t>RIM</t>
+          <t>SMA</t>
         </is>
       </c>
       <c r="C85" s="14" t="inlineStr">
         <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="D85" s="14" t="n">
-        <v>140</v>
-      </c>
-      <c r="E85" s="14" t="n">
-        <v>140</v>
-      </c>
-      <c r="F85" s="14" t="n">
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D85" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="E85" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="F85" s="52" t="n">
         <v>0</v>
       </c>
       <c r="G85" s="15" t="n">
-        <v>14847</v>
+        <v>2597</v>
       </c>
       <c r="H85" s="15" t="n">
-        <v>460257</v>
+        <v>80507</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="14" t="inlineStr">
         <is>
-          <t>KR&gt;FENI KM15</t>
+          <t>BLB&gt;FENI KM0</t>
         </is>
       </c>
       <c r="B86" s="14" t="inlineStr">
         <is>
-          <t>SMA</t>
+          <t>RIM</t>
         </is>
       </c>
       <c r="C86" s="14" t="inlineStr">
@@ -3157,26 +3096,26 @@
           <t>SAP</t>
         </is>
       </c>
-      <c r="D86" s="14" t="n">
-        <v>49</v>
-      </c>
-      <c r="E86" s="14" t="n">
-        <v>49</v>
-      </c>
-      <c r="F86" s="14" t="n">
+      <c r="D86" s="15" t="n">
+        <v>202</v>
+      </c>
+      <c r="E86" s="15" t="n">
+        <v>202</v>
+      </c>
+      <c r="F86" s="52" t="n">
         <v>0</v>
       </c>
       <c r="G86" s="15" t="n">
-        <v>7929</v>
+        <v>45786</v>
       </c>
       <c r="H86" s="15" t="n">
-        <v>245799</v>
+        <v>1419366</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="14" t="inlineStr">
         <is>
-          <t>TF&gt;POS 12</t>
+          <t>TF&gt;FENI KM15</t>
         </is>
       </c>
       <c r="B87" s="14" t="inlineStr">
@@ -3189,31 +3128,31 @@
           <t>SAP</t>
         </is>
       </c>
-      <c r="D87" s="14" t="n">
-        <v>18</v>
-      </c>
-      <c r="E87" s="14" t="n">
-        <v>18</v>
-      </c>
-      <c r="F87" s="14" t="n">
+      <c r="D87" s="15" t="n">
+        <v>140</v>
+      </c>
+      <c r="E87" s="15" t="n">
+        <v>140</v>
+      </c>
+      <c r="F87" s="52" t="n">
         <v>0</v>
       </c>
       <c r="G87" s="15" t="n">
-        <v>2045</v>
+        <v>14847</v>
       </c>
       <c r="H87" s="15" t="n">
-        <v>63395</v>
+        <v>460257</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="14" t="inlineStr">
         <is>
-          <t>BLB&gt;POS 14</t>
+          <t>KR&gt;FENI KM15</t>
         </is>
       </c>
       <c r="B88" s="14" t="inlineStr">
         <is>
-          <t>RIM</t>
+          <t>SMA</t>
         </is>
       </c>
       <c r="C88" s="14" t="inlineStr">
@@ -3221,573 +3160,512 @@
           <t>SAP</t>
         </is>
       </c>
-      <c r="D88" s="14" t="n">
-        <v>7</v>
-      </c>
-      <c r="E88" s="14" t="n">
-        <v>7</v>
-      </c>
-      <c r="F88" s="14" t="n">
+      <c r="D88" s="15" t="n">
+        <v>49</v>
+      </c>
+      <c r="E88" s="15" t="n">
+        <v>49</v>
+      </c>
+      <c r="F88" s="52" t="n">
         <v>0</v>
       </c>
       <c r="G88" s="15" t="n">
-        <v>2044</v>
+        <v>7929</v>
       </c>
       <c r="H88" s="15" t="n">
-        <v>63364</v>
+        <v>245799</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="14" t="inlineStr">
         <is>
+          <t>TF&gt;POS 12</t>
+        </is>
+      </c>
+      <c r="B89" s="14" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C89" s="14" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D89" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="E89" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="F89" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" s="15" t="n">
+        <v>2045</v>
+      </c>
+      <c r="H89" s="15" t="n">
+        <v>63395</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="14" t="inlineStr">
+        <is>
+          <t>BLB&gt;POS 14</t>
+        </is>
+      </c>
+      <c r="B90" s="14" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C90" s="14" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D90" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="E90" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="F90" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" s="15" t="n">
+        <v>2044</v>
+      </c>
+      <c r="H90" s="15" t="n">
+        <v>63364</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="14" t="inlineStr">
+        <is>
           <t>KR&gt;POS 12</t>
         </is>
       </c>
-      <c r="B89" s="14" t="inlineStr">
+      <c r="B91" s="14" t="inlineStr">
         <is>
           <t>SMA</t>
         </is>
       </c>
-      <c r="C89" s="14" t="inlineStr">
+      <c r="C91" s="14" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="D89" s="14" t="n">
+      <c r="D91" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="E89" s="14" t="n">
+      <c r="E91" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="F89" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G89" s="15" t="n">
+      <c r="F91" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" s="15" t="n">
         <v>2042</v>
       </c>
-      <c r="H89" s="15" t="n">
+      <c r="H91" s="15" t="n">
         <v>63302</v>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="20" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="28" t="inlineStr">
         <is>
           <t>KR&gt;FENI KM0</t>
         </is>
       </c>
-      <c r="B90" s="20" t="inlineStr">
+      <c r="B92" s="28" t="inlineStr">
         <is>
           <t>reallocated</t>
         </is>
       </c>
-      <c r="C90" s="20" t="inlineStr">
+      <c r="C92" s="28" t="inlineStr">
         <is>
           <t>SAP (stock at FeNi KM0)</t>
         </is>
       </c>
-      <c r="D90" s="20" t="inlineStr">
+      <c r="D92" s="53" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E90" s="28" t="n">
-        <v>24</v>
-      </c>
-      <c r="F90" s="28" t="n">
-        <v>24</v>
-      </c>
-      <c r="G90" s="29" t="n">
-        <v>3255</v>
-      </c>
-      <c r="H90" s="29" t="n">
-        <v>100911</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="20" t="inlineStr">
+      <c r="E92" s="54" t="n">
+        <v>51</v>
+      </c>
+      <c r="F92" s="54" t="n">
+        <v>51</v>
+      </c>
+      <c r="G92" s="54" t="n">
+        <v>6917</v>
+      </c>
+      <c r="H92" s="54" t="n">
+        <v>214423</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="28" t="inlineStr">
         <is>
           <t>TF&gt;FENI KM0</t>
         </is>
       </c>
-      <c r="B91" s="20" t="inlineStr">
+      <c r="B93" s="28" t="inlineStr">
         <is>
           <t>reallocated</t>
         </is>
       </c>
-      <c r="C91" s="20" t="inlineStr">
+      <c r="C93" s="28" t="inlineStr">
         <is>
           <t>SAP (stock at FeNi KM0)</t>
         </is>
       </c>
-      <c r="D91" s="20" t="inlineStr">
+      <c r="D93" s="53" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E91" s="28" t="n">
-        <v>24</v>
-      </c>
-      <c r="F91" s="28" t="n">
-        <v>24</v>
-      </c>
-      <c r="G91" s="29" t="n">
-        <v>2640</v>
-      </c>
-      <c r="H91" s="29" t="n">
-        <v>81856</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="24" t="inlineStr">
+      <c r="E93" s="54" t="n">
+        <v>50</v>
+      </c>
+      <c r="F93" s="54" t="n">
+        <v>50</v>
+      </c>
+      <c r="G93" s="54" t="n">
+        <v>5500</v>
+      </c>
+      <c r="H93" s="54" t="n">
+        <v>170500</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="38" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B92" s="24" t="n"/>
-      <c r="C92" s="24" t="n"/>
-      <c r="D92" s="25" t="n">
+      <c r="D94" s="32" t="n">
         <v>1052</v>
       </c>
-      <c r="E92" s="25" t="n">
-        <v>1051</v>
-      </c>
-      <c r="F92" s="24" t="n"/>
-      <c r="G92" s="24" t="n"/>
-      <c r="H92" s="25" t="n">
-        <v>4994394</v>
-      </c>
-    </row>
-    <row r="93"/>
-    <row r="94">
-      <c r="A94" s="16" t="inlineStr">
+      <c r="E94" s="32" t="n">
+        <v>1052</v>
+      </c>
+      <c r="H94" s="32" t="n">
+        <v>5027004</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="16" t="inlineStr">
         <is>
           <t>OPTION 2 — tonnage by material (December)</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="3" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="B95" s="3" t="inlineStr">
+      <c r="B97" s="3" t="inlineStr">
         <is>
           <t>BEFORE re-dispatch t/mo</t>
         </is>
       </c>
-      <c r="C95" s="3" t="inlineStr">
+      <c r="C97" s="3" t="inlineStr">
         <is>
           <t>AFTER re-dispatch t/mo</t>
         </is>
       </c>
-      <c r="D95" s="3" t="inlineStr">
+      <c r="D97" s="3" t="inlineStr">
         <is>
           <t>Δ t/mo</t>
         </is>
       </c>
-      <c r="E95" s="3" t="inlineStr">
+      <c r="E97" s="3" t="inlineStr">
         <is>
           <t>Change %</t>
         </is>
       </c>
-      <c r="F95" s="3" t="inlineStr">
-        <is>
-          <t>Dec sales share</t>
-        </is>
-      </c>
-      <c r="G95" s="3" t="inlineStr">
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t>December TARGET t</t>
+        </is>
+      </c>
+      <c r="G97" s="3" t="inlineStr">
         <is>
           <t>Coverage after</t>
         </is>
       </c>
-      <c r="H95" s="31" t="n"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="19" t="inlineStr">
+    </row>
+    <row r="98">
+      <c r="A98" s="19" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="B96" s="15" t="n">
+      <c r="B98" s="15" t="n">
         <v>2315483</v>
       </c>
-      <c r="C96" s="32" t="n">
-        <v>2498250</v>
-      </c>
-      <c r="D96" s="27" t="n">
-        <v>182767</v>
-      </c>
-      <c r="E96" s="39" t="n">
-        <v>0.07893255964306367</v>
-      </c>
-      <c r="F96" s="15" t="n">
+      <c r="C98" s="32" t="n">
+        <v>2700406</v>
+      </c>
+      <c r="D98" s="27" t="n">
+        <v>384923</v>
+      </c>
+      <c r="E98" s="39" t="n">
+        <v>0.1662387501873259</v>
+      </c>
+      <c r="F98" s="15" t="n">
         <v>2311213</v>
       </c>
-      <c r="G96" s="34" t="n">
-        <v>1.080925903410893</v>
-      </c>
-      <c r="H96" s="31" t="n"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="14" t="inlineStr">
+      <c r="G98" s="34" t="n">
+        <v>1.168393393425876</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="14" t="inlineStr">
         <is>
           <t>LIM-TOS</t>
         </is>
       </c>
-      <c r="B97" s="15" t="n">
+      <c r="B99" s="15" t="n">
         <v>1332318</v>
       </c>
-      <c r="C97" s="32" t="n">
+      <c r="C99" s="32" t="n">
         <v>1332318</v>
       </c>
-      <c r="D97" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="E97" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="F97" s="15" t="n">
+      <c r="D99" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" s="15" t="n">
         <v>1326082</v>
       </c>
-      <c r="G97" s="34" t="n">
+      <c r="G99" s="34" t="n">
         <v>1.004702574953887</v>
       </c>
-      <c r="H97" s="31" t="n"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="14" t="inlineStr">
+    </row>
+    <row r="100">
+      <c r="A100" s="14" t="inlineStr">
         <is>
           <t>LIM-LD</t>
         </is>
       </c>
-      <c r="B98" s="15" t="n">
-        <v>1323607</v>
-      </c>
-      <c r="C98" s="32" t="n">
-        <v>1163826</v>
-      </c>
-      <c r="D98" s="35" t="n">
-        <v>-159781</v>
-      </c>
-      <c r="E98" s="42" t="n">
-        <v>-0.1207163455617868</v>
-      </c>
-      <c r="F98" s="15" t="n">
+      <c r="B100" s="15" t="n">
+        <v>1323632</v>
+      </c>
+      <c r="C100" s="32" t="n">
+        <v>994280</v>
+      </c>
+      <c r="D100" s="35" t="n">
+        <v>-329352</v>
+      </c>
+      <c r="E100" s="42" t="n">
+        <v>-0.248824446674</v>
+      </c>
+      <c r="F100" s="15" t="n">
         <v>992213</v>
       </c>
-      <c r="G98" s="34" t="n">
-        <v>1.172959838260535</v>
-      </c>
-      <c r="H98" s="31" t="n"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="43" t="inlineStr">
-        <is>
-          <t>of which reallocated to FeNi KM0 stockpile (KR/TF&gt;FENI KM0)</t>
-        </is>
-      </c>
-      <c r="B99" s="44" t="n"/>
-      <c r="C99" s="27" t="n">
-        <v>182767</v>
-      </c>
-      <c r="D99" s="27" t="n">
-        <v>182767</v>
-      </c>
-      <c r="E99" s="45" t="inlineStr">
-        <is>
-          <t>in SAP row</t>
-        </is>
-      </c>
-      <c r="F99" s="30" t="n"/>
-      <c r="G99" s="37" t="n"/>
-      <c r="H99" s="31" t="n"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="38" t="inlineStr">
+      <c r="G100" s="34" t="n">
+        <v>1.002083222050104</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="43" t="inlineStr">
+        <is>
+          <t>of which SAP stocked at FeNi KM0 (KR 51 DT + TF 50 DT reallocated)</t>
+        </is>
+      </c>
+      <c r="B101" s="56" t="n"/>
+      <c r="C101" s="27" t="n">
+        <v>384923</v>
+      </c>
+      <c r="D101" s="27" t="n">
+        <v>384923</v>
+      </c>
+      <c r="E101" s="45" t="inlineStr">
+        <is>
+          <t>inside the SAP row</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="38" t="inlineStr">
         <is>
           <t>TOTAL moved</t>
         </is>
       </c>
-      <c r="B100" s="32" t="n">
-        <v>4971408</v>
-      </c>
-      <c r="C100" s="32" t="n">
-        <v>4994394</v>
-      </c>
-      <c r="D100" s="27" t="n">
-        <v>22986</v>
-      </c>
-      <c r="E100" s="39" t="n">
-        <v>0.004623639821957884</v>
-      </c>
-      <c r="F100" s="31" t="n"/>
-      <c r="G100" s="31" t="n"/>
-      <c r="H100" s="31" t="n"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="31" t="n"/>
-      <c r="B101" s="31" t="n"/>
-      <c r="C101" s="31" t="n"/>
-      <c r="D101" s="31" t="n"/>
-      <c r="E101" s="31" t="n"/>
-      <c r="F101" s="31" t="n"/>
-      <c r="G101" s="31" t="n"/>
-      <c r="H101" s="31" t="n"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="46" t="n"/>
-      <c r="B102" s="31" t="n"/>
-      <c r="C102" s="31" t="n"/>
-      <c r="D102" s="31" t="n"/>
-      <c r="E102" s="31" t="n"/>
-      <c r="F102" s="31" t="n"/>
-      <c r="G102" s="31" t="n"/>
-      <c r="H102" s="31" t="n"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="3" t="inlineStr"/>
-      <c r="B103" s="3" t="inlineStr">
+      <c r="B102" s="32" t="n">
+        <v>4971433</v>
+      </c>
+      <c r="C102" s="32" t="n">
+        <v>5027004</v>
+      </c>
+      <c r="D102" s="27" t="n">
+        <v>55571</v>
+      </c>
+      <c r="E102" s="39" t="n">
+        <v>0.0111780647551722</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="48" t="inlineStr">
+        <is>
+          <t>Scenario 3.1.2 — December</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr"/>
+      <c r="B106" s="3" t="inlineStr">
         <is>
           <t>Target t</t>
         </is>
       </c>
-      <c r="C103" s="3" t="inlineStr">
+      <c r="C106" s="3" t="inlineStr">
         <is>
           <t>Predicted t</t>
         </is>
       </c>
-      <c r="D103" s="3" t="inlineStr">
+      <c r="D106" s="3" t="inlineStr">
         <is>
           <t>Coverage</t>
         </is>
       </c>
-      <c r="E103" s="3" t="inlineStr">
+      <c r="E106" s="3" t="inlineStr">
         <is>
           <t>Fleet DT</t>
         </is>
       </c>
-      <c r="F103" s="3" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="11" t="inlineStr">
+      <c r="F106" s="3" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="19" t="inlineStr">
         <is>
           <t>As frozen</t>
         </is>
       </c>
-      <c r="B104" s="5" t="n">
+      <c r="B107" s="15" t="n">
         <v>4810381</v>
       </c>
-      <c r="C104" s="5" t="n">
+      <c r="C107" s="15" t="n">
         <v>5045234</v>
       </c>
-      <c r="D104" s="7" t="n">
+      <c r="D107" s="49" t="n">
         <v>1.048822120326852</v>
       </c>
-      <c r="E104" s="5" t="n">
+      <c r="E107" s="15" t="n">
         <v>1052</v>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="12" t="inlineStr">
-        <is>
-          <t>OPTION 1 · park 59 DT</t>
-        </is>
-      </c>
-      <c r="B105" s="5" t="n">
+    <row r="108">
+      <c r="A108" s="19" t="inlineStr">
+        <is>
+          <t>OPTION 1 · park 59 DT (total month → 100.0%)</t>
+        </is>
+      </c>
+      <c r="B108" s="15" t="n">
         <v>4810381</v>
       </c>
-      <c r="C105" s="5" t="n">
+      <c r="C108" s="15" t="n">
         <v>4811739</v>
       </c>
-      <c r="D105" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E105" s="5" t="n">
+      <c r="D108" s="34" t="n">
+        <v>1.000282306120867</v>
+      </c>
+      <c r="E108" s="15" t="n">
         <v>993</v>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="13" t="inlineStr">
-        <is>
-          <t>OPTION 2 · re-dispatch 59 DT to stock</t>
-        </is>
-      </c>
-      <c r="B106" s="5" t="n">
+    <row r="109">
+      <c r="A109" s="19" t="inlineStr">
+        <is>
+          <t>OPTION 2 · re-dispatch 104 DT (LIM-LD → 100.0%)</t>
+        </is>
+      </c>
+      <c r="B109" s="15" t="n">
         <v>4810381</v>
       </c>
-      <c r="C106" s="5" t="n">
-        <v>4811739</v>
-      </c>
-      <c r="D106" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E106" s="5" t="n">
+      <c r="C109" s="15" t="n">
+        <v>5035551</v>
+      </c>
+      <c r="D109" s="50" t="n">
+        <v>1.046809182058552</v>
+      </c>
+      <c r="E109" s="15" t="n">
         <v>1052</v>
       </c>
-      <c r="F106" s="13" t="inlineStr">
-        <is>
-          <t>+ 228,303 t stock to FeNi KM0</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>Cut: TF&gt;POS 6 (RIM, LD): −59 DT  →  re-dispatched to KR&gt;FENI KM0 (30 DT) + TF&gt;FENI KM0 (30 DT)</t>
-        </is>
-      </c>
-    </row>
-    <row r="108"/>
-    <row r="109">
-      <c r="A109" s="16" t="inlineStr">
+      <c r="F109" s="51" t="inlineStr">
+        <is>
+          <t>+ 395,746 t SAP stocked at FeNi KM0</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>Option 2 cut (sized so LIM-LD lands exactly on its line): TF&gt;POS 6 (RIM, LD): −86 DT @ 127.7 t/day/DT · TF&gt;POS 6 (SMA, LD): −18 DT @ 116.6 t/day/DT</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="16" t="inlineStr">
         <is>
           <t>OPTION 2 — full December plan (re-dispatched)</t>
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="3" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="3" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="B110" s="3" t="inlineStr">
+      <c r="B113" s="3" t="inlineStr">
         <is>
           <t>Contractor</t>
         </is>
       </c>
-      <c r="C110" s="3" t="inlineStr">
+      <c r="C113" s="3" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="D110" s="3" t="inlineStr">
+      <c r="D113" s="3" t="inlineStr">
         <is>
           <t>DT before</t>
         </is>
       </c>
-      <c r="E110" s="3" t="inlineStr">
+      <c r="E113" s="3" t="inlineStr">
         <is>
           <t>DT after</t>
         </is>
       </c>
-      <c r="F110" s="3" t="inlineStr">
+      <c r="F113" s="3" t="inlineStr">
         <is>
           <t>Δ DT</t>
         </is>
       </c>
-      <c r="G110" s="3" t="inlineStr">
+      <c r="G113" s="3" t="inlineStr">
         <is>
           <t>t/day</t>
         </is>
       </c>
-      <c r="H110" s="3" t="inlineStr">
+      <c r="H113" s="3" t="inlineStr">
         <is>
           <t>t/month</t>
         </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="14" t="inlineStr">
-        <is>
-          <t>TF&gt;HUAFEI</t>
-        </is>
-      </c>
-      <c r="B111" s="14" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C111" s="14" t="inlineStr">
-        <is>
-          <t>LIM-LD</t>
-        </is>
-      </c>
-      <c r="D111" s="14" t="n">
-        <v>233</v>
-      </c>
-      <c r="E111" s="14" t="n">
-        <v>233</v>
-      </c>
-      <c r="F111" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G111" s="15" t="n">
-        <v>24482</v>
-      </c>
-      <c r="H111" s="15" t="n">
-        <v>758942</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="14" t="inlineStr">
-        <is>
-          <t>TF&gt;POS 6</t>
-        </is>
-      </c>
-      <c r="B112" s="14" t="inlineStr">
-        <is>
-          <t>SMA</t>
-        </is>
-      </c>
-      <c r="C112" s="14" t="inlineStr">
-        <is>
-          <t>LIM-LD</t>
-        </is>
-      </c>
-      <c r="D112" s="14" t="n">
-        <v>43</v>
-      </c>
-      <c r="E112" s="14" t="n">
-        <v>43</v>
-      </c>
-      <c r="F112" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G112" s="15" t="n">
-        <v>5014</v>
-      </c>
-      <c r="H112" s="15" t="n">
-        <v>155434</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="14" t="inlineStr">
-        <is>
-          <t>TF&gt;HUAFEI</t>
-        </is>
-      </c>
-      <c r="B113" s="14" t="inlineStr">
-        <is>
-          <t>SMA</t>
-        </is>
-      </c>
-      <c r="C113" s="14" t="inlineStr">
-        <is>
-          <t>LIM-LD</t>
-        </is>
-      </c>
-      <c r="D113" s="14" t="n">
-        <v>44</v>
-      </c>
-      <c r="E113" s="14" t="n">
-        <v>44</v>
-      </c>
-      <c r="F113" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G113" s="15" t="n">
-        <v>4618</v>
-      </c>
-      <c r="H113" s="15" t="n">
-        <v>143158</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="14" t="inlineStr">
         <is>
-          <t>TF&gt;POS 6</t>
+          <t>TF&gt;HUAFEI</t>
         </is>
       </c>
       <c r="B114" s="14" t="inlineStr">
@@ -3800,26 +3678,26 @@
           <t>LIM-LD</t>
         </is>
       </c>
-      <c r="D114" s="14" t="n">
-        <v>86</v>
-      </c>
-      <c r="E114" s="19" t="n">
-        <v>27</v>
-      </c>
-      <c r="F114" s="19" t="n">
-        <v>-59</v>
+      <c r="D114" s="15" t="n">
+        <v>233</v>
+      </c>
+      <c r="E114" s="15" t="n">
+        <v>233</v>
+      </c>
+      <c r="F114" s="52" t="n">
+        <v>0</v>
       </c>
       <c r="G114" s="15" t="n">
-        <v>3447</v>
+        <v>24482</v>
       </c>
       <c r="H114" s="15" t="n">
-        <v>106854</v>
+        <v>758942</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="14" t="inlineStr">
         <is>
-          <t>BLB&gt;HUAFEI</t>
+          <t>TF&gt;POS 6</t>
         </is>
       </c>
       <c r="B115" s="14" t="inlineStr">
@@ -3829,61 +3707,61 @@
       </c>
       <c r="C115" s="14" t="inlineStr">
         <is>
-          <t>LIM-TOS</t>
-        </is>
-      </c>
-      <c r="D115" s="14" t="n">
-        <v>139</v>
-      </c>
-      <c r="E115" s="14" t="n">
-        <v>139</v>
-      </c>
-      <c r="F115" s="14" t="n">
-        <v>0</v>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D115" s="15" t="n">
+        <v>86</v>
+      </c>
+      <c r="E115" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" s="35" t="n">
+        <v>-86</v>
       </c>
       <c r="G115" s="15" t="n">
-        <v>33859</v>
+        <v>0</v>
       </c>
       <c r="H115" s="15" t="n">
-        <v>1049629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="14" t="inlineStr">
         <is>
-          <t>TF&gt;HUAFEI</t>
+          <t>TF&gt;POS 6</t>
         </is>
       </c>
       <c r="B116" s="14" t="inlineStr">
         <is>
-          <t>RIM</t>
+          <t>SMA</t>
         </is>
       </c>
       <c r="C116" s="14" t="inlineStr">
         <is>
-          <t>LIM-TOS</t>
-        </is>
-      </c>
-      <c r="D116" s="14" t="n">
-        <v>62</v>
-      </c>
-      <c r="E116" s="14" t="n">
-        <v>62</v>
-      </c>
-      <c r="F116" s="14" t="n">
-        <v>0</v>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D116" s="15" t="n">
+        <v>43</v>
+      </c>
+      <c r="E116" s="32" t="n">
+        <v>25</v>
+      </c>
+      <c r="F116" s="35" t="n">
+        <v>-18</v>
       </c>
       <c r="G116" s="15" t="n">
-        <v>6514</v>
+        <v>2915</v>
       </c>
       <c r="H116" s="15" t="n">
-        <v>201934</v>
+        <v>90369</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="14" t="inlineStr">
         <is>
-          <t>KR&gt;HUAFEI</t>
+          <t>TF&gt;HUAFEI</t>
         </is>
       </c>
       <c r="B117" s="14" t="inlineStr">
@@ -3893,29 +3771,29 @@
       </c>
       <c r="C117" s="14" t="inlineStr">
         <is>
-          <t>LIM-TOS</t>
-        </is>
-      </c>
-      <c r="D117" s="14" t="n">
-        <v>19</v>
-      </c>
-      <c r="E117" s="14" t="n">
-        <v>19</v>
-      </c>
-      <c r="F117" s="14" t="n">
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D117" s="15" t="n">
+        <v>44</v>
+      </c>
+      <c r="E117" s="15" t="n">
+        <v>44</v>
+      </c>
+      <c r="F117" s="52" t="n">
         <v>0</v>
       </c>
       <c r="G117" s="15" t="n">
-        <v>2590</v>
+        <v>4618</v>
       </c>
       <c r="H117" s="15" t="n">
-        <v>80290</v>
+        <v>143158</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="14" t="inlineStr">
         <is>
-          <t>BLB&gt;FENI KM0</t>
+          <t>BLB&gt;HUAFEI</t>
         </is>
       </c>
       <c r="B118" s="14" t="inlineStr">
@@ -3925,29 +3803,29 @@
       </c>
       <c r="C118" s="14" t="inlineStr">
         <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="D118" s="14" t="n">
-        <v>202</v>
-      </c>
-      <c r="E118" s="14" t="n">
-        <v>202</v>
-      </c>
-      <c r="F118" s="14" t="n">
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D118" s="15" t="n">
+        <v>139</v>
+      </c>
+      <c r="E118" s="15" t="n">
+        <v>139</v>
+      </c>
+      <c r="F118" s="52" t="n">
         <v>0</v>
       </c>
       <c r="G118" s="15" t="n">
-        <v>45786</v>
+        <v>33859</v>
       </c>
       <c r="H118" s="15" t="n">
-        <v>1419366</v>
+        <v>1049629</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="14" t="inlineStr">
         <is>
-          <t>TF&gt;FENI KM15</t>
+          <t>TF&gt;HUAFEI</t>
         </is>
       </c>
       <c r="B119" s="14" t="inlineStr">
@@ -3957,29 +3835,29 @@
       </c>
       <c r="C119" s="14" t="inlineStr">
         <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="D119" s="14" t="n">
-        <v>140</v>
-      </c>
-      <c r="E119" s="14" t="n">
-        <v>140</v>
-      </c>
-      <c r="F119" s="14" t="n">
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D119" s="15" t="n">
+        <v>62</v>
+      </c>
+      <c r="E119" s="15" t="n">
+        <v>62</v>
+      </c>
+      <c r="F119" s="52" t="n">
         <v>0</v>
       </c>
       <c r="G119" s="15" t="n">
-        <v>14847</v>
+        <v>6514</v>
       </c>
       <c r="H119" s="15" t="n">
-        <v>460257</v>
+        <v>201934</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="14" t="inlineStr">
         <is>
-          <t>KR&gt;FENI KM15</t>
+          <t>KR&gt;HUAFEI</t>
         </is>
       </c>
       <c r="B120" s="14" t="inlineStr">
@@ -3989,29 +3867,29 @@
       </c>
       <c r="C120" s="14" t="inlineStr">
         <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="D120" s="14" t="n">
-        <v>49</v>
-      </c>
-      <c r="E120" s="14" t="n">
-        <v>49</v>
-      </c>
-      <c r="F120" s="14" t="n">
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D120" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="E120" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="F120" s="52" t="n">
         <v>0</v>
       </c>
       <c r="G120" s="15" t="n">
-        <v>7929</v>
+        <v>2590</v>
       </c>
       <c r="H120" s="15" t="n">
-        <v>245799</v>
+        <v>80290</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="14" t="inlineStr">
         <is>
-          <t>TF&gt;POS 12</t>
+          <t>BLB&gt;FENI KM0</t>
         </is>
       </c>
       <c r="B121" s="14" t="inlineStr">
@@ -4024,26 +3902,26 @@
           <t>SAP</t>
         </is>
       </c>
-      <c r="D121" s="14" t="n">
-        <v>18</v>
-      </c>
-      <c r="E121" s="14" t="n">
-        <v>18</v>
-      </c>
-      <c r="F121" s="14" t="n">
+      <c r="D121" s="15" t="n">
+        <v>202</v>
+      </c>
+      <c r="E121" s="15" t="n">
+        <v>202</v>
+      </c>
+      <c r="F121" s="52" t="n">
         <v>0</v>
       </c>
       <c r="G121" s="15" t="n">
-        <v>2045</v>
+        <v>45786</v>
       </c>
       <c r="H121" s="15" t="n">
-        <v>63395</v>
+        <v>1419366</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="14" t="inlineStr">
         <is>
-          <t>BLB&gt;POS 14</t>
+          <t>TF&gt;FENI KM15</t>
         </is>
       </c>
       <c r="B122" s="14" t="inlineStr">
@@ -4056,341 +3934,397 @@
           <t>SAP</t>
         </is>
       </c>
-      <c r="D122" s="14" t="n">
-        <v>7</v>
-      </c>
-      <c r="E122" s="14" t="n">
-        <v>7</v>
-      </c>
-      <c r="F122" s="14" t="n">
+      <c r="D122" s="15" t="n">
+        <v>140</v>
+      </c>
+      <c r="E122" s="15" t="n">
+        <v>140</v>
+      </c>
+      <c r="F122" s="52" t="n">
         <v>0</v>
       </c>
       <c r="G122" s="15" t="n">
-        <v>2044</v>
+        <v>14847</v>
       </c>
       <c r="H122" s="15" t="n">
-        <v>63364</v>
+        <v>460257</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="14" t="inlineStr">
         <is>
+          <t>KR&gt;FENI KM15</t>
+        </is>
+      </c>
+      <c r="B123" s="14" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C123" s="14" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D123" s="15" t="n">
+        <v>49</v>
+      </c>
+      <c r="E123" s="15" t="n">
+        <v>49</v>
+      </c>
+      <c r="F123" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G123" s="15" t="n">
+        <v>7929</v>
+      </c>
+      <c r="H123" s="15" t="n">
+        <v>245799</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="14" t="inlineStr">
+        <is>
+          <t>TF&gt;POS 12</t>
+        </is>
+      </c>
+      <c r="B124" s="14" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C124" s="14" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D124" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="E124" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="F124" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G124" s="15" t="n">
+        <v>2045</v>
+      </c>
+      <c r="H124" s="15" t="n">
+        <v>63395</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="14" t="inlineStr">
+        <is>
+          <t>BLB&gt;POS 14</t>
+        </is>
+      </c>
+      <c r="B125" s="14" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C125" s="14" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D125" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="E125" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="F125" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G125" s="15" t="n">
+        <v>2044</v>
+      </c>
+      <c r="H125" s="15" t="n">
+        <v>63364</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="14" t="inlineStr">
+        <is>
           <t>KR&gt;POS 12</t>
         </is>
       </c>
-      <c r="B123" s="14" t="inlineStr">
+      <c r="B126" s="14" t="inlineStr">
         <is>
           <t>SMA</t>
         </is>
       </c>
-      <c r="C123" s="14" t="inlineStr">
+      <c r="C126" s="14" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="D123" s="14" t="n">
+      <c r="D126" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="E123" s="14" t="n">
+      <c r="E126" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="F123" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G123" s="15" t="n">
+      <c r="F126" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G126" s="15" t="n">
         <v>2042</v>
       </c>
-      <c r="H123" s="15" t="n">
+      <c r="H126" s="15" t="n">
         <v>63302</v>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="20" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="28" t="inlineStr">
         <is>
           <t>KR&gt;FENI KM0</t>
         </is>
       </c>
-      <c r="B124" s="20" t="inlineStr">
+      <c r="B127" s="28" t="inlineStr">
         <is>
           <t>reallocated</t>
         </is>
       </c>
-      <c r="C124" s="20" t="inlineStr">
+      <c r="C127" s="28" t="inlineStr">
         <is>
           <t>SAP (stock at FeNi KM0)</t>
         </is>
       </c>
-      <c r="D124" s="20" t="inlineStr">
+      <c r="D127" s="53" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E124" s="28" t="n">
-        <v>30</v>
-      </c>
-      <c r="F124" s="28" t="n">
-        <v>30</v>
-      </c>
-      <c r="G124" s="29" t="n">
-        <v>4067</v>
-      </c>
-      <c r="H124" s="29" t="n">
-        <v>126074</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="20" t="inlineStr">
+      <c r="E127" s="54" t="n">
+        <v>52</v>
+      </c>
+      <c r="F127" s="54" t="n">
+        <v>52</v>
+      </c>
+      <c r="G127" s="54" t="n">
+        <v>7049</v>
+      </c>
+      <c r="H127" s="54" t="n">
+        <v>218533</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="28" t="inlineStr">
         <is>
           <t>TF&gt;FENI KM0</t>
         </is>
       </c>
-      <c r="B125" s="20" t="inlineStr">
+      <c r="B128" s="28" t="inlineStr">
         <is>
           <t>reallocated</t>
         </is>
       </c>
-      <c r="C125" s="20" t="inlineStr">
+      <c r="C128" s="28" t="inlineStr">
         <is>
           <t>SAP (stock at FeNi KM0)</t>
         </is>
       </c>
-      <c r="D125" s="20" t="inlineStr">
+      <c r="D128" s="53" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E125" s="28" t="n">
-        <v>30</v>
-      </c>
-      <c r="F125" s="28" t="n">
-        <v>30</v>
-      </c>
-      <c r="G125" s="29" t="n">
-        <v>3298</v>
-      </c>
-      <c r="H125" s="29" t="n">
-        <v>102229</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="24" t="inlineStr">
+      <c r="E128" s="54" t="n">
+        <v>52</v>
+      </c>
+      <c r="F128" s="54" t="n">
+        <v>52</v>
+      </c>
+      <c r="G128" s="54" t="n">
+        <v>5717</v>
+      </c>
+      <c r="H128" s="54" t="n">
+        <v>177213</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="38" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B126" s="24" t="n"/>
-      <c r="C126" s="24" t="n"/>
-      <c r="D126" s="25" t="n">
+      <c r="D129" s="32" t="n">
         <v>1052</v>
       </c>
-      <c r="E126" s="25" t="n">
-        <v>1053</v>
-      </c>
-      <c r="F126" s="24" t="n"/>
-      <c r="G126" s="24" t="n"/>
-      <c r="H126" s="25" t="n">
-        <v>5040027</v>
-      </c>
-    </row>
-    <row r="127"/>
-    <row r="128">
-      <c r="A128" s="16" t="inlineStr">
+      <c r="E129" s="32" t="n">
+        <v>1052</v>
+      </c>
+      <c r="H129" s="32" t="n">
+        <v>5035551</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="16" t="inlineStr">
         <is>
           <t>OPTION 2 — tonnage by material (December)</t>
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="3" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="3" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="B129" s="3" t="inlineStr">
+      <c r="B132" s="3" t="inlineStr">
         <is>
           <t>BEFORE re-dispatch t/mo</t>
         </is>
       </c>
-      <c r="C129" s="3" t="inlineStr">
+      <c r="C132" s="3" t="inlineStr">
         <is>
           <t>AFTER re-dispatch t/mo</t>
         </is>
       </c>
-      <c r="D129" s="3" t="inlineStr">
+      <c r="D132" s="3" t="inlineStr">
         <is>
           <t>Δ t/mo</t>
         </is>
       </c>
-      <c r="E129" s="3" t="inlineStr">
+      <c r="E132" s="3" t="inlineStr">
         <is>
           <t>Change %</t>
         </is>
       </c>
-      <c r="F129" s="3" t="inlineStr">
-        <is>
-          <t>Dec sales share</t>
-        </is>
-      </c>
-      <c r="G129" s="3" t="inlineStr">
+      <c r="F132" s="3" t="inlineStr">
+        <is>
+          <t>December TARGET t</t>
+        </is>
+      </c>
+      <c r="G132" s="3" t="inlineStr">
         <is>
           <t>Coverage after</t>
         </is>
       </c>
-      <c r="H129" s="31" t="n"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="19" t="inlineStr">
+    </row>
+    <row r="133">
+      <c r="A133" s="19" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="B130" s="15" t="n">
+      <c r="B133" s="15" t="n">
         <v>2315483</v>
       </c>
-      <c r="C130" s="32" t="n">
-        <v>2543786</v>
-      </c>
-      <c r="D130" s="27" t="n">
-        <v>228303</v>
-      </c>
-      <c r="E130" s="39" t="n">
-        <v>0.09859843497015526</v>
-      </c>
-      <c r="F130" s="15" t="n">
+      <c r="C133" s="32" t="n">
+        <v>2711229</v>
+      </c>
+      <c r="D133" s="27" t="n">
+        <v>395746</v>
+      </c>
+      <c r="E133" s="39" t="n">
+        <v>0.1709129369552702</v>
+      </c>
+      <c r="F133" s="15" t="n">
         <v>2311213</v>
       </c>
-      <c r="G130" s="34" t="n">
-        <v>1.100628111731805</v>
-      </c>
-      <c r="H130" s="31" t="n"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="14" t="inlineStr">
+      <c r="G133" s="34" t="n">
+        <v>1.1730762158226</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="14" t="inlineStr">
         <is>
           <t>LIM-TOS</t>
         </is>
       </c>
-      <c r="B131" s="15" t="n">
+      <c r="B134" s="15" t="n">
         <v>1331853</v>
       </c>
-      <c r="C131" s="32" t="n">
+      <c r="C134" s="32" t="n">
         <v>1331853</v>
       </c>
-      <c r="D131" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="E131" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="F131" s="15" t="n">
+      <c r="D134" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F134" s="15" t="n">
         <v>1326082</v>
       </c>
-      <c r="G131" s="34" t="n">
+      <c r="G134" s="34" t="n">
         <v>1.004351917905529</v>
       </c>
-      <c r="H131" s="31" t="n"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="14" t="inlineStr">
+    </row>
+    <row r="135">
+      <c r="A135" s="14" t="inlineStr">
         <is>
           <t>LIM-LD</t>
         </is>
       </c>
-      <c r="B132" s="15" t="n">
-        <v>1397883</v>
-      </c>
-      <c r="C132" s="32" t="n">
-        <v>1164388</v>
-      </c>
-      <c r="D132" s="35" t="n">
-        <v>-233495</v>
-      </c>
-      <c r="E132" s="42" t="n">
-        <v>-0.167034723220756</v>
-      </c>
-      <c r="F132" s="15" t="n">
+      <c r="B135" s="15" t="n">
+        <v>1397954</v>
+      </c>
+      <c r="C135" s="32" t="n">
+        <v>992469</v>
+      </c>
+      <c r="D135" s="35" t="n">
+        <v>-405485</v>
+      </c>
+      <c r="E135" s="42" t="n">
+        <v>-0.2900560390399112</v>
+      </c>
+      <c r="F135" s="15" t="n">
         <v>992213</v>
       </c>
-      <c r="G132" s="34" t="n">
-        <v>1.173526248900186</v>
-      </c>
-      <c r="H132" s="31" t="n"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="43" t="inlineStr">
-        <is>
-          <t>of which reallocated to FeNi KM0 stockpile (KR/TF&gt;FENI KM0)</t>
-        </is>
-      </c>
-      <c r="B133" s="44" t="n"/>
-      <c r="C133" s="27" t="n">
-        <v>228303</v>
-      </c>
-      <c r="D133" s="27" t="n">
-        <v>228303</v>
-      </c>
-      <c r="E133" s="45" t="inlineStr">
-        <is>
-          <t>in SAP row</t>
-        </is>
-      </c>
-      <c r="F133" s="30" t="n"/>
-      <c r="G133" s="37" t="n"/>
-      <c r="H133" s="31" t="n"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="38" t="inlineStr">
+      <c r="G135" s="34" t="n">
+        <v>1.000258009116994</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="43" t="inlineStr">
+        <is>
+          <t>of which SAP stocked at FeNi KM0 (KR 52 DT + TF 52 DT reallocated)</t>
+        </is>
+      </c>
+      <c r="B136" s="56" t="n"/>
+      <c r="C136" s="27" t="n">
+        <v>395746</v>
+      </c>
+      <c r="D136" s="27" t="n">
+        <v>395746</v>
+      </c>
+      <c r="E136" s="45" t="inlineStr">
+        <is>
+          <t>inside the SAP row</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="38" t="inlineStr">
         <is>
           <t>TOTAL moved</t>
         </is>
       </c>
-      <c r="B134" s="32" t="n">
-        <v>5045219</v>
-      </c>
-      <c r="C134" s="32" t="n">
-        <v>5040027</v>
-      </c>
-      <c r="D134" s="35" t="n">
-        <v>-5192</v>
-      </c>
-      <c r="E134" s="42" t="n">
-        <v>-0.001029093087931366</v>
-      </c>
-      <c r="F134" s="31" t="n"/>
-      <c r="G134" s="31" t="n"/>
-      <c r="H134" s="31" t="n"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="31" t="n"/>
-      <c r="B135" s="31" t="n"/>
-      <c r="C135" s="31" t="n"/>
-      <c r="D135" s="31" t="n"/>
-      <c r="E135" s="31" t="n"/>
-      <c r="F135" s="31" t="n"/>
-      <c r="G135" s="31" t="n"/>
-      <c r="H135" s="31" t="n"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="31" t="n"/>
-      <c r="B136" s="31" t="n"/>
-      <c r="C136" s="31" t="n"/>
-      <c r="D136" s="31" t="n"/>
-      <c r="E136" s="31" t="n"/>
-      <c r="F136" s="31" t="n"/>
-      <c r="G136" s="31" t="n"/>
-      <c r="H136" s="31" t="n"/>
+      <c r="B137" s="32" t="n">
+        <v>5045290</v>
+      </c>
+      <c r="C137" s="32" t="n">
+        <v>5035551</v>
+      </c>
+      <c r="D137" s="35" t="n">
+        <v>-9739</v>
+      </c>
+      <c r="E137" s="42" t="n">
+        <v>-0.001930315204874249</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="A9:H9"/>
+  <mergeCells count="4">
+    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="A101:B101"/>
+    <mergeCell ref="A136:B136"/>
     <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A107:H107"/>
-    <mergeCell ref="A99:B99"/>
-    <mergeCell ref="A133:B133"/>
-    <mergeCell ref="A41:H41"/>
-    <mergeCell ref="A75:H75"/>
-    <mergeCell ref="A67:B67"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4415,6 +4349,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="16" t="inlineStr">
         <is>
@@ -4429,6 +4364,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="16" t="inlineStr">
         <is>
@@ -4443,6 +4379,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="16" t="inlineStr">
         <is>
@@ -4457,6 +4394,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="16" t="inlineStr">
         <is>
@@ -4467,10 +4405,11 @@
     <row r="13" ht="42" customHeight="1">
       <c r="A13" s="17" t="inlineStr">
         <is>
-          <t>Parking 26-59 DT lands December at exactly 100.0%. Simple, but those trucks produce nothing and the plants build no buffer.</t>
-        </is>
-      </c>
-    </row>
+          <t>Parking 26-59 DT lands the total month at exactly 100.0%. Simple, but those trucks produce nothing and the plants build no buffer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="16" t="inlineStr">
         <is>
@@ -4481,10 +4420,11 @@
     <row r="16" ht="42" customHeight="1">
       <c r="A16" s="17" t="inlineStr">
         <is>
-          <t>The same trucks moved to KR&gt;FENI KM0 + TF&gt;FENI KM0 build 99-266 kt of December stock at the plants while the sales lines still land at exactly 100%. The long hauls absorb many trucks per tonne (1.6-2.6 trips/DT/day) - exactly what surplus capacity is for. Cost: more traffic on the KR corridor (v/c already ~1 at KM15-coast); check the Road crowding sheet before committing.</t>
-        </is>
-      </c>
-    </row>
+          <t>Sized to the real goal — LIM-LD at exactly 100% — the cut is 56-104 DT, and re-dispatching them to KR&gt;FENI KM0 + TF&gt;FENI KM0 builds 213-396 kt of kilnable SAP stock at the plant in December while every sales line still clears (SAP rises to 109-117%). Requires KM0 to accept stock.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="16" t="inlineStr">
         <is>

--- a/reports/scenario_comparison_dec_options.xlsx
+++ b/reports/scenario_comparison_dec_options.xlsx
@@ -2015,300 +2015,218 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G89"/>
+  <dimension ref="A1:H137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="38" t="inlineStr">
         <is>
-          <t>December — the full 1,281-DT pool works (frozen 2026-08-27)</t>
+          <t>December runs over target in every scenario — two ways to spend the surplus</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="39" t="inlineStr">
         <is>
-          <t>Owner's rule: SAP 100%, LIM-TOS 100%, and EVERY remaining truck hauls LIM-LD — the target is a goal, not a ceiling. The previously idle trucks (91 SMA in 3.0.x, 74 RIM + 155 SMA in 3.1.x) now ride the TF&gt;HUAFEI LD rows. This is the frozen plan, not an option.</t>
+          <t>Option 1: park the surplus DT (total month lands at 100.0%). Option 2: cut LIM-LD to exactly its December line and re-dispatch every freed DT to KR&gt;FENI KM0 + TF&gt;FENI KM0 — the hauled material is kilnable SAP feed stocked at the plant.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="40" t="inlineStr">
         <is>
-          <t>Scenario 3.0.1 — December (frozen, 1,281 DT)</t>
+          <t>Scenario 3.0.1 — December</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="41" t="inlineStr">
+      <c r="A5" s="41" t="inlineStr"/>
+      <c r="B5" s="41" t="inlineStr">
+        <is>
+          <t>Target t</t>
+        </is>
+      </c>
+      <c r="C5" s="41" t="inlineStr">
+        <is>
+          <t>Predicted t</t>
+        </is>
+      </c>
+      <c r="D5" s="41" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="E5" s="41" t="inlineStr">
+        <is>
+          <t>Fleet DT</t>
+        </is>
+      </c>
+      <c r="F5" s="41" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="42" t="inlineStr">
+        <is>
+          <t>As frozen</t>
+        </is>
+      </c>
+      <c r="B6" s="43" t="n">
+        <v>5131386</v>
+      </c>
+      <c r="C6" s="43" t="n">
+        <v>5216721</v>
+      </c>
+      <c r="D6" s="44" t="n">
+        <v>1.016630009903757</v>
+      </c>
+      <c r="E6" s="43" t="n">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="42" t="inlineStr">
+        <is>
+          <t>OPTION 1 · park 26 DT (total month → 100.0%)</t>
+        </is>
+      </c>
+      <c r="B7" s="43" t="n">
+        <v>5131386</v>
+      </c>
+      <c r="C7" s="43" t="n">
+        <v>5132370</v>
+      </c>
+      <c r="D7" s="45" t="n">
+        <v>1.00019176105637</v>
+      </c>
+      <c r="E7" s="43" t="n">
+        <v>1164</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="42" t="inlineStr">
+        <is>
+          <t>OPTION 2 · re-dispatch 56 DT (LIM-LD → 100.0%)</t>
+        </is>
+      </c>
+      <c r="B8" s="43" t="n">
+        <v>5131386</v>
+      </c>
+      <c r="C8" s="43" t="n">
+        <v>5248586</v>
+      </c>
+      <c r="D8" s="46" t="n">
+        <v>1.0228398331367</v>
+      </c>
+      <c r="E8" s="43" t="n">
+        <v>1190</v>
+      </c>
+      <c r="F8" s="48" t="inlineStr">
+        <is>
+          <t>+ 213,461 t SAP stocked at FeNi KM0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="49" t="inlineStr">
+        <is>
+          <t>Option 2 cut (sized so LIM-LD lands exactly on its line): TF&gt;HUAFEI (RIM, LD): −56 DT @ 104.7 t/day/DT</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="50" t="inlineStr">
+        <is>
+          <t>OPTION 2 — full December plan (re-dispatched)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="41" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="B5" s="41" t="inlineStr">
+      <c r="B12" s="41" t="inlineStr">
         <is>
           <t>Contractor</t>
         </is>
       </c>
-      <c r="C5" s="41" t="inlineStr">
+      <c r="C12" s="41" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="D5" s="41" t="inlineStr">
-        <is>
-          <t>DT</t>
-        </is>
-      </c>
-      <c r="E5" s="41" t="inlineStr">
+      <c r="D12" s="41" t="inlineStr">
+        <is>
+          <t>DT before</t>
+        </is>
+      </c>
+      <c r="E12" s="41" t="inlineStr">
+        <is>
+          <t>DT after</t>
+        </is>
+      </c>
+      <c r="F12" s="41" t="inlineStr">
+        <is>
+          <t>Δ DT</t>
+        </is>
+      </c>
+      <c r="G12" s="41" t="inlineStr">
         <is>
           <t>t/day</t>
         </is>
       </c>
-      <c r="F5" s="41" t="inlineStr">
+      <c r="H12" s="41" t="inlineStr">
         <is>
           <t>t/month</t>
         </is>
       </c>
-      <c r="G5" s="41" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="67" t="inlineStr">
-        <is>
-          <t>TF&gt;HUAFEI</t>
-        </is>
-      </c>
-      <c r="B6" s="67" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C6" s="67" t="inlineStr">
-        <is>
-          <t>LIM-LD</t>
-        </is>
-      </c>
-      <c r="D6" s="68" t="n">
-        <v>436</v>
-      </c>
-      <c r="E6" s="43" t="n">
-        <v>45474</v>
-      </c>
-      <c r="F6" s="43" t="n">
-        <v>1409694</v>
-      </c>
-      <c r="G6" s="69" t="inlineStr">
-        <is>
-          <t>includes activated idle DT</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="67" t="inlineStr">
-        <is>
-          <t>TF&gt;HUAFEI</t>
-        </is>
-      </c>
-      <c r="B7" s="67" t="inlineStr">
-        <is>
-          <t>SMA</t>
-        </is>
-      </c>
-      <c r="C7" s="67" t="inlineStr">
-        <is>
-          <t>LIM-LD</t>
-        </is>
-      </c>
-      <c r="D7" s="68" t="n">
-        <v>240</v>
-      </c>
-      <c r="E7" s="43" t="n">
-        <v>24987</v>
-      </c>
-      <c r="F7" s="43" t="n">
-        <v>774597</v>
-      </c>
-      <c r="G7" s="69" t="inlineStr">
-        <is>
-          <t>includes activated idle DT</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="51" t="inlineStr">
-        <is>
-          <t>BLB&gt;HUAFEI</t>
-        </is>
-      </c>
-      <c r="B8" s="51" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C8" s="51" t="inlineStr">
-        <is>
-          <t>LIM-TOS</t>
-        </is>
-      </c>
-      <c r="D8" s="43" t="n">
-        <v>95</v>
-      </c>
-      <c r="E8" s="43" t="n">
-        <v>23244</v>
-      </c>
-      <c r="F8" s="43" t="n">
-        <v>720564</v>
-      </c>
-      <c r="G8" s="66" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="51" t="inlineStr">
-        <is>
-          <t>TF&gt;HUAFEI</t>
-        </is>
-      </c>
-      <c r="B9" s="51" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C9" s="51" t="inlineStr">
-        <is>
-          <t>LIM-TOS</t>
-        </is>
-      </c>
-      <c r="D9" s="43" t="n">
-        <v>62</v>
-      </c>
-      <c r="E9" s="43" t="n">
-        <v>6467</v>
-      </c>
-      <c r="F9" s="43" t="n">
-        <v>200477</v>
-      </c>
-      <c r="G9" s="66" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="51" t="inlineStr">
-        <is>
-          <t>KR&gt;HUAFEI</t>
-        </is>
-      </c>
-      <c r="B10" s="51" t="inlineStr">
-        <is>
-          <t>SMA</t>
-        </is>
-      </c>
-      <c r="C10" s="51" t="inlineStr">
-        <is>
-          <t>LIM-TOS</t>
-        </is>
-      </c>
-      <c r="D10" s="43" t="n">
-        <v>19</v>
-      </c>
-      <c r="E10" s="43" t="n">
-        <v>2540</v>
-      </c>
-      <c r="F10" s="43" t="n">
-        <v>78740</v>
-      </c>
-      <c r="G10" s="66" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="51" t="inlineStr">
-        <is>
-          <t>BLB&gt;FENI KM0</t>
-        </is>
-      </c>
-      <c r="B11" s="51" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C11" s="51" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="D11" s="43" t="n">
-        <v>202</v>
-      </c>
-      <c r="E11" s="43" t="n">
-        <v>45774</v>
-      </c>
-      <c r="F11" s="43" t="n">
-        <v>1418994</v>
-      </c>
-      <c r="G11" s="66" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="51" t="inlineStr">
-        <is>
-          <t>TF&gt;FENI KM15</t>
-        </is>
-      </c>
-      <c r="B12" s="51" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C12" s="51" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="D12" s="43" t="n">
-        <v>141</v>
-      </c>
-      <c r="E12" s="43" t="n">
-        <v>14776</v>
-      </c>
-      <c r="F12" s="43" t="n">
-        <v>458056</v>
-      </c>
-      <c r="G12" s="66" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="51" t="inlineStr">
         <is>
-          <t>KR&gt;FENI KM15</t>
+          <t>TF&gt;HUAFEI</t>
         </is>
       </c>
       <c r="B13" s="51" t="inlineStr">
         <is>
-          <t>SMA</t>
+          <t>RIM</t>
         </is>
       </c>
       <c r="C13" s="51" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>LIM-LD</t>
         </is>
       </c>
       <c r="D13" s="43" t="n">
-        <v>50</v>
-      </c>
-      <c r="E13" s="43" t="n">
-        <v>7885</v>
-      </c>
-      <c r="F13" s="43" t="n">
-        <v>244435</v>
-      </c>
-      <c r="G13" s="66" t="n"/>
+        <v>437</v>
+      </c>
+      <c r="E13" s="47" t="n">
+        <v>381</v>
+      </c>
+      <c r="F13" s="52" t="n">
+        <v>-56</v>
+      </c>
+      <c r="G13" s="43" t="n">
+        <v>39874</v>
+      </c>
+      <c r="H13" s="43" t="n">
+        <v>1236106</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="51" t="inlineStr">
         <is>
-          <t>KR&gt;POS 12</t>
+          <t>TF&gt;HUAFEI</t>
         </is>
       </c>
       <c r="B14" s="51" t="inlineStr">
@@ -2318,24 +2236,29 @@
       </c>
       <c r="C14" s="51" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>LIM-LD</t>
         </is>
       </c>
       <c r="D14" s="43" t="n">
-        <v>11</v>
+        <v>150</v>
       </c>
       <c r="E14" s="43" t="n">
-        <v>2187</v>
-      </c>
-      <c r="F14" s="43" t="n">
-        <v>67797</v>
-      </c>
-      <c r="G14" s="66" t="n"/>
+        <v>150</v>
+      </c>
+      <c r="F14" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="43" t="n">
+        <v>15675</v>
+      </c>
+      <c r="H14" s="43" t="n">
+        <v>485925</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="51" t="inlineStr">
         <is>
-          <t>BLB&gt;POS 14</t>
+          <t>BLB&gt;HUAFEI</t>
         </is>
       </c>
       <c r="B15" s="51" t="inlineStr">
@@ -2345,24 +2268,29 @@
       </c>
       <c r="C15" s="51" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>LIM-TOS</t>
         </is>
       </c>
       <c r="D15" s="43" t="n">
-        <v>7</v>
+        <v>95</v>
       </c>
       <c r="E15" s="43" t="n">
-        <v>2043</v>
-      </c>
-      <c r="F15" s="43" t="n">
-        <v>63333</v>
-      </c>
-      <c r="G15" s="66" t="n"/>
+        <v>95</v>
+      </c>
+      <c r="F15" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="43" t="n">
+        <v>23250</v>
+      </c>
+      <c r="H15" s="43" t="n">
+        <v>720750</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="51" t="inlineStr">
         <is>
-          <t>TF&gt;POS 12</t>
+          <t>TF&gt;HUAFEI</t>
         </is>
       </c>
       <c r="B16" s="51" t="inlineStr">
@@ -2372,712 +2300,840 @@
       </c>
       <c r="C16" s="51" t="inlineStr">
         <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D16" s="43" t="n">
+        <v>62</v>
+      </c>
+      <c r="E16" s="43" t="n">
+        <v>62</v>
+      </c>
+      <c r="F16" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="43" t="n">
+        <v>6489</v>
+      </c>
+      <c r="H16" s="43" t="n">
+        <v>201159</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="51" t="inlineStr">
+        <is>
+          <t>KR&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B17" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C17" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D17" s="43" t="n">
+        <v>19</v>
+      </c>
+      <c r="E17" s="43" t="n">
+        <v>19</v>
+      </c>
+      <c r="F17" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="43" t="n">
+        <v>2563</v>
+      </c>
+      <c r="H17" s="43" t="n">
+        <v>79453</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="51" t="inlineStr">
+        <is>
+          <t>BLB&gt;FENI KM0</t>
+        </is>
+      </c>
+      <c r="B18" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C18" s="51" t="inlineStr">
+        <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="D16" s="43" t="n">
-        <v>18</v>
-      </c>
-      <c r="E16" s="43" t="n">
-        <v>2036</v>
-      </c>
-      <c r="F16" s="43" t="n">
-        <v>63116</v>
-      </c>
-      <c r="G16" s="66" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="60" t="inlineStr">
-        <is>
-          <t>TOTAL (full matrix pool)</t>
-        </is>
-      </c>
-      <c r="D17" s="47" t="n">
-        <v>1281</v>
-      </c>
-      <c r="F17" s="47" t="n">
-        <v>5499803</v>
+      <c r="D18" s="43" t="n">
+        <v>202</v>
+      </c>
+      <c r="E18" s="43" t="n">
+        <v>202</v>
+      </c>
+      <c r="F18" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="43" t="n">
+        <v>45786</v>
+      </c>
+      <c r="H18" s="43" t="n">
+        <v>1419366</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="41" t="inlineStr">
-        <is>
-          <t>Material</t>
-        </is>
-      </c>
-      <c r="B19" s="41" t="inlineStr">
-        <is>
-          <t>t/month (frozen)</t>
-        </is>
-      </c>
-      <c r="C19" s="41" t="inlineStr">
-        <is>
-          <t>December TARGET t</t>
-        </is>
-      </c>
-      <c r="D19" s="41" t="inlineStr">
-        <is>
-          <t>Coverage</t>
-        </is>
-      </c>
-      <c r="E19" s="41" t="inlineStr"/>
-      <c r="F19" s="41" t="inlineStr"/>
-      <c r="G19" s="41" t="inlineStr"/>
+      <c r="A19" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;FENI KM15</t>
+        </is>
+      </c>
+      <c r="B19" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C19" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D19" s="43" t="n">
+        <v>140</v>
+      </c>
+      <c r="E19" s="43" t="n">
+        <v>140</v>
+      </c>
+      <c r="F19" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="43" t="n">
+        <v>14736</v>
+      </c>
+      <c r="H19" s="43" t="n">
+        <v>456816</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="51" t="inlineStr">
         <is>
+          <t>KR&gt;FENI KM15</t>
+        </is>
+      </c>
+      <c r="B20" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C20" s="51" t="inlineStr">
+        <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="B20" s="47" t="n">
-        <v>2315731</v>
-      </c>
-      <c r="C20" s="43" t="n">
-        <v>2311213</v>
-      </c>
-      <c r="D20" s="45" t="n">
-        <v>1.00195481766501</v>
+      <c r="D20" s="43" t="n">
+        <v>50</v>
+      </c>
+      <c r="E20" s="43" t="n">
+        <v>50</v>
+      </c>
+      <c r="F20" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="43" t="n">
+        <v>7958</v>
+      </c>
+      <c r="H20" s="43" t="n">
+        <v>246698</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="51" t="inlineStr">
         <is>
-          <t>LIM-TOS</t>
-        </is>
-      </c>
-      <c r="B21" s="47" t="n">
-        <v>999781</v>
-      </c>
-      <c r="C21" s="43" t="n">
-        <v>996084</v>
-      </c>
-      <c r="D21" s="45" t="n">
-        <v>1.003711534368587</v>
+          <t>BLB&gt;POS 14</t>
+        </is>
+      </c>
+      <c r="B21" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C21" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D21" s="43" t="n">
+        <v>7</v>
+      </c>
+      <c r="E21" s="43" t="n">
+        <v>7</v>
+      </c>
+      <c r="F21" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="43" t="n">
+        <v>2044</v>
+      </c>
+      <c r="H21" s="43" t="n">
+        <v>63364</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="51" t="inlineStr">
         <is>
-          <t>LIM-LD</t>
-        </is>
-      </c>
-      <c r="B22" s="47" t="n">
-        <v>2184291</v>
-      </c>
-      <c r="C22" s="43" t="n">
-        <v>1719964</v>
-      </c>
-      <c r="D22" s="45" t="n">
-        <v>1.269963208532272</v>
-      </c>
-      <c r="E22" s="70" t="inlineStr">
-        <is>
-          <t>above target by design — surplus fleet hauls LD</t>
-        </is>
+          <t>TF&gt;POS 12</t>
+        </is>
+      </c>
+      <c r="B22" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C22" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D22" s="43" t="n">
+        <v>18</v>
+      </c>
+      <c r="E22" s="43" t="n">
+        <v>18</v>
+      </c>
+      <c r="F22" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="43" t="n">
+        <v>2039</v>
+      </c>
+      <c r="H22" s="43" t="n">
+        <v>63209</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="51" t="inlineStr">
+        <is>
+          <t>KR&gt;POS 12</t>
+        </is>
+      </c>
+      <c r="B23" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C23" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D23" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="F23" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="43" t="n">
+        <v>2009</v>
+      </c>
+      <c r="H23" s="43" t="n">
+        <v>62279</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="54" t="inlineStr">
+        <is>
+          <t>KR&gt;FENI KM0</t>
+        </is>
+      </c>
+      <c r="B24" s="54" t="inlineStr">
+        <is>
+          <t>reallocated</t>
+        </is>
+      </c>
+      <c r="C24" s="54" t="inlineStr">
+        <is>
+          <t>SAP (stock at FeNi KM0)</t>
+        </is>
+      </c>
+      <c r="D24" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E24" s="56" t="n">
+        <v>28</v>
+      </c>
+      <c r="F24" s="56" t="n">
+        <v>28</v>
+      </c>
+      <c r="G24" s="56" t="n">
+        <v>3802</v>
+      </c>
+      <c r="H24" s="56" t="n">
+        <v>117848</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="40" t="inlineStr">
-        <is>
-          <t>Scenario 3.0.2 — December (frozen, 1,281 DT)</t>
-        </is>
+      <c r="A25" s="54" t="inlineStr">
+        <is>
+          <t>TF&gt;FENI KM0</t>
+        </is>
+      </c>
+      <c r="B25" s="54" t="inlineStr">
+        <is>
+          <t>reallocated</t>
+        </is>
+      </c>
+      <c r="C25" s="54" t="inlineStr">
+        <is>
+          <t>SAP (stock at FeNi KM0)</t>
+        </is>
+      </c>
+      <c r="D25" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E25" s="56" t="n">
+        <v>28</v>
+      </c>
+      <c r="F25" s="56" t="n">
+        <v>28</v>
+      </c>
+      <c r="G25" s="56" t="n">
+        <v>3084</v>
+      </c>
+      <c r="H25" s="56" t="n">
+        <v>95614</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="41" t="inlineStr">
-        <is>
-          <t>Route</t>
-        </is>
-      </c>
-      <c r="B26" s="41" t="inlineStr">
-        <is>
-          <t>Contractor</t>
-        </is>
-      </c>
-      <c r="C26" s="41" t="inlineStr">
+      <c r="A26" s="60" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D26" s="47" t="n">
+        <v>1190</v>
+      </c>
+      <c r="E26" s="47" t="n">
+        <v>1190</v>
+      </c>
+      <c r="H26" s="47" t="n">
+        <v>5248587</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="50" t="inlineStr">
+        <is>
+          <t>OPTION 2 — tonnage by material (December)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="41" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="D26" s="41" t="inlineStr">
-        <is>
-          <t>DT</t>
-        </is>
-      </c>
-      <c r="E26" s="41" t="inlineStr">
-        <is>
-          <t>t/day</t>
-        </is>
-      </c>
-      <c r="F26" s="41" t="inlineStr">
-        <is>
-          <t>t/month</t>
-        </is>
-      </c>
-      <c r="G26" s="41" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="67" t="inlineStr">
-        <is>
-          <t>TF&gt;HUAFEI</t>
-        </is>
-      </c>
-      <c r="B27" s="67" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C27" s="67" t="inlineStr">
-        <is>
-          <t>LIM-LD</t>
-        </is>
-      </c>
-      <c r="D27" s="68" t="n">
-        <v>285</v>
-      </c>
-      <c r="E27" s="43" t="n">
-        <v>29654</v>
-      </c>
-      <c r="F27" s="43" t="n">
-        <v>919274</v>
-      </c>
-      <c r="G27" s="69" t="inlineStr">
-        <is>
-          <t>includes activated idle DT</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="51" t="inlineStr">
-        <is>
-          <t>TF&gt;POS 6</t>
-        </is>
-      </c>
-      <c r="B28" s="51" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C28" s="51" t="inlineStr">
-        <is>
-          <t>LIM-LD</t>
-        </is>
-      </c>
-      <c r="D28" s="43" t="n">
-        <v>150</v>
-      </c>
-      <c r="E28" s="43" t="n">
-        <v>18989</v>
-      </c>
-      <c r="F28" s="43" t="n">
-        <v>588659</v>
-      </c>
-      <c r="G28" s="66" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="51" t="inlineStr">
-        <is>
-          <t>TF&gt;POS 6</t>
-        </is>
-      </c>
-      <c r="B29" s="51" t="inlineStr">
-        <is>
-          <t>SMA</t>
-        </is>
-      </c>
-      <c r="C29" s="51" t="inlineStr">
-        <is>
-          <t>LIM-LD</t>
-        </is>
-      </c>
-      <c r="D29" s="43" t="n">
-        <v>120</v>
-      </c>
-      <c r="E29" s="43" t="n">
-        <v>13876</v>
-      </c>
-      <c r="F29" s="43" t="n">
-        <v>430156</v>
-      </c>
-      <c r="G29" s="66" t="n"/>
+      <c r="B29" s="41" t="inlineStr">
+        <is>
+          <t>BEFORE re-dispatch t/mo</t>
+        </is>
+      </c>
+      <c r="C29" s="41" t="inlineStr">
+        <is>
+          <t>AFTER re-dispatch t/mo</t>
+        </is>
+      </c>
+      <c r="D29" s="41" t="inlineStr">
+        <is>
+          <t>Δ t/mo</t>
+        </is>
+      </c>
+      <c r="E29" s="41" t="inlineStr">
+        <is>
+          <t>Change %</t>
+        </is>
+      </c>
+      <c r="F29" s="41" t="inlineStr">
+        <is>
+          <t>December TARGET t</t>
+        </is>
+      </c>
+      <c r="G29" s="41" t="inlineStr">
+        <is>
+          <t>Coverage after</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="67" t="inlineStr">
-        <is>
-          <t>TF&gt;HUAFEI</t>
-        </is>
-      </c>
-      <c r="B30" s="67" t="inlineStr">
-        <is>
-          <t>SMA</t>
-        </is>
-      </c>
-      <c r="C30" s="67" t="inlineStr">
-        <is>
-          <t>LIM-LD</t>
-        </is>
-      </c>
-      <c r="D30" s="68" t="n">
-        <v>120</v>
-      </c>
-      <c r="E30" s="43" t="n">
-        <v>12461</v>
+      <c r="A30" s="42" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B30" s="43" t="n">
+        <v>2311732</v>
+      </c>
+      <c r="C30" s="47" t="n">
+        <v>2525193</v>
+      </c>
+      <c r="D30" s="61" t="n">
+        <v>213461</v>
+      </c>
+      <c r="E30" s="62" t="n">
+        <v>0.09233812569969184</v>
       </c>
       <c r="F30" s="43" t="n">
-        <v>386291</v>
-      </c>
-      <c r="G30" s="69" t="inlineStr">
-        <is>
-          <t>includes activated idle DT</t>
-        </is>
+        <v>2311213</v>
+      </c>
+      <c r="G30" s="45" t="n">
+        <v>1.092583418317567</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="51" t="inlineStr">
         <is>
-          <t>BLB&gt;HUAFEI</t>
-        </is>
-      </c>
-      <c r="B31" s="51" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C31" s="51" t="inlineStr">
-        <is>
           <t>LIM-TOS</t>
         </is>
       </c>
-      <c r="D31" s="43" t="n">
-        <v>95</v>
-      </c>
-      <c r="E31" s="43" t="n">
-        <v>23244</v>
+      <c r="B31" s="43" t="n">
+        <v>1001362</v>
+      </c>
+      <c r="C31" s="47" t="n">
+        <v>1001362</v>
+      </c>
+      <c r="D31" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="63" t="n">
+        <v>0</v>
       </c>
       <c r="F31" s="43" t="n">
-        <v>720564</v>
-      </c>
-      <c r="G31" s="66" t="n"/>
+        <v>996084</v>
+      </c>
+      <c r="G31" s="45" t="n">
+        <v>1.005298749904626</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="51" t="inlineStr">
         <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="B32" s="43" t="n">
+        <v>1903716</v>
+      </c>
+      <c r="C32" s="47" t="n">
+        <v>1722031</v>
+      </c>
+      <c r="D32" s="52" t="n">
+        <v>-181685</v>
+      </c>
+      <c r="E32" s="64" t="n">
+        <v>-0.09543702947288356</v>
+      </c>
+      <c r="F32" s="43" t="n">
+        <v>1719964</v>
+      </c>
+      <c r="G32" s="45" t="n">
+        <v>1.001201769339358</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="65" t="inlineStr">
+        <is>
+          <t>of which SAP stocked at FeNi KM0 (KR 28 DT + TF 28 DT reallocated)</t>
+        </is>
+      </c>
+      <c r="B33" s="66" t="n"/>
+      <c r="C33" s="61" t="n">
+        <v>213461</v>
+      </c>
+      <c r="D33" s="61" t="n">
+        <v>213461</v>
+      </c>
+      <c r="E33" s="70" t="inlineStr">
+        <is>
+          <t>inside the SAP row</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="60" t="inlineStr">
+        <is>
+          <t>TOTAL moved</t>
+        </is>
+      </c>
+      <c r="B34" s="47" t="n">
+        <v>5216810</v>
+      </c>
+      <c r="C34" s="47" t="n">
+        <v>5248586</v>
+      </c>
+      <c r="D34" s="61" t="n">
+        <v>31776</v>
+      </c>
+      <c r="E34" s="62" t="n">
+        <v>0.006091078647679329</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="40" t="inlineStr">
+        <is>
+          <t>Scenario 3.0.2 — December</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="41" t="inlineStr"/>
+      <c r="B38" s="41" t="inlineStr">
+        <is>
+          <t>Target t</t>
+        </is>
+      </c>
+      <c r="C38" s="41" t="inlineStr">
+        <is>
+          <t>Predicted t</t>
+        </is>
+      </c>
+      <c r="D38" s="41" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="E38" s="41" t="inlineStr">
+        <is>
+          <t>Fleet DT</t>
+        </is>
+      </c>
+      <c r="F38" s="41" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="42" t="inlineStr">
+        <is>
+          <t>As frozen</t>
+        </is>
+      </c>
+      <c r="B39" s="43" t="n">
+        <v>5131386</v>
+      </c>
+      <c r="C39" s="43" t="n">
+        <v>5343787</v>
+      </c>
+      <c r="D39" s="44" t="n">
+        <v>1.041392520461333</v>
+      </c>
+      <c r="E39" s="43" t="n">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="42" t="inlineStr">
+        <is>
+          <t>OPTION 1 · park 54 DT (total month → 100.0%)</t>
+        </is>
+      </c>
+      <c r="B40" s="43" t="n">
+        <v>5131386</v>
+      </c>
+      <c r="C40" s="43" t="n">
+        <v>5131167</v>
+      </c>
+      <c r="D40" s="45" t="n">
+        <v>0.9999573214722104</v>
+      </c>
+      <c r="E40" s="43" t="n">
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="42" t="inlineStr">
+        <is>
+          <t>OPTION 2 · re-dispatch 79 DT (LIM-LD → 100.0%)</t>
+        </is>
+      </c>
+      <c r="B41" s="43" t="n">
+        <v>5131386</v>
+      </c>
+      <c r="C41" s="43" t="n">
+        <v>5333821</v>
+      </c>
+      <c r="D41" s="46" t="n">
+        <v>1.039450355128225</v>
+      </c>
+      <c r="E41" s="43" t="n">
+        <v>1190</v>
+      </c>
+      <c r="F41" s="48" t="inlineStr">
+        <is>
+          <t>+ 301,080 t SAP stocked at FeNi KM0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="49" t="inlineStr">
+        <is>
+          <t>Option 2 cut (sized so LIM-LD lands exactly on its line): TF&gt;POS 6 (RIM, LD): −79 DT @ 127.0 t/day/DT</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="50" t="inlineStr">
+        <is>
+          <t>OPTION 2 — full December plan (re-dispatched)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="41" t="inlineStr">
+        <is>
+          <t>Route</t>
+        </is>
+      </c>
+      <c r="B45" s="41" t="inlineStr">
+        <is>
+          <t>Contractor</t>
+        </is>
+      </c>
+      <c r="C45" s="41" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="D45" s="41" t="inlineStr">
+        <is>
+          <t>DT before</t>
+        </is>
+      </c>
+      <c r="E45" s="41" t="inlineStr">
+        <is>
+          <t>DT after</t>
+        </is>
+      </c>
+      <c r="F45" s="41" t="inlineStr">
+        <is>
+          <t>Δ DT</t>
+        </is>
+      </c>
+      <c r="G45" s="41" t="inlineStr">
+        <is>
+          <t>t/day</t>
+        </is>
+      </c>
+      <c r="H45" s="41" t="inlineStr">
+        <is>
+          <t>t/month</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="51" t="inlineStr">
+        <is>
           <t>TF&gt;HUAFEI</t>
         </is>
       </c>
-      <c r="B32" s="51" t="inlineStr">
+      <c r="B46" s="51" t="inlineStr">
         <is>
           <t>RIM</t>
         </is>
       </c>
-      <c r="C32" s="51" t="inlineStr">
+      <c r="C46" s="51" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D46" s="43" t="n">
+        <v>288</v>
+      </c>
+      <c r="E46" s="43" t="n">
+        <v>288</v>
+      </c>
+      <c r="F46" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="43" t="n">
+        <v>30085</v>
+      </c>
+      <c r="H46" s="43" t="n">
+        <v>932635</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;POS 6</t>
+        </is>
+      </c>
+      <c r="B47" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C47" s="51" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D47" s="43" t="n">
+        <v>149</v>
+      </c>
+      <c r="E47" s="47" t="n">
+        <v>70</v>
+      </c>
+      <c r="F47" s="52" t="n">
+        <v>-79</v>
+      </c>
+      <c r="G47" s="43" t="n">
+        <v>8890</v>
+      </c>
+      <c r="H47" s="43" t="n">
+        <v>275605</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;POS 6</t>
+        </is>
+      </c>
+      <c r="B48" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C48" s="51" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D48" s="43" t="n">
+        <v>75</v>
+      </c>
+      <c r="E48" s="43" t="n">
+        <v>75</v>
+      </c>
+      <c r="F48" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="43" t="n">
+        <v>8701</v>
+      </c>
+      <c r="H48" s="43" t="n">
+        <v>269731</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B49" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C49" s="51" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D49" s="43" t="n">
+        <v>75</v>
+      </c>
+      <c r="E49" s="43" t="n">
+        <v>75</v>
+      </c>
+      <c r="F49" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="43" t="n">
+        <v>7822</v>
+      </c>
+      <c r="H49" s="43" t="n">
+        <v>242482</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="51" t="inlineStr">
+        <is>
+          <t>BLB&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B50" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C50" s="51" t="inlineStr">
         <is>
           <t>LIM-TOS</t>
         </is>
       </c>
-      <c r="D32" s="43" t="n">
-        <v>63</v>
-      </c>
-      <c r="E32" s="43" t="n">
-        <v>6555</v>
-      </c>
-      <c r="F32" s="43" t="n">
-        <v>203205</v>
-      </c>
-      <c r="G32" s="66" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="51" t="inlineStr">
-        <is>
-          <t>KR&gt;HUAFEI</t>
-        </is>
-      </c>
-      <c r="B33" s="51" t="inlineStr">
-        <is>
-          <t>SMA</t>
-        </is>
-      </c>
-      <c r="C33" s="51" t="inlineStr">
+      <c r="D50" s="43" t="n">
+        <v>95</v>
+      </c>
+      <c r="E50" s="43" t="n">
+        <v>95</v>
+      </c>
+      <c r="F50" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="43" t="n">
+        <v>23250</v>
+      </c>
+      <c r="H50" s="43" t="n">
+        <v>720750</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B51" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C51" s="51" t="inlineStr">
         <is>
           <t>LIM-TOS</t>
         </is>
       </c>
-      <c r="D33" s="43" t="n">
-        <v>19</v>
-      </c>
-      <c r="E33" s="43" t="n">
-        <v>2522</v>
-      </c>
-      <c r="F33" s="43" t="n">
-        <v>78182</v>
-      </c>
-      <c r="G33" s="66" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="51" t="inlineStr">
-        <is>
-          <t>BLB&gt;FENI KM0</t>
-        </is>
-      </c>
-      <c r="B34" s="51" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C34" s="51" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="D34" s="43" t="n">
-        <v>202</v>
-      </c>
-      <c r="E34" s="43" t="n">
-        <v>45774</v>
-      </c>
-      <c r="F34" s="43" t="n">
-        <v>1418994</v>
-      </c>
-      <c r="G34" s="66" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="51" t="inlineStr">
-        <is>
-          <t>TF&gt;FENI KM15</t>
-        </is>
-      </c>
-      <c r="B35" s="51" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C35" s="51" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="D35" s="43" t="n">
-        <v>141</v>
-      </c>
-      <c r="E35" s="43" t="n">
-        <v>14776</v>
-      </c>
-      <c r="F35" s="43" t="n">
-        <v>458056</v>
-      </c>
-      <c r="G35" s="66" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="51" t="inlineStr">
-        <is>
-          <t>KR&gt;FENI KM15</t>
-        </is>
-      </c>
-      <c r="B36" s="51" t="inlineStr">
-        <is>
-          <t>SMA</t>
-        </is>
-      </c>
-      <c r="C36" s="51" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="D36" s="43" t="n">
-        <v>50</v>
-      </c>
-      <c r="E36" s="43" t="n">
-        <v>7885</v>
-      </c>
-      <c r="F36" s="43" t="n">
-        <v>244435</v>
-      </c>
-      <c r="G36" s="66" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="51" t="inlineStr">
-        <is>
-          <t>KR&gt;POS 12</t>
-        </is>
-      </c>
-      <c r="B37" s="51" t="inlineStr">
-        <is>
-          <t>SMA</t>
-        </is>
-      </c>
-      <c r="C37" s="51" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="D37" s="43" t="n">
-        <v>11</v>
-      </c>
-      <c r="E37" s="43" t="n">
-        <v>2187</v>
-      </c>
-      <c r="F37" s="43" t="n">
-        <v>67797</v>
-      </c>
-      <c r="G37" s="66" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="51" t="inlineStr">
-        <is>
-          <t>BLB&gt;POS 14</t>
-        </is>
-      </c>
-      <c r="B38" s="51" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C38" s="51" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="D38" s="43" t="n">
-        <v>7</v>
-      </c>
-      <c r="E38" s="43" t="n">
-        <v>2043</v>
-      </c>
-      <c r="F38" s="43" t="n">
-        <v>63333</v>
-      </c>
-      <c r="G38" s="66" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="51" t="inlineStr">
-        <is>
-          <t>TF&gt;POS 12</t>
-        </is>
-      </c>
-      <c r="B39" s="51" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C39" s="51" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="D39" s="43" t="n">
-        <v>18</v>
-      </c>
-      <c r="E39" s="43" t="n">
-        <v>2036</v>
-      </c>
-      <c r="F39" s="43" t="n">
-        <v>63116</v>
-      </c>
-      <c r="G39" s="66" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="60" t="inlineStr">
-        <is>
-          <t>TOTAL (full matrix pool)</t>
-        </is>
-      </c>
-      <c r="D40" s="47" t="n">
-        <v>1281</v>
-      </c>
-      <c r="F40" s="47" t="n">
-        <v>5642062</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="41" t="inlineStr">
-        <is>
-          <t>Material</t>
-        </is>
-      </c>
-      <c r="B42" s="41" t="inlineStr">
-        <is>
-          <t>t/month (frozen)</t>
-        </is>
-      </c>
-      <c r="C42" s="41" t="inlineStr">
-        <is>
-          <t>December TARGET t</t>
-        </is>
-      </c>
-      <c r="D42" s="41" t="inlineStr">
-        <is>
-          <t>Coverage</t>
-        </is>
-      </c>
-      <c r="E42" s="41" t="inlineStr"/>
-      <c r="F42" s="41" t="inlineStr"/>
-      <c r="G42" s="41" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="51" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="B43" s="47" t="n">
-        <v>2315731</v>
-      </c>
-      <c r="C43" s="43" t="n">
-        <v>2311213</v>
-      </c>
-      <c r="D43" s="45" t="n">
-        <v>1.00195481766501</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="51" t="inlineStr">
-        <is>
-          <t>LIM-TOS</t>
-        </is>
-      </c>
-      <c r="B44" s="47" t="n">
-        <v>1001951</v>
-      </c>
-      <c r="C44" s="43" t="n">
-        <v>996084</v>
-      </c>
-      <c r="D44" s="45" t="n">
-        <v>1.005890065496484</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="51" t="inlineStr">
-        <is>
-          <t>LIM-LD</t>
-        </is>
-      </c>
-      <c r="B45" s="47" t="n">
-        <v>2324380</v>
-      </c>
-      <c r="C45" s="43" t="n">
-        <v>1719964</v>
-      </c>
-      <c r="D45" s="45" t="n">
-        <v>1.351412006297806</v>
-      </c>
-      <c r="E45" s="70" t="inlineStr">
-        <is>
-          <t>above target by design — surplus fleet hauls LD</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="40" t="inlineStr">
-        <is>
-          <t>Scenario 3.1.1 — December (frozen, 1,281 DT)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="41" t="inlineStr">
-        <is>
-          <t>Route</t>
-        </is>
-      </c>
-      <c r="B49" s="41" t="inlineStr">
-        <is>
-          <t>Contractor</t>
-        </is>
-      </c>
-      <c r="C49" s="41" t="inlineStr">
-        <is>
-          <t>Material</t>
-        </is>
-      </c>
-      <c r="D49" s="41" t="inlineStr">
-        <is>
-          <t>DT</t>
-        </is>
-      </c>
-      <c r="E49" s="41" t="inlineStr">
-        <is>
-          <t>t/day</t>
-        </is>
-      </c>
-      <c r="F49" s="41" t="inlineStr">
-        <is>
-          <t>t/month</t>
-        </is>
-      </c>
-      <c r="G49" s="41" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="67" t="inlineStr">
-        <is>
-          <t>TF&gt;HUAFEI</t>
-        </is>
-      </c>
-      <c r="B50" s="67" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C50" s="67" t="inlineStr">
-        <is>
-          <t>LIM-LD</t>
-        </is>
-      </c>
-      <c r="D50" s="68" t="n">
-        <v>393</v>
-      </c>
-      <c r="E50" s="43" t="n">
-        <v>41017</v>
-      </c>
-      <c r="F50" s="43" t="n">
-        <v>1271527</v>
-      </c>
-      <c r="G50" s="69" t="inlineStr">
-        <is>
-          <t>includes activated idle DT</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="67" t="inlineStr">
-        <is>
-          <t>TF&gt;HUAFEI</t>
-        </is>
-      </c>
-      <c r="B51" s="67" t="inlineStr">
-        <is>
-          <t>SMA</t>
-        </is>
-      </c>
-      <c r="C51" s="67" t="inlineStr">
-        <is>
-          <t>LIM-LD</t>
-        </is>
-      </c>
-      <c r="D51" s="68" t="n">
-        <v>241</v>
+      <c r="D51" s="43" t="n">
+        <v>62</v>
       </c>
       <c r="E51" s="43" t="n">
-        <v>25110</v>
-      </c>
-      <c r="F51" s="43" t="n">
-        <v>778410</v>
-      </c>
-      <c r="G51" s="69" t="inlineStr">
-        <is>
-          <t>includes activated idle DT</t>
-        </is>
+        <v>62</v>
+      </c>
+      <c r="F51" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="43" t="n">
+        <v>6477</v>
+      </c>
+      <c r="H51" s="43" t="n">
+        <v>200787</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="51" t="inlineStr">
         <is>
-          <t>BLB&gt;HUAFEI</t>
+          <t>KR&gt;HUAFEI</t>
         </is>
       </c>
       <c r="B52" s="51" t="inlineStr">
         <is>
-          <t>RIM</t>
+          <t>SMA</t>
         </is>
       </c>
       <c r="C52" s="51" t="inlineStr">
@@ -3086,20 +3142,25 @@
         </is>
       </c>
       <c r="D52" s="43" t="n">
-        <v>139</v>
+        <v>19</v>
       </c>
       <c r="E52" s="43" t="n">
-        <v>33851</v>
-      </c>
-      <c r="F52" s="43" t="n">
-        <v>1049381</v>
-      </c>
-      <c r="G52" s="66" t="n"/>
+        <v>19</v>
+      </c>
+      <c r="F52" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="43" t="n">
+        <v>2549</v>
+      </c>
+      <c r="H52" s="43" t="n">
+        <v>79019</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="51" t="inlineStr">
         <is>
-          <t>TF&gt;HUAFEI</t>
+          <t>BLB&gt;FENI KM0</t>
         </is>
       </c>
       <c r="B53" s="51" t="inlineStr">
@@ -3109,56 +3170,66 @@
       </c>
       <c r="C53" s="51" t="inlineStr">
         <is>
-          <t>LIM-TOS</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D53" s="43" t="n">
-        <v>62</v>
+        <v>202</v>
       </c>
       <c r="E53" s="43" t="n">
-        <v>6471</v>
-      </c>
-      <c r="F53" s="43" t="n">
-        <v>200601</v>
-      </c>
-      <c r="G53" s="66" t="n"/>
+        <v>202</v>
+      </c>
+      <c r="F53" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="43" t="n">
+        <v>45786</v>
+      </c>
+      <c r="H53" s="43" t="n">
+        <v>1419366</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="51" t="inlineStr">
         <is>
-          <t>KR&gt;HUAFEI</t>
+          <t>TF&gt;FENI KM15</t>
         </is>
       </c>
       <c r="B54" s="51" t="inlineStr">
         <is>
-          <t>SMA</t>
+          <t>RIM</t>
         </is>
       </c>
       <c r="C54" s="51" t="inlineStr">
         <is>
-          <t>LIM-TOS</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D54" s="43" t="n">
-        <v>19</v>
+        <v>140</v>
       </c>
       <c r="E54" s="43" t="n">
-        <v>2545</v>
-      </c>
-      <c r="F54" s="43" t="n">
-        <v>78895</v>
-      </c>
-      <c r="G54" s="66" t="n"/>
+        <v>140</v>
+      </c>
+      <c r="F54" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="43" t="n">
+        <v>14736</v>
+      </c>
+      <c r="H54" s="43" t="n">
+        <v>456816</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="51" t="inlineStr">
         <is>
-          <t>BLB&gt;FENI KM0</t>
+          <t>KR&gt;FENI KM15</t>
         </is>
       </c>
       <c r="B55" s="51" t="inlineStr">
         <is>
-          <t>RIM</t>
+          <t>SMA</t>
         </is>
       </c>
       <c r="C55" s="51" t="inlineStr">
@@ -3167,20 +3238,25 @@
         </is>
       </c>
       <c r="D55" s="43" t="n">
-        <v>202</v>
+        <v>50</v>
       </c>
       <c r="E55" s="43" t="n">
-        <v>45774</v>
-      </c>
-      <c r="F55" s="43" t="n">
-        <v>1418994</v>
-      </c>
-      <c r="G55" s="66" t="n"/>
+        <v>50</v>
+      </c>
+      <c r="F55" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="43" t="n">
+        <v>7958</v>
+      </c>
+      <c r="H55" s="43" t="n">
+        <v>246698</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="51" t="inlineStr">
         <is>
-          <t>TF&gt;FENI KM15</t>
+          <t>BLB&gt;POS 14</t>
         </is>
       </c>
       <c r="B56" s="51" t="inlineStr">
@@ -3194,25 +3270,30 @@
         </is>
       </c>
       <c r="D56" s="43" t="n">
-        <v>140</v>
+        <v>7</v>
       </c>
       <c r="E56" s="43" t="n">
-        <v>14702</v>
-      </c>
-      <c r="F56" s="43" t="n">
-        <v>455762</v>
-      </c>
-      <c r="G56" s="66" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="F56" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="43" t="n">
+        <v>2044</v>
+      </c>
+      <c r="H56" s="43" t="n">
+        <v>63364</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="51" t="inlineStr">
         <is>
-          <t>KR&gt;FENI KM15</t>
+          <t>TF&gt;POS 12</t>
         </is>
       </c>
       <c r="B57" s="51" t="inlineStr">
         <is>
-          <t>SMA</t>
+          <t>RIM</t>
         </is>
       </c>
       <c r="C57" s="51" t="inlineStr">
@@ -3221,25 +3302,30 @@
         </is>
       </c>
       <c r="D57" s="43" t="n">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="E57" s="43" t="n">
-        <v>7919</v>
-      </c>
-      <c r="F57" s="43" t="n">
-        <v>245489</v>
-      </c>
-      <c r="G57" s="66" t="n"/>
+        <v>18</v>
+      </c>
+      <c r="F57" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="43" t="n">
+        <v>2039</v>
+      </c>
+      <c r="H57" s="43" t="n">
+        <v>63209</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="51" t="inlineStr">
         <is>
-          <t>BLB&gt;POS 14</t>
+          <t>KR&gt;POS 12</t>
         </is>
       </c>
       <c r="B58" s="51" t="inlineStr">
         <is>
-          <t>RIM</t>
+          <t>SMA</t>
         </is>
       </c>
       <c r="C58" s="51" t="inlineStr">
@@ -3248,483 +3334,415 @@
         </is>
       </c>
       <c r="D58" s="43" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E58" s="43" t="n">
-        <v>2043</v>
-      </c>
-      <c r="F58" s="43" t="n">
-        <v>63333</v>
-      </c>
-      <c r="G58" s="66" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="F58" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="43" t="n">
+        <v>2009</v>
+      </c>
+      <c r="H58" s="43" t="n">
+        <v>62279</v>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" s="51" t="inlineStr">
-        <is>
-          <t>TF&gt;POS 12</t>
-        </is>
-      </c>
-      <c r="B59" s="51" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C59" s="51" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="D59" s="43" t="n">
-        <v>18</v>
-      </c>
-      <c r="E59" s="43" t="n">
-        <v>2037</v>
-      </c>
-      <c r="F59" s="43" t="n">
-        <v>63147</v>
-      </c>
-      <c r="G59" s="66" t="n"/>
+      <c r="A59" s="54" t="inlineStr">
+        <is>
+          <t>KR&gt;FENI KM0</t>
+        </is>
+      </c>
+      <c r="B59" s="54" t="inlineStr">
+        <is>
+          <t>reallocated</t>
+        </is>
+      </c>
+      <c r="C59" s="54" t="inlineStr">
+        <is>
+          <t>SAP (stock at FeNi KM0)</t>
+        </is>
+      </c>
+      <c r="D59" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E59" s="56" t="n">
+        <v>40</v>
+      </c>
+      <c r="F59" s="56" t="n">
+        <v>40</v>
+      </c>
+      <c r="G59" s="56" t="n">
+        <v>5424</v>
+      </c>
+      <c r="H59" s="56" t="n">
+        <v>168135</v>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" s="51" t="inlineStr">
-        <is>
-          <t>KR&gt;POS 12</t>
-        </is>
-      </c>
-      <c r="B60" s="51" t="inlineStr">
-        <is>
-          <t>SMA</t>
-        </is>
-      </c>
-      <c r="C60" s="51" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="D60" s="43" t="n">
-        <v>10</v>
-      </c>
-      <c r="E60" s="43" t="n">
-        <v>1999</v>
-      </c>
-      <c r="F60" s="43" t="n">
-        <v>61969</v>
-      </c>
-      <c r="G60" s="66" t="n"/>
+      <c r="A60" s="54" t="inlineStr">
+        <is>
+          <t>TF&gt;FENI KM0</t>
+        </is>
+      </c>
+      <c r="B60" s="54" t="inlineStr">
+        <is>
+          <t>reallocated</t>
+        </is>
+      </c>
+      <c r="C60" s="54" t="inlineStr">
+        <is>
+          <t>SAP (stock at FeNi KM0)</t>
+        </is>
+      </c>
+      <c r="D60" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E60" s="56" t="n">
+        <v>39</v>
+      </c>
+      <c r="F60" s="56" t="n">
+        <v>39</v>
+      </c>
+      <c r="G60" s="56" t="n">
+        <v>4289</v>
+      </c>
+      <c r="H60" s="56" t="n">
+        <v>132945</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="60" t="inlineStr">
         <is>
-          <t>TOTAL (full matrix pool)</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="D61" s="47" t="n">
-        <v>1281</v>
-      </c>
-      <c r="F61" s="47" t="n">
-        <v>5687508</v>
+        <v>1190</v>
+      </c>
+      <c r="E61" s="47" t="n">
+        <v>1190</v>
+      </c>
+      <c r="H61" s="47" t="n">
+        <v>5333821</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="41" t="inlineStr">
+      <c r="A63" s="50" t="inlineStr">
+        <is>
+          <t>OPTION 2 — tonnage by material (December)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="41" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="B63" s="41" t="inlineStr">
-        <is>
-          <t>t/month (frozen)</t>
-        </is>
-      </c>
-      <c r="C63" s="41" t="inlineStr">
+      <c r="B64" s="41" t="inlineStr">
+        <is>
+          <t>BEFORE re-dispatch t/mo</t>
+        </is>
+      </c>
+      <c r="C64" s="41" t="inlineStr">
+        <is>
+          <t>AFTER re-dispatch t/mo</t>
+        </is>
+      </c>
+      <c r="D64" s="41" t="inlineStr">
+        <is>
+          <t>Δ t/mo</t>
+        </is>
+      </c>
+      <c r="E64" s="41" t="inlineStr">
+        <is>
+          <t>Change %</t>
+        </is>
+      </c>
+      <c r="F64" s="41" t="inlineStr">
         <is>
           <t>December TARGET t</t>
         </is>
       </c>
-      <c r="D63" s="41" t="inlineStr">
-        <is>
-          <t>Coverage</t>
-        </is>
-      </c>
-      <c r="E63" s="41" t="inlineStr"/>
-      <c r="F63" s="41" t="inlineStr"/>
-      <c r="G63" s="41" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="51" t="inlineStr">
+      <c r="G64" s="41" t="inlineStr">
+        <is>
+          <t>Coverage after</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="42" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="B64" s="47" t="n">
-        <v>2308694</v>
-      </c>
-      <c r="C64" s="43" t="n">
+      <c r="B65" s="43" t="n">
+        <v>2311732</v>
+      </c>
+      <c r="C65" s="47" t="n">
+        <v>2612812</v>
+      </c>
+      <c r="D65" s="61" t="n">
+        <v>301080</v>
+      </c>
+      <c r="E65" s="62" t="n">
+        <v>0.1302400105202506</v>
+      </c>
+      <c r="F65" s="43" t="n">
         <v>2311213</v>
       </c>
-      <c r="D64" s="71" t="n">
-        <v>0.9989100961270121</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="51" t="inlineStr">
-        <is>
-          <t>LIM-TOS</t>
-        </is>
-      </c>
-      <c r="B65" s="47" t="n">
-        <v>1328877</v>
-      </c>
-      <c r="C65" s="43" t="n">
-        <v>1326082</v>
-      </c>
-      <c r="D65" s="45" t="n">
-        <v>1.002107712796041</v>
+      <c r="G65" s="45" t="n">
+        <v>1.13049381428713</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="51" t="inlineStr">
         <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="B66" s="43" t="n">
+        <v>1000556</v>
+      </c>
+      <c r="C66" s="47" t="n">
+        <v>1000556</v>
+      </c>
+      <c r="D66" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" s="63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" s="43" t="n">
+        <v>996084</v>
+      </c>
+      <c r="G66" s="45" t="n">
+        <v>1.004489581199979</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="51" t="inlineStr">
+        <is>
           <t>LIM-LD</t>
         </is>
       </c>
-      <c r="B66" s="47" t="n">
-        <v>2049937</v>
-      </c>
-      <c r="C66" s="43" t="n">
-        <v>992213</v>
-      </c>
-      <c r="D66" s="45" t="n">
-        <v>2.066025137747641</v>
-      </c>
-      <c r="E66" s="70" t="inlineStr">
-        <is>
-          <t>above target by design — surplus fleet hauls LD</t>
+      <c r="B67" s="43" t="n">
+        <v>2031492</v>
+      </c>
+      <c r="C67" s="47" t="n">
+        <v>1720453</v>
+      </c>
+      <c r="D67" s="52" t="n">
+        <v>-311039</v>
+      </c>
+      <c r="E67" s="64" t="n">
+        <v>-0.1531086511785427</v>
+      </c>
+      <c r="F67" s="43" t="n">
+        <v>1719964</v>
+      </c>
+      <c r="G67" s="45" t="n">
+        <v>1.00028430827622</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="65" t="inlineStr">
+        <is>
+          <t>of which SAP stocked at FeNi KM0 (KR 40 DT + TF 39 DT reallocated)</t>
+        </is>
+      </c>
+      <c r="B68" s="66" t="n"/>
+      <c r="C68" s="61" t="n">
+        <v>301080</v>
+      </c>
+      <c r="D68" s="61" t="n">
+        <v>301080</v>
+      </c>
+      <c r="E68" s="70" t="inlineStr">
+        <is>
+          <t>inside the SAP row</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="40" t="inlineStr">
-        <is>
-          <t>Scenario 3.1.2 — December (frozen, 1,281 DT)</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="41" t="inlineStr">
+      <c r="A69" s="60" t="inlineStr">
+        <is>
+          <t>TOTAL moved</t>
+        </is>
+      </c>
+      <c r="B69" s="47" t="n">
+        <v>5343780</v>
+      </c>
+      <c r="C69" s="47" t="n">
+        <v>5333821</v>
+      </c>
+      <c r="D69" s="52" t="n">
+        <v>-9959</v>
+      </c>
+      <c r="E69" s="64" t="n">
+        <v>-0.001863662051955732</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="40" t="inlineStr">
+        <is>
+          <t>Scenario 3.1.1 — December</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="41" t="inlineStr"/>
+      <c r="B73" s="41" t="inlineStr">
+        <is>
+          <t>Target t</t>
+        </is>
+      </c>
+      <c r="C73" s="41" t="inlineStr">
+        <is>
+          <t>Predicted t</t>
+        </is>
+      </c>
+      <c r="D73" s="41" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="E73" s="41" t="inlineStr">
+        <is>
+          <t>Fleet DT</t>
+        </is>
+      </c>
+      <c r="F73" s="41" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="42" t="inlineStr">
+        <is>
+          <t>As frozen</t>
+        </is>
+      </c>
+      <c r="B74" s="43" t="n">
+        <v>4810381</v>
+      </c>
+      <c r="C74" s="43" t="n">
+        <v>4971401</v>
+      </c>
+      <c r="D74" s="44" t="n">
+        <v>1.033473440045601</v>
+      </c>
+      <c r="E74" s="43" t="n">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="42" t="inlineStr">
+        <is>
+          <t>OPTION 1 · park 49 DT (total month → 100.0%)</t>
+        </is>
+      </c>
+      <c r="B75" s="43" t="n">
+        <v>4810381</v>
+      </c>
+      <c r="C75" s="43" t="n">
+        <v>4811620</v>
+      </c>
+      <c r="D75" s="45" t="n">
+        <v>1.000257567955636</v>
+      </c>
+      <c r="E75" s="43" t="n">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="42" t="inlineStr">
+        <is>
+          <t>OPTION 2 · re-dispatch 101 DT (LIM-LD → 100.0%)</t>
+        </is>
+      </c>
+      <c r="B76" s="43" t="n">
+        <v>4810381</v>
+      </c>
+      <c r="C76" s="43" t="n">
+        <v>5027004</v>
+      </c>
+      <c r="D76" s="46" t="n">
+        <v>1.045032399720521</v>
+      </c>
+      <c r="E76" s="43" t="n">
+        <v>1052</v>
+      </c>
+      <c r="F76" s="48" t="inlineStr">
+        <is>
+          <t>+ 384,923 t SAP stocked at FeNi KM0</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="49" t="inlineStr">
+        <is>
+          <t>Option 2 cut (sized so LIM-LD lands exactly on its line): TF&gt;HUAFEI (RIM, LD): −101 DT @ 105.2 t/day/DT</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="50" t="inlineStr">
+        <is>
+          <t>OPTION 2 — full December plan (re-dispatched)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="41" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="B70" s="41" t="inlineStr">
+      <c r="B80" s="41" t="inlineStr">
         <is>
           <t>Contractor</t>
         </is>
       </c>
-      <c r="C70" s="41" t="inlineStr">
+      <c r="C80" s="41" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="D70" s="41" t="inlineStr">
-        <is>
-          <t>DT</t>
-        </is>
-      </c>
-      <c r="E70" s="41" t="inlineStr">
+      <c r="D80" s="41" t="inlineStr">
+        <is>
+          <t>DT before</t>
+        </is>
+      </c>
+      <c r="E80" s="41" t="inlineStr">
+        <is>
+          <t>DT after</t>
+        </is>
+      </c>
+      <c r="F80" s="41" t="inlineStr">
+        <is>
+          <t>Δ DT</t>
+        </is>
+      </c>
+      <c r="G80" s="41" t="inlineStr">
         <is>
           <t>t/day</t>
         </is>
       </c>
-      <c r="F70" s="41" t="inlineStr">
+      <c r="H80" s="41" t="inlineStr">
         <is>
           <t>t/month</t>
         </is>
       </c>
-      <c r="G70" s="41" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="67" t="inlineStr">
-        <is>
-          <t>TF&gt;HUAFEI</t>
-        </is>
-      </c>
-      <c r="B71" s="67" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C71" s="67" t="inlineStr">
-        <is>
-          <t>LIM-LD</t>
-        </is>
-      </c>
-      <c r="D71" s="68" t="n">
-        <v>266</v>
-      </c>
-      <c r="E71" s="43" t="n">
-        <v>27708</v>
-      </c>
-      <c r="F71" s="43" t="n">
-        <v>858948</v>
-      </c>
-      <c r="G71" s="69" t="inlineStr">
-        <is>
-          <t>includes activated idle DT</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="51" t="inlineStr">
-        <is>
-          <t>TF&gt;POS 6</t>
-        </is>
-      </c>
-      <c r="B72" s="51" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C72" s="51" t="inlineStr">
-        <is>
-          <t>LIM-LD</t>
-        </is>
-      </c>
-      <c r="D72" s="43" t="n">
-        <v>126</v>
-      </c>
-      <c r="E72" s="43" t="n">
-        <v>15972</v>
-      </c>
-      <c r="F72" s="43" t="n">
-        <v>495132</v>
-      </c>
-      <c r="G72" s="66" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="51" t="inlineStr">
-        <is>
-          <t>TF&gt;POS 6</t>
-        </is>
-      </c>
-      <c r="B73" s="51" t="inlineStr">
-        <is>
-          <t>SMA</t>
-        </is>
-      </c>
-      <c r="C73" s="51" t="inlineStr">
-        <is>
-          <t>LIM-LD</t>
-        </is>
-      </c>
-      <c r="D73" s="43" t="n">
-        <v>120</v>
-      </c>
-      <c r="E73" s="43" t="n">
-        <v>13894</v>
-      </c>
-      <c r="F73" s="43" t="n">
-        <v>430714</v>
-      </c>
-      <c r="G73" s="66" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="67" t="inlineStr">
-        <is>
-          <t>TF&gt;HUAFEI</t>
-        </is>
-      </c>
-      <c r="B74" s="67" t="inlineStr">
-        <is>
-          <t>SMA</t>
-        </is>
-      </c>
-      <c r="C74" s="67" t="inlineStr">
-        <is>
-          <t>LIM-LD</t>
-        </is>
-      </c>
-      <c r="D74" s="68" t="n">
-        <v>121</v>
-      </c>
-      <c r="E74" s="43" t="n">
-        <v>12580</v>
-      </c>
-      <c r="F74" s="43" t="n">
-        <v>389980</v>
-      </c>
-      <c r="G74" s="69" t="inlineStr">
-        <is>
-          <t>includes activated idle DT</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="51" t="inlineStr">
-        <is>
-          <t>BLB&gt;HUAFEI</t>
-        </is>
-      </c>
-      <c r="B75" s="51" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C75" s="51" t="inlineStr">
-        <is>
-          <t>LIM-TOS</t>
-        </is>
-      </c>
-      <c r="D75" s="43" t="n">
-        <v>139</v>
-      </c>
-      <c r="E75" s="43" t="n">
-        <v>33851</v>
-      </c>
-      <c r="F75" s="43" t="n">
-        <v>1049381</v>
-      </c>
-      <c r="G75" s="66" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="51" t="inlineStr">
-        <is>
-          <t>TF&gt;HUAFEI</t>
-        </is>
-      </c>
-      <c r="B76" s="51" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C76" s="51" t="inlineStr">
-        <is>
-          <t>LIM-TOS</t>
-        </is>
-      </c>
-      <c r="D76" s="43" t="n">
-        <v>63</v>
-      </c>
-      <c r="E76" s="43" t="n">
-        <v>6562</v>
-      </c>
-      <c r="F76" s="43" t="n">
-        <v>203422</v>
-      </c>
-      <c r="G76" s="66" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="51" t="inlineStr">
-        <is>
-          <t>KR&gt;HUAFEI</t>
-        </is>
-      </c>
-      <c r="B77" s="51" t="inlineStr">
-        <is>
-          <t>SMA</t>
-        </is>
-      </c>
-      <c r="C77" s="51" t="inlineStr">
-        <is>
-          <t>LIM-TOS</t>
-        </is>
-      </c>
-      <c r="D77" s="43" t="n">
-        <v>19</v>
-      </c>
-      <c r="E77" s="43" t="n">
-        <v>2528</v>
-      </c>
-      <c r="F77" s="43" t="n">
-        <v>78368</v>
-      </c>
-      <c r="G77" s="66" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="51" t="inlineStr">
-        <is>
-          <t>BLB&gt;FENI KM0</t>
-        </is>
-      </c>
-      <c r="B78" s="51" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C78" s="51" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="D78" s="43" t="n">
-        <v>202</v>
-      </c>
-      <c r="E78" s="43" t="n">
-        <v>45774</v>
-      </c>
-      <c r="F78" s="43" t="n">
-        <v>1418994</v>
-      </c>
-      <c r="G78" s="66" t="n"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="51" t="inlineStr">
-        <is>
-          <t>TF&gt;FENI KM15</t>
-        </is>
-      </c>
-      <c r="B79" s="51" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C79" s="51" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="D79" s="43" t="n">
-        <v>140</v>
-      </c>
-      <c r="E79" s="43" t="n">
-        <v>14702</v>
-      </c>
-      <c r="F79" s="43" t="n">
-        <v>455762</v>
-      </c>
-      <c r="G79" s="66" t="n"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="51" t="inlineStr">
-        <is>
-          <t>KR&gt;FENI KM15</t>
-        </is>
-      </c>
-      <c r="B80" s="51" t="inlineStr">
-        <is>
-          <t>SMA</t>
-        </is>
-      </c>
-      <c r="C80" s="51" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="D80" s="43" t="n">
-        <v>50</v>
-      </c>
-      <c r="E80" s="43" t="n">
-        <v>7919</v>
-      </c>
-      <c r="F80" s="43" t="n">
-        <v>245489</v>
-      </c>
-      <c r="G80" s="66" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="51" t="inlineStr">
         <is>
-          <t>BLB&gt;POS 14</t>
+          <t>TF&gt;HUAFEI</t>
         </is>
       </c>
       <c r="B81" s="51" t="inlineStr">
@@ -3734,166 +3752,1399 @@
       </c>
       <c r="C81" s="51" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>LIM-LD</t>
         </is>
       </c>
       <c r="D81" s="43" t="n">
-        <v>7</v>
-      </c>
-      <c r="E81" s="43" t="n">
-        <v>2043</v>
-      </c>
-      <c r="F81" s="43" t="n">
-        <v>63333</v>
-      </c>
-      <c r="G81" s="66" t="n"/>
+        <v>319</v>
+      </c>
+      <c r="E81" s="47" t="n">
+        <v>218</v>
+      </c>
+      <c r="F81" s="52" t="n">
+        <v>-101</v>
+      </c>
+      <c r="G81" s="43" t="n">
+        <v>22932</v>
+      </c>
+      <c r="H81" s="43" t="n">
+        <v>710878</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="51" t="inlineStr">
         <is>
-          <t>TF&gt;POS 12</t>
+          <t>TF&gt;HUAFEI</t>
         </is>
       </c>
       <c r="B82" s="51" t="inlineStr">
         <is>
-          <t>RIM</t>
+          <t>SMA</t>
         </is>
       </c>
       <c r="C82" s="51" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>LIM-LD</t>
         </is>
       </c>
       <c r="D82" s="43" t="n">
-        <v>18</v>
+        <v>87</v>
       </c>
       <c r="E82" s="43" t="n">
-        <v>2037</v>
-      </c>
-      <c r="F82" s="43" t="n">
-        <v>63147</v>
-      </c>
-      <c r="G82" s="66" t="n"/>
+        <v>87</v>
+      </c>
+      <c r="F82" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" s="43" t="n">
+        <v>9142</v>
+      </c>
+      <c r="H82" s="43" t="n">
+        <v>283402</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="51" t="inlineStr">
         <is>
-          <t>KR&gt;POS 12</t>
+          <t>BLB&gt;HUAFEI</t>
         </is>
       </c>
       <c r="B83" s="51" t="inlineStr">
         <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C83" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D83" s="43" t="n">
+        <v>139</v>
+      </c>
+      <c r="E83" s="43" t="n">
+        <v>139</v>
+      </c>
+      <c r="F83" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" s="43" t="n">
+        <v>33859</v>
+      </c>
+      <c r="H83" s="43" t="n">
+        <v>1049629</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B84" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C84" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D84" s="43" t="n">
+        <v>62</v>
+      </c>
+      <c r="E84" s="43" t="n">
+        <v>62</v>
+      </c>
+      <c r="F84" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" s="43" t="n">
+        <v>6522</v>
+      </c>
+      <c r="H84" s="43" t="n">
+        <v>202182</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="51" t="inlineStr">
+        <is>
+          <t>KR&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B85" s="51" t="inlineStr">
+        <is>
           <t>SMA</t>
         </is>
       </c>
-      <c r="C83" s="51" t="inlineStr">
+      <c r="C85" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D85" s="43" t="n">
+        <v>19</v>
+      </c>
+      <c r="E85" s="43" t="n">
+        <v>19</v>
+      </c>
+      <c r="F85" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" s="43" t="n">
+        <v>2597</v>
+      </c>
+      <c r="H85" s="43" t="n">
+        <v>80507</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="51" t="inlineStr">
+        <is>
+          <t>BLB&gt;FENI KM0</t>
+        </is>
+      </c>
+      <c r="B86" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C86" s="51" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="D83" s="43" t="n">
-        <v>10</v>
-      </c>
-      <c r="E83" s="43" t="n">
-        <v>1999</v>
-      </c>
-      <c r="F83" s="43" t="n">
-        <v>61969</v>
-      </c>
-      <c r="G83" s="66" t="n"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="60" t="inlineStr">
-        <is>
-          <t>TOTAL (full matrix pool)</t>
-        </is>
-      </c>
-      <c r="D84" s="47" t="n">
-        <v>1281</v>
-      </c>
-      <c r="F84" s="47" t="n">
-        <v>5814639</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="41" t="inlineStr">
-        <is>
-          <t>Material</t>
-        </is>
-      </c>
-      <c r="B86" s="41" t="inlineStr">
-        <is>
-          <t>t/month (frozen)</t>
-        </is>
-      </c>
-      <c r="C86" s="41" t="inlineStr">
-        <is>
-          <t>December TARGET t</t>
-        </is>
-      </c>
-      <c r="D86" s="41" t="inlineStr">
-        <is>
-          <t>Coverage</t>
-        </is>
-      </c>
-      <c r="E86" s="41" t="inlineStr"/>
-      <c r="F86" s="41" t="inlineStr"/>
-      <c r="G86" s="41" t="inlineStr"/>
+      <c r="D86" s="43" t="n">
+        <v>202</v>
+      </c>
+      <c r="E86" s="43" t="n">
+        <v>202</v>
+      </c>
+      <c r="F86" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="43" t="n">
+        <v>45786</v>
+      </c>
+      <c r="H86" s="43" t="n">
+        <v>1419366</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="51" t="inlineStr">
         <is>
+          <t>TF&gt;FENI KM15</t>
+        </is>
+      </c>
+      <c r="B87" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C87" s="51" t="inlineStr">
+        <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="B87" s="47" t="n">
-        <v>2308694</v>
-      </c>
-      <c r="C87" s="43" t="n">
-        <v>2311213</v>
-      </c>
-      <c r="D87" s="71" t="n">
-        <v>0.9989100961270121</v>
+      <c r="D87" s="43" t="n">
+        <v>140</v>
+      </c>
+      <c r="E87" s="43" t="n">
+        <v>140</v>
+      </c>
+      <c r="F87" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="43" t="n">
+        <v>14847</v>
+      </c>
+      <c r="H87" s="43" t="n">
+        <v>460257</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="51" t="inlineStr">
         <is>
-          <t>LIM-TOS</t>
-        </is>
-      </c>
-      <c r="B88" s="47" t="n">
-        <v>1331171</v>
-      </c>
-      <c r="C88" s="43" t="n">
-        <v>1326082</v>
-      </c>
-      <c r="D88" s="45" t="n">
-        <v>1.003837620901272</v>
+          <t>KR&gt;FENI KM15</t>
+        </is>
+      </c>
+      <c r="B88" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C88" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D88" s="43" t="n">
+        <v>49</v>
+      </c>
+      <c r="E88" s="43" t="n">
+        <v>49</v>
+      </c>
+      <c r="F88" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="43" t="n">
+        <v>7929</v>
+      </c>
+      <c r="H88" s="43" t="n">
+        <v>245799</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="51" t="inlineStr">
         <is>
+          <t>TF&gt;POS 12</t>
+        </is>
+      </c>
+      <c r="B89" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C89" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D89" s="43" t="n">
+        <v>18</v>
+      </c>
+      <c r="E89" s="43" t="n">
+        <v>18</v>
+      </c>
+      <c r="F89" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" s="43" t="n">
+        <v>2045</v>
+      </c>
+      <c r="H89" s="43" t="n">
+        <v>63395</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="51" t="inlineStr">
+        <is>
+          <t>BLB&gt;POS 14</t>
+        </is>
+      </c>
+      <c r="B90" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C90" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D90" s="43" t="n">
+        <v>7</v>
+      </c>
+      <c r="E90" s="43" t="n">
+        <v>7</v>
+      </c>
+      <c r="F90" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" s="43" t="n">
+        <v>2044</v>
+      </c>
+      <c r="H90" s="43" t="n">
+        <v>63364</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="51" t="inlineStr">
+        <is>
+          <t>KR&gt;POS 12</t>
+        </is>
+      </c>
+      <c r="B91" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C91" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D91" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E91" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="F91" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" s="43" t="n">
+        <v>2042</v>
+      </c>
+      <c r="H91" s="43" t="n">
+        <v>63302</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="54" t="inlineStr">
+        <is>
+          <t>KR&gt;FENI KM0</t>
+        </is>
+      </c>
+      <c r="B92" s="54" t="inlineStr">
+        <is>
+          <t>reallocated</t>
+        </is>
+      </c>
+      <c r="C92" s="54" t="inlineStr">
+        <is>
+          <t>SAP (stock at FeNi KM0)</t>
+        </is>
+      </c>
+      <c r="D92" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E92" s="56" t="n">
+        <v>51</v>
+      </c>
+      <c r="F92" s="56" t="n">
+        <v>51</v>
+      </c>
+      <c r="G92" s="56" t="n">
+        <v>6917</v>
+      </c>
+      <c r="H92" s="56" t="n">
+        <v>214423</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="54" t="inlineStr">
+        <is>
+          <t>TF&gt;FENI KM0</t>
+        </is>
+      </c>
+      <c r="B93" s="54" t="inlineStr">
+        <is>
+          <t>reallocated</t>
+        </is>
+      </c>
+      <c r="C93" s="54" t="inlineStr">
+        <is>
+          <t>SAP (stock at FeNi KM0)</t>
+        </is>
+      </c>
+      <c r="D93" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E93" s="56" t="n">
+        <v>50</v>
+      </c>
+      <c r="F93" s="56" t="n">
+        <v>50</v>
+      </c>
+      <c r="G93" s="56" t="n">
+        <v>5500</v>
+      </c>
+      <c r="H93" s="56" t="n">
+        <v>170500</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="60" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D94" s="47" t="n">
+        <v>1052</v>
+      </c>
+      <c r="E94" s="47" t="n">
+        <v>1052</v>
+      </c>
+      <c r="H94" s="47" t="n">
+        <v>5027004</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="50" t="inlineStr">
+        <is>
+          <t>OPTION 2 — tonnage by material (December)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="41" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="B97" s="41" t="inlineStr">
+        <is>
+          <t>BEFORE re-dispatch t/mo</t>
+        </is>
+      </c>
+      <c r="C97" s="41" t="inlineStr">
+        <is>
+          <t>AFTER re-dispatch t/mo</t>
+        </is>
+      </c>
+      <c r="D97" s="41" t="inlineStr">
+        <is>
+          <t>Δ t/mo</t>
+        </is>
+      </c>
+      <c r="E97" s="41" t="inlineStr">
+        <is>
+          <t>Change %</t>
+        </is>
+      </c>
+      <c r="F97" s="41" t="inlineStr">
+        <is>
+          <t>December TARGET t</t>
+        </is>
+      </c>
+      <c r="G97" s="41" t="inlineStr">
+        <is>
+          <t>Coverage after</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="42" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B98" s="43" t="n">
+        <v>2315483</v>
+      </c>
+      <c r="C98" s="47" t="n">
+        <v>2700406</v>
+      </c>
+      <c r="D98" s="61" t="n">
+        <v>384923</v>
+      </c>
+      <c r="E98" s="62" t="n">
+        <v>0.1662387501873259</v>
+      </c>
+      <c r="F98" s="43" t="n">
+        <v>2311213</v>
+      </c>
+      <c r="G98" s="45" t="n">
+        <v>1.168393393425876</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="B99" s="43" t="n">
+        <v>1332318</v>
+      </c>
+      <c r="C99" s="47" t="n">
+        <v>1332318</v>
+      </c>
+      <c r="D99" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" s="63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" s="43" t="n">
+        <v>1326082</v>
+      </c>
+      <c r="G99" s="45" t="n">
+        <v>1.004702574953887</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="51" t="inlineStr">
+        <is>
           <t>LIM-LD</t>
         </is>
       </c>
-      <c r="B89" s="47" t="n">
-        <v>2174774</v>
-      </c>
-      <c r="C89" s="43" t="n">
+      <c r="B100" s="43" t="n">
+        <v>1323632</v>
+      </c>
+      <c r="C100" s="47" t="n">
+        <v>994280</v>
+      </c>
+      <c r="D100" s="52" t="n">
+        <v>-329352</v>
+      </c>
+      <c r="E100" s="64" t="n">
+        <v>-0.248824446674</v>
+      </c>
+      <c r="F100" s="43" t="n">
         <v>992213</v>
       </c>
-      <c r="D89" s="45" t="n">
-        <v>2.191841872662422</v>
-      </c>
-      <c r="E89" s="70" t="inlineStr">
-        <is>
-          <t>above target by design — surplus fleet hauls LD</t>
-        </is>
+      <c r="G100" s="45" t="n">
+        <v>1.002083222050104</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="65" t="inlineStr">
+        <is>
+          <t>of which SAP stocked at FeNi KM0 (KR 51 DT + TF 50 DT reallocated)</t>
+        </is>
+      </c>
+      <c r="B101" s="66" t="n"/>
+      <c r="C101" s="61" t="n">
+        <v>384923</v>
+      </c>
+      <c r="D101" s="61" t="n">
+        <v>384923</v>
+      </c>
+      <c r="E101" s="70" t="inlineStr">
+        <is>
+          <t>inside the SAP row</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="60" t="inlineStr">
+        <is>
+          <t>TOTAL moved</t>
+        </is>
+      </c>
+      <c r="B102" s="47" t="n">
+        <v>4971433</v>
+      </c>
+      <c r="C102" s="47" t="n">
+        <v>5027004</v>
+      </c>
+      <c r="D102" s="61" t="n">
+        <v>55571</v>
+      </c>
+      <c r="E102" s="62" t="n">
+        <v>0.0111780647551722</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="40" t="inlineStr">
+        <is>
+          <t>Scenario 3.1.2 — December</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="41" t="inlineStr"/>
+      <c r="B106" s="41" t="inlineStr">
+        <is>
+          <t>Target t</t>
+        </is>
+      </c>
+      <c r="C106" s="41" t="inlineStr">
+        <is>
+          <t>Predicted t</t>
+        </is>
+      </c>
+      <c r="D106" s="41" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="E106" s="41" t="inlineStr">
+        <is>
+          <t>Fleet DT</t>
+        </is>
+      </c>
+      <c r="F106" s="41" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="42" t="inlineStr">
+        <is>
+          <t>As frozen</t>
+        </is>
+      </c>
+      <c r="B107" s="43" t="n">
+        <v>4810381</v>
+      </c>
+      <c r="C107" s="43" t="n">
+        <v>5045234</v>
+      </c>
+      <c r="D107" s="44" t="n">
+        <v>1.048822120326852</v>
+      </c>
+      <c r="E107" s="43" t="n">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="42" t="inlineStr">
+        <is>
+          <t>OPTION 1 · park 59 DT (total month → 100.0%)</t>
+        </is>
+      </c>
+      <c r="B108" s="43" t="n">
+        <v>4810381</v>
+      </c>
+      <c r="C108" s="43" t="n">
+        <v>4811739</v>
+      </c>
+      <c r="D108" s="45" t="n">
+        <v>1.000282306120867</v>
+      </c>
+      <c r="E108" s="43" t="n">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="42" t="inlineStr">
+        <is>
+          <t>OPTION 2 · re-dispatch 104 DT (LIM-LD → 100.0%)</t>
+        </is>
+      </c>
+      <c r="B109" s="43" t="n">
+        <v>4810381</v>
+      </c>
+      <c r="C109" s="43" t="n">
+        <v>5035551</v>
+      </c>
+      <c r="D109" s="46" t="n">
+        <v>1.046809182058552</v>
+      </c>
+      <c r="E109" s="43" t="n">
+        <v>1052</v>
+      </c>
+      <c r="F109" s="48" t="inlineStr">
+        <is>
+          <t>+ 395,746 t SAP stocked at FeNi KM0</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="49" t="inlineStr">
+        <is>
+          <t>Option 2 cut (sized so LIM-LD lands exactly on its line): TF&gt;POS 6 (RIM, LD): −86 DT @ 127.7 t/day/DT · TF&gt;POS 6 (SMA, LD): −18 DT @ 116.6 t/day/DT</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="50" t="inlineStr">
+        <is>
+          <t>OPTION 2 — full December plan (re-dispatched)</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="41" t="inlineStr">
+        <is>
+          <t>Route</t>
+        </is>
+      </c>
+      <c r="B113" s="41" t="inlineStr">
+        <is>
+          <t>Contractor</t>
+        </is>
+      </c>
+      <c r="C113" s="41" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="D113" s="41" t="inlineStr">
+        <is>
+          <t>DT before</t>
+        </is>
+      </c>
+      <c r="E113" s="41" t="inlineStr">
+        <is>
+          <t>DT after</t>
+        </is>
+      </c>
+      <c r="F113" s="41" t="inlineStr">
+        <is>
+          <t>Δ DT</t>
+        </is>
+      </c>
+      <c r="G113" s="41" t="inlineStr">
+        <is>
+          <t>t/day</t>
+        </is>
+      </c>
+      <c r="H113" s="41" t="inlineStr">
+        <is>
+          <t>t/month</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B114" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C114" s="51" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D114" s="43" t="n">
+        <v>233</v>
+      </c>
+      <c r="E114" s="43" t="n">
+        <v>233</v>
+      </c>
+      <c r="F114" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" s="43" t="n">
+        <v>24482</v>
+      </c>
+      <c r="H114" s="43" t="n">
+        <v>758942</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;POS 6</t>
+        </is>
+      </c>
+      <c r="B115" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C115" s="51" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D115" s="43" t="n">
+        <v>86</v>
+      </c>
+      <c r="E115" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" s="52" t="n">
+        <v>-86</v>
+      </c>
+      <c r="G115" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" s="43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;POS 6</t>
+        </is>
+      </c>
+      <c r="B116" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C116" s="51" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D116" s="43" t="n">
+        <v>43</v>
+      </c>
+      <c r="E116" s="47" t="n">
+        <v>25</v>
+      </c>
+      <c r="F116" s="52" t="n">
+        <v>-18</v>
+      </c>
+      <c r="G116" s="43" t="n">
+        <v>2915</v>
+      </c>
+      <c r="H116" s="43" t="n">
+        <v>90369</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B117" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C117" s="51" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D117" s="43" t="n">
+        <v>44</v>
+      </c>
+      <c r="E117" s="43" t="n">
+        <v>44</v>
+      </c>
+      <c r="F117" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G117" s="43" t="n">
+        <v>4618</v>
+      </c>
+      <c r="H117" s="43" t="n">
+        <v>143158</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="51" t="inlineStr">
+        <is>
+          <t>BLB&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B118" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C118" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D118" s="43" t="n">
+        <v>139</v>
+      </c>
+      <c r="E118" s="43" t="n">
+        <v>139</v>
+      </c>
+      <c r="F118" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G118" s="43" t="n">
+        <v>33859</v>
+      </c>
+      <c r="H118" s="43" t="n">
+        <v>1049629</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B119" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C119" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D119" s="43" t="n">
+        <v>62</v>
+      </c>
+      <c r="E119" s="43" t="n">
+        <v>62</v>
+      </c>
+      <c r="F119" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G119" s="43" t="n">
+        <v>6514</v>
+      </c>
+      <c r="H119" s="43" t="n">
+        <v>201934</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="51" t="inlineStr">
+        <is>
+          <t>KR&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B120" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C120" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D120" s="43" t="n">
+        <v>19</v>
+      </c>
+      <c r="E120" s="43" t="n">
+        <v>19</v>
+      </c>
+      <c r="F120" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G120" s="43" t="n">
+        <v>2590</v>
+      </c>
+      <c r="H120" s="43" t="n">
+        <v>80290</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="51" t="inlineStr">
+        <is>
+          <t>BLB&gt;FENI KM0</t>
+        </is>
+      </c>
+      <c r="B121" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C121" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D121" s="43" t="n">
+        <v>202</v>
+      </c>
+      <c r="E121" s="43" t="n">
+        <v>202</v>
+      </c>
+      <c r="F121" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G121" s="43" t="n">
+        <v>45786</v>
+      </c>
+      <c r="H121" s="43" t="n">
+        <v>1419366</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;FENI KM15</t>
+        </is>
+      </c>
+      <c r="B122" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C122" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D122" s="43" t="n">
+        <v>140</v>
+      </c>
+      <c r="E122" s="43" t="n">
+        <v>140</v>
+      </c>
+      <c r="F122" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G122" s="43" t="n">
+        <v>14847</v>
+      </c>
+      <c r="H122" s="43" t="n">
+        <v>460257</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="51" t="inlineStr">
+        <is>
+          <t>KR&gt;FENI KM15</t>
+        </is>
+      </c>
+      <c r="B123" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C123" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D123" s="43" t="n">
+        <v>49</v>
+      </c>
+      <c r="E123" s="43" t="n">
+        <v>49</v>
+      </c>
+      <c r="F123" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G123" s="43" t="n">
+        <v>7929</v>
+      </c>
+      <c r="H123" s="43" t="n">
+        <v>245799</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;POS 12</t>
+        </is>
+      </c>
+      <c r="B124" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C124" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D124" s="43" t="n">
+        <v>18</v>
+      </c>
+      <c r="E124" s="43" t="n">
+        <v>18</v>
+      </c>
+      <c r="F124" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G124" s="43" t="n">
+        <v>2045</v>
+      </c>
+      <c r="H124" s="43" t="n">
+        <v>63395</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="51" t="inlineStr">
+        <is>
+          <t>BLB&gt;POS 14</t>
+        </is>
+      </c>
+      <c r="B125" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C125" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D125" s="43" t="n">
+        <v>7</v>
+      </c>
+      <c r="E125" s="43" t="n">
+        <v>7</v>
+      </c>
+      <c r="F125" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G125" s="43" t="n">
+        <v>2044</v>
+      </c>
+      <c r="H125" s="43" t="n">
+        <v>63364</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="51" t="inlineStr">
+        <is>
+          <t>KR&gt;POS 12</t>
+        </is>
+      </c>
+      <c r="B126" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C126" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D126" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E126" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="F126" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G126" s="43" t="n">
+        <v>2042</v>
+      </c>
+      <c r="H126" s="43" t="n">
+        <v>63302</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="54" t="inlineStr">
+        <is>
+          <t>KR&gt;FENI KM0</t>
+        </is>
+      </c>
+      <c r="B127" s="54" t="inlineStr">
+        <is>
+          <t>reallocated</t>
+        </is>
+      </c>
+      <c r="C127" s="54" t="inlineStr">
+        <is>
+          <t>SAP (stock at FeNi KM0)</t>
+        </is>
+      </c>
+      <c r="D127" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E127" s="56" t="n">
+        <v>52</v>
+      </c>
+      <c r="F127" s="56" t="n">
+        <v>52</v>
+      </c>
+      <c r="G127" s="56" t="n">
+        <v>7049</v>
+      </c>
+      <c r="H127" s="56" t="n">
+        <v>218533</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="54" t="inlineStr">
+        <is>
+          <t>TF&gt;FENI KM0</t>
+        </is>
+      </c>
+      <c r="B128" s="54" t="inlineStr">
+        <is>
+          <t>reallocated</t>
+        </is>
+      </c>
+      <c r="C128" s="54" t="inlineStr">
+        <is>
+          <t>SAP (stock at FeNi KM0)</t>
+        </is>
+      </c>
+      <c r="D128" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E128" s="56" t="n">
+        <v>52</v>
+      </c>
+      <c r="F128" s="56" t="n">
+        <v>52</v>
+      </c>
+      <c r="G128" s="56" t="n">
+        <v>5717</v>
+      </c>
+      <c r="H128" s="56" t="n">
+        <v>177213</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="60" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D129" s="47" t="n">
+        <v>1052</v>
+      </c>
+      <c r="E129" s="47" t="n">
+        <v>1052</v>
+      </c>
+      <c r="H129" s="47" t="n">
+        <v>5035551</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="50" t="inlineStr">
+        <is>
+          <t>OPTION 2 — tonnage by material (December)</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="41" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="B132" s="41" t="inlineStr">
+        <is>
+          <t>BEFORE re-dispatch t/mo</t>
+        </is>
+      </c>
+      <c r="C132" s="41" t="inlineStr">
+        <is>
+          <t>AFTER re-dispatch t/mo</t>
+        </is>
+      </c>
+      <c r="D132" s="41" t="inlineStr">
+        <is>
+          <t>Δ t/mo</t>
+        </is>
+      </c>
+      <c r="E132" s="41" t="inlineStr">
+        <is>
+          <t>Change %</t>
+        </is>
+      </c>
+      <c r="F132" s="41" t="inlineStr">
+        <is>
+          <t>December TARGET t</t>
+        </is>
+      </c>
+      <c r="G132" s="41" t="inlineStr">
+        <is>
+          <t>Coverage after</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="42" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B133" s="43" t="n">
+        <v>2315483</v>
+      </c>
+      <c r="C133" s="47" t="n">
+        <v>2711229</v>
+      </c>
+      <c r="D133" s="61" t="n">
+        <v>395746</v>
+      </c>
+      <c r="E133" s="62" t="n">
+        <v>0.1709129369552702</v>
+      </c>
+      <c r="F133" s="43" t="n">
+        <v>2311213</v>
+      </c>
+      <c r="G133" s="45" t="n">
+        <v>1.1730762158226</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="B134" s="43" t="n">
+        <v>1331853</v>
+      </c>
+      <c r="C134" s="47" t="n">
+        <v>1331853</v>
+      </c>
+      <c r="D134" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" s="63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F134" s="43" t="n">
+        <v>1326082</v>
+      </c>
+      <c r="G134" s="45" t="n">
+        <v>1.004351917905529</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="51" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="B135" s="43" t="n">
+        <v>1397954</v>
+      </c>
+      <c r="C135" s="47" t="n">
+        <v>992469</v>
+      </c>
+      <c r="D135" s="52" t="n">
+        <v>-405485</v>
+      </c>
+      <c r="E135" s="64" t="n">
+        <v>-0.2900560390399112</v>
+      </c>
+      <c r="F135" s="43" t="n">
+        <v>992213</v>
+      </c>
+      <c r="G135" s="45" t="n">
+        <v>1.000258009116994</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="65" t="inlineStr">
+        <is>
+          <t>of which SAP stocked at FeNi KM0 (KR 52 DT + TF 52 DT reallocated)</t>
+        </is>
+      </c>
+      <c r="B136" s="66" t="n"/>
+      <c r="C136" s="61" t="n">
+        <v>395746</v>
+      </c>
+      <c r="D136" s="61" t="n">
+        <v>395746</v>
+      </c>
+      <c r="E136" s="70" t="inlineStr">
+        <is>
+          <t>inside the SAP row</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="60" t="inlineStr">
+        <is>
+          <t>TOTAL moved</t>
+        </is>
+      </c>
+      <c r="B137" s="47" t="n">
+        <v>5045290</v>
+      </c>
+      <c r="C137" s="47" t="n">
+        <v>5035551</v>
+      </c>
+      <c r="D137" s="52" t="n">
+        <v>-9739</v>
+      </c>
+      <c r="E137" s="64" t="n">
+        <v>-0.001930315204874249</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="A101:B101"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A136:B136"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/scenario_comparison_dec_options.xlsx
+++ b/reports/scenario_comparison_dec_options.xlsx
@@ -24,7 +24,7 @@
     <numFmt numFmtId="167" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="168" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="53">
+  <fonts count="55">
     <font>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -380,6 +380,17 @@
       <name val="Arial"/>
       <color rgb="008A6100"/>
       <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="000F4C81"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="001A2332"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="40">
@@ -974,7 +985,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1165,6 +1176,10 @@
     </xf>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1578,436 +1593,561 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K26"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <dimension ref="A1:H33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23.2" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Four scenarios · Sep–Dec 2026 · one clock (sales targets)</t>
+    <row r="1">
+      <c r="A1" s="38" t="inlineStr">
+        <is>
+          <t>Four scenarios · Sep–Dec 2026 · refrozen at the full 1,281-DT December pool</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr">
-        <is>
-          <t>3.0 = base mining plan · 3.1 = +330 kt/month BLB LIM Oct–Dec (the sales table already contains it). .1 = all leftover LD trucks to HUAFEI/BSE · .2 = half to POS 6 from October. All targets are the sales lines distributed over months in the plan shape.</t>
+      <c r="A2" s="39" t="inlineStr">
+        <is>
+          <t>3.0 = base mining plan · 3.1 = +330 kt/mo BLB LIM Oct–Dec · .1 = all leftover LD to HUAFEI/BSE · .2 = half the TF LD trucks to POS 6 from October (exact 50/50). Every truck in the matrix pool works: SAP 100%, LIM-TOS 100%, all remaining DT haul LIM-LD past its target.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="41" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="41" t="inlineStr">
         <is>
           <t>Year sales target</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="41" t="inlineStr">
         <is>
           <t>Predicted plan</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="41" t="inlineStr">
         <is>
           <t>Coverage</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="41" t="inlineStr">
         <is>
           <t>SAP %</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F4" s="41" t="inlineStr">
         <is>
           <t>LIM-TOS %</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="41" t="inlineStr">
         <is>
           <t>LIM-LD %</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
+      <c r="H4" s="41" t="inlineStr">
         <is>
           <t>Dec DT</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="30" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="42" t="inlineStr">
         <is>
           <t>3.0.1</t>
         </is>
       </c>
-      <c r="B5" s="31" t="n">
+      <c r="B5" s="43" t="n">
         <v>17003193</v>
       </c>
-      <c r="C5" s="31" t="n">
-        <v>16453539</v>
-      </c>
-      <c r="D5" s="36" t="n">
-        <v>0.968</v>
-      </c>
-      <c r="E5" s="37" t="n">
-        <v>1.00547485908476</v>
-      </c>
-      <c r="F5" s="37" t="n">
-        <v>1.00502547667923</v>
-      </c>
-      <c r="G5" s="36" t="n">
-        <v>0.921500002750741</v>
-      </c>
-      <c r="H5" s="31" t="n">
-        <v>1190</v>
-      </c>
-    </row>
-    <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="30" t="inlineStr">
+      <c r="C5" s="43" t="n">
+        <v>16738008</v>
+      </c>
+      <c r="D5" s="71" t="n">
+        <v>0.9840000000000001</v>
+      </c>
+      <c r="E5" s="45" t="n">
+        <v>1.006</v>
+      </c>
+      <c r="F5" s="45" t="n">
+        <v>1.005</v>
+      </c>
+      <c r="G5" s="71" t="n">
+        <v>0.958</v>
+      </c>
+      <c r="H5" s="47" t="n">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="42" t="inlineStr">
         <is>
           <t>3.0.2</t>
         </is>
       </c>
-      <c r="B6" s="31" t="n">
+      <c r="B6" s="43" t="n">
         <v>17003193</v>
       </c>
-      <c r="C6" s="31" t="n">
-        <v>16941732</v>
-      </c>
-      <c r="D6" s="36" t="n">
-        <v>0.996</v>
-      </c>
-      <c r="E6" s="37" t="n">
-        <v>1.00547485908476</v>
-      </c>
-      <c r="F6" s="37" t="n">
-        <v>1.00587063561705</v>
-      </c>
-      <c r="G6" s="36" t="n">
-        <v>0.985040159511552</v>
-      </c>
-      <c r="H6" s="31" t="n">
-        <v>1190</v>
-      </c>
-    </row>
-    <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="30" t="inlineStr">
+      <c r="C6" s="43" t="n">
+        <v>17286699</v>
+      </c>
+      <c r="D6" s="45" t="n">
+        <v>1.017</v>
+      </c>
+      <c r="E6" s="45" t="n">
+        <v>1.006</v>
+      </c>
+      <c r="F6" s="45" t="n">
+        <v>1.006</v>
+      </c>
+      <c r="G6" s="45" t="n">
+        <v>1.029</v>
+      </c>
+      <c r="H6" s="47" t="n">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="42" t="inlineStr">
         <is>
           <t>3.1.1</t>
         </is>
       </c>
-      <c r="B7" s="31" t="n">
+      <c r="B7" s="43" t="n">
         <v>17003193</v>
       </c>
-      <c r="C7" s="31" t="n">
-        <v>16580201</v>
-      </c>
-      <c r="D7" s="36" t="n">
-        <v>0.975</v>
-      </c>
-      <c r="E7" s="37" t="n">
-        <v>1.00506182714001</v>
-      </c>
-      <c r="F7" s="37" t="n">
-        <v>1.00347592701264</v>
-      </c>
-      <c r="G7" s="36" t="n">
-        <v>0.92954674272979</v>
-      </c>
-      <c r="H7" s="31" t="n">
-        <v>1052</v>
-      </c>
-    </row>
-    <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="30" t="inlineStr">
+      <c r="C7" s="43" t="n">
+        <v>17296329</v>
+      </c>
+      <c r="D7" s="45" t="n">
+        <v>1.017</v>
+      </c>
+      <c r="E7" s="45" t="n">
+        <v>1.004</v>
+      </c>
+      <c r="F7" s="45" t="n">
+        <v>1.003</v>
+      </c>
+      <c r="G7" s="45" t="n">
+        <v>1.039</v>
+      </c>
+      <c r="H7" s="47" t="n">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="42" t="inlineStr">
         <is>
           <t>3.1.2</t>
         </is>
       </c>
-      <c r="B8" s="31" t="n">
+      <c r="B8" s="43" t="n">
         <v>17003193</v>
       </c>
-      <c r="C8" s="31" t="n">
-        <v>16974809</v>
-      </c>
-      <c r="D8" s="36" t="n">
-        <v>0.998</v>
-      </c>
-      <c r="E8" s="37" t="n">
-        <v>1.00506182714001</v>
-      </c>
-      <c r="F8" s="37" t="n">
-        <v>1.00347161685453</v>
-      </c>
-      <c r="G8" s="36" t="n">
-        <v>0.9889440672961179</v>
-      </c>
-      <c r="H8" s="31" t="n">
-        <v>1052</v>
-      </c>
-    </row>
-    <row r="11" ht="19.2" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Month by month — Predicted % of the distributed sales target</t>
+      <c r="C8" s="43" t="n">
+        <v>17791858</v>
+      </c>
+      <c r="D8" s="45" t="n">
+        <v>1.046</v>
+      </c>
+      <c r="E8" s="45" t="n">
+        <v>1.004</v>
+      </c>
+      <c r="F8" s="45" t="n">
+        <v>1.003</v>
+      </c>
+      <c r="G8" s="45" t="n">
+        <v>1.113</v>
+      </c>
+      <c r="H8" s="47" t="n">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="50" t="inlineStr">
+        <is>
+          <t>Month by month — Predicted ÷ target</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="41" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="41" t="inlineStr">
         <is>
           <t>3.0.1</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" s="41" t="inlineStr">
         <is>
           <t>3.0.2</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D12" s="41" t="inlineStr">
         <is>
           <t>3.1.1</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E12" s="41" t="inlineStr">
         <is>
           <t>3.1.2</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="34" t="inlineStr">
+      <c r="A13" s="42" t="inlineStr">
         <is>
           <t>Sep</t>
         </is>
       </c>
-      <c r="B13" s="36" t="n">
-        <v>0.962</v>
-      </c>
-      <c r="C13" s="36" t="n">
-        <v>0.962</v>
-      </c>
-      <c r="D13" s="36" t="n">
-        <v>0.962</v>
-      </c>
-      <c r="E13" s="36" t="n">
-        <v>0.962</v>
+      <c r="B13" s="45" t="n">
+        <v>1.045482521411984</v>
+      </c>
+      <c r="C13" s="45" t="n">
+        <v>1.045482521411984</v>
+      </c>
+      <c r="D13" s="45" t="n">
+        <v>1.045482521411984</v>
+      </c>
+      <c r="E13" s="45" t="n">
+        <v>1.045482521411984</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="34" t="inlineStr">
+      <c r="A14" s="42" t="inlineStr">
         <is>
           <t>Oct</t>
         </is>
       </c>
-      <c r="B14" s="36" t="n">
-        <v>0.9320000000000001</v>
-      </c>
-      <c r="C14" s="36" t="n">
-        <v>0.971</v>
-      </c>
-      <c r="D14" s="36" t="n">
-        <v>0.9350000000000001</v>
-      </c>
-      <c r="E14" s="36" t="n">
-        <v>0.968</v>
+      <c r="B14" s="45" t="n">
+        <v>1.012856749072166</v>
+      </c>
+      <c r="C14" s="45" t="n">
+        <v>1.055805550922092</v>
+      </c>
+      <c r="D14" s="45" t="n">
+        <v>1.016155521828965</v>
+      </c>
+      <c r="E14" s="45" t="n">
+        <v>1.051434176532733</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="34" t="inlineStr">
+      <c r="A15" s="42" t="inlineStr">
         <is>
           <t>Nov</t>
         </is>
       </c>
-      <c r="B15" s="36" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C15" s="36" t="n">
-        <v>0.988</v>
-      </c>
-      <c r="D15" s="36" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="E15" s="36" t="n">
-        <v>0.994</v>
+      <c r="B15" s="45" t="n">
+        <v>1.033122002370932</v>
+      </c>
+      <c r="C15" s="45" t="n">
+        <v>1.074038091902804</v>
+      </c>
+      <c r="D15" s="45" t="n">
+        <v>1.043424413593518</v>
+      </c>
+      <c r="E15" s="45" t="n">
+        <v>1.079733218673122</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="34" t="inlineStr">
+      <c r="A16" s="42" t="inlineStr">
         <is>
           <t>Dec</t>
         </is>
       </c>
-      <c r="B16" s="37" t="n">
-        <v>1.017</v>
-      </c>
-      <c r="C16" s="37" t="n">
-        <v>1.041</v>
-      </c>
-      <c r="D16" s="37" t="n">
-        <v>1.033</v>
-      </c>
-      <c r="E16" s="37" t="n">
-        <v>1.049</v>
+      <c r="B16" s="45" t="n">
+        <v>1.099858328904862</v>
+      </c>
+      <c r="C16" s="45" t="n">
+        <v>1.137358183954899</v>
+      </c>
+      <c r="D16" s="45" t="n">
+        <v>1.09793766371253</v>
+      </c>
+      <c r="E16" s="45" t="n">
+        <v>1.131672700225648</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="14" t="inlineStr">
-        <is>
-          <t>Reading: every month judges its share of the sales target. December is the only month above 100% in all four scenarios — the December sheet gives the two options to land it at exactly 100%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="19.2" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>Month by month — Predicted tonnes</t>
+      <c r="A18" s="49" t="inlineStr">
+        <is>
+          <t>Reading: every month is now run with its whole fleet, so coverage is at or above 100% from October on. September is short because the matrix only fields 581 DT that month.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="50" t="inlineStr">
+        <is>
+          <t>Month by month — Predicted plan t</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="41" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="41" t="inlineStr">
         <is>
           <t>3.0.1</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C21" s="41" t="inlineStr">
         <is>
           <t>3.0.2</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D21" s="41" t="inlineStr">
         <is>
           <t>3.1.1</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E21" s="41" t="inlineStr">
         <is>
           <t>3.1.2</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="34" t="inlineStr">
+      <c r="A22" s="42" t="inlineStr">
         <is>
           <t>Sep</t>
         </is>
       </c>
-      <c r="B22" s="31" t="n">
+      <c r="B22" s="43" t="n">
         <v>2381536</v>
       </c>
-      <c r="C22" s="31" t="n">
+      <c r="C22" s="43" t="n">
         <v>2381536</v>
       </c>
-      <c r="D22" s="31" t="n">
+      <c r="D22" s="43" t="n">
         <v>2381536</v>
       </c>
-      <c r="E22" s="31" t="n">
+      <c r="E22" s="43" t="n">
         <v>2381536</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="34" t="inlineStr">
+      <c r="A23" s="42" t="inlineStr">
         <is>
           <t>Oct</t>
         </is>
       </c>
-      <c r="B23" s="31" t="n">
+      <c r="B23" s="43" t="n">
         <v>3722205</v>
       </c>
-      <c r="C23" s="31" t="n">
+      <c r="C23" s="43" t="n">
         <v>3880040</v>
       </c>
-      <c r="D23" s="31" t="n">
+      <c r="D23" s="43" t="n">
         <v>3912780</v>
       </c>
-      <c r="E23" s="31" t="n">
+      <c r="E23" s="43" t="n">
         <v>4048623</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="34" t="inlineStr">
+      <c r="A24" s="42" t="inlineStr">
         <is>
           <t>Nov</t>
         </is>
       </c>
-      <c r="B24" s="31" t="n">
+      <c r="B24" s="43" t="n">
         <v>5133077</v>
       </c>
-      <c r="C24" s="31" t="n">
+      <c r="C24" s="43" t="n">
         <v>5336369</v>
       </c>
-      <c r="D24" s="31" t="n">
+      <c r="D24" s="43" t="n">
         <v>5314484</v>
       </c>
-      <c r="E24" s="31" t="n">
+      <c r="E24" s="43" t="n">
         <v>5499416</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="34" t="inlineStr">
+      <c r="A25" s="42" t="inlineStr">
         <is>
           <t>Dec</t>
         </is>
       </c>
-      <c r="B25" s="31" t="n">
-        <v>5216721</v>
-      </c>
-      <c r="C25" s="31" t="n">
-        <v>5343787</v>
-      </c>
-      <c r="D25" s="31" t="n">
-        <v>4971401</v>
-      </c>
-      <c r="E25" s="31" t="n">
-        <v>5045234</v>
+      <c r="B25" s="43" t="n">
+        <v>5501190</v>
+      </c>
+      <c r="C25" s="43" t="n">
+        <v>5688754</v>
+      </c>
+      <c r="D25" s="43" t="n">
+        <v>5687529</v>
+      </c>
+      <c r="E25" s="43" t="n">
+        <v>5862283</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="34" t="inlineStr">
+      <c r="A26" s="60" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B26" s="35" t="n">
-        <v>16453539</v>
-      </c>
-      <c r="C26" s="35" t="n">
-        <v>16941732</v>
-      </c>
-      <c r="D26" s="35" t="n">
-        <v>16580201</v>
-      </c>
-      <c r="E26" s="35" t="n">
-        <v>16974809</v>
+      <c r="B26" s="47" t="n">
+        <v>16738008</v>
+      </c>
+      <c r="C26" s="47" t="n">
+        <v>17286699</v>
+      </c>
+      <c r="D26" s="47" t="n">
+        <v>17296329</v>
+      </c>
+      <c r="E26" s="47" t="n">
+        <v>17791858</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="50" t="inlineStr">
+        <is>
+          <t>Year tonnage by material (t) — predicted vs sales line</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="41" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="B29" s="41" t="inlineStr">
+        <is>
+          <t>Sales line</t>
+        </is>
+      </c>
+      <c r="C29" s="41" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="D29" s="41" t="inlineStr">
+        <is>
+          <t>3.0.2</t>
+        </is>
+      </c>
+      <c r="E29" s="41" t="inlineStr">
+        <is>
+          <t>3.1.1</t>
+        </is>
+      </c>
+      <c r="F29" s="41" t="inlineStr">
+        <is>
+          <t>3.1.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="42" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B30" s="43" t="n">
+        <v>5718686</v>
+      </c>
+      <c r="C30" s="43" t="n">
+        <v>5754583</v>
+      </c>
+      <c r="D30" s="43" t="n">
+        <v>5754366</v>
+      </c>
+      <c r="E30" s="43" t="n">
+        <v>5740906</v>
+      </c>
+      <c r="F30" s="43" t="n">
+        <v>5740906</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="42" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="B31" s="43" t="n">
+        <v>3650201</v>
+      </c>
+      <c r="C31" s="43" t="n">
+        <v>3667243</v>
+      </c>
+      <c r="D31" s="43" t="n">
+        <v>3672901</v>
+      </c>
+      <c r="E31" s="43" t="n">
+        <v>4652858</v>
+      </c>
+      <c r="F31" s="43" t="n">
+        <v>4655256</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="42" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="B32" s="43" t="n">
+        <v>7634306</v>
+      </c>
+      <c r="C32" s="43" t="n">
+        <v>7316183</v>
+      </c>
+      <c r="D32" s="43" t="n">
+        <v>7859393</v>
+      </c>
+      <c r="E32" s="43" t="n">
+        <v>6902523</v>
+      </c>
+      <c r="F32" s="43" t="n">
+        <v>7395695</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="60" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B33" s="47" t="n">
+        <v>17003193</v>
+      </c>
+      <c r="C33" s="47" t="n">
+        <v>16738008</v>
+      </c>
+      <c r="D33" s="47" t="n">
+        <v>17286699</v>
+      </c>
+      <c r="E33" s="47" t="n">
+        <v>17296329</v>
+      </c>
+      <c r="F33" s="47" t="n">
+        <v>17791858</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A18:I18"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3923,112 +4063,104 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <dimension ref="A1:A19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="110" customWidth="1" min="1" max="1"/>
+    <col width="140" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23.2" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="73" t="inlineStr">
         <is>
           <t>Insights</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>1 · The scenarios are separated by LD, nothing else.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="42" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>SAP and LIM-TOS clear their sales lines in all four scenarios (100.3–100.5%). The whole difference between plans is how much LIM-LD the leftover fleet can move: 92.2–93.0% of its line. TF&gt;HUAFEI is the binding corridor.</t>
+      <c r="A3" s="50" t="inlineStr">
+        <is>
+          <t>1 · Every truck now works, so the year clears its line in three of four scenarios.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="74" t="inlineStr">
+        <is>
+          <t>With the full December pool fielded (1,281 DT: RIM 961 + SMA 320) the year predicts 16,738,008 / 17,286,699 / 17,296,329 / 17,791,858 t — 98.4%, 101.7%, 101.7% and 104.6% of the 17,003,193 t sales line. Only 3.0.1 stays just under.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>2 · The .2 split scenarios move more total tonnes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="42" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>3.0.2 predicts ~488 kt more than 3.0.1 (97.7% vs 96.8% of 17.0 Mt); 3.1.2 ~395 kt more than 3.1.1. Splitting leftover LD trucks to POS 6 relieves the saturated HUAFEI corridor - the split is worth roughly half a million tonnes over the quarter.</t>
+      <c r="A6" s="50" t="inlineStr">
+        <is>
+          <t>2 · The scenarios still differ only in LIM-LD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="74" t="inlineStr">
+        <is>
+          <t>SAP and LIM-TOS clear their lines in all four (99.9-100.6%). The whole spread between plans is how much LIM-LD the leftover fleet moves — and since the surplus now rides LD by rule, LD is where the extra tonnage lands.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>3 · December is the only month with slack.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="42" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Sep-Nov run 93-97% of their distributed sales share in every scenario; December runs 101.7-104.9%. The fleet grows to 1,190-1,280 DT while the remaining target shrinks - December has spare trucks.</t>
+      <c r="A9" s="50" t="inlineStr">
+        <is>
+          <t>3 · The .2 split is worth roughly half a megatonne a year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="74" t="inlineStr">
+        <is>
+          <t>3.0.2 predicts 548,691 t more than 3.0.1 and 3.1.2 predicts 495,529 t more than 3.1.1. Splitting the leftover TF LD trucks to POS 6 (exact 50/50 per contractor since the 2026-08-27 fix) relieves the saturated HUAFEI corridor.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>4 · Option 1 (park) reaches 100% but wastes capacity.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="42" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Parking 26-59 DT lands the total month at exactly 100.0%. Simple, but those trucks produce nothing and the plants build no buffer.</t>
+      <c r="A12" s="50" t="inlineStr">
+        <is>
+          <t>4 · The 3.1 uplift pays for itself.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" s="74" t="inlineStr">
+        <is>
+          <t>3.1 adds 330 kt/mo of BLB LIM TOS in Oct-Dec. It lifts LIM-TOS from 3.65 Mt to 4.64 Mt and still leaves enough fleet for LD, because the total haulage line is constant at 17.0 Mt — 3.0 simply carries the difference in LD.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>5 · Option 2 (re-dispatch to stock) is strictly better if KM0 can take stock.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="42" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Sized to the real goal — LIM-LD at exactly 100% — the cut is 56-104 DT, and re-dispatching them to KR&gt;FENI KM0 + TF&gt;FENI KM0 builds 213-396 kt of kilnable SAP stock at the plant in December while every sales line still clears (SAP rises to 109-117%). Requires KM0 to accept stock.</t>
+      <c r="A15" s="50" t="inlineStr">
+        <is>
+          <t>5 · December is the month with real slack.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" s="74" t="inlineStr">
+        <is>
+          <t>Sep-Nov are fleet-limited (581 / 931 / 1,280 DT from the matrix). December fields 1,281 and lands above every line: SAP ~100%, TOS ~100%, LD 127-224% depending on scenario. The surplus is deliberate — the target is a goal, not a ceiling.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>6 · Where the cuts come from.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="42" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>In .1 scenarios the donor is TF&gt;HUAFEI RIM (the biggest untensioned LD row); in .2 scenarios the donor is the TF&gt;POS 6 split flow (untargeted by design). No targeted route drops below its own line in any option.</t>
+      <c r="A18" s="50" t="inlineStr">
+        <is>
+          <t>6 · The road carries far more than our fleet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="32" customHeight="1">
+      <c r="A19" s="74" t="inlineStr">
+        <is>
+          <t>Road crowding is priced on 1,948 / 2,299 / 2,650 / 2,650 DT for Sep-Dec: our plan plus IWIP transit plus the 1,340-DT tenant register (POSITION 500, HUAFEI&gt;RSF 500, PMA 150, MHM 100, HSM 50, KR&gt;RSF 40). POS 12-KM15 runs RED on that basis in every month. Those trucks are not ours to schedule but they take the lane.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A16:H16"/>
-    <mergeCell ref="A10:H10"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A19:H19"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/scenario_comparison_dec_options.xlsx
+++ b/reports/scenario_comparison_dec_options.xlsx
@@ -24,7 +24,7 @@
     <numFmt numFmtId="167" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="168" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="55">
+  <fonts count="60">
     <font>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -390,6 +390,32 @@
     <font>
       <name val="Arial"/>
       <color rgb="001A2332"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="005B6B7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00A52929"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00A52929"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="001B7A41"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="000F4C81"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -985,7 +1011,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1180,6 +1206,34 @@
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="57" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="58" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="39" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="38" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="47" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2158,1901 +2212,1324 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G89"/>
+  <dimension ref="A1:H75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="38" t="inlineStr">
-        <is>
-          <t>December — the full 1,281-DT pool works (refrozen 2026-08-27, audited)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="39" t="inlineStr">
-        <is>
-          <t>Owner's rule: SAP 100%, LIM-TOS 100%, every remaining truck hauls LIM-LD — the target is a goal, not a ceiling. Ex-idle trucks (91 SMA in 3.0.x; 74 RIM + 155 SMA in 3.1.x) ride the TF LD rows. On .2 scenarios the POS 6 half-split is now exact (50/50 per contractor).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="40" t="inlineStr">
-        <is>
-          <t>Scenario 3.0.1 — December (frozen, 1,281 DT)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="41" t="inlineStr">
-        <is>
-          <t>Route</t>
-        </is>
-      </c>
-      <c r="B5" s="41" t="inlineStr">
-        <is>
-          <t>Contractor</t>
-        </is>
-      </c>
-      <c r="C5" s="41" t="inlineStr">
+      <c r="A1" s="73" t="inlineStr">
+        <is>
+          <t>December — what to do with the surplus fleet</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="75" t="inlineStr">
+        <is>
+          <t>AS FROZEN (today's plan): all 1,281 DT work. SAP and LIM-TOS land on their lines; every remaining truck hauls LIM-LD, so LD finishes 129-144% of its target. Nothing is parked, nothing is wasted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="75" t="inlineStr">
+        <is>
+          <t>OPTION 1 — PARK: take LD down to exactly 100% of its line and stand the freed trucks down. Simplest, lands the month on target, but those trucks earn nothing and the plants build no buffer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="75" t="inlineStr">
+        <is>
+          <t>OPTION 2 — RE-DISPATCH: take the same trucks off LD and send them to KR&gt;FENI KM0 and TF&gt;FENI KM0 instead. They haul kilnable SAP feed into the plant stockpile, so LD still lands at 100% and the tonnage is kept, not lost. Needs FeNi KM0 to accept stock.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="40" t="inlineStr">
+        <is>
+          <t>Scenario 3.0.1 — December</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="41" t="inlineStr"/>
+      <c r="B7" s="41" t="inlineStr">
+        <is>
+          <t>Fleet DT</t>
+        </is>
+      </c>
+      <c r="C7" s="41" t="inlineStr">
+        <is>
+          <t>SAP t/mo</t>
+        </is>
+      </c>
+      <c r="D7" s="41" t="inlineStr">
+        <is>
+          <t>LIM-TOS t/mo</t>
+        </is>
+      </c>
+      <c r="E7" s="41" t="inlineStr">
+        <is>
+          <t>LIM-LD t/mo</t>
+        </is>
+      </c>
+      <c r="F7" s="41" t="inlineStr">
+        <is>
+          <t>TOTAL t/mo</t>
+        </is>
+      </c>
+      <c r="G7" s="41" t="inlineStr">
+        <is>
+          <t>What happens</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="42" t="inlineStr">
+        <is>
+          <t>AS FROZEN</t>
+        </is>
+      </c>
+      <c r="B8" s="47" t="n">
+        <v>1281</v>
+      </c>
+      <c r="C8" s="43" t="n">
+        <v>2316351</v>
+      </c>
+      <c r="D8" s="43" t="n">
+        <v>1000029</v>
+      </c>
+      <c r="E8" s="68" t="n">
+        <v>2184818</v>
+      </c>
+      <c r="F8" s="47" t="n">
+        <v>5501198</v>
+      </c>
+      <c r="G8" s="76" t="inlineStr">
+        <is>
+          <t>LD runs 129% of its line — surplus fleet piles onto LD</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="42" t="inlineStr">
+        <is>
+          <t>OPTION 1 · park 151 DT</t>
+        </is>
+      </c>
+      <c r="B9" s="52" t="n">
+        <v>1130</v>
+      </c>
+      <c r="C9" s="43" t="n">
+        <v>2316351</v>
+      </c>
+      <c r="D9" s="43" t="n">
+        <v>1000029</v>
+      </c>
+      <c r="E9" s="47" t="n">
+        <v>1696480</v>
+      </c>
+      <c r="F9" s="52" t="n">
+        <v>5012860</v>
+      </c>
+      <c r="G9" s="77" t="inlineStr">
+        <is>
+          <t>LD → 100.0% · 488,338 t NOT hauled · 151 trucks idle</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="42" t="inlineStr">
+        <is>
+          <t>OPTION 2 · re-dispatch 151 DT</t>
+        </is>
+      </c>
+      <c r="B10" s="61" t="n">
+        <v>1281</v>
+      </c>
+      <c r="C10" s="61" t="n">
+        <v>2891575</v>
+      </c>
+      <c r="D10" s="43" t="n">
+        <v>1000029</v>
+      </c>
+      <c r="E10" s="47" t="n">
+        <v>1696480</v>
+      </c>
+      <c r="F10" s="61" t="n">
+        <v>5588084</v>
+      </c>
+      <c r="G10" s="78" t="inlineStr">
+        <is>
+          <t>LD → 100.0% · +575,224 t SAP stock at FeNi KM0 · no truck idle</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="41" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="D5" s="41" t="inlineStr">
-        <is>
-          <t>DT</t>
-        </is>
-      </c>
-      <c r="E5" s="41" t="inlineStr">
-        <is>
-          <t>t/day</t>
-        </is>
-      </c>
-      <c r="F5" s="41" t="inlineStr">
-        <is>
-          <t>t/month</t>
-        </is>
-      </c>
-      <c r="G5" s="41" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="67" t="inlineStr">
-        <is>
-          <t>TF&gt;HUAFEI</t>
-        </is>
-      </c>
-      <c r="B6" s="67" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C6" s="67" t="inlineStr">
+      <c r="B12" s="41" t="inlineStr">
+        <is>
+          <t>December TARGET t</t>
+        </is>
+      </c>
+      <c r="C12" s="41" t="inlineStr">
+        <is>
+          <t>As frozen</t>
+        </is>
+      </c>
+      <c r="D12" s="41" t="inlineStr">
+        <is>
+          <t>Option 1 (park)</t>
+        </is>
+      </c>
+      <c r="E12" s="41" t="inlineStr">
+        <is>
+          <t>Option 2 (re-dispatch)</t>
+        </is>
+      </c>
+      <c r="F12" s="41" t="inlineStr"/>
+      <c r="G12" s="41" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="42" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B13" s="43" t="n">
+        <v>2311205</v>
+      </c>
+      <c r="C13" s="45" t="n">
+        <v>1.002226544162028</v>
+      </c>
+      <c r="D13" s="45" t="n">
+        <v>1.002226544162028</v>
+      </c>
+      <c r="E13" s="45" t="n">
+        <v>1.251111260143518</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="42" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="B14" s="43" t="n">
+        <v>996092</v>
+      </c>
+      <c r="C14" s="45" t="n">
+        <v>1.003952446159592</v>
+      </c>
+      <c r="D14" s="45" t="n">
+        <v>1.003952446159592</v>
+      </c>
+      <c r="E14" s="45" t="n">
+        <v>1.003952446159592</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="42" t="inlineStr">
         <is>
           <t>LIM-LD</t>
         </is>
       </c>
-      <c r="D6" s="68" t="n">
-        <v>436</v>
-      </c>
-      <c r="E6" s="43" t="n">
-        <v>45485</v>
-      </c>
-      <c r="F6" s="43" t="n">
-        <v>1410035</v>
-      </c>
-      <c r="G6" s="69" t="inlineStr">
-        <is>
-          <t>LD — carries the surplus fleet</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="67" t="inlineStr">
-        <is>
-          <t>TF&gt;HUAFEI</t>
-        </is>
-      </c>
-      <c r="B7" s="67" t="inlineStr">
-        <is>
-          <t>SMA</t>
-        </is>
-      </c>
-      <c r="C7" s="67" t="inlineStr">
-        <is>
-          <t>LIM-LD</t>
-        </is>
-      </c>
-      <c r="D7" s="68" t="n">
-        <v>240</v>
-      </c>
-      <c r="E7" s="43" t="n">
-        <v>24993</v>
-      </c>
-      <c r="F7" s="43" t="n">
-        <v>774783</v>
-      </c>
-      <c r="G7" s="69" t="inlineStr">
-        <is>
-          <t>LD — carries the surplus fleet</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="51" t="inlineStr">
-        <is>
-          <t>BLB&gt;HUAFEI</t>
-        </is>
-      </c>
-      <c r="B8" s="51" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C8" s="51" t="inlineStr">
-        <is>
-          <t>LIM-TOS</t>
-        </is>
-      </c>
-      <c r="D8" s="43" t="n">
-        <v>95</v>
-      </c>
-      <c r="E8" s="43" t="n">
-        <v>23250</v>
-      </c>
-      <c r="F8" s="43" t="n">
-        <v>720750</v>
-      </c>
-      <c r="G8" s="72" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="51" t="inlineStr">
-        <is>
-          <t>TF&gt;HUAFEI</t>
-        </is>
-      </c>
-      <c r="B9" s="51" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C9" s="51" t="inlineStr">
-        <is>
-          <t>LIM-TOS</t>
-        </is>
-      </c>
-      <c r="D9" s="43" t="n">
-        <v>62</v>
-      </c>
-      <c r="E9" s="43" t="n">
-        <v>6468</v>
-      </c>
-      <c r="F9" s="43" t="n">
-        <v>200508</v>
-      </c>
-      <c r="G9" s="72" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="51" t="inlineStr">
-        <is>
-          <t>KR&gt;HUAFEI</t>
-        </is>
-      </c>
-      <c r="B10" s="51" t="inlineStr">
-        <is>
-          <t>SMA</t>
-        </is>
-      </c>
-      <c r="C10" s="51" t="inlineStr">
-        <is>
-          <t>LIM-TOS</t>
-        </is>
-      </c>
-      <c r="D10" s="43" t="n">
-        <v>19</v>
-      </c>
-      <c r="E10" s="43" t="n">
-        <v>2541</v>
-      </c>
-      <c r="F10" s="43" t="n">
-        <v>78771</v>
-      </c>
-      <c r="G10" s="72" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="51" t="inlineStr">
-        <is>
-          <t>BLB&gt;FENI KM0</t>
-        </is>
-      </c>
-      <c r="B11" s="51" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C11" s="51" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="D11" s="43" t="n">
-        <v>202</v>
-      </c>
-      <c r="E11" s="43" t="n">
-        <v>45786</v>
-      </c>
-      <c r="F11" s="43" t="n">
-        <v>1419366</v>
-      </c>
-      <c r="G11" s="72" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="51" t="inlineStr">
-        <is>
-          <t>TF&gt;FENI KM15</t>
-        </is>
-      </c>
-      <c r="B12" s="51" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C12" s="51" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="D12" s="43" t="n">
-        <v>141</v>
-      </c>
-      <c r="E12" s="43" t="n">
-        <v>14780</v>
-      </c>
-      <c r="F12" s="43" t="n">
-        <v>458180</v>
-      </c>
-      <c r="G12" s="72" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="51" t="inlineStr">
-        <is>
-          <t>KR&gt;FENI KM15</t>
-        </is>
-      </c>
-      <c r="B13" s="51" t="inlineStr">
-        <is>
-          <t>SMA</t>
-        </is>
-      </c>
-      <c r="C13" s="51" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="D13" s="43" t="n">
-        <v>50</v>
-      </c>
-      <c r="E13" s="43" t="n">
-        <v>7887</v>
-      </c>
-      <c r="F13" s="43" t="n">
-        <v>244497</v>
-      </c>
-      <c r="G13" s="72" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="51" t="inlineStr">
-        <is>
-          <t>KR&gt;POS 12</t>
-        </is>
-      </c>
-      <c r="B14" s="51" t="inlineStr">
-        <is>
-          <t>SMA</t>
-        </is>
-      </c>
-      <c r="C14" s="51" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="D14" s="43" t="n">
-        <v>11</v>
-      </c>
-      <c r="E14" s="43" t="n">
-        <v>2188</v>
-      </c>
-      <c r="F14" s="43" t="n">
-        <v>67828</v>
-      </c>
-      <c r="G14" s="72" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="51" t="inlineStr">
-        <is>
-          <t>BLB&gt;POS 14</t>
-        </is>
-      </c>
-      <c r="B15" s="51" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C15" s="51" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="D15" s="43" t="n">
-        <v>7</v>
-      </c>
-      <c r="E15" s="43" t="n">
-        <v>2044</v>
-      </c>
-      <c r="F15" s="43" t="n">
-        <v>63364</v>
-      </c>
-      <c r="G15" s="72" t="inlineStr"/>
+      <c r="B15" s="43" t="n">
+        <v>1694429</v>
+      </c>
+      <c r="C15" s="45" t="n">
+        <v>1.289412539563475</v>
+      </c>
+      <c r="D15" s="45" t="n">
+        <v>1.001210549611092</v>
+      </c>
+      <c r="E15" s="45" t="n">
+        <v>1.001210549611092</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="51" t="inlineStr">
-        <is>
-          <t>TF&gt;POS 12</t>
-        </is>
-      </c>
-      <c r="B16" s="51" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C16" s="51" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="D16" s="43" t="n">
-        <v>18</v>
-      </c>
-      <c r="E16" s="43" t="n">
-        <v>2036</v>
-      </c>
-      <c r="F16" s="43" t="n">
-        <v>63116</v>
-      </c>
-      <c r="G16" s="72" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="60" t="inlineStr">
-        <is>
-          <t>TOTAL (full matrix pool)</t>
-        </is>
-      </c>
-      <c r="D17" s="47" t="n">
-        <v>1281</v>
-      </c>
-      <c r="F17" s="47" t="n">
+      <c r="A16" s="60" t="inlineStr">
+        <is>
+          <t>TOTAL t/month</t>
+        </is>
+      </c>
+      <c r="B16" s="43" t="n">
+        <v>5001726</v>
+      </c>
+      <c r="C16" s="43" t="n">
         <v>5501198</v>
+      </c>
+      <c r="D16" s="79" t="n">
+        <v>5012860</v>
+      </c>
+      <c r="E16" s="80" t="n">
+        <v>5588084</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="81" t="inlineStr">
+        <is>
+          <t>Which trucks move (same 151 DT in both options)</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="41" t="inlineStr">
         <is>
+          <t>Taken off (LIM-LD)</t>
+        </is>
+      </c>
+      <c r="B19" s="41" t="inlineStr">
+        <is>
+          <t>Contractor</t>
+        </is>
+      </c>
+      <c r="C19" s="41" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="D19" s="41" t="inlineStr"/>
+      <c r="E19" s="41" t="inlineStr">
+        <is>
+          <t>Option 2 sends them to</t>
+        </is>
+      </c>
+      <c r="F19" s="41" t="inlineStr">
+        <is>
+          <t>Contractor</t>
+        </is>
+      </c>
+      <c r="G19" s="41" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="82" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B20" s="82" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C20" s="68" t="n">
+        <v>151</v>
+      </c>
+      <c r="D20" s="66" t="n"/>
+      <c r="E20" s="54" t="inlineStr">
+        <is>
+          <t>KR&gt;FENI KM0</t>
+        </is>
+      </c>
+      <c r="F20" s="83" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="G20" s="61" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="66" t="n"/>
+      <c r="B21" s="66" t="n"/>
+      <c r="C21" s="66" t="n"/>
+      <c r="D21" s="66" t="n"/>
+      <c r="E21" s="54" t="inlineStr">
+        <is>
+          <t>TF&gt;FENI KM0</t>
+        </is>
+      </c>
+      <c r="F21" s="83" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="G21" s="61" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="40" t="inlineStr">
+        <is>
+          <t>Scenario 3.0.2 — December</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="41" t="inlineStr"/>
+      <c r="B25" s="41" t="inlineStr">
+        <is>
+          <t>Fleet DT</t>
+        </is>
+      </c>
+      <c r="C25" s="41" t="inlineStr">
+        <is>
+          <t>SAP t/mo</t>
+        </is>
+      </c>
+      <c r="D25" s="41" t="inlineStr">
+        <is>
+          <t>LIM-TOS t/mo</t>
+        </is>
+      </c>
+      <c r="E25" s="41" t="inlineStr">
+        <is>
+          <t>LIM-LD t/mo</t>
+        </is>
+      </c>
+      <c r="F25" s="41" t="inlineStr">
+        <is>
+          <t>TOTAL t/mo</t>
+        </is>
+      </c>
+      <c r="G25" s="41" t="inlineStr">
+        <is>
+          <t>What happens</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="42" t="inlineStr">
+        <is>
+          <t>AS FROZEN</t>
+        </is>
+      </c>
+      <c r="B26" s="47" t="n">
+        <v>1281</v>
+      </c>
+      <c r="C26" s="43" t="n">
+        <v>2316134</v>
+      </c>
+      <c r="D26" s="43" t="n">
+        <v>1001827</v>
+      </c>
+      <c r="E26" s="68" t="n">
+        <v>2370849</v>
+      </c>
+      <c r="F26" s="47" t="n">
+        <v>5688810</v>
+      </c>
+      <c r="G26" s="76" t="inlineStr">
+        <is>
+          <t>LD runs 140% of its line — surplus fleet piles onto LD</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="42" t="inlineStr">
+        <is>
+          <t>OPTION 1 · park 172 DT</t>
+        </is>
+      </c>
+      <c r="B27" s="52" t="n">
+        <v>1109</v>
+      </c>
+      <c r="C27" s="43" t="n">
+        <v>2316134</v>
+      </c>
+      <c r="D27" s="43" t="n">
+        <v>1001827</v>
+      </c>
+      <c r="E27" s="47" t="n">
+        <v>1695626</v>
+      </c>
+      <c r="F27" s="52" t="n">
+        <v>5013587</v>
+      </c>
+      <c r="G27" s="77" t="inlineStr">
+        <is>
+          <t>LD → 100.0% · 675,223 t NOT hauled · 172 trucks idle</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="42" t="inlineStr">
+        <is>
+          <t>OPTION 2 · re-dispatch 172 DT</t>
+        </is>
+      </c>
+      <c r="B28" s="61" t="n">
+        <v>1281</v>
+      </c>
+      <c r="C28" s="61" t="n">
+        <v>2970904</v>
+      </c>
+      <c r="D28" s="43" t="n">
+        <v>1001827</v>
+      </c>
+      <c r="E28" s="47" t="n">
+        <v>1695626</v>
+      </c>
+      <c r="F28" s="61" t="n">
+        <v>5668357</v>
+      </c>
+      <c r="G28" s="78" t="inlineStr">
+        <is>
+          <t>LD → 100.0% · +654,770 t SAP stock at FeNi KM0 · no truck idle</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="41" t="inlineStr">
+        <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="B19" s="41" t="inlineStr">
-        <is>
-          <t>t/month (frozen)</t>
-        </is>
-      </c>
-      <c r="C19" s="41" t="inlineStr">
+      <c r="B30" s="41" t="inlineStr">
         <is>
           <t>December TARGET t</t>
         </is>
       </c>
-      <c r="D19" s="41" t="inlineStr">
-        <is>
-          <t>Coverage</t>
-        </is>
-      </c>
-      <c r="E19" s="41" t="inlineStr"/>
-      <c r="F19" s="41" t="inlineStr"/>
-      <c r="G19" s="41" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="51" t="inlineStr">
+      <c r="C30" s="41" t="inlineStr">
+        <is>
+          <t>As frozen</t>
+        </is>
+      </c>
+      <c r="D30" s="41" t="inlineStr">
+        <is>
+          <t>Option 1 (park)</t>
+        </is>
+      </c>
+      <c r="E30" s="41" t="inlineStr">
+        <is>
+          <t>Option 2 (re-dispatch)</t>
+        </is>
+      </c>
+      <c r="F30" s="41" t="inlineStr"/>
+      <c r="G30" s="41" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="42" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="B20" s="47" t="n">
-        <v>2316351</v>
-      </c>
-      <c r="C20" s="43" t="n">
-        <v>2311213</v>
-      </c>
-      <c r="D20" s="45" t="n">
-        <v>1.002223075069238</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="51" t="inlineStr">
+      <c r="B31" s="43" t="n">
+        <v>2311205</v>
+      </c>
+      <c r="C31" s="45" t="n">
+        <v>1.002132653745557</v>
+      </c>
+      <c r="D31" s="45" t="n">
+        <v>1.002132653745557</v>
+      </c>
+      <c r="E31" s="45" t="n">
+        <v>1.285434913822011</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="42" t="inlineStr">
         <is>
           <t>LIM-TOS</t>
         </is>
       </c>
-      <c r="B21" s="47" t="n">
-        <v>1000029</v>
-      </c>
-      <c r="C21" s="43" t="n">
-        <v>996084</v>
-      </c>
-      <c r="D21" s="45" t="n">
-        <v>1.003960509354633</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="51" t="inlineStr">
+      <c r="B32" s="43" t="n">
+        <v>996092</v>
+      </c>
+      <c r="C32" s="45" t="n">
+        <v>1.005757500311216</v>
+      </c>
+      <c r="D32" s="45" t="n">
+        <v>1.005757500311216</v>
+      </c>
+      <c r="E32" s="45" t="n">
+        <v>1.005757500311216</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="42" t="inlineStr">
         <is>
           <t>LIM-LD</t>
         </is>
       </c>
-      <c r="B22" s="47" t="n">
-        <v>2184818</v>
-      </c>
-      <c r="C22" s="43" t="n">
-        <v>1719964</v>
-      </c>
-      <c r="D22" s="45" t="n">
-        <v>1.270269610294169</v>
-      </c>
-      <c r="E22" s="70" t="inlineStr">
-        <is>
-          <t>above target by design</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="40" t="inlineStr">
-        <is>
-          <t>Scenario 3.0.2 — December (frozen, 1,281 DT)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="41" t="inlineStr">
-        <is>
-          <t>Route</t>
-        </is>
-      </c>
-      <c r="B26" s="41" t="inlineStr">
+      <c r="B33" s="43" t="n">
+        <v>1694429</v>
+      </c>
+      <c r="C33" s="45" t="n">
+        <v>1.399202327155638</v>
+      </c>
+      <c r="D33" s="45" t="n">
+        <v>1.00070651697837</v>
+      </c>
+      <c r="E33" s="45" t="n">
+        <v>1.00070651697837</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="60" t="inlineStr">
+        <is>
+          <t>TOTAL t/month</t>
+        </is>
+      </c>
+      <c r="B34" s="43" t="n">
+        <v>5001726</v>
+      </c>
+      <c r="C34" s="43" t="n">
+        <v>5688810</v>
+      </c>
+      <c r="D34" s="79" t="n">
+        <v>5013587</v>
+      </c>
+      <c r="E34" s="80" t="n">
+        <v>5668357</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="81" t="inlineStr">
+        <is>
+          <t>Which trucks move (same 172 DT in both options)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="41" t="inlineStr">
+        <is>
+          <t>Taken off (LIM-LD)</t>
+        </is>
+      </c>
+      <c r="B37" s="41" t="inlineStr">
         <is>
           <t>Contractor</t>
         </is>
       </c>
-      <c r="C26" s="41" t="inlineStr">
+      <c r="C37" s="41" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="D37" s="41" t="inlineStr"/>
+      <c r="E37" s="41" t="inlineStr">
+        <is>
+          <t>Option 2 sends them to</t>
+        </is>
+      </c>
+      <c r="F37" s="41" t="inlineStr">
+        <is>
+          <t>Contractor</t>
+        </is>
+      </c>
+      <c r="G37" s="41" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="82" t="inlineStr">
+        <is>
+          <t>TF&gt;POS 6</t>
+        </is>
+      </c>
+      <c r="B38" s="82" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C38" s="68" t="n">
+        <v>172</v>
+      </c>
+      <c r="D38" s="66" t="n"/>
+      <c r="E38" s="54" t="inlineStr">
+        <is>
+          <t>KR&gt;FENI KM0</t>
+        </is>
+      </c>
+      <c r="F38" s="83" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="G38" s="61" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="66" t="n"/>
+      <c r="B39" s="66" t="n"/>
+      <c r="C39" s="66" t="n"/>
+      <c r="D39" s="66" t="n"/>
+      <c r="E39" s="54" t="inlineStr">
+        <is>
+          <t>TF&gt;FENI KM0</t>
+        </is>
+      </c>
+      <c r="F39" s="83" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="G39" s="61" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="40" t="inlineStr">
+        <is>
+          <t>Scenario 3.1.1 — December</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="41" t="inlineStr"/>
+      <c r="B43" s="41" t="inlineStr">
+        <is>
+          <t>Fleet DT</t>
+        </is>
+      </c>
+      <c r="C43" s="41" t="inlineStr">
+        <is>
+          <t>SAP t/mo</t>
+        </is>
+      </c>
+      <c r="D43" s="41" t="inlineStr">
+        <is>
+          <t>LIM-TOS t/mo</t>
+        </is>
+      </c>
+      <c r="E43" s="41" t="inlineStr">
+        <is>
+          <t>LIM-LD t/mo</t>
+        </is>
+      </c>
+      <c r="F43" s="41" t="inlineStr">
+        <is>
+          <t>TOTAL t/mo</t>
+        </is>
+      </c>
+      <c r="G43" s="41" t="inlineStr">
+        <is>
+          <t>What happens</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="42" t="inlineStr">
+        <is>
+          <t>AS FROZEN</t>
+        </is>
+      </c>
+      <c r="B44" s="47" t="n">
+        <v>1281</v>
+      </c>
+      <c r="C44" s="43" t="n">
+        <v>2308694</v>
+      </c>
+      <c r="D44" s="43" t="n">
+        <v>1328877</v>
+      </c>
+      <c r="E44" s="68" t="n">
+        <v>2049937</v>
+      </c>
+      <c r="F44" s="47" t="n">
+        <v>5687508</v>
+      </c>
+      <c r="G44" s="76" t="inlineStr">
+        <is>
+          <t>LD runs 133% of its line — surplus fleet piles onto LD</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="42" t="inlineStr">
+        <is>
+          <t>OPTION 1 · park 156 DT</t>
+        </is>
+      </c>
+      <c r="B45" s="52" t="n">
+        <v>1125</v>
+      </c>
+      <c r="C45" s="43" t="n">
+        <v>2308694</v>
+      </c>
+      <c r="D45" s="43" t="n">
+        <v>1328877</v>
+      </c>
+      <c r="E45" s="47" t="n">
+        <v>1545209</v>
+      </c>
+      <c r="F45" s="52" t="n">
+        <v>5182780</v>
+      </c>
+      <c r="G45" s="77" t="inlineStr">
+        <is>
+          <t>LD → 100.0% · 504,728 t NOT hauled · 156 trucks idle</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="42" t="inlineStr">
+        <is>
+          <t>OPTION 2 · re-dispatch 156 DT</t>
+        </is>
+      </c>
+      <c r="B46" s="61" t="n">
+        <v>1281</v>
+      </c>
+      <c r="C46" s="61" t="n">
+        <v>2902555</v>
+      </c>
+      <c r="D46" s="43" t="n">
+        <v>1328877</v>
+      </c>
+      <c r="E46" s="47" t="n">
+        <v>1545209</v>
+      </c>
+      <c r="F46" s="61" t="n">
+        <v>5776641</v>
+      </c>
+      <c r="G46" s="78" t="inlineStr">
+        <is>
+          <t>LD → 100.0% · +593,861 t SAP stock at FeNi KM0 · no truck idle</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="41" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="D26" s="41" t="inlineStr">
+      <c r="B48" s="41" t="inlineStr">
+        <is>
+          <t>December TARGET t</t>
+        </is>
+      </c>
+      <c r="C48" s="41" t="inlineStr">
+        <is>
+          <t>As frozen</t>
+        </is>
+      </c>
+      <c r="D48" s="41" t="inlineStr">
+        <is>
+          <t>Option 1 (park)</t>
+        </is>
+      </c>
+      <c r="E48" s="41" t="inlineStr">
+        <is>
+          <t>Option 2 (re-dispatch)</t>
+        </is>
+      </c>
+      <c r="F48" s="41" t="inlineStr"/>
+      <c r="G48" s="41" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="42" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B49" s="43" t="n">
+        <v>2311205</v>
+      </c>
+      <c r="C49" s="84" t="n">
+        <v>0.9989135537522634</v>
+      </c>
+      <c r="D49" s="84" t="n">
+        <v>0.9989135537522634</v>
+      </c>
+      <c r="E49" s="45" t="n">
+        <v>1.255862115216954</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="42" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="B50" s="43" t="n">
+        <v>1326087</v>
+      </c>
+      <c r="C50" s="45" t="n">
+        <v>1.002103934357248</v>
+      </c>
+      <c r="D50" s="45" t="n">
+        <v>1.002103934357248</v>
+      </c>
+      <c r="E50" s="45" t="n">
+        <v>1.002103934357248</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="42" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="B51" s="43" t="n">
+        <v>1542901</v>
+      </c>
+      <c r="C51" s="45" t="n">
+        <v>1.32862510297161</v>
+      </c>
+      <c r="D51" s="45" t="n">
+        <v>1.00149570529207</v>
+      </c>
+      <c r="E51" s="45" t="n">
+        <v>1.00149570529207</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="60" t="inlineStr">
+        <is>
+          <t>TOTAL t/month</t>
+        </is>
+      </c>
+      <c r="B52" s="43" t="n">
+        <v>5180193</v>
+      </c>
+      <c r="C52" s="43" t="n">
+        <v>5687508</v>
+      </c>
+      <c r="D52" s="79" t="n">
+        <v>5182780</v>
+      </c>
+      <c r="E52" s="80" t="n">
+        <v>5776641</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="81" t="inlineStr">
+        <is>
+          <t>Which trucks move (same 156 DT in both options)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="41" t="inlineStr">
+        <is>
+          <t>Taken off (LIM-LD)</t>
+        </is>
+      </c>
+      <c r="B55" s="41" t="inlineStr">
+        <is>
+          <t>Contractor</t>
+        </is>
+      </c>
+      <c r="C55" s="41" t="inlineStr">
         <is>
           <t>DT</t>
         </is>
       </c>
-      <c r="E26" s="41" t="inlineStr">
-        <is>
-          <t>t/day</t>
-        </is>
-      </c>
-      <c r="F26" s="41" t="inlineStr">
-        <is>
-          <t>t/month</t>
-        </is>
-      </c>
-      <c r="G26" s="41" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="67" t="inlineStr">
+      <c r="D55" s="41" t="inlineStr"/>
+      <c r="E55" s="41" t="inlineStr">
+        <is>
+          <t>Option 2 sends them to</t>
+        </is>
+      </c>
+      <c r="F55" s="41" t="inlineStr">
+        <is>
+          <t>Contractor</t>
+        </is>
+      </c>
+      <c r="G55" s="41" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="82" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B56" s="82" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C56" s="68" t="n">
+        <v>156</v>
+      </c>
+      <c r="D56" s="66" t="n"/>
+      <c r="E56" s="54" t="inlineStr">
+        <is>
+          <t>KR&gt;FENI KM0</t>
+        </is>
+      </c>
+      <c r="F56" s="83" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="G56" s="61" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="66" t="n"/>
+      <c r="B57" s="66" t="n"/>
+      <c r="C57" s="66" t="n"/>
+      <c r="D57" s="66" t="n"/>
+      <c r="E57" s="54" t="inlineStr">
+        <is>
+          <t>TF&gt;FENI KM0</t>
+        </is>
+      </c>
+      <c r="F57" s="83" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="G57" s="61" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="40" t="inlineStr">
+        <is>
+          <t>Scenario 3.1.2 — December</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="41" t="inlineStr"/>
+      <c r="B61" s="41" t="inlineStr">
+        <is>
+          <t>Fleet DT</t>
+        </is>
+      </c>
+      <c r="C61" s="41" t="inlineStr">
+        <is>
+          <t>SAP t/mo</t>
+        </is>
+      </c>
+      <c r="D61" s="41" t="inlineStr">
+        <is>
+          <t>LIM-TOS t/mo</t>
+        </is>
+      </c>
+      <c r="E61" s="41" t="inlineStr">
+        <is>
+          <t>LIM-LD t/mo</t>
+        </is>
+      </c>
+      <c r="F61" s="41" t="inlineStr">
+        <is>
+          <t>TOTAL t/mo</t>
+        </is>
+      </c>
+      <c r="G61" s="41" t="inlineStr">
+        <is>
+          <t>What happens</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="42" t="inlineStr">
+        <is>
+          <t>AS FROZEN</t>
+        </is>
+      </c>
+      <c r="B62" s="47" t="n">
+        <v>1281</v>
+      </c>
+      <c r="C62" s="43" t="n">
+        <v>2308694</v>
+      </c>
+      <c r="D62" s="43" t="n">
+        <v>1330830</v>
+      </c>
+      <c r="E62" s="68" t="n">
+        <v>2222731</v>
+      </c>
+      <c r="F62" s="47" t="n">
+        <v>5862255</v>
+      </c>
+      <c r="G62" s="76" t="inlineStr">
+        <is>
+          <t>LD runs 144% of its line — surplus fleet piles onto LD</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="42" t="inlineStr">
+        <is>
+          <t>OPTION 1 · park 173 DT</t>
+        </is>
+      </c>
+      <c r="B63" s="52" t="n">
+        <v>1108</v>
+      </c>
+      <c r="C63" s="43" t="n">
+        <v>2308694</v>
+      </c>
+      <c r="D63" s="43" t="n">
+        <v>1330830</v>
+      </c>
+      <c r="E63" s="47" t="n">
+        <v>1543053</v>
+      </c>
+      <c r="F63" s="52" t="n">
+        <v>5182577</v>
+      </c>
+      <c r="G63" s="77" t="inlineStr">
+        <is>
+          <t>LD → 100.0% · 679,678 t NOT hauled · 173 trucks idle</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="42" t="inlineStr">
+        <is>
+          <t>OPTION 2 · re-dispatch 173 DT</t>
+        </is>
+      </c>
+      <c r="B64" s="61" t="n">
+        <v>1281</v>
+      </c>
+      <c r="C64" s="61" t="n">
+        <v>2967667</v>
+      </c>
+      <c r="D64" s="43" t="n">
+        <v>1330830</v>
+      </c>
+      <c r="E64" s="47" t="n">
+        <v>1543053</v>
+      </c>
+      <c r="F64" s="61" t="n">
+        <v>5841550</v>
+      </c>
+      <c r="G64" s="78" t="inlineStr">
+        <is>
+          <t>LD → 100.0% · +658,973 t SAP stock at FeNi KM0 · no truck idle</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="41" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="B66" s="41" t="inlineStr">
+        <is>
+          <t>December TARGET t</t>
+        </is>
+      </c>
+      <c r="C66" s="41" t="inlineStr">
+        <is>
+          <t>As frozen</t>
+        </is>
+      </c>
+      <c r="D66" s="41" t="inlineStr">
+        <is>
+          <t>Option 1 (park)</t>
+        </is>
+      </c>
+      <c r="E66" s="41" t="inlineStr">
+        <is>
+          <t>Option 2 (re-dispatch)</t>
+        </is>
+      </c>
+      <c r="F66" s="41" t="inlineStr"/>
+      <c r="G66" s="41" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="42" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B67" s="43" t="n">
+        <v>2311205</v>
+      </c>
+      <c r="C67" s="84" t="n">
+        <v>0.9989135537522634</v>
+      </c>
+      <c r="D67" s="84" t="n">
+        <v>0.9989135537522634</v>
+      </c>
+      <c r="E67" s="45" t="n">
+        <v>1.284034605324928</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="42" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="B68" s="43" t="n">
+        <v>1326087</v>
+      </c>
+      <c r="C68" s="45" t="n">
+        <v>1.003576688407322</v>
+      </c>
+      <c r="D68" s="45" t="n">
+        <v>1.003576688407322</v>
+      </c>
+      <c r="E68" s="45" t="n">
+        <v>1.003576688407322</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="42" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="B69" s="43" t="n">
+        <v>1542901</v>
+      </c>
+      <c r="C69" s="45" t="n">
+        <v>1.440618030580057</v>
+      </c>
+      <c r="D69" s="45" t="n">
+        <v>1.00009840990102</v>
+      </c>
+      <c r="E69" s="45" t="n">
+        <v>1.00009840990102</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="60" t="inlineStr">
+        <is>
+          <t>TOTAL t/month</t>
+        </is>
+      </c>
+      <c r="B70" s="43" t="n">
+        <v>5180193</v>
+      </c>
+      <c r="C70" s="43" t="n">
+        <v>5862255</v>
+      </c>
+      <c r="D70" s="79" t="n">
+        <v>5182577</v>
+      </c>
+      <c r="E70" s="80" t="n">
+        <v>5841550</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="81" t="inlineStr">
+        <is>
+          <t>Which trucks move (same 173 DT in both options)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="41" t="inlineStr">
+        <is>
+          <t>Taken off (LIM-LD)</t>
+        </is>
+      </c>
+      <c r="B73" s="41" t="inlineStr">
+        <is>
+          <t>Contractor</t>
+        </is>
+      </c>
+      <c r="C73" s="41" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="D73" s="41" t="inlineStr"/>
+      <c r="E73" s="41" t="inlineStr">
+        <is>
+          <t>Option 2 sends them to</t>
+        </is>
+      </c>
+      <c r="F73" s="41" t="inlineStr">
+        <is>
+          <t>Contractor</t>
+        </is>
+      </c>
+      <c r="G73" s="41" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="82" t="inlineStr">
         <is>
           <t>TF&gt;POS 6</t>
         </is>
       </c>
-      <c r="B27" s="67" t="inlineStr">
+      <c r="B74" s="82" t="inlineStr">
         <is>
           <t>RIM</t>
         </is>
       </c>
-      <c r="C27" s="67" t="inlineStr">
-        <is>
-          <t>LIM-LD</t>
-        </is>
-      </c>
-      <c r="D27" s="68" t="n">
-        <v>217</v>
-      </c>
-      <c r="E27" s="43" t="n">
-        <v>27480</v>
-      </c>
-      <c r="F27" s="43" t="n">
-        <v>851880</v>
-      </c>
-      <c r="G27" s="69" t="inlineStr">
-        <is>
-          <t>LD — carries the surplus fleet</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="67" t="inlineStr">
-        <is>
-          <t>TF&gt;HUAFEI</t>
-        </is>
-      </c>
-      <c r="B28" s="67" t="inlineStr">
+      <c r="C74" s="68" t="n">
+        <v>173</v>
+      </c>
+      <c r="D74" s="66" t="n"/>
+      <c r="E74" s="54" t="inlineStr">
+        <is>
+          <t>KR&gt;FENI KM0</t>
+        </is>
+      </c>
+      <c r="F74" s="83" t="inlineStr">
         <is>
           <t>RIM</t>
         </is>
       </c>
-      <c r="C28" s="67" t="inlineStr">
-        <is>
-          <t>LIM-LD</t>
-        </is>
-      </c>
-      <c r="D28" s="68" t="n">
-        <v>218</v>
-      </c>
-      <c r="E28" s="43" t="n">
-        <v>22667</v>
-      </c>
-      <c r="F28" s="43" t="n">
-        <v>702677</v>
-      </c>
-      <c r="G28" s="69" t="inlineStr">
-        <is>
-          <t>LD — carries the surplus fleet</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="67" t="inlineStr">
-        <is>
-          <t>TF&gt;POS 6</t>
-        </is>
-      </c>
-      <c r="B29" s="67" t="inlineStr">
-        <is>
-          <t>SMA</t>
-        </is>
-      </c>
-      <c r="C29" s="67" t="inlineStr">
-        <is>
-          <t>LIM-LD</t>
-        </is>
-      </c>
-      <c r="D29" s="68" t="n">
-        <v>120</v>
-      </c>
-      <c r="E29" s="43" t="n">
-        <v>13881</v>
-      </c>
-      <c r="F29" s="43" t="n">
-        <v>430311</v>
-      </c>
-      <c r="G29" s="69" t="inlineStr">
-        <is>
-          <t>LD — carries the surplus fleet</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="67" t="inlineStr">
-        <is>
-          <t>TF&gt;HUAFEI</t>
-        </is>
-      </c>
-      <c r="B30" s="67" t="inlineStr">
-        <is>
-          <t>SMA</t>
-        </is>
-      </c>
-      <c r="C30" s="67" t="inlineStr">
-        <is>
-          <t>LIM-LD</t>
-        </is>
-      </c>
-      <c r="D30" s="68" t="n">
-        <v>120</v>
-      </c>
-      <c r="E30" s="43" t="n">
-        <v>12451</v>
-      </c>
-      <c r="F30" s="43" t="n">
-        <v>385981</v>
-      </c>
-      <c r="G30" s="69" t="inlineStr">
-        <is>
-          <t>LD — carries the surplus fleet</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="51" t="inlineStr">
-        <is>
-          <t>BLB&gt;HUAFEI</t>
-        </is>
-      </c>
-      <c r="B31" s="51" t="inlineStr">
+      <c r="G74" s="61" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="66" t="n"/>
+      <c r="B75" s="66" t="n"/>
+      <c r="C75" s="66" t="n"/>
+      <c r="D75" s="66" t="n"/>
+      <c r="E75" s="54" t="inlineStr">
+        <is>
+          <t>TF&gt;FENI KM0</t>
+        </is>
+      </c>
+      <c r="F75" s="83" t="inlineStr">
         <is>
           <t>RIM</t>
         </is>
       </c>
-      <c r="C31" s="51" t="inlineStr">
-        <is>
-          <t>LIM-TOS</t>
-        </is>
-      </c>
-      <c r="D31" s="43" t="n">
-        <v>95</v>
-      </c>
-      <c r="E31" s="43" t="n">
-        <v>23250</v>
-      </c>
-      <c r="F31" s="43" t="n">
-        <v>720750</v>
-      </c>
-      <c r="G31" s="72" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="51" t="inlineStr">
-        <is>
-          <t>TF&gt;HUAFEI</t>
-        </is>
-      </c>
-      <c r="B32" s="51" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C32" s="51" t="inlineStr">
-        <is>
-          <t>LIM-TOS</t>
-        </is>
-      </c>
-      <c r="D32" s="43" t="n">
-        <v>63</v>
-      </c>
-      <c r="E32" s="43" t="n">
-        <v>6551</v>
-      </c>
-      <c r="F32" s="43" t="n">
-        <v>203081</v>
-      </c>
-      <c r="G32" s="72" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="51" t="inlineStr">
-        <is>
-          <t>KR&gt;HUAFEI</t>
-        </is>
-      </c>
-      <c r="B33" s="51" t="inlineStr">
-        <is>
-          <t>SMA</t>
-        </is>
-      </c>
-      <c r="C33" s="51" t="inlineStr">
-        <is>
-          <t>LIM-TOS</t>
-        </is>
-      </c>
-      <c r="D33" s="43" t="n">
-        <v>19</v>
-      </c>
-      <c r="E33" s="43" t="n">
-        <v>2516</v>
-      </c>
-      <c r="F33" s="43" t="n">
-        <v>77996</v>
-      </c>
-      <c r="G33" s="72" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="51" t="inlineStr">
-        <is>
-          <t>BLB&gt;FENI KM0</t>
-        </is>
-      </c>
-      <c r="B34" s="51" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C34" s="51" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="D34" s="43" t="n">
-        <v>202</v>
-      </c>
-      <c r="E34" s="43" t="n">
-        <v>45786</v>
-      </c>
-      <c r="F34" s="43" t="n">
-        <v>1419366</v>
-      </c>
-      <c r="G34" s="72" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="51" t="inlineStr">
-        <is>
-          <t>TF&gt;FENI KM15</t>
-        </is>
-      </c>
-      <c r="B35" s="51" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C35" s="51" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="D35" s="43" t="n">
-        <v>141</v>
-      </c>
-      <c r="E35" s="43" t="n">
-        <v>14775</v>
-      </c>
-      <c r="F35" s="43" t="n">
-        <v>458025</v>
-      </c>
-      <c r="G35" s="72" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="51" t="inlineStr">
-        <is>
-          <t>KR&gt;FENI KM15</t>
-        </is>
-      </c>
-      <c r="B36" s="51" t="inlineStr">
-        <is>
-          <t>SMA</t>
-        </is>
-      </c>
-      <c r="C36" s="51" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="D36" s="43" t="n">
-        <v>50</v>
-      </c>
-      <c r="E36" s="43" t="n">
-        <v>7885</v>
-      </c>
-      <c r="F36" s="43" t="n">
-        <v>244435</v>
-      </c>
-      <c r="G36" s="72" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="51" t="inlineStr">
-        <is>
-          <t>KR&gt;POS 12</t>
-        </is>
-      </c>
-      <c r="B37" s="51" t="inlineStr">
-        <is>
-          <t>SMA</t>
-        </is>
-      </c>
-      <c r="C37" s="51" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="D37" s="43" t="n">
-        <v>11</v>
-      </c>
-      <c r="E37" s="43" t="n">
-        <v>2188</v>
-      </c>
-      <c r="F37" s="43" t="n">
-        <v>67828</v>
-      </c>
-      <c r="G37" s="72" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="51" t="inlineStr">
-        <is>
-          <t>BLB&gt;POS 14</t>
-        </is>
-      </c>
-      <c r="B38" s="51" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C38" s="51" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="D38" s="43" t="n">
-        <v>7</v>
-      </c>
-      <c r="E38" s="43" t="n">
-        <v>2044</v>
-      </c>
-      <c r="F38" s="43" t="n">
-        <v>63364</v>
-      </c>
-      <c r="G38" s="72" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="51" t="inlineStr">
-        <is>
-          <t>TF&gt;POS 12</t>
-        </is>
-      </c>
-      <c r="B39" s="51" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C39" s="51" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="D39" s="43" t="n">
-        <v>18</v>
-      </c>
-      <c r="E39" s="43" t="n">
-        <v>2036</v>
-      </c>
-      <c r="F39" s="43" t="n">
-        <v>63116</v>
-      </c>
-      <c r="G39" s="72" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="60" t="inlineStr">
-        <is>
-          <t>TOTAL (full matrix pool)</t>
-        </is>
-      </c>
-      <c r="D40" s="47" t="n">
-        <v>1281</v>
-      </c>
-      <c r="F40" s="47" t="n">
-        <v>5688810</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="41" t="inlineStr">
-        <is>
-          <t>Material</t>
-        </is>
-      </c>
-      <c r="B42" s="41" t="inlineStr">
-        <is>
-          <t>t/month (frozen)</t>
-        </is>
-      </c>
-      <c r="C42" s="41" t="inlineStr">
-        <is>
-          <t>December TARGET t</t>
-        </is>
-      </c>
-      <c r="D42" s="41" t="inlineStr">
-        <is>
-          <t>Coverage</t>
-        </is>
-      </c>
-      <c r="E42" s="41" t="inlineStr"/>
-      <c r="F42" s="41" t="inlineStr"/>
-      <c r="G42" s="41" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="51" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="B43" s="47" t="n">
-        <v>2316134</v>
-      </c>
-      <c r="C43" s="43" t="n">
-        <v>2311213</v>
-      </c>
-      <c r="D43" s="45" t="n">
-        <v>1.002129184977758</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="51" t="inlineStr">
-        <is>
-          <t>LIM-TOS</t>
-        </is>
-      </c>
-      <c r="B44" s="47" t="n">
-        <v>1001827</v>
-      </c>
-      <c r="C44" s="43" t="n">
-        <v>996084</v>
-      </c>
-      <c r="D44" s="45" t="n">
-        <v>1.005765578003462</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="51" t="inlineStr">
-        <is>
-          <t>LIM-LD</t>
-        </is>
-      </c>
-      <c r="B45" s="47" t="n">
-        <v>2370849</v>
-      </c>
-      <c r="C45" s="43" t="n">
-        <v>1719964</v>
-      </c>
-      <c r="D45" s="45" t="n">
-        <v>1.378429432243931</v>
-      </c>
-      <c r="E45" s="70" t="inlineStr">
-        <is>
-          <t>above target by design</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="40" t="inlineStr">
-        <is>
-          <t>Scenario 3.1.1 — December (frozen, 1,281 DT)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="41" t="inlineStr">
-        <is>
-          <t>Route</t>
-        </is>
-      </c>
-      <c r="B49" s="41" t="inlineStr">
-        <is>
-          <t>Contractor</t>
-        </is>
-      </c>
-      <c r="C49" s="41" t="inlineStr">
-        <is>
-          <t>Material</t>
-        </is>
-      </c>
-      <c r="D49" s="41" t="inlineStr">
-        <is>
-          <t>DT</t>
-        </is>
-      </c>
-      <c r="E49" s="41" t="inlineStr">
-        <is>
-          <t>t/day</t>
-        </is>
-      </c>
-      <c r="F49" s="41" t="inlineStr">
-        <is>
-          <t>t/month</t>
-        </is>
-      </c>
-      <c r="G49" s="41" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="67" t="inlineStr">
-        <is>
-          <t>TF&gt;HUAFEI</t>
-        </is>
-      </c>
-      <c r="B50" s="67" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C50" s="67" t="inlineStr">
-        <is>
-          <t>LIM-LD</t>
-        </is>
-      </c>
-      <c r="D50" s="68" t="n">
-        <v>393</v>
-      </c>
-      <c r="E50" s="43" t="n">
-        <v>41017</v>
-      </c>
-      <c r="F50" s="43" t="n">
-        <v>1271527</v>
-      </c>
-      <c r="G50" s="69" t="inlineStr">
-        <is>
-          <t>LD — carries the surplus fleet</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="67" t="inlineStr">
-        <is>
-          <t>TF&gt;HUAFEI</t>
-        </is>
-      </c>
-      <c r="B51" s="67" t="inlineStr">
-        <is>
-          <t>SMA</t>
-        </is>
-      </c>
-      <c r="C51" s="67" t="inlineStr">
-        <is>
-          <t>LIM-LD</t>
-        </is>
-      </c>
-      <c r="D51" s="68" t="n">
-        <v>241</v>
-      </c>
-      <c r="E51" s="43" t="n">
-        <v>25110</v>
-      </c>
-      <c r="F51" s="43" t="n">
-        <v>778410</v>
-      </c>
-      <c r="G51" s="69" t="inlineStr">
-        <is>
-          <t>LD — carries the surplus fleet</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="51" t="inlineStr">
-        <is>
-          <t>BLB&gt;HUAFEI</t>
-        </is>
-      </c>
-      <c r="B52" s="51" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C52" s="51" t="inlineStr">
-        <is>
-          <t>LIM-TOS</t>
-        </is>
-      </c>
-      <c r="D52" s="43" t="n">
-        <v>139</v>
-      </c>
-      <c r="E52" s="43" t="n">
-        <v>33851</v>
-      </c>
-      <c r="F52" s="43" t="n">
-        <v>1049381</v>
-      </c>
-      <c r="G52" s="72" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="51" t="inlineStr">
-        <is>
-          <t>TF&gt;HUAFEI</t>
-        </is>
-      </c>
-      <c r="B53" s="51" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C53" s="51" t="inlineStr">
-        <is>
-          <t>LIM-TOS</t>
-        </is>
-      </c>
-      <c r="D53" s="43" t="n">
-        <v>62</v>
-      </c>
-      <c r="E53" s="43" t="n">
-        <v>6471</v>
-      </c>
-      <c r="F53" s="43" t="n">
-        <v>200601</v>
-      </c>
-      <c r="G53" s="72" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="51" t="inlineStr">
-        <is>
-          <t>KR&gt;HUAFEI</t>
-        </is>
-      </c>
-      <c r="B54" s="51" t="inlineStr">
-        <is>
-          <t>SMA</t>
-        </is>
-      </c>
-      <c r="C54" s="51" t="inlineStr">
-        <is>
-          <t>LIM-TOS</t>
-        </is>
-      </c>
-      <c r="D54" s="43" t="n">
-        <v>19</v>
-      </c>
-      <c r="E54" s="43" t="n">
-        <v>2545</v>
-      </c>
-      <c r="F54" s="43" t="n">
-        <v>78895</v>
-      </c>
-      <c r="G54" s="72" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="51" t="inlineStr">
-        <is>
-          <t>BLB&gt;FENI KM0</t>
-        </is>
-      </c>
-      <c r="B55" s="51" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C55" s="51" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="D55" s="43" t="n">
-        <v>202</v>
-      </c>
-      <c r="E55" s="43" t="n">
-        <v>45774</v>
-      </c>
-      <c r="F55" s="43" t="n">
-        <v>1418994</v>
-      </c>
-      <c r="G55" s="72" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="51" t="inlineStr">
-        <is>
-          <t>TF&gt;FENI KM15</t>
-        </is>
-      </c>
-      <c r="B56" s="51" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C56" s="51" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="D56" s="43" t="n">
-        <v>140</v>
-      </c>
-      <c r="E56" s="43" t="n">
-        <v>14702</v>
-      </c>
-      <c r="F56" s="43" t="n">
-        <v>455762</v>
-      </c>
-      <c r="G56" s="72" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="51" t="inlineStr">
-        <is>
-          <t>KR&gt;FENI KM15</t>
-        </is>
-      </c>
-      <c r="B57" s="51" t="inlineStr">
-        <is>
-          <t>SMA</t>
-        </is>
-      </c>
-      <c r="C57" s="51" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="D57" s="43" t="n">
-        <v>50</v>
-      </c>
-      <c r="E57" s="43" t="n">
-        <v>7919</v>
-      </c>
-      <c r="F57" s="43" t="n">
-        <v>245489</v>
-      </c>
-      <c r="G57" s="72" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="51" t="inlineStr">
-        <is>
-          <t>BLB&gt;POS 14</t>
-        </is>
-      </c>
-      <c r="B58" s="51" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C58" s="51" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="D58" s="43" t="n">
-        <v>7</v>
-      </c>
-      <c r="E58" s="43" t="n">
-        <v>2043</v>
-      </c>
-      <c r="F58" s="43" t="n">
-        <v>63333</v>
-      </c>
-      <c r="G58" s="72" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="51" t="inlineStr">
-        <is>
-          <t>TF&gt;POS 12</t>
-        </is>
-      </c>
-      <c r="B59" s="51" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C59" s="51" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="D59" s="43" t="n">
-        <v>18</v>
-      </c>
-      <c r="E59" s="43" t="n">
-        <v>2037</v>
-      </c>
-      <c r="F59" s="43" t="n">
-        <v>63147</v>
-      </c>
-      <c r="G59" s="72" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="51" t="inlineStr">
-        <is>
-          <t>KR&gt;POS 12</t>
-        </is>
-      </c>
-      <c r="B60" s="51" t="inlineStr">
-        <is>
-          <t>SMA</t>
-        </is>
-      </c>
-      <c r="C60" s="51" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="D60" s="43" t="n">
-        <v>10</v>
-      </c>
-      <c r="E60" s="43" t="n">
-        <v>1999</v>
-      </c>
-      <c r="F60" s="43" t="n">
-        <v>61969</v>
-      </c>
-      <c r="G60" s="72" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="60" t="inlineStr">
-        <is>
-          <t>TOTAL (full matrix pool)</t>
-        </is>
-      </c>
-      <c r="D61" s="47" t="n">
-        <v>1281</v>
-      </c>
-      <c r="F61" s="47" t="n">
-        <v>5687508</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="41" t="inlineStr">
-        <is>
-          <t>Material</t>
-        </is>
-      </c>
-      <c r="B63" s="41" t="inlineStr">
-        <is>
-          <t>t/month (frozen)</t>
-        </is>
-      </c>
-      <c r="C63" s="41" t="inlineStr">
-        <is>
-          <t>December TARGET t</t>
-        </is>
-      </c>
-      <c r="D63" s="41" t="inlineStr">
-        <is>
-          <t>Coverage</t>
-        </is>
-      </c>
-      <c r="E63" s="41" t="inlineStr"/>
-      <c r="F63" s="41" t="inlineStr"/>
-      <c r="G63" s="41" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="51" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="B64" s="47" t="n">
-        <v>2308694</v>
-      </c>
-      <c r="C64" s="43" t="n">
-        <v>2311213</v>
-      </c>
-      <c r="D64" s="71" t="n">
-        <v>0.9989100961270121</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="51" t="inlineStr">
-        <is>
-          <t>LIM-TOS</t>
-        </is>
-      </c>
-      <c r="B65" s="47" t="n">
-        <v>1328877</v>
-      </c>
-      <c r="C65" s="43" t="n">
-        <v>1326082</v>
-      </c>
-      <c r="D65" s="45" t="n">
-        <v>1.002107712796041</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="51" t="inlineStr">
-        <is>
-          <t>LIM-LD</t>
-        </is>
-      </c>
-      <c r="B66" s="47" t="n">
-        <v>2049937</v>
-      </c>
-      <c r="C66" s="43" t="n">
-        <v>992213</v>
-      </c>
-      <c r="D66" s="45" t="n">
-        <v>2.066025137747641</v>
-      </c>
-      <c r="E66" s="70" t="inlineStr">
-        <is>
-          <t>above target by design</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="40" t="inlineStr">
-        <is>
-          <t>Scenario 3.1.2 — December (frozen, 1,281 DT)</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="41" t="inlineStr">
-        <is>
-          <t>Route</t>
-        </is>
-      </c>
-      <c r="B70" s="41" t="inlineStr">
-        <is>
-          <t>Contractor</t>
-        </is>
-      </c>
-      <c r="C70" s="41" t="inlineStr">
-        <is>
-          <t>Material</t>
-        </is>
-      </c>
-      <c r="D70" s="41" t="inlineStr">
-        <is>
-          <t>DT</t>
-        </is>
-      </c>
-      <c r="E70" s="41" t="inlineStr">
-        <is>
-          <t>t/day</t>
-        </is>
-      </c>
-      <c r="F70" s="41" t="inlineStr">
-        <is>
-          <t>t/month</t>
-        </is>
-      </c>
-      <c r="G70" s="41" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="67" t="inlineStr">
-        <is>
-          <t>TF&gt;POS 6</t>
-        </is>
-      </c>
-      <c r="B71" s="67" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C71" s="67" t="inlineStr">
-        <is>
-          <t>LIM-LD</t>
-        </is>
-      </c>
-      <c r="D71" s="68" t="n">
-        <v>196</v>
-      </c>
-      <c r="E71" s="43" t="n">
-        <v>24840</v>
-      </c>
-      <c r="F71" s="43" t="n">
-        <v>770040</v>
-      </c>
-      <c r="G71" s="69" t="inlineStr">
-        <is>
-          <t>LD — carries the surplus fleet</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="67" t="inlineStr">
-        <is>
-          <t>TF&gt;HUAFEI</t>
-        </is>
-      </c>
-      <c r="B72" s="67" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C72" s="67" t="inlineStr">
-        <is>
-          <t>LIM-LD</t>
-        </is>
-      </c>
-      <c r="D72" s="68" t="n">
-        <v>196</v>
-      </c>
-      <c r="E72" s="43" t="n">
-        <v>20400</v>
-      </c>
-      <c r="F72" s="43" t="n">
-        <v>632400</v>
-      </c>
-      <c r="G72" s="69" t="inlineStr">
-        <is>
-          <t>LD — carries the surplus fleet</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="67" t="inlineStr">
-        <is>
-          <t>TF&gt;POS 6</t>
-        </is>
-      </c>
-      <c r="B73" s="67" t="inlineStr">
-        <is>
-          <t>SMA</t>
-        </is>
-      </c>
-      <c r="C73" s="67" t="inlineStr">
-        <is>
-          <t>LIM-LD</t>
-        </is>
-      </c>
-      <c r="D73" s="68" t="n">
-        <v>120</v>
-      </c>
-      <c r="E73" s="43" t="n">
-        <v>13892</v>
-      </c>
-      <c r="F73" s="43" t="n">
-        <v>430652</v>
-      </c>
-      <c r="G73" s="69" t="inlineStr">
-        <is>
-          <t>LD — carries the surplus fleet</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="67" t="inlineStr">
-        <is>
-          <t>TF&gt;HUAFEI</t>
-        </is>
-      </c>
-      <c r="B74" s="67" t="inlineStr">
-        <is>
-          <t>SMA</t>
-        </is>
-      </c>
-      <c r="C74" s="67" t="inlineStr">
-        <is>
-          <t>LIM-LD</t>
-        </is>
-      </c>
-      <c r="D74" s="68" t="n">
-        <v>121</v>
-      </c>
-      <c r="E74" s="43" t="n">
-        <v>12569</v>
-      </c>
-      <c r="F74" s="43" t="n">
-        <v>389639</v>
-      </c>
-      <c r="G74" s="69" t="inlineStr">
-        <is>
-          <t>LD — carries the surplus fleet</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="51" t="inlineStr">
-        <is>
-          <t>BLB&gt;HUAFEI</t>
-        </is>
-      </c>
-      <c r="B75" s="51" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C75" s="51" t="inlineStr">
-        <is>
-          <t>LIM-TOS</t>
-        </is>
-      </c>
-      <c r="D75" s="43" t="n">
-        <v>139</v>
-      </c>
-      <c r="E75" s="43" t="n">
-        <v>33851</v>
-      </c>
-      <c r="F75" s="43" t="n">
-        <v>1049381</v>
-      </c>
-      <c r="G75" s="72" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="51" t="inlineStr">
-        <is>
-          <t>TF&gt;HUAFEI</t>
-        </is>
-      </c>
-      <c r="B76" s="51" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C76" s="51" t="inlineStr">
-        <is>
-          <t>LIM-TOS</t>
-        </is>
-      </c>
-      <c r="D76" s="43" t="n">
-        <v>63</v>
-      </c>
-      <c r="E76" s="43" t="n">
-        <v>6557</v>
-      </c>
-      <c r="F76" s="43" t="n">
-        <v>203267</v>
-      </c>
-      <c r="G76" s="72" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="51" t="inlineStr">
-        <is>
-          <t>KR&gt;HUAFEI</t>
-        </is>
-      </c>
-      <c r="B77" s="51" t="inlineStr">
-        <is>
-          <t>SMA</t>
-        </is>
-      </c>
-      <c r="C77" s="51" t="inlineStr">
-        <is>
-          <t>LIM-TOS</t>
-        </is>
-      </c>
-      <c r="D77" s="43" t="n">
-        <v>19</v>
-      </c>
-      <c r="E77" s="43" t="n">
-        <v>2522</v>
-      </c>
-      <c r="F77" s="43" t="n">
-        <v>78182</v>
-      </c>
-      <c r="G77" s="72" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="51" t="inlineStr">
-        <is>
-          <t>BLB&gt;FENI KM0</t>
-        </is>
-      </c>
-      <c r="B78" s="51" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C78" s="51" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="D78" s="43" t="n">
-        <v>202</v>
-      </c>
-      <c r="E78" s="43" t="n">
-        <v>45774</v>
-      </c>
-      <c r="F78" s="43" t="n">
-        <v>1418994</v>
-      </c>
-      <c r="G78" s="72" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="51" t="inlineStr">
-        <is>
-          <t>TF&gt;FENI KM15</t>
-        </is>
-      </c>
-      <c r="B79" s="51" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C79" s="51" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="D79" s="43" t="n">
-        <v>140</v>
-      </c>
-      <c r="E79" s="43" t="n">
-        <v>14702</v>
-      </c>
-      <c r="F79" s="43" t="n">
-        <v>455762</v>
-      </c>
-      <c r="G79" s="72" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="51" t="inlineStr">
-        <is>
-          <t>KR&gt;FENI KM15</t>
-        </is>
-      </c>
-      <c r="B80" s="51" t="inlineStr">
-        <is>
-          <t>SMA</t>
-        </is>
-      </c>
-      <c r="C80" s="51" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="D80" s="43" t="n">
-        <v>50</v>
-      </c>
-      <c r="E80" s="43" t="n">
-        <v>7919</v>
-      </c>
-      <c r="F80" s="43" t="n">
-        <v>245489</v>
-      </c>
-      <c r="G80" s="72" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="51" t="inlineStr">
-        <is>
-          <t>BLB&gt;POS 14</t>
-        </is>
-      </c>
-      <c r="B81" s="51" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C81" s="51" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="D81" s="43" t="n">
-        <v>7</v>
-      </c>
-      <c r="E81" s="43" t="n">
-        <v>2043</v>
-      </c>
-      <c r="F81" s="43" t="n">
-        <v>63333</v>
-      </c>
-      <c r="G81" s="72" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="51" t="inlineStr">
-        <is>
-          <t>TF&gt;POS 12</t>
-        </is>
-      </c>
-      <c r="B82" s="51" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C82" s="51" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="D82" s="43" t="n">
-        <v>18</v>
-      </c>
-      <c r="E82" s="43" t="n">
-        <v>2037</v>
-      </c>
-      <c r="F82" s="43" t="n">
-        <v>63147</v>
-      </c>
-      <c r="G82" s="72" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="51" t="inlineStr">
-        <is>
-          <t>KR&gt;POS 12</t>
-        </is>
-      </c>
-      <c r="B83" s="51" t="inlineStr">
-        <is>
-          <t>SMA</t>
-        </is>
-      </c>
-      <c r="C83" s="51" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="D83" s="43" t="n">
-        <v>10</v>
-      </c>
-      <c r="E83" s="43" t="n">
-        <v>1999</v>
-      </c>
-      <c r="F83" s="43" t="n">
-        <v>61969</v>
-      </c>
-      <c r="G83" s="72" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="60" t="inlineStr">
-        <is>
-          <t>TOTAL (full matrix pool)</t>
-        </is>
-      </c>
-      <c r="D84" s="47" t="n">
-        <v>1281</v>
-      </c>
-      <c r="F84" s="47" t="n">
-        <v>5862255</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="41" t="inlineStr">
-        <is>
-          <t>Material</t>
-        </is>
-      </c>
-      <c r="B86" s="41" t="inlineStr">
-        <is>
-          <t>t/month (frozen)</t>
-        </is>
-      </c>
-      <c r="C86" s="41" t="inlineStr">
-        <is>
-          <t>December TARGET t</t>
-        </is>
-      </c>
-      <c r="D86" s="41" t="inlineStr">
-        <is>
-          <t>Coverage</t>
-        </is>
-      </c>
-      <c r="E86" s="41" t="inlineStr"/>
-      <c r="F86" s="41" t="inlineStr"/>
-      <c r="G86" s="41" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="51" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="B87" s="47" t="n">
-        <v>2308694</v>
-      </c>
-      <c r="C87" s="43" t="n">
-        <v>2311213</v>
-      </c>
-      <c r="D87" s="71" t="n">
-        <v>0.9989100961270121</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="51" t="inlineStr">
-        <is>
-          <t>LIM-TOS</t>
-        </is>
-      </c>
-      <c r="B88" s="47" t="n">
-        <v>1330830</v>
-      </c>
-      <c r="C88" s="43" t="n">
-        <v>1326082</v>
-      </c>
-      <c r="D88" s="45" t="n">
-        <v>1.003580472399143</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="51" t="inlineStr">
-        <is>
-          <t>LIM-LD</t>
-        </is>
-      </c>
-      <c r="B89" s="47" t="n">
-        <v>2222731</v>
-      </c>
-      <c r="C89" s="43" t="n">
-        <v>992213</v>
-      </c>
-      <c r="D89" s="45" t="n">
-        <v>2.240175244629933</v>
-      </c>
-      <c r="E89" s="70" t="inlineStr">
-        <is>
-          <t>above target by design</t>
-        </is>
+      <c r="G75" s="61" t="n">
+        <v>86</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A2:H2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/scenario_comparison_dec_options.xlsx
+++ b/reports/scenario_comparison_dec_options.xlsx
@@ -1647,7 +1647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1670,7 +1670,7 @@
     <row r="2">
       <c r="A2" s="39" t="inlineStr">
         <is>
-          <t>3.0 = base mining plan · 3.1 = +330 kt/mo BLB LIM Oct–Dec · .1 = all leftover LD to HUAFEI/BSE · .2 = half the TF LD trucks to POS 6 from October (exact 50/50). Every truck in the matrix pool works: SAP 100%, LIM-TOS 100%, all remaining DT haul LIM-LD past its target.</t>
+          <t>3.0 = base mining plan · 3.1 = +330 kt/mo BLB LIM Oct–Dec · .1 = all leftover LD to HUAFEI/BSE · .2 = half the TF LD trucks to POS 6 from October. Monthly targets are the SALES lines distributed in the plan shape, so the months sum exactly to 17,003,193 t. Every truck works: SAP 100%, LIM-TOS 100%, the rest haul LIM-LD.</t>
         </is>
       </c>
     </row>
@@ -1868,17 +1868,17 @@
           <t>Sep</t>
         </is>
       </c>
-      <c r="B13" s="45" t="n">
-        <v>1.045482521411984</v>
-      </c>
-      <c r="C13" s="45" t="n">
-        <v>1.045482521411984</v>
+      <c r="B13" s="71" t="n">
+        <v>0.9790716575886876</v>
+      </c>
+      <c r="C13" s="71" t="n">
+        <v>0.9790716575886876</v>
       </c>
       <c r="D13" s="45" t="n">
-        <v>1.045482521411984</v>
+        <v>1.008516894890541</v>
       </c>
       <c r="E13" s="45" t="n">
-        <v>1.045482521411984</v>
+        <v>1.008516894890541</v>
       </c>
     </row>
     <row r="14">
@@ -1887,17 +1887,17 @@
           <t>Oct</t>
         </is>
       </c>
-      <c r="B14" s="45" t="n">
-        <v>1.012856749072166</v>
-      </c>
-      <c r="C14" s="45" t="n">
-        <v>1.055805550922092</v>
-      </c>
-      <c r="D14" s="45" t="n">
-        <v>1.016155521828965</v>
+      <c r="B14" s="71" t="n">
+        <v>0.9485185628773033</v>
+      </c>
+      <c r="C14" s="71" t="n">
+        <v>0.9887391921472493</v>
+      </c>
+      <c r="D14" s="71" t="n">
+        <v>0.9802270105929592</v>
       </c>
       <c r="E14" s="45" t="n">
-        <v>1.051434176532733</v>
+        <v>1.014258307471388</v>
       </c>
     </row>
     <row r="15">
@@ -1906,17 +1906,17 @@
           <t>Nov</t>
         </is>
       </c>
-      <c r="B15" s="45" t="n">
-        <v>1.033122002370932</v>
+      <c r="B15" s="71" t="n">
+        <v>0.967496524849096</v>
       </c>
       <c r="C15" s="45" t="n">
-        <v>1.074038091902804</v>
+        <v>1.00581356227706</v>
       </c>
       <c r="D15" s="45" t="n">
-        <v>1.043424413593518</v>
+        <v>1.006531632499034</v>
       </c>
       <c r="E15" s="45" t="n">
-        <v>1.079733218673122</v>
+        <v>1.041556652399613</v>
       </c>
     </row>
     <row r="16">
@@ -1926,36 +1926,36 @@
         </is>
       </c>
       <c r="B16" s="45" t="n">
-        <v>1.099858328904862</v>
+        <v>1.029993474998572</v>
       </c>
       <c r="C16" s="45" t="n">
-        <v>1.137358183954899</v>
+        <v>1.065111276082453</v>
       </c>
       <c r="D16" s="45" t="n">
-        <v>1.09793766371253</v>
+        <v>1.059117544967807</v>
       </c>
       <c r="E16" s="45" t="n">
-        <v>1.131672700225648</v>
+        <v>1.091659801447431</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="49" t="inlineStr">
         <is>
-          <t>Reading: every month is now run with its whole fleet, so coverage is at or above 100% from October on. September is short because the matrix only fields 581 DT that month.</t>
+          <t>Reading: every month runs its whole fleet, so coverage is at or above 100% from October on. September is short because the matrix only fields 581 DT that month.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="50" t="inlineStr">
         <is>
-          <t>Month by month — Predicted plan t</t>
+          <t>December targets by material (sales line distributed)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="41" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Material</t>
         </is>
       </c>
       <c r="B21" s="41" t="inlineStr">
@@ -1982,201 +1982,168 @@
     <row r="22">
       <c r="A22" s="42" t="inlineStr">
         <is>
-          <t>Sep</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B22" s="43" t="n">
-        <v>2381536</v>
+        <v>2311213</v>
       </c>
       <c r="C22" s="43" t="n">
-        <v>2381536</v>
+        <v>2311213</v>
       </c>
       <c r="D22" s="43" t="n">
-        <v>2381536</v>
+        <v>2311213</v>
       </c>
       <c r="E22" s="43" t="n">
-        <v>2381536</v>
+        <v>2311213</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="42" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>LIM-TOS</t>
         </is>
       </c>
       <c r="B23" s="43" t="n">
-        <v>3722205</v>
+        <v>996084</v>
       </c>
       <c r="C23" s="43" t="n">
-        <v>3880040</v>
+        <v>996084</v>
       </c>
       <c r="D23" s="43" t="n">
-        <v>3912780</v>
+        <v>1326082</v>
       </c>
       <c r="E23" s="43" t="n">
-        <v>4048623</v>
+        <v>1326082</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="42" t="inlineStr">
         <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="B24" s="43" t="n">
-        <v>5133077</v>
-      </c>
-      <c r="C24" s="43" t="n">
-        <v>5336369</v>
-      </c>
-      <c r="D24" s="43" t="n">
-        <v>5314484</v>
-      </c>
-      <c r="E24" s="43" t="n">
-        <v>5499416</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="42" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="B25" s="43" t="n">
-        <v>5501190</v>
-      </c>
-      <c r="C25" s="43" t="n">
-        <v>5688754</v>
-      </c>
-      <c r="D25" s="43" t="n">
-        <v>5687529</v>
-      </c>
-      <c r="E25" s="43" t="n">
-        <v>5862283</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="60" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B26" s="47" t="n">
-        <v>16738008</v>
-      </c>
-      <c r="C26" s="47" t="n">
-        <v>17286699</v>
-      </c>
-      <c r="D26" s="47" t="n">
-        <v>17296329</v>
-      </c>
-      <c r="E26" s="47" t="n">
-        <v>17791858</v>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="B24" s="47" t="n">
+        <v>1973655</v>
+      </c>
+      <c r="C24" s="47" t="n">
+        <v>1973655</v>
+      </c>
+      <c r="D24" s="47" t="n">
+        <v>1696393</v>
+      </c>
+      <c r="E24" s="47" t="n">
+        <v>1696393</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="50" t="inlineStr">
+        <is>
+          <t>Month by month — Predicted plan t</t>
+        </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="50" t="inlineStr">
-        <is>
-          <t>Year tonnage by material (t) — predicted vs sales line</t>
+      <c r="A28" s="41" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B28" s="41" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="C28" s="41" t="inlineStr">
+        <is>
+          <t>3.0.2</t>
+        </is>
+      </c>
+      <c r="D28" s="41" t="inlineStr">
+        <is>
+          <t>3.1.1</t>
+        </is>
+      </c>
+      <c r="E28" s="41" t="inlineStr">
+        <is>
+          <t>3.1.2</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="41" t="inlineStr">
-        <is>
-          <t>Material</t>
-        </is>
-      </c>
-      <c r="B29" s="41" t="inlineStr">
-        <is>
-          <t>Sales line</t>
-        </is>
-      </c>
-      <c r="C29" s="41" t="inlineStr">
-        <is>
-          <t>3.0.1</t>
-        </is>
-      </c>
-      <c r="D29" s="41" t="inlineStr">
-        <is>
-          <t>3.0.2</t>
-        </is>
-      </c>
-      <c r="E29" s="41" t="inlineStr">
-        <is>
-          <t>3.1.1</t>
-        </is>
-      </c>
-      <c r="F29" s="41" t="inlineStr">
-        <is>
-          <t>3.1.2</t>
-        </is>
+      <c r="A29" s="42" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="B29" s="43" t="n">
+        <v>2381536</v>
+      </c>
+      <c r="C29" s="43" t="n">
+        <v>2381536</v>
+      </c>
+      <c r="D29" s="43" t="n">
+        <v>2381536</v>
+      </c>
+      <c r="E29" s="43" t="n">
+        <v>2381536</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="42" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="B30" s="43" t="n">
-        <v>5718686</v>
+        <v>3722205</v>
       </c>
       <c r="C30" s="43" t="n">
-        <v>5754583</v>
+        <v>3880040</v>
       </c>
       <c r="D30" s="43" t="n">
-        <v>5754366</v>
+        <v>3912780</v>
       </c>
       <c r="E30" s="43" t="n">
-        <v>5740906</v>
-      </c>
-      <c r="F30" s="43" t="n">
-        <v>5740906</v>
+        <v>4048623</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="42" t="inlineStr">
         <is>
-          <t>LIM-TOS</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="B31" s="43" t="n">
-        <v>3650201</v>
+        <v>5133077</v>
       </c>
       <c r="C31" s="43" t="n">
-        <v>3667243</v>
+        <v>5336369</v>
       </c>
       <c r="D31" s="43" t="n">
-        <v>3672901</v>
+        <v>5314484</v>
       </c>
       <c r="E31" s="43" t="n">
-        <v>4652858</v>
-      </c>
-      <c r="F31" s="43" t="n">
-        <v>4655256</v>
+        <v>5499416</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="42" t="inlineStr">
         <is>
-          <t>LIM-LD</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="B32" s="43" t="n">
-        <v>7634306</v>
+        <v>5501190</v>
       </c>
       <c r="C32" s="43" t="n">
-        <v>7316183</v>
+        <v>5688754</v>
       </c>
       <c r="D32" s="43" t="n">
-        <v>7859393</v>
+        <v>5687529</v>
       </c>
       <c r="E32" s="43" t="n">
-        <v>6902523</v>
-      </c>
-      <c r="F32" s="43" t="n">
-        <v>7395695</v>
+        <v>5862283</v>
       </c>
     </row>
     <row r="33">
@@ -2186,18 +2153,142 @@
         </is>
       </c>
       <c r="B33" s="47" t="n">
+        <v>16738008</v>
+      </c>
+      <c r="C33" s="47" t="n">
+        <v>17286699</v>
+      </c>
+      <c r="D33" s="47" t="n">
+        <v>17296329</v>
+      </c>
+      <c r="E33" s="47" t="n">
+        <v>17791858</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="50" t="inlineStr">
+        <is>
+          <t>Year tonnage by material (t) — predicted vs sales line</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="41" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="B36" s="41" t="inlineStr">
+        <is>
+          <t>Sales line</t>
+        </is>
+      </c>
+      <c r="C36" s="41" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="D36" s="41" t="inlineStr">
+        <is>
+          <t>3.0.2</t>
+        </is>
+      </c>
+      <c r="E36" s="41" t="inlineStr">
+        <is>
+          <t>3.1.1</t>
+        </is>
+      </c>
+      <c r="F36" s="41" t="inlineStr">
+        <is>
+          <t>3.1.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="42" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B37" s="43" t="n">
+        <v>5718686</v>
+      </c>
+      <c r="C37" s="43" t="n">
+        <v>5754583</v>
+      </c>
+      <c r="D37" s="43" t="n">
+        <v>5754366</v>
+      </c>
+      <c r="E37" s="43" t="n">
+        <v>5740906</v>
+      </c>
+      <c r="F37" s="43" t="n">
+        <v>5740906</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="42" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="B38" s="43" t="n">
+        <v>3650201</v>
+      </c>
+      <c r="C38" s="43" t="n">
+        <v>3667243</v>
+      </c>
+      <c r="D38" s="43" t="n">
+        <v>3672901</v>
+      </c>
+      <c r="E38" s="43" t="n">
+        <v>4652858</v>
+      </c>
+      <c r="F38" s="43" t="n">
+        <v>4655256</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="42" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="B39" s="43" t="n">
+        <v>7634306</v>
+      </c>
+      <c r="C39" s="43" t="n">
+        <v>7316183</v>
+      </c>
+      <c r="D39" s="43" t="n">
+        <v>7859393</v>
+      </c>
+      <c r="E39" s="43" t="n">
+        <v>6902523</v>
+      </c>
+      <c r="F39" s="43" t="n">
+        <v>7395695</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="60" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B40" s="47" t="n">
         <v>17003193</v>
       </c>
-      <c r="C33" s="47" t="n">
+      <c r="C40" s="47" t="n">
         <v>16738008</v>
       </c>
-      <c r="D33" s="47" t="n">
+      <c r="D40" s="47" t="n">
         <v>17286699</v>
       </c>
-      <c r="E33" s="47" t="n">
+      <c r="E40" s="47" t="n">
         <v>17296329</v>
       </c>
-      <c r="F33" s="47" t="n">
+      <c r="F40" s="47" t="n">
         <v>17791858</v>
       </c>
     </row>
@@ -2212,7 +2303,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:H77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2221,7 +2312,7 @@
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="48" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2234,99 +2325,79 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="75" t="inlineStr">
         <is>
-          <t>AS FROZEN (today's plan): all 1,281 DT work. SAP and LIM-TOS land on their lines; every remaining truck hauls LIM-LD, so LD finishes 129-144% of its target. Nothing is parked, nothing is wasted.</t>
+          <t>TARGETS: each month's target is the SALES line distributed in the plan's shape, so the twelve months sum exactly to the sales total. December LIM-LD is 1,973,655 t in 3.0.x and 1,696,393 t in 3.1.x — the same clock the dashboard and every Excel book use.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="75" t="inlineStr">
         <is>
-          <t>OPTION 1 — PARK: take LD down to exactly 100% of its line and stand the freed trucks down. Simplest, lands the month on target, but those trucks earn nothing and the plants build no buffer.</t>
+          <t>AS FROZEN (today's plan): all 1,281 DT work. SAP and LIM-TOS land on their lines; every remaining truck hauls LIM-LD, so LD finishes 111-131% of its December target. Nothing is parked.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="75" t="inlineStr">
         <is>
-          <t>OPTION 2 — RE-DISPATCH: take the same trucks off LD and send them to KR&gt;FENI KM0 and TF&gt;FENI KM0 instead. They haul kilnable SAP feed into the plant stockpile, so LD still lands at 100% and the tonnage is kept, not lost. Needs FeNi KM0 to accept stock.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="40" t="inlineStr">
+          <t>OPTION 1 — PARK: take LD down to exactly 100% of its line and stand the freed trucks down. Lands the month on target, but those trucks earn nothing and the plants build no buffer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="75" t="inlineStr">
+        <is>
+          <t>OPTION 2 — RE-DISPATCH: send the same trucks to KR&gt;FENI KM0 and TF&gt;FENI KM0 instead. They haul kilnable SAP feed into the plant stockpile, so LD still lands at 100% and the tonnage is kept. Needs FeNi KM0 to accept stock.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="40" t="inlineStr">
         <is>
           <t>Scenario 3.0.1 — December</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="41" t="inlineStr"/>
-      <c r="B7" s="41" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="41" t="inlineStr"/>
+      <c r="B8" s="41" t="inlineStr">
         <is>
           <t>Fleet DT</t>
         </is>
       </c>
-      <c r="C7" s="41" t="inlineStr">
+      <c r="C8" s="41" t="inlineStr">
         <is>
           <t>SAP t/mo</t>
         </is>
       </c>
-      <c r="D7" s="41" t="inlineStr">
+      <c r="D8" s="41" t="inlineStr">
         <is>
           <t>LIM-TOS t/mo</t>
         </is>
       </c>
-      <c r="E7" s="41" t="inlineStr">
+      <c r="E8" s="41" t="inlineStr">
         <is>
           <t>LIM-LD t/mo</t>
         </is>
       </c>
-      <c r="F7" s="41" t="inlineStr">
+      <c r="F8" s="41" t="inlineStr">
         <is>
           <t>TOTAL t/mo</t>
         </is>
       </c>
-      <c r="G7" s="41" t="inlineStr">
+      <c r="G8" s="41" t="inlineStr">
         <is>
           <t>What happens</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="42" t="inlineStr">
-        <is>
-          <t>AS FROZEN</t>
-        </is>
-      </c>
-      <c r="B8" s="47" t="n">
-        <v>1281</v>
-      </c>
-      <c r="C8" s="43" t="n">
-        <v>2316351</v>
-      </c>
-      <c r="D8" s="43" t="n">
-        <v>1000029</v>
-      </c>
-      <c r="E8" s="68" t="n">
-        <v>2184818</v>
-      </c>
-      <c r="F8" s="47" t="n">
-        <v>5501198</v>
-      </c>
-      <c r="G8" s="76" t="inlineStr">
-        <is>
-          <t>LD runs 129% of its line — surplus fleet piles onto LD</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="42" t="inlineStr">
         <is>
-          <t>OPTION 1 · park 151 DT</t>
-        </is>
-      </c>
-      <c r="B9" s="52" t="n">
-        <v>1130</v>
+          <t>AS FROZEN</t>
+        </is>
+      </c>
+      <c r="B9" s="47" t="n">
+        <v>1281</v>
       </c>
       <c r="C9" s="43" t="n">
         <v>2316351</v>
@@ -2334,317 +2405,317 @@
       <c r="D9" s="43" t="n">
         <v>1000029</v>
       </c>
-      <c r="E9" s="47" t="n">
-        <v>1696480</v>
-      </c>
-      <c r="F9" s="52" t="n">
-        <v>5012860</v>
-      </c>
-      <c r="G9" s="77" t="inlineStr">
-        <is>
-          <t>LD → 100.0% · 488,338 t NOT hauled · 151 trucks idle</t>
+      <c r="E9" s="68" t="n">
+        <v>2184818</v>
+      </c>
+      <c r="F9" s="47" t="n">
+        <v>5501198</v>
+      </c>
+      <c r="G9" s="76" t="inlineStr">
+        <is>
+          <t>LD runs 111% of its 1,973,655 t line — surplus fleet piles onto LD</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="42" t="inlineStr">
         <is>
-          <t>OPTION 2 · re-dispatch 151 DT</t>
-        </is>
-      </c>
-      <c r="B10" s="61" t="n">
-        <v>1281</v>
-      </c>
-      <c r="C10" s="61" t="n">
-        <v>2891575</v>
+          <t>OPTION 1 · park 65 DT</t>
+        </is>
+      </c>
+      <c r="B10" s="52" t="n">
+        <v>1216</v>
+      </c>
+      <c r="C10" s="43" t="n">
+        <v>2316351</v>
       </c>
       <c r="D10" s="43" t="n">
         <v>1000029</v>
       </c>
       <c r="E10" s="47" t="n">
-        <v>1696480</v>
-      </c>
-      <c r="F10" s="61" t="n">
-        <v>5588084</v>
-      </c>
-      <c r="G10" s="78" t="inlineStr">
-        <is>
-          <t>LD → 100.0% · +575,224 t SAP stock at FeNi KM0 · no truck idle</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="41" t="inlineStr">
+        <v>1974606</v>
+      </c>
+      <c r="F10" s="52" t="n">
+        <v>5290986</v>
+      </c>
+      <c r="G10" s="77" t="inlineStr">
+        <is>
+          <t>LD → 100.0% · 210,212 t NOT hauled · 65 trucks idle</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="42" t="inlineStr">
+        <is>
+          <t>OPTION 2 · re-dispatch 65 DT</t>
+        </is>
+      </c>
+      <c r="B11" s="61" t="n">
+        <v>1281</v>
+      </c>
+      <c r="C11" s="61" t="n">
+        <v>2564190</v>
+      </c>
+      <c r="D11" s="43" t="n">
+        <v>1000029</v>
+      </c>
+      <c r="E11" s="47" t="n">
+        <v>1974606</v>
+      </c>
+      <c r="F11" s="61" t="n">
+        <v>5538825</v>
+      </c>
+      <c r="G11" s="78" t="inlineStr">
+        <is>
+          <t>LD → 100.0% · +247,839 t SAP stock at FeNi KM0 · no truck idle</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="41" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="B12" s="41" t="inlineStr">
+      <c r="B13" s="41" t="inlineStr">
         <is>
           <t>December TARGET t</t>
         </is>
       </c>
-      <c r="C12" s="41" t="inlineStr">
+      <c r="C13" s="41" t="inlineStr">
         <is>
           <t>As frozen</t>
         </is>
       </c>
-      <c r="D12" s="41" t="inlineStr">
+      <c r="D13" s="41" t="inlineStr">
         <is>
           <t>Option 1 (park)</t>
         </is>
       </c>
-      <c r="E12" s="41" t="inlineStr">
+      <c r="E13" s="41" t="inlineStr">
         <is>
           <t>Option 2 (re-dispatch)</t>
         </is>
       </c>
-      <c r="F12" s="41" t="inlineStr"/>
-      <c r="G12" s="41" t="inlineStr">
+      <c r="F13" s="41" t="inlineStr"/>
+      <c r="G13" s="41" t="inlineStr">
         <is>
           <t> </t>
         </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="42" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="B13" s="43" t="n">
-        <v>2311205</v>
-      </c>
-      <c r="C13" s="45" t="n">
-        <v>1.002226544162028</v>
-      </c>
-      <c r="D13" s="45" t="n">
-        <v>1.002226544162028</v>
-      </c>
-      <c r="E13" s="45" t="n">
-        <v>1.251111260143518</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="42" t="inlineStr">
         <is>
-          <t>LIM-TOS</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B14" s="43" t="n">
-        <v>996092</v>
+        <v>2311213</v>
       </c>
       <c r="C14" s="45" t="n">
-        <v>1.003952446159592</v>
+        <v>1.002223075069238</v>
       </c>
       <c r="D14" s="45" t="n">
-        <v>1.003952446159592</v>
+        <v>1.002223075069238</v>
       </c>
       <c r="E14" s="45" t="n">
-        <v>1.003952446159592</v>
+        <v>1.109456289835684</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="42" t="inlineStr">
         <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="B15" s="43" t="n">
+        <v>996084</v>
+      </c>
+      <c r="C15" s="45" t="n">
+        <v>1.003960509354633</v>
+      </c>
+      <c r="D15" s="45" t="n">
+        <v>1.003960509354633</v>
+      </c>
+      <c r="E15" s="45" t="n">
+        <v>1.003960509354633</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="42" t="inlineStr">
+        <is>
           <t>LIM-LD</t>
         </is>
       </c>
-      <c r="B15" s="43" t="n">
-        <v>1694429</v>
-      </c>
-      <c r="C15" s="45" t="n">
-        <v>1.289412539563475</v>
-      </c>
-      <c r="D15" s="45" t="n">
-        <v>1.001210549611092</v>
-      </c>
-      <c r="E15" s="45" t="n">
-        <v>1.001210549611092</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="60" t="inlineStr">
+      <c r="B16" s="43" t="n">
+        <v>1973655</v>
+      </c>
+      <c r="C16" s="45" t="n">
+        <v>1.106990836797718</v>
+      </c>
+      <c r="D16" s="45" t="n">
+        <v>1.000482029580521</v>
+      </c>
+      <c r="E16" s="45" t="n">
+        <v>1.000482029580521</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="60" t="inlineStr">
         <is>
           <t>TOTAL t/month</t>
         </is>
       </c>
-      <c r="B16" s="43" t="n">
-        <v>5001726</v>
-      </c>
-      <c r="C16" s="43" t="n">
+      <c r="B17" s="43" t="n">
+        <v>5280952</v>
+      </c>
+      <c r="C17" s="43" t="n">
         <v>5501198</v>
       </c>
-      <c r="D16" s="79" t="n">
-        <v>5012860</v>
-      </c>
-      <c r="E16" s="80" t="n">
-        <v>5588084</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="81" t="inlineStr">
-        <is>
-          <t>Which trucks move (same 151 DT in both options)</t>
-        </is>
+      <c r="D17" s="79" t="n">
+        <v>5290986</v>
+      </c>
+      <c r="E17" s="80" t="n">
+        <v>5538825</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="41" t="inlineStr">
+      <c r="A19" s="81" t="inlineStr">
+        <is>
+          <t>Which trucks move (same 65 DT in both options)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="41" t="inlineStr">
         <is>
           <t>Taken off (LIM-LD)</t>
         </is>
       </c>
-      <c r="B19" s="41" t="inlineStr">
+      <c r="B20" s="41" t="inlineStr">
         <is>
           <t>Contractor</t>
         </is>
       </c>
-      <c r="C19" s="41" t="inlineStr">
+      <c r="C20" s="41" t="inlineStr">
         <is>
           <t>DT</t>
         </is>
       </c>
-      <c r="D19" s="41" t="inlineStr"/>
-      <c r="E19" s="41" t="inlineStr">
+      <c r="D20" s="41" t="inlineStr"/>
+      <c r="E20" s="41" t="inlineStr">
         <is>
           <t>Option 2 sends them to</t>
         </is>
       </c>
-      <c r="F19" s="41" t="inlineStr">
+      <c r="F20" s="41" t="inlineStr">
         <is>
           <t>Contractor</t>
         </is>
       </c>
-      <c r="G19" s="41" t="inlineStr">
+      <c r="G20" s="41" t="inlineStr">
         <is>
           <t>DT</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="82" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="82" t="inlineStr">
         <is>
           <t>TF&gt;HUAFEI</t>
         </is>
       </c>
-      <c r="B20" s="82" t="inlineStr">
+      <c r="B21" s="82" t="inlineStr">
         <is>
           <t>RIM</t>
         </is>
       </c>
-      <c r="C20" s="68" t="n">
-        <v>151</v>
-      </c>
-      <c r="D20" s="66" t="n"/>
-      <c r="E20" s="54" t="inlineStr">
-        <is>
-          <t>KR&gt;FENI KM0</t>
-        </is>
-      </c>
-      <c r="F20" s="83" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="G20" s="61" t="n">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="66" t="n"/>
-      <c r="B21" s="66" t="n"/>
-      <c r="C21" s="66" t="n"/>
+      <c r="C21" s="68" t="n">
+        <v>65</v>
+      </c>
       <c r="D21" s="66" t="n"/>
       <c r="E21" s="54" t="inlineStr">
         <is>
+          <t>KR&gt;FENI KM0</t>
+        </is>
+      </c>
+      <c r="F21" s="83" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="G21" s="61" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="66" t="n"/>
+      <c r="B22" s="66" t="n"/>
+      <c r="C22" s="66" t="n"/>
+      <c r="D22" s="66" t="n"/>
+      <c r="E22" s="54" t="inlineStr">
+        <is>
           <t>TF&gt;FENI KM0</t>
         </is>
       </c>
-      <c r="F21" s="83" t="inlineStr">
+      <c r="F22" s="83" t="inlineStr">
         <is>
           <t>RIM</t>
         </is>
       </c>
-      <c r="G21" s="61" t="n">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="40" t="inlineStr">
+      <c r="G22" s="61" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="40" t="inlineStr">
         <is>
           <t>Scenario 3.0.2 — December</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="41" t="inlineStr"/>
-      <c r="B25" s="41" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="41" t="inlineStr"/>
+      <c r="B26" s="41" t="inlineStr">
         <is>
           <t>Fleet DT</t>
         </is>
       </c>
-      <c r="C25" s="41" t="inlineStr">
+      <c r="C26" s="41" t="inlineStr">
         <is>
           <t>SAP t/mo</t>
         </is>
       </c>
-      <c r="D25" s="41" t="inlineStr">
+      <c r="D26" s="41" t="inlineStr">
         <is>
           <t>LIM-TOS t/mo</t>
         </is>
       </c>
-      <c r="E25" s="41" t="inlineStr">
+      <c r="E26" s="41" t="inlineStr">
         <is>
           <t>LIM-LD t/mo</t>
         </is>
       </c>
-      <c r="F25" s="41" t="inlineStr">
+      <c r="F26" s="41" t="inlineStr">
         <is>
           <t>TOTAL t/mo</t>
         </is>
       </c>
-      <c r="G25" s="41" t="inlineStr">
+      <c r="G26" s="41" t="inlineStr">
         <is>
           <t>What happens</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="42" t="inlineStr">
-        <is>
-          <t>AS FROZEN</t>
-        </is>
-      </c>
-      <c r="B26" s="47" t="n">
-        <v>1281</v>
-      </c>
-      <c r="C26" s="43" t="n">
-        <v>2316134</v>
-      </c>
-      <c r="D26" s="43" t="n">
-        <v>1001827</v>
-      </c>
-      <c r="E26" s="68" t="n">
-        <v>2370849</v>
-      </c>
-      <c r="F26" s="47" t="n">
-        <v>5688810</v>
-      </c>
-      <c r="G26" s="76" t="inlineStr">
-        <is>
-          <t>LD runs 140% of its line — surplus fleet piles onto LD</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="42" t="inlineStr">
         <is>
-          <t>OPTION 1 · park 172 DT</t>
-        </is>
-      </c>
-      <c r="B27" s="52" t="n">
-        <v>1109</v>
+          <t>AS FROZEN</t>
+        </is>
+      </c>
+      <c r="B27" s="47" t="n">
+        <v>1281</v>
       </c>
       <c r="C27" s="43" t="n">
         <v>2316134</v>
@@ -2652,317 +2723,317 @@
       <c r="D27" s="43" t="n">
         <v>1001827</v>
       </c>
-      <c r="E27" s="47" t="n">
-        <v>1695626</v>
-      </c>
-      <c r="F27" s="52" t="n">
-        <v>5013587</v>
-      </c>
-      <c r="G27" s="77" t="inlineStr">
-        <is>
-          <t>LD → 100.0% · 675,223 t NOT hauled · 172 trucks idle</t>
+      <c r="E27" s="68" t="n">
+        <v>2370849</v>
+      </c>
+      <c r="F27" s="47" t="n">
+        <v>5688810</v>
+      </c>
+      <c r="G27" s="76" t="inlineStr">
+        <is>
+          <t>LD runs 120% of its 1,973,655 t line — surplus fleet piles onto LD</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="42" t="inlineStr">
         <is>
-          <t>OPTION 2 · re-dispatch 172 DT</t>
-        </is>
-      </c>
-      <c r="B28" s="61" t="n">
-        <v>1281</v>
-      </c>
-      <c r="C28" s="61" t="n">
-        <v>2970904</v>
+          <t>OPTION 1 · park 101 DT</t>
+        </is>
+      </c>
+      <c r="B28" s="52" t="n">
+        <v>1180</v>
+      </c>
+      <c r="C28" s="43" t="n">
+        <v>2316134</v>
       </c>
       <c r="D28" s="43" t="n">
         <v>1001827</v>
       </c>
       <c r="E28" s="47" t="n">
-        <v>1695626</v>
-      </c>
-      <c r="F28" s="61" t="n">
-        <v>5668357</v>
-      </c>
-      <c r="G28" s="78" t="inlineStr">
-        <is>
-          <t>LD → 100.0% · +654,770 t SAP stock at FeNi KM0 · no truck idle</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="41" t="inlineStr">
+        <v>1974352</v>
+      </c>
+      <c r="F28" s="52" t="n">
+        <v>5292313</v>
+      </c>
+      <c r="G28" s="77" t="inlineStr">
+        <is>
+          <t>LD → 100.0% · 396,497 t NOT hauled · 101 trucks idle</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="42" t="inlineStr">
+        <is>
+          <t>OPTION 2 · re-dispatch 101 DT</t>
+        </is>
+      </c>
+      <c r="B29" s="61" t="n">
+        <v>1281</v>
+      </c>
+      <c r="C29" s="61" t="n">
+        <v>2701018</v>
+      </c>
+      <c r="D29" s="43" t="n">
+        <v>1001827</v>
+      </c>
+      <c r="E29" s="47" t="n">
+        <v>1974352</v>
+      </c>
+      <c r="F29" s="61" t="n">
+        <v>5677196</v>
+      </c>
+      <c r="G29" s="78" t="inlineStr">
+        <is>
+          <t>LD → 100.0% · +384,884 t SAP stock at FeNi KM0 · no truck idle</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="41" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="B30" s="41" t="inlineStr">
+      <c r="B31" s="41" t="inlineStr">
         <is>
           <t>December TARGET t</t>
         </is>
       </c>
-      <c r="C30" s="41" t="inlineStr">
+      <c r="C31" s="41" t="inlineStr">
         <is>
           <t>As frozen</t>
         </is>
       </c>
-      <c r="D30" s="41" t="inlineStr">
+      <c r="D31" s="41" t="inlineStr">
         <is>
           <t>Option 1 (park)</t>
         </is>
       </c>
-      <c r="E30" s="41" t="inlineStr">
+      <c r="E31" s="41" t="inlineStr">
         <is>
           <t>Option 2 (re-dispatch)</t>
         </is>
       </c>
-      <c r="F30" s="41" t="inlineStr"/>
-      <c r="G30" s="41" t="inlineStr">
+      <c r="F31" s="41" t="inlineStr"/>
+      <c r="G31" s="41" t="inlineStr">
         <is>
           <t> </t>
         </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="42" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="B31" s="43" t="n">
-        <v>2311205</v>
-      </c>
-      <c r="C31" s="45" t="n">
-        <v>1.002132653745557</v>
-      </c>
-      <c r="D31" s="45" t="n">
-        <v>1.002132653745557</v>
-      </c>
-      <c r="E31" s="45" t="n">
-        <v>1.285434913822011</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="42" t="inlineStr">
         <is>
-          <t>LIM-TOS</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B32" s="43" t="n">
-        <v>996092</v>
+        <v>2311213</v>
       </c>
       <c r="C32" s="45" t="n">
-        <v>1.005757500311216</v>
+        <v>1.002129184977758</v>
       </c>
       <c r="D32" s="45" t="n">
-        <v>1.005757500311216</v>
+        <v>1.002129184977758</v>
       </c>
       <c r="E32" s="45" t="n">
-        <v>1.005757500311216</v>
+        <v>1.168658016374951</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="42" t="inlineStr">
         <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="B33" s="43" t="n">
+        <v>996084</v>
+      </c>
+      <c r="C33" s="45" t="n">
+        <v>1.005765578003462</v>
+      </c>
+      <c r="D33" s="45" t="n">
+        <v>1.005765578003462</v>
+      </c>
+      <c r="E33" s="45" t="n">
+        <v>1.005765578003462</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="42" t="inlineStr">
+        <is>
           <t>LIM-LD</t>
         </is>
       </c>
-      <c r="B33" s="43" t="n">
-        <v>1694429</v>
-      </c>
-      <c r="C33" s="45" t="n">
-        <v>1.399202327155638</v>
-      </c>
-      <c r="D33" s="45" t="n">
-        <v>1.00070651697837</v>
-      </c>
-      <c r="E33" s="45" t="n">
-        <v>1.00070651697837</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="60" t="inlineStr">
+      <c r="B34" s="43" t="n">
+        <v>1973655</v>
+      </c>
+      <c r="C34" s="45" t="n">
+        <v>1.201247938469489</v>
+      </c>
+      <c r="D34" s="45" t="n">
+        <v>1.000353079511291</v>
+      </c>
+      <c r="E34" s="45" t="n">
+        <v>1.000353079511291</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="60" t="inlineStr">
         <is>
           <t>TOTAL t/month</t>
         </is>
       </c>
-      <c r="B34" s="43" t="n">
-        <v>5001726</v>
-      </c>
-      <c r="C34" s="43" t="n">
+      <c r="B35" s="43" t="n">
+        <v>5280952</v>
+      </c>
+      <c r="C35" s="43" t="n">
         <v>5688810</v>
       </c>
-      <c r="D34" s="79" t="n">
-        <v>5013587</v>
-      </c>
-      <c r="E34" s="80" t="n">
-        <v>5668357</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="81" t="inlineStr">
-        <is>
-          <t>Which trucks move (same 172 DT in both options)</t>
-        </is>
+      <c r="D35" s="79" t="n">
+        <v>5292313</v>
+      </c>
+      <c r="E35" s="80" t="n">
+        <v>5677196</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="41" t="inlineStr">
+      <c r="A37" s="81" t="inlineStr">
+        <is>
+          <t>Which trucks move (same 101 DT in both options)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="41" t="inlineStr">
         <is>
           <t>Taken off (LIM-LD)</t>
         </is>
       </c>
-      <c r="B37" s="41" t="inlineStr">
+      <c r="B38" s="41" t="inlineStr">
         <is>
           <t>Contractor</t>
         </is>
       </c>
-      <c r="C37" s="41" t="inlineStr">
+      <c r="C38" s="41" t="inlineStr">
         <is>
           <t>DT</t>
         </is>
       </c>
-      <c r="D37" s="41" t="inlineStr"/>
-      <c r="E37" s="41" t="inlineStr">
+      <c r="D38" s="41" t="inlineStr"/>
+      <c r="E38" s="41" t="inlineStr">
         <is>
           <t>Option 2 sends them to</t>
         </is>
       </c>
-      <c r="F37" s="41" t="inlineStr">
+      <c r="F38" s="41" t="inlineStr">
         <is>
           <t>Contractor</t>
         </is>
       </c>
-      <c r="G37" s="41" t="inlineStr">
+      <c r="G38" s="41" t="inlineStr">
         <is>
           <t>DT</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="82" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="82" t="inlineStr">
         <is>
           <t>TF&gt;POS 6</t>
         </is>
       </c>
-      <c r="B38" s="82" t="inlineStr">
+      <c r="B39" s="82" t="inlineStr">
         <is>
           <t>RIM</t>
         </is>
       </c>
-      <c r="C38" s="68" t="n">
-        <v>172</v>
-      </c>
-      <c r="D38" s="66" t="n"/>
-      <c r="E38" s="54" t="inlineStr">
-        <is>
-          <t>KR&gt;FENI KM0</t>
-        </is>
-      </c>
-      <c r="F38" s="83" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="G38" s="61" t="n">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="66" t="n"/>
-      <c r="B39" s="66" t="n"/>
-      <c r="C39" s="66" t="n"/>
+      <c r="C39" s="68" t="n">
+        <v>101</v>
+      </c>
       <c r="D39" s="66" t="n"/>
       <c r="E39" s="54" t="inlineStr">
         <is>
+          <t>KR&gt;FENI KM0</t>
+        </is>
+      </c>
+      <c r="F39" s="83" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="G39" s="61" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="66" t="n"/>
+      <c r="B40" s="66" t="n"/>
+      <c r="C40" s="66" t="n"/>
+      <c r="D40" s="66" t="n"/>
+      <c r="E40" s="54" t="inlineStr">
+        <is>
           <t>TF&gt;FENI KM0</t>
         </is>
       </c>
-      <c r="F39" s="83" t="inlineStr">
+      <c r="F40" s="83" t="inlineStr">
         <is>
           <t>RIM</t>
         </is>
       </c>
-      <c r="G39" s="61" t="n">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="40" t="inlineStr">
+      <c r="G40" s="61" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="40" t="inlineStr">
         <is>
           <t>Scenario 3.1.1 — December</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="41" t="inlineStr"/>
-      <c r="B43" s="41" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="41" t="inlineStr"/>
+      <c r="B44" s="41" t="inlineStr">
         <is>
           <t>Fleet DT</t>
         </is>
       </c>
-      <c r="C43" s="41" t="inlineStr">
+      <c r="C44" s="41" t="inlineStr">
         <is>
           <t>SAP t/mo</t>
         </is>
       </c>
-      <c r="D43" s="41" t="inlineStr">
+      <c r="D44" s="41" t="inlineStr">
         <is>
           <t>LIM-TOS t/mo</t>
         </is>
       </c>
-      <c r="E43" s="41" t="inlineStr">
+      <c r="E44" s="41" t="inlineStr">
         <is>
           <t>LIM-LD t/mo</t>
         </is>
       </c>
-      <c r="F43" s="41" t="inlineStr">
+      <c r="F44" s="41" t="inlineStr">
         <is>
           <t>TOTAL t/mo</t>
         </is>
       </c>
-      <c r="G43" s="41" t="inlineStr">
+      <c r="G44" s="41" t="inlineStr">
         <is>
           <t>What happens</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="42" t="inlineStr">
-        <is>
-          <t>AS FROZEN</t>
-        </is>
-      </c>
-      <c r="B44" s="47" t="n">
-        <v>1281</v>
-      </c>
-      <c r="C44" s="43" t="n">
-        <v>2308694</v>
-      </c>
-      <c r="D44" s="43" t="n">
-        <v>1328877</v>
-      </c>
-      <c r="E44" s="68" t="n">
-        <v>2049937</v>
-      </c>
-      <c r="F44" s="47" t="n">
-        <v>5687508</v>
-      </c>
-      <c r="G44" s="76" t="inlineStr">
-        <is>
-          <t>LD runs 133% of its line — surplus fleet piles onto LD</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="42" t="inlineStr">
         <is>
-          <t>OPTION 1 · park 156 DT</t>
-        </is>
-      </c>
-      <c r="B45" s="52" t="n">
-        <v>1125</v>
+          <t>AS FROZEN</t>
+        </is>
+      </c>
+      <c r="B45" s="47" t="n">
+        <v>1281</v>
       </c>
       <c r="C45" s="43" t="n">
         <v>2308694</v>
@@ -2970,317 +3041,317 @@
       <c r="D45" s="43" t="n">
         <v>1328877</v>
       </c>
-      <c r="E45" s="47" t="n">
-        <v>1545209</v>
-      </c>
-      <c r="F45" s="52" t="n">
-        <v>5182780</v>
-      </c>
-      <c r="G45" s="77" t="inlineStr">
-        <is>
-          <t>LD → 100.0% · 504,728 t NOT hauled · 156 trucks idle</t>
+      <c r="E45" s="68" t="n">
+        <v>2049937</v>
+      </c>
+      <c r="F45" s="47" t="n">
+        <v>5687508</v>
+      </c>
+      <c r="G45" s="76" t="inlineStr">
+        <is>
+          <t>LD runs 121% of its 1,696,393 t line — surplus fleet piles onto LD</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="42" t="inlineStr">
         <is>
-          <t>OPTION 2 · re-dispatch 156 DT</t>
-        </is>
-      </c>
-      <c r="B46" s="61" t="n">
-        <v>1281</v>
-      </c>
-      <c r="C46" s="61" t="n">
-        <v>2902555</v>
+          <t>OPTION 1 · park 109 DT</t>
+        </is>
+      </c>
+      <c r="B46" s="52" t="n">
+        <v>1172</v>
+      </c>
+      <c r="C46" s="43" t="n">
+        <v>2308694</v>
       </c>
       <c r="D46" s="43" t="n">
         <v>1328877</v>
       </c>
       <c r="E46" s="47" t="n">
-        <v>1545209</v>
-      </c>
-      <c r="F46" s="61" t="n">
-        <v>5776641</v>
-      </c>
-      <c r="G46" s="78" t="inlineStr">
-        <is>
-          <t>LD → 100.0% · +593,861 t SAP stock at FeNi KM0 · no truck idle</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="41" t="inlineStr">
+        <v>1697274</v>
+      </c>
+      <c r="F46" s="52" t="n">
+        <v>5334845</v>
+      </c>
+      <c r="G46" s="77" t="inlineStr">
+        <is>
+          <t>LD → 100.0% · 352,663 t NOT hauled · 109 trucks idle</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="42" t="inlineStr">
+        <is>
+          <t>OPTION 2 · re-dispatch 109 DT</t>
+        </is>
+      </c>
+      <c r="B47" s="61" t="n">
+        <v>1281</v>
+      </c>
+      <c r="C47" s="61" t="n">
+        <v>2724032</v>
+      </c>
+      <c r="D47" s="43" t="n">
+        <v>1328877</v>
+      </c>
+      <c r="E47" s="47" t="n">
+        <v>1697274</v>
+      </c>
+      <c r="F47" s="61" t="n">
+        <v>5750183</v>
+      </c>
+      <c r="G47" s="78" t="inlineStr">
+        <is>
+          <t>LD → 100.0% · +415,338 t SAP stock at FeNi KM0 · no truck idle</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="41" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="B48" s="41" t="inlineStr">
+      <c r="B49" s="41" t="inlineStr">
         <is>
           <t>December TARGET t</t>
         </is>
       </c>
-      <c r="C48" s="41" t="inlineStr">
+      <c r="C49" s="41" t="inlineStr">
         <is>
           <t>As frozen</t>
         </is>
       </c>
-      <c r="D48" s="41" t="inlineStr">
+      <c r="D49" s="41" t="inlineStr">
         <is>
           <t>Option 1 (park)</t>
         </is>
       </c>
-      <c r="E48" s="41" t="inlineStr">
+      <c r="E49" s="41" t="inlineStr">
         <is>
           <t>Option 2 (re-dispatch)</t>
         </is>
       </c>
-      <c r="F48" s="41" t="inlineStr"/>
-      <c r="G48" s="41" t="inlineStr">
+      <c r="F49" s="41" t="inlineStr"/>
+      <c r="G49" s="41" t="inlineStr">
         <is>
           <t> </t>
         </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="42" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="B49" s="43" t="n">
-        <v>2311205</v>
-      </c>
-      <c r="C49" s="84" t="n">
-        <v>0.9989135537522634</v>
-      </c>
-      <c r="D49" s="84" t="n">
-        <v>0.9989135537522634</v>
-      </c>
-      <c r="E49" s="45" t="n">
-        <v>1.255862115216954</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="42" t="inlineStr">
         <is>
-          <t>LIM-TOS</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B50" s="43" t="n">
-        <v>1326087</v>
-      </c>
-      <c r="C50" s="45" t="n">
-        <v>1.002103934357248</v>
-      </c>
-      <c r="D50" s="45" t="n">
-        <v>1.002103934357248</v>
+        <v>2311213</v>
+      </c>
+      <c r="C50" s="84" t="n">
+        <v>0.9989100961270121</v>
+      </c>
+      <c r="D50" s="84" t="n">
+        <v>0.9989100961270121</v>
       </c>
       <c r="E50" s="45" t="n">
-        <v>1.002103934357248</v>
+        <v>1.178615731219927</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="42" t="inlineStr">
         <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="B51" s="43" t="n">
+        <v>1326082</v>
+      </c>
+      <c r="C51" s="45" t="n">
+        <v>1.002107712796041</v>
+      </c>
+      <c r="D51" s="45" t="n">
+        <v>1.002107712796041</v>
+      </c>
+      <c r="E51" s="45" t="n">
+        <v>1.002107712796041</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="42" t="inlineStr">
+        <is>
           <t>LIM-LD</t>
         </is>
       </c>
-      <c r="B51" s="43" t="n">
-        <v>1542901</v>
-      </c>
-      <c r="C51" s="45" t="n">
-        <v>1.32862510297161</v>
-      </c>
-      <c r="D51" s="45" t="n">
-        <v>1.00149570529207</v>
-      </c>
-      <c r="E51" s="45" t="n">
-        <v>1.00149570529207</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="60" t="inlineStr">
+      <c r="B52" s="43" t="n">
+        <v>1696393</v>
+      </c>
+      <c r="C52" s="45" t="n">
+        <v>1.20840925422352</v>
+      </c>
+      <c r="D52" s="45" t="n">
+        <v>1.000519511201352</v>
+      </c>
+      <c r="E52" s="45" t="n">
+        <v>1.000519511201352</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="60" t="inlineStr">
         <is>
           <t>TOTAL t/month</t>
         </is>
       </c>
-      <c r="B52" s="43" t="n">
-        <v>5180193</v>
-      </c>
-      <c r="C52" s="43" t="n">
+      <c r="B53" s="43" t="n">
+        <v>5333688</v>
+      </c>
+      <c r="C53" s="43" t="n">
         <v>5687508</v>
       </c>
-      <c r="D52" s="79" t="n">
-        <v>5182780</v>
-      </c>
-      <c r="E52" s="80" t="n">
-        <v>5776641</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="81" t="inlineStr">
-        <is>
-          <t>Which trucks move (same 156 DT in both options)</t>
-        </is>
+      <c r="D53" s="79" t="n">
+        <v>5334845</v>
+      </c>
+      <c r="E53" s="80" t="n">
+        <v>5750183</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="41" t="inlineStr">
+      <c r="A55" s="81" t="inlineStr">
+        <is>
+          <t>Which trucks move (same 109 DT in both options)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="41" t="inlineStr">
         <is>
           <t>Taken off (LIM-LD)</t>
         </is>
       </c>
-      <c r="B55" s="41" t="inlineStr">
+      <c r="B56" s="41" t="inlineStr">
         <is>
           <t>Contractor</t>
         </is>
       </c>
-      <c r="C55" s="41" t="inlineStr">
+      <c r="C56" s="41" t="inlineStr">
         <is>
           <t>DT</t>
         </is>
       </c>
-      <c r="D55" s="41" t="inlineStr"/>
-      <c r="E55" s="41" t="inlineStr">
+      <c r="D56" s="41" t="inlineStr"/>
+      <c r="E56" s="41" t="inlineStr">
         <is>
           <t>Option 2 sends them to</t>
         </is>
       </c>
-      <c r="F55" s="41" t="inlineStr">
+      <c r="F56" s="41" t="inlineStr">
         <is>
           <t>Contractor</t>
         </is>
       </c>
-      <c r="G55" s="41" t="inlineStr">
+      <c r="G56" s="41" t="inlineStr">
         <is>
           <t>DT</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="82" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="82" t="inlineStr">
         <is>
           <t>TF&gt;HUAFEI</t>
         </is>
       </c>
-      <c r="B56" s="82" t="inlineStr">
+      <c r="B57" s="82" t="inlineStr">
         <is>
           <t>RIM</t>
         </is>
       </c>
-      <c r="C56" s="68" t="n">
-        <v>156</v>
-      </c>
-      <c r="D56" s="66" t="n"/>
-      <c r="E56" s="54" t="inlineStr">
-        <is>
-          <t>KR&gt;FENI KM0</t>
-        </is>
-      </c>
-      <c r="F56" s="83" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="G56" s="61" t="n">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="66" t="n"/>
-      <c r="B57" s="66" t="n"/>
-      <c r="C57" s="66" t="n"/>
+      <c r="C57" s="68" t="n">
+        <v>109</v>
+      </c>
       <c r="D57" s="66" t="n"/>
       <c r="E57" s="54" t="inlineStr">
         <is>
+          <t>KR&gt;FENI KM0</t>
+        </is>
+      </c>
+      <c r="F57" s="83" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="G57" s="61" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="66" t="n"/>
+      <c r="B58" s="66" t="n"/>
+      <c r="C58" s="66" t="n"/>
+      <c r="D58" s="66" t="n"/>
+      <c r="E58" s="54" t="inlineStr">
+        <is>
           <t>TF&gt;FENI KM0</t>
         </is>
       </c>
-      <c r="F57" s="83" t="inlineStr">
+      <c r="F58" s="83" t="inlineStr">
         <is>
           <t>RIM</t>
         </is>
       </c>
-      <c r="G57" s="61" t="n">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="40" t="inlineStr">
+      <c r="G58" s="61" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="40" t="inlineStr">
         <is>
           <t>Scenario 3.1.2 — December</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="41" t="inlineStr"/>
-      <c r="B61" s="41" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="41" t="inlineStr"/>
+      <c r="B62" s="41" t="inlineStr">
         <is>
           <t>Fleet DT</t>
         </is>
       </c>
-      <c r="C61" s="41" t="inlineStr">
+      <c r="C62" s="41" t="inlineStr">
         <is>
           <t>SAP t/mo</t>
         </is>
       </c>
-      <c r="D61" s="41" t="inlineStr">
+      <c r="D62" s="41" t="inlineStr">
         <is>
           <t>LIM-TOS t/mo</t>
         </is>
       </c>
-      <c r="E61" s="41" t="inlineStr">
+      <c r="E62" s="41" t="inlineStr">
         <is>
           <t>LIM-LD t/mo</t>
         </is>
       </c>
-      <c r="F61" s="41" t="inlineStr">
+      <c r="F62" s="41" t="inlineStr">
         <is>
           <t>TOTAL t/mo</t>
         </is>
       </c>
-      <c r="G61" s="41" t="inlineStr">
+      <c r="G62" s="41" t="inlineStr">
         <is>
           <t>What happens</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="42" t="inlineStr">
-        <is>
-          <t>AS FROZEN</t>
-        </is>
-      </c>
-      <c r="B62" s="47" t="n">
-        <v>1281</v>
-      </c>
-      <c r="C62" s="43" t="n">
-        <v>2308694</v>
-      </c>
-      <c r="D62" s="43" t="n">
-        <v>1330830</v>
-      </c>
-      <c r="E62" s="68" t="n">
-        <v>2222731</v>
-      </c>
-      <c r="F62" s="47" t="n">
-        <v>5862255</v>
-      </c>
-      <c r="G62" s="76" t="inlineStr">
-        <is>
-          <t>LD runs 144% of its line — surplus fleet piles onto LD</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="42" t="inlineStr">
         <is>
-          <t>OPTION 1 · park 173 DT</t>
-        </is>
-      </c>
-      <c r="B63" s="52" t="n">
-        <v>1108</v>
+          <t>AS FROZEN</t>
+        </is>
+      </c>
+      <c r="B63" s="47" t="n">
+        <v>1281</v>
       </c>
       <c r="C63" s="43" t="n">
         <v>2308694</v>
@@ -3288,247 +3359,304 @@
       <c r="D63" s="43" t="n">
         <v>1330830</v>
       </c>
-      <c r="E63" s="47" t="n">
-        <v>1543053</v>
-      </c>
-      <c r="F63" s="52" t="n">
-        <v>5182577</v>
-      </c>
-      <c r="G63" s="77" t="inlineStr">
-        <is>
-          <t>LD → 100.0% · 679,678 t NOT hauled · 173 trucks idle</t>
+      <c r="E63" s="68" t="n">
+        <v>2222731</v>
+      </c>
+      <c r="F63" s="47" t="n">
+        <v>5862255</v>
+      </c>
+      <c r="G63" s="76" t="inlineStr">
+        <is>
+          <t>LD runs 131% of its 1,696,393 t line — surplus fleet piles onto LD</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="42" t="inlineStr">
         <is>
-          <t>OPTION 2 · re-dispatch 173 DT</t>
-        </is>
-      </c>
-      <c r="B64" s="61" t="n">
-        <v>1281</v>
-      </c>
-      <c r="C64" s="61" t="n">
-        <v>2967667</v>
+          <t>OPTION 1 · park 134 DT</t>
+        </is>
+      </c>
+      <c r="B64" s="52" t="n">
+        <v>1147</v>
+      </c>
+      <c r="C64" s="43" t="n">
+        <v>2308694</v>
       </c>
       <c r="D64" s="43" t="n">
         <v>1330830</v>
       </c>
       <c r="E64" s="47" t="n">
-        <v>1543053</v>
-      </c>
-      <c r="F64" s="61" t="n">
-        <v>5841550</v>
-      </c>
-      <c r="G64" s="78" t="inlineStr">
-        <is>
-          <t>LD → 100.0% · +658,973 t SAP stock at FeNi KM0 · no truck idle</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="41" t="inlineStr">
+        <v>1696615</v>
+      </c>
+      <c r="F64" s="52" t="n">
+        <v>5336139</v>
+      </c>
+      <c r="G64" s="77" t="inlineStr">
+        <is>
+          <t>LD → 100.0% · 526,116 t NOT hauled · 134 trucks idle</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="42" t="inlineStr">
+        <is>
+          <t>OPTION 2 · re-dispatch 134 DT</t>
+        </is>
+      </c>
+      <c r="B65" s="61" t="n">
+        <v>1281</v>
+      </c>
+      <c r="C65" s="61" t="n">
+        <v>2819118</v>
+      </c>
+      <c r="D65" s="43" t="n">
+        <v>1330830</v>
+      </c>
+      <c r="E65" s="47" t="n">
+        <v>1696615</v>
+      </c>
+      <c r="F65" s="61" t="n">
+        <v>5846563</v>
+      </c>
+      <c r="G65" s="78" t="inlineStr">
+        <is>
+          <t>LD → 100.0% · +510,424 t SAP stock at FeNi KM0 · no truck idle</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="41" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="B66" s="41" t="inlineStr">
+      <c r="B67" s="41" t="inlineStr">
         <is>
           <t>December TARGET t</t>
         </is>
       </c>
-      <c r="C66" s="41" t="inlineStr">
+      <c r="C67" s="41" t="inlineStr">
         <is>
           <t>As frozen</t>
         </is>
       </c>
-      <c r="D66" s="41" t="inlineStr">
+      <c r="D67" s="41" t="inlineStr">
         <is>
           <t>Option 1 (park)</t>
         </is>
       </c>
-      <c r="E66" s="41" t="inlineStr">
+      <c r="E67" s="41" t="inlineStr">
         <is>
           <t>Option 2 (re-dispatch)</t>
         </is>
       </c>
-      <c r="F66" s="41" t="inlineStr"/>
-      <c r="G66" s="41" t="inlineStr">
+      <c r="F67" s="41" t="inlineStr"/>
+      <c r="G67" s="41" t="inlineStr">
         <is>
           <t> </t>
         </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="42" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="B67" s="43" t="n">
-        <v>2311205</v>
-      </c>
-      <c r="C67" s="84" t="n">
-        <v>0.9989135537522634</v>
-      </c>
-      <c r="D67" s="84" t="n">
-        <v>0.9989135537522634</v>
-      </c>
-      <c r="E67" s="45" t="n">
-        <v>1.284034605324928</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="42" t="inlineStr">
         <is>
-          <t>LIM-TOS</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B68" s="43" t="n">
-        <v>1326087</v>
-      </c>
-      <c r="C68" s="45" t="n">
-        <v>1.003576688407322</v>
-      </c>
-      <c r="D68" s="45" t="n">
-        <v>1.003576688407322</v>
+        <v>2311213</v>
+      </c>
+      <c r="C68" s="84" t="n">
+        <v>0.9989100961270121</v>
+      </c>
+      <c r="D68" s="84" t="n">
+        <v>0.9989100961270121</v>
       </c>
       <c r="E68" s="45" t="n">
-        <v>1.003576688407322</v>
+        <v>1.219757028019486</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="42" t="inlineStr">
         <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="B69" s="43" t="n">
+        <v>1326082</v>
+      </c>
+      <c r="C69" s="45" t="n">
+        <v>1.003580472399143</v>
+      </c>
+      <c r="D69" s="45" t="n">
+        <v>1.003580472399143</v>
+      </c>
+      <c r="E69" s="45" t="n">
+        <v>1.003580472399143</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="42" t="inlineStr">
+        <is>
           <t>LIM-LD</t>
         </is>
       </c>
-      <c r="B69" s="43" t="n">
-        <v>1542901</v>
-      </c>
-      <c r="C69" s="45" t="n">
-        <v>1.440618030580057</v>
-      </c>
-      <c r="D69" s="45" t="n">
-        <v>1.00009840990102</v>
-      </c>
-      <c r="E69" s="45" t="n">
-        <v>1.00009840990102</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="60" t="inlineStr">
+      <c r="B70" s="43" t="n">
+        <v>1696393</v>
+      </c>
+      <c r="C70" s="45" t="n">
+        <v>1.310268905849057</v>
+      </c>
+      <c r="D70" s="45" t="n">
+        <v>1.000130919236398</v>
+      </c>
+      <c r="E70" s="45" t="n">
+        <v>1.000130919236398</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="60" t="inlineStr">
         <is>
           <t>TOTAL t/month</t>
         </is>
       </c>
-      <c r="B70" s="43" t="n">
-        <v>5180193</v>
-      </c>
-      <c r="C70" s="43" t="n">
+      <c r="B71" s="43" t="n">
+        <v>5333688</v>
+      </c>
+      <c r="C71" s="43" t="n">
         <v>5862255</v>
       </c>
-      <c r="D70" s="79" t="n">
-        <v>5182577</v>
-      </c>
-      <c r="E70" s="80" t="n">
-        <v>5841550</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="81" t="inlineStr">
-        <is>
-          <t>Which trucks move (same 173 DT in both options)</t>
-        </is>
+      <c r="D71" s="79" t="n">
+        <v>5336139</v>
+      </c>
+      <c r="E71" s="80" t="n">
+        <v>5846563</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="41" t="inlineStr">
+      <c r="A73" s="81" t="inlineStr">
+        <is>
+          <t>Which trucks move (same 134 DT in both options)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="41" t="inlineStr">
         <is>
           <t>Taken off (LIM-LD)</t>
         </is>
       </c>
-      <c r="B73" s="41" t="inlineStr">
+      <c r="B74" s="41" t="inlineStr">
         <is>
           <t>Contractor</t>
         </is>
       </c>
-      <c r="C73" s="41" t="inlineStr">
+      <c r="C74" s="41" t="inlineStr">
         <is>
           <t>DT</t>
         </is>
       </c>
-      <c r="D73" s="41" t="inlineStr"/>
-      <c r="E73" s="41" t="inlineStr">
+      <c r="D74" s="41" t="inlineStr"/>
+      <c r="E74" s="41" t="inlineStr">
         <is>
           <t>Option 2 sends them to</t>
         </is>
       </c>
-      <c r="F73" s="41" t="inlineStr">
+      <c r="F74" s="41" t="inlineStr">
         <is>
           <t>Contractor</t>
         </is>
       </c>
-      <c r="G73" s="41" t="inlineStr">
+      <c r="G74" s="41" t="inlineStr">
         <is>
           <t>DT</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="82" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="82" t="inlineStr">
         <is>
           <t>TF&gt;POS 6</t>
         </is>
       </c>
-      <c r="B74" s="82" t="inlineStr">
+      <c r="B75" s="82" t="inlineStr">
         <is>
           <t>RIM</t>
         </is>
       </c>
-      <c r="C74" s="68" t="n">
-        <v>173</v>
-      </c>
-      <c r="D74" s="66" t="n"/>
-      <c r="E74" s="54" t="inlineStr">
-        <is>
-          <t>KR&gt;FENI KM0</t>
-        </is>
-      </c>
-      <c r="F74" s="83" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="G74" s="61" t="n">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="66" t="n"/>
-      <c r="B75" s="66" t="n"/>
-      <c r="C75" s="66" t="n"/>
+      <c r="C75" s="68" t="n">
+        <v>133</v>
+      </c>
       <c r="D75" s="66" t="n"/>
       <c r="E75" s="54" t="inlineStr">
         <is>
+          <t>KR&gt;FENI KM0</t>
+        </is>
+      </c>
+      <c r="F75" s="83" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="G75" s="61" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="82" t="inlineStr">
+        <is>
+          <t>TF&gt;POS 6</t>
+        </is>
+      </c>
+      <c r="B76" s="82" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C76" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="D76" s="66" t="n"/>
+      <c r="E76" s="54" t="inlineStr">
+        <is>
           <t>TF&gt;FENI KM0</t>
         </is>
       </c>
-      <c r="F75" s="83" t="inlineStr">
+      <c r="F76" s="83" t="inlineStr">
         <is>
           <t>RIM</t>
         </is>
       </c>
-      <c r="G75" s="61" t="n">
-        <v>86</v>
+      <c r="G76" s="61" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="66" t="n"/>
+      <c r="B77" s="66" t="n"/>
+      <c r="C77" s="66" t="n"/>
+      <c r="D77" s="66" t="n"/>
+      <c r="E77" s="54" t="inlineStr">
+        <is>
+          <t>KR&gt;FENI KM0</t>
+        </is>
+      </c>
+      <c r="F77" s="83" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="G77" s="61" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A5:H5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/scenario_comparison_dec_options.xlsx
+++ b/reports/scenario_comparison_dec_options.xlsx
@@ -419,7 +419,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="40">
+  <fills count="41">
     <fill>
       <patternFill/>
     </fill>
@@ -650,6 +650,11 @@
         <fgColor rgb="00FFF4DC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFF3FA"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="18">
     <border>
@@ -1011,7 +1016,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1234,6 +1239,22 @@
     </xf>
     <xf numFmtId="164" fontId="47" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="43" fillId="40" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="40" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="49" fillId="40" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="40" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="55" fillId="40" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1647,7 +1668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2292,6 +2313,256 @@
         <v>17791858</v>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" s="50" t="inlineStr">
+        <is>
+          <t>RECLAIMING — WMT moved out of the POS stockpiles (IWIP own fleet)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="28" customHeight="1">
+      <c r="A44" s="49" t="inlineStr">
+        <is>
+          <t>Material we dump INTO a POS has to come back out to the plant. IWIP runs that leg with its own trucks (not in our 1,281 DT and not in the sales tonnage above), and input must equal output — so the reclaim WMT below equals what the plan tips into POS 12 / POS 14 / POS 6 that month. The .2 scenarios reclaim far more because the POS 6 split sends half the TF LD trucks there.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="41" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B45" s="41" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="C45" s="41" t="inlineStr">
+        <is>
+          <t>3.0.2</t>
+        </is>
+      </c>
+      <c r="D45" s="41" t="inlineStr">
+        <is>
+          <t>3.1.1</t>
+        </is>
+      </c>
+      <c r="E45" s="41" t="inlineStr">
+        <is>
+          <t>3.1.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="42" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="B46" s="85" t="n">
+        <v>184890</v>
+      </c>
+      <c r="C46" s="85" t="n">
+        <v>184890</v>
+      </c>
+      <c r="D46" s="85" t="n">
+        <v>184890</v>
+      </c>
+      <c r="E46" s="85" t="n">
+        <v>184890</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="42" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="B47" s="85" t="n">
+        <v>189472</v>
+      </c>
+      <c r="C47" s="85" t="n">
+        <v>1294622</v>
+      </c>
+      <c r="D47" s="85" t="n">
+        <v>189751</v>
+      </c>
+      <c r="E47" s="85" t="n">
+        <v>1129826</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="42" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="B48" s="85" t="n">
+        <v>187650</v>
+      </c>
+      <c r="C48" s="85" t="n">
+        <v>1594740</v>
+      </c>
+      <c r="D48" s="85" t="n">
+        <v>182130</v>
+      </c>
+      <c r="E48" s="85" t="n">
+        <v>1465470</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="42" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="B49" s="85" t="n">
+        <v>194308</v>
+      </c>
+      <c r="C49" s="85" t="n">
+        <v>1476499</v>
+      </c>
+      <c r="D49" s="85" t="n">
+        <v>188449</v>
+      </c>
+      <c r="E49" s="85" t="n">
+        <v>1389141</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="60" t="inlineStr">
+        <is>
+          <t>TOTAL Sep–Dec</t>
+        </is>
+      </c>
+      <c r="B50" s="61" t="n">
+        <v>756320</v>
+      </c>
+      <c r="C50" s="61" t="n">
+        <v>4550751</v>
+      </c>
+      <c r="D50" s="61" t="n">
+        <v>745220</v>
+      </c>
+      <c r="E50" s="61" t="n">
+        <v>4169327</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="42" t="inlineStr">
+        <is>
+          <t>IWIP DT (Dec)</t>
+        </is>
+      </c>
+      <c r="B51" s="43" t="n">
+        <v>29</v>
+      </c>
+      <c r="C51" s="43" t="n">
+        <v>178</v>
+      </c>
+      <c r="D51" s="43" t="n">
+        <v>28</v>
+      </c>
+      <c r="E51" s="43" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="81" t="inlineStr">
+        <is>
+          <t>December reclaim by stockpile (t/month)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="41" t="inlineStr">
+        <is>
+          <t>Stockpile</t>
+        </is>
+      </c>
+      <c r="B54" s="41" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="C54" s="41" t="inlineStr">
+        <is>
+          <t>3.0.2</t>
+        </is>
+      </c>
+      <c r="D54" s="41" t="inlineStr">
+        <is>
+          <t>3.1.1</t>
+        </is>
+      </c>
+      <c r="E54" s="41" t="inlineStr">
+        <is>
+          <t>3.1.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="42" t="inlineStr">
+        <is>
+          <t>POS 12</t>
+        </is>
+      </c>
+      <c r="B55" s="85" t="n">
+        <v>130944</v>
+      </c>
+      <c r="C55" s="85" t="n">
+        <v>130944</v>
+      </c>
+      <c r="D55" s="85" t="n">
+        <v>125116</v>
+      </c>
+      <c r="E55" s="85" t="n">
+        <v>125116</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="42" t="inlineStr">
+        <is>
+          <t>POS 14</t>
+        </is>
+      </c>
+      <c r="B56" s="85" t="n">
+        <v>63364</v>
+      </c>
+      <c r="C56" s="85" t="n">
+        <v>63364</v>
+      </c>
+      <c r="D56" s="85" t="n">
+        <v>63333</v>
+      </c>
+      <c r="E56" s="85" t="n">
+        <v>63333</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="42" t="inlineStr">
+        <is>
+          <t>POS 6</t>
+        </is>
+      </c>
+      <c r="B57" s="86" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C57" s="85" t="n">
+        <v>1282191</v>
+      </c>
+      <c r="D57" s="86" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E57" s="85" t="n">
+        <v>1200692</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2303,7 +2574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H77"/>
+  <dimension ref="A1:H81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2350,6 +2621,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="40" t="inlineStr">
         <is>
@@ -2471,278 +2743,276 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="41" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="87" t="inlineStr">
+        <is>
+          <t>RECLAIMING (IWIP own fleet)</t>
+        </is>
+      </c>
+      <c r="B12" s="88" t="n">
+        <v>29</v>
+      </c>
+      <c r="C12" s="89" t="n"/>
+      <c r="D12" s="89" t="n"/>
+      <c r="E12" s="89" t="n"/>
+      <c r="F12" s="88" t="n">
+        <v>194308</v>
+      </c>
+      <c r="G12" s="90" t="inlineStr">
+        <is>
+          <t>WMT hauled back out of the stockpiles: POS 12 130,944 t · POS 14 63,364 t. Same in all three options — it follows what the plan tips IN, not which option we pick.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="41" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="B13" s="41" t="inlineStr">
+      <c r="B14" s="41" t="inlineStr">
         <is>
           <t>December TARGET t</t>
         </is>
       </c>
-      <c r="C13" s="41" t="inlineStr">
+      <c r="C14" s="41" t="inlineStr">
         <is>
           <t>As frozen</t>
         </is>
       </c>
-      <c r="D13" s="41" t="inlineStr">
+      <c r="D14" s="41" t="inlineStr">
         <is>
           <t>Option 1 (park)</t>
         </is>
       </c>
-      <c r="E13" s="41" t="inlineStr">
+      <c r="E14" s="41" t="inlineStr">
         <is>
           <t>Option 2 (re-dispatch)</t>
         </is>
       </c>
-      <c r="F13" s="41" t="inlineStr"/>
-      <c r="G13" s="41" t="inlineStr">
+      <c r="F14" s="41" t="inlineStr"/>
+      <c r="G14" s="41" t="inlineStr">
         <is>
           <t> </t>
         </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="42" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="B14" s="43" t="n">
-        <v>2311213</v>
-      </c>
-      <c r="C14" s="45" t="n">
-        <v>1.002223075069238</v>
-      </c>
-      <c r="D14" s="45" t="n">
-        <v>1.002223075069238</v>
-      </c>
-      <c r="E14" s="45" t="n">
-        <v>1.109456289835684</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="42" t="inlineStr">
         <is>
-          <t>LIM-TOS</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B15" s="43" t="n">
-        <v>996084</v>
+        <v>2311213</v>
       </c>
       <c r="C15" s="45" t="n">
-        <v>1.003960509354633</v>
+        <v>1.002223075069238</v>
       </c>
       <c r="D15" s="45" t="n">
-        <v>1.003960509354633</v>
+        <v>1.002223075069238</v>
       </c>
       <c r="E15" s="45" t="n">
-        <v>1.003960509354633</v>
+        <v>1.109456289835684</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="42" t="inlineStr">
         <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="B16" s="43" t="n">
+        <v>996084</v>
+      </c>
+      <c r="C16" s="45" t="n">
+        <v>1.003960509354633</v>
+      </c>
+      <c r="D16" s="45" t="n">
+        <v>1.003960509354633</v>
+      </c>
+      <c r="E16" s="45" t="n">
+        <v>1.003960509354633</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="42" t="inlineStr">
+        <is>
           <t>LIM-LD</t>
         </is>
       </c>
-      <c r="B16" s="43" t="n">
+      <c r="B17" s="43" t="n">
         <v>1973655</v>
       </c>
-      <c r="C16" s="45" t="n">
+      <c r="C17" s="45" t="n">
         <v>1.106990836797718</v>
       </c>
-      <c r="D16" s="45" t="n">
+      <c r="D17" s="45" t="n">
         <v>1.000482029580521</v>
       </c>
-      <c r="E16" s="45" t="n">
+      <c r="E17" s="45" t="n">
         <v>1.000482029580521</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="60" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="60" t="inlineStr">
         <is>
           <t>TOTAL t/month</t>
         </is>
       </c>
-      <c r="B17" s="43" t="n">
+      <c r="B18" s="43" t="n">
         <v>5280952</v>
       </c>
-      <c r="C17" s="43" t="n">
+      <c r="C18" s="43" t="n">
         <v>5501198</v>
       </c>
-      <c r="D17" s="79" t="n">
+      <c r="D18" s="79" t="n">
         <v>5290986</v>
       </c>
-      <c r="E17" s="80" t="n">
+      <c r="E18" s="80" t="n">
         <v>5538825</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="81" t="inlineStr">
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="81" t="inlineStr">
         <is>
           <t>Which trucks move (same 65 DT in both options)</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="41" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="41" t="inlineStr">
         <is>
           <t>Taken off (LIM-LD)</t>
         </is>
       </c>
-      <c r="B20" s="41" t="inlineStr">
+      <c r="B21" s="41" t="inlineStr">
         <is>
           <t>Contractor</t>
         </is>
       </c>
-      <c r="C20" s="41" t="inlineStr">
+      <c r="C21" s="41" t="inlineStr">
         <is>
           <t>DT</t>
         </is>
       </c>
-      <c r="D20" s="41" t="inlineStr"/>
-      <c r="E20" s="41" t="inlineStr">
+      <c r="D21" s="41" t="inlineStr"/>
+      <c r="E21" s="41" t="inlineStr">
         <is>
           <t>Option 2 sends them to</t>
         </is>
       </c>
-      <c r="F20" s="41" t="inlineStr">
+      <c r="F21" s="41" t="inlineStr">
         <is>
           <t>Contractor</t>
         </is>
       </c>
-      <c r="G20" s="41" t="inlineStr">
+      <c r="G21" s="41" t="inlineStr">
         <is>
           <t>DT</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="82" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="82" t="inlineStr">
         <is>
           <t>TF&gt;HUAFEI</t>
         </is>
       </c>
-      <c r="B21" s="82" t="inlineStr">
+      <c r="B22" s="82" t="inlineStr">
         <is>
           <t>RIM</t>
         </is>
       </c>
-      <c r="C21" s="68" t="n">
+      <c r="C22" s="68" t="n">
         <v>65</v>
       </c>
-      <c r="D21" s="66" t="n"/>
-      <c r="E21" s="54" t="inlineStr">
-        <is>
-          <t>KR&gt;FENI KM0</t>
-        </is>
-      </c>
-      <c r="F21" s="83" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="G21" s="61" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="66" t="n"/>
-      <c r="B22" s="66" t="n"/>
-      <c r="C22" s="66" t="n"/>
       <c r="D22" s="66" t="n"/>
       <c r="E22" s="54" t="inlineStr">
         <is>
+          <t>KR&gt;FENI KM0</t>
+        </is>
+      </c>
+      <c r="F22" s="83" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="G22" s="61" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="66" t="n"/>
+      <c r="B23" s="66" t="n"/>
+      <c r="C23" s="66" t="n"/>
+      <c r="D23" s="66" t="n"/>
+      <c r="E23" s="54" t="inlineStr">
+        <is>
           <t>TF&gt;FENI KM0</t>
         </is>
       </c>
-      <c r="F22" s="83" t="inlineStr">
+      <c r="F23" s="83" t="inlineStr">
         <is>
           <t>RIM</t>
         </is>
       </c>
-      <c r="G22" s="61" t="n">
+      <c r="G23" s="61" t="n">
         <v>32</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="40" t="inlineStr">
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="40" t="inlineStr">
         <is>
           <t>Scenario 3.0.2 — December</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="41" t="inlineStr"/>
-      <c r="B26" s="41" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="41" t="inlineStr"/>
+      <c r="B27" s="41" t="inlineStr">
         <is>
           <t>Fleet DT</t>
         </is>
       </c>
-      <c r="C26" s="41" t="inlineStr">
+      <c r="C27" s="41" t="inlineStr">
         <is>
           <t>SAP t/mo</t>
         </is>
       </c>
-      <c r="D26" s="41" t="inlineStr">
+      <c r="D27" s="41" t="inlineStr">
         <is>
           <t>LIM-TOS t/mo</t>
         </is>
       </c>
-      <c r="E26" s="41" t="inlineStr">
+      <c r="E27" s="41" t="inlineStr">
         <is>
           <t>LIM-LD t/mo</t>
         </is>
       </c>
-      <c r="F26" s="41" t="inlineStr">
+      <c r="F27" s="41" t="inlineStr">
         <is>
           <t>TOTAL t/mo</t>
         </is>
       </c>
-      <c r="G26" s="41" t="inlineStr">
+      <c r="G27" s="41" t="inlineStr">
         <is>
           <t>What happens</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="42" t="inlineStr">
-        <is>
-          <t>AS FROZEN</t>
-        </is>
-      </c>
-      <c r="B27" s="47" t="n">
-        <v>1281</v>
-      </c>
-      <c r="C27" s="43" t="n">
-        <v>2316134</v>
-      </c>
-      <c r="D27" s="43" t="n">
-        <v>1001827</v>
-      </c>
-      <c r="E27" s="68" t="n">
-        <v>2370849</v>
-      </c>
-      <c r="F27" s="47" t="n">
-        <v>5688810</v>
-      </c>
-      <c r="G27" s="76" t="inlineStr">
-        <is>
-          <t>LD runs 120% of its 1,973,655 t line — surplus fleet piles onto LD</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="42" t="inlineStr">
         <is>
-          <t>OPTION 1 · park 101 DT</t>
-        </is>
-      </c>
-      <c r="B28" s="52" t="n">
-        <v>1180</v>
+          <t>AS FROZEN</t>
+        </is>
+      </c>
+      <c r="B28" s="47" t="n">
+        <v>1281</v>
       </c>
       <c r="C28" s="43" t="n">
         <v>2316134</v>
@@ -2750,29 +3020,29 @@
       <c r="D28" s="43" t="n">
         <v>1001827</v>
       </c>
-      <c r="E28" s="47" t="n">
-        <v>1974352</v>
-      </c>
-      <c r="F28" s="52" t="n">
-        <v>5292313</v>
-      </c>
-      <c r="G28" s="77" t="inlineStr">
-        <is>
-          <t>LD → 100.0% · 396,497 t NOT hauled · 101 trucks idle</t>
+      <c r="E28" s="68" t="n">
+        <v>2370849</v>
+      </c>
+      <c r="F28" s="47" t="n">
+        <v>5688810</v>
+      </c>
+      <c r="G28" s="76" t="inlineStr">
+        <is>
+          <t>LD runs 120% of its 1,973,655 t line — surplus fleet piles onto LD</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="42" t="inlineStr">
         <is>
-          <t>OPTION 2 · re-dispatch 101 DT</t>
-        </is>
-      </c>
-      <c r="B29" s="61" t="n">
-        <v>1281</v>
-      </c>
-      <c r="C29" s="61" t="n">
-        <v>2701018</v>
+          <t>OPTION 1 · park 101 DT</t>
+        </is>
+      </c>
+      <c r="B29" s="52" t="n">
+        <v>1180</v>
+      </c>
+      <c r="C29" s="43" t="n">
+        <v>2316134</v>
       </c>
       <c r="D29" s="43" t="n">
         <v>1001827</v>
@@ -2780,874 +3050,974 @@
       <c r="E29" s="47" t="n">
         <v>1974352</v>
       </c>
-      <c r="F29" s="61" t="n">
+      <c r="F29" s="52" t="n">
+        <v>5292313</v>
+      </c>
+      <c r="G29" s="77" t="inlineStr">
+        <is>
+          <t>LD → 100.0% · 396,497 t NOT hauled · 101 trucks idle</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="42" t="inlineStr">
+        <is>
+          <t>OPTION 2 · re-dispatch 101 DT</t>
+        </is>
+      </c>
+      <c r="B30" s="61" t="n">
+        <v>1281</v>
+      </c>
+      <c r="C30" s="61" t="n">
+        <v>2701018</v>
+      </c>
+      <c r="D30" s="43" t="n">
+        <v>1001827</v>
+      </c>
+      <c r="E30" s="47" t="n">
+        <v>1974352</v>
+      </c>
+      <c r="F30" s="61" t="n">
         <v>5677196</v>
       </c>
-      <c r="G29" s="78" t="inlineStr">
+      <c r="G30" s="78" t="inlineStr">
         <is>
           <t>LD → 100.0% · +384,884 t SAP stock at FeNi KM0 · no truck idle</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="41" t="inlineStr">
+      <c r="A31" s="87" t="inlineStr">
+        <is>
+          <t>RECLAIMING (IWIP own fleet)</t>
+        </is>
+      </c>
+      <c r="B31" s="88" t="n">
+        <v>178</v>
+      </c>
+      <c r="C31" s="89" t="n"/>
+      <c r="D31" s="89" t="n"/>
+      <c r="E31" s="89" t="n"/>
+      <c r="F31" s="88" t="n">
+        <v>1476499</v>
+      </c>
+      <c r="G31" s="90" t="inlineStr">
+        <is>
+          <t>WMT hauled back out of the stockpiles: POS 12 130,944 t · POS 14 63,364 t · POS 6 1,282,191 t. Same in all three options — it follows what the plan tips IN, not which option we pick.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="41" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="B31" s="41" t="inlineStr">
+      <c r="B33" s="41" t="inlineStr">
         <is>
           <t>December TARGET t</t>
         </is>
       </c>
-      <c r="C31" s="41" t="inlineStr">
+      <c r="C33" s="41" t="inlineStr">
         <is>
           <t>As frozen</t>
         </is>
       </c>
-      <c r="D31" s="41" t="inlineStr">
+      <c r="D33" s="41" t="inlineStr">
         <is>
           <t>Option 1 (park)</t>
         </is>
       </c>
-      <c r="E31" s="41" t="inlineStr">
+      <c r="E33" s="41" t="inlineStr">
         <is>
           <t>Option 2 (re-dispatch)</t>
         </is>
       </c>
-      <c r="F31" s="41" t="inlineStr"/>
-      <c r="G31" s="41" t="inlineStr">
+      <c r="F33" s="41" t="inlineStr"/>
+      <c r="G33" s="41" t="inlineStr">
         <is>
           <t> </t>
         </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="42" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="B32" s="43" t="n">
-        <v>2311213</v>
-      </c>
-      <c r="C32" s="45" t="n">
-        <v>1.002129184977758</v>
-      </c>
-      <c r="D32" s="45" t="n">
-        <v>1.002129184977758</v>
-      </c>
-      <c r="E32" s="45" t="n">
-        <v>1.168658016374951</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="42" t="inlineStr">
-        <is>
-          <t>LIM-TOS</t>
-        </is>
-      </c>
-      <c r="B33" s="43" t="n">
-        <v>996084</v>
-      </c>
-      <c r="C33" s="45" t="n">
-        <v>1.005765578003462</v>
-      </c>
-      <c r="D33" s="45" t="n">
-        <v>1.005765578003462</v>
-      </c>
-      <c r="E33" s="45" t="n">
-        <v>1.005765578003462</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="42" t="inlineStr">
         <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B34" s="43" t="n">
+        <v>2311213</v>
+      </c>
+      <c r="C34" s="45" t="n">
+        <v>1.002129184977758</v>
+      </c>
+      <c r="D34" s="45" t="n">
+        <v>1.002129184977758</v>
+      </c>
+      <c r="E34" s="45" t="n">
+        <v>1.168658016374951</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="42" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="B35" s="43" t="n">
+        <v>996084</v>
+      </c>
+      <c r="C35" s="45" t="n">
+        <v>1.005765578003462</v>
+      </c>
+      <c r="D35" s="45" t="n">
+        <v>1.005765578003462</v>
+      </c>
+      <c r="E35" s="45" t="n">
+        <v>1.005765578003462</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="42" t="inlineStr">
+        <is>
           <t>LIM-LD</t>
         </is>
       </c>
-      <c r="B34" s="43" t="n">
+      <c r="B36" s="43" t="n">
         <v>1973655</v>
       </c>
-      <c r="C34" s="45" t="n">
+      <c r="C36" s="45" t="n">
         <v>1.201247938469489</v>
       </c>
-      <c r="D34" s="45" t="n">
+      <c r="D36" s="45" t="n">
         <v>1.000353079511291</v>
       </c>
-      <c r="E34" s="45" t="n">
+      <c r="E36" s="45" t="n">
         <v>1.000353079511291</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="60" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="60" t="inlineStr">
         <is>
           <t>TOTAL t/month</t>
         </is>
       </c>
-      <c r="B35" s="43" t="n">
+      <c r="B37" s="43" t="n">
         <v>5280952</v>
       </c>
-      <c r="C35" s="43" t="n">
+      <c r="C37" s="43" t="n">
         <v>5688810</v>
       </c>
-      <c r="D35" s="79" t="n">
+      <c r="D37" s="79" t="n">
         <v>5292313</v>
       </c>
-      <c r="E35" s="80" t="n">
+      <c r="E37" s="80" t="n">
         <v>5677196</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="81" t="inlineStr">
+    <row r="38"/>
+    <row r="39">
+      <c r="A39" s="81" t="inlineStr">
         <is>
           <t>Which trucks move (same 101 DT in both options)</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="41" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="41" t="inlineStr">
         <is>
           <t>Taken off (LIM-LD)</t>
         </is>
       </c>
-      <c r="B38" s="41" t="inlineStr">
+      <c r="B40" s="41" t="inlineStr">
         <is>
           <t>Contractor</t>
         </is>
       </c>
-      <c r="C38" s="41" t="inlineStr">
+      <c r="C40" s="41" t="inlineStr">
         <is>
           <t>DT</t>
         </is>
       </c>
-      <c r="D38" s="41" t="inlineStr"/>
-      <c r="E38" s="41" t="inlineStr">
+      <c r="D40" s="41" t="inlineStr"/>
+      <c r="E40" s="41" t="inlineStr">
         <is>
           <t>Option 2 sends them to</t>
         </is>
       </c>
-      <c r="F38" s="41" t="inlineStr">
+      <c r="F40" s="41" t="inlineStr">
         <is>
           <t>Contractor</t>
         </is>
       </c>
-      <c r="G38" s="41" t="inlineStr">
+      <c r="G40" s="41" t="inlineStr">
         <is>
           <t>DT</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="82" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="82" t="inlineStr">
         <is>
           <t>TF&gt;POS 6</t>
         </is>
       </c>
-      <c r="B39" s="82" t="inlineStr">
+      <c r="B41" s="82" t="inlineStr">
         <is>
           <t>RIM</t>
         </is>
       </c>
-      <c r="C39" s="68" t="n">
+      <c r="C41" s="68" t="n">
         <v>101</v>
       </c>
-      <c r="D39" s="66" t="n"/>
-      <c r="E39" s="54" t="inlineStr">
+      <c r="D41" s="66" t="n"/>
+      <c r="E41" s="54" t="inlineStr">
         <is>
           <t>KR&gt;FENI KM0</t>
         </is>
       </c>
-      <c r="F39" s="83" t="inlineStr">
+      <c r="F41" s="83" t="inlineStr">
         <is>
           <t>RIM</t>
         </is>
       </c>
-      <c r="G39" s="61" t="n">
+      <c r="G41" s="61" t="n">
         <v>51</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="66" t="n"/>
-      <c r="B40" s="66" t="n"/>
-      <c r="C40" s="66" t="n"/>
-      <c r="D40" s="66" t="n"/>
-      <c r="E40" s="54" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="66" t="n"/>
+      <c r="B42" s="66" t="n"/>
+      <c r="C42" s="66" t="n"/>
+      <c r="D42" s="66" t="n"/>
+      <c r="E42" s="54" t="inlineStr">
         <is>
           <t>TF&gt;FENI KM0</t>
         </is>
       </c>
-      <c r="F40" s="83" t="inlineStr">
+      <c r="F42" s="83" t="inlineStr">
         <is>
           <t>RIM</t>
         </is>
       </c>
-      <c r="G40" s="61" t="n">
+      <c r="G42" s="61" t="n">
         <v>50</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="40" t="inlineStr">
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45">
+      <c r="A45" s="40" t="inlineStr">
         <is>
           <t>Scenario 3.1.1 — December</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="41" t="inlineStr"/>
-      <c r="B44" s="41" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="41" t="inlineStr"/>
+      <c r="B46" s="41" t="inlineStr">
         <is>
           <t>Fleet DT</t>
         </is>
       </c>
-      <c r="C44" s="41" t="inlineStr">
+      <c r="C46" s="41" t="inlineStr">
         <is>
           <t>SAP t/mo</t>
         </is>
       </c>
-      <c r="D44" s="41" t="inlineStr">
+      <c r="D46" s="41" t="inlineStr">
         <is>
           <t>LIM-TOS t/mo</t>
         </is>
       </c>
-      <c r="E44" s="41" t="inlineStr">
+      <c r="E46" s="41" t="inlineStr">
         <is>
           <t>LIM-LD t/mo</t>
         </is>
       </c>
-      <c r="F44" s="41" t="inlineStr">
+      <c r="F46" s="41" t="inlineStr">
         <is>
           <t>TOTAL t/mo</t>
         </is>
       </c>
-      <c r="G44" s="41" t="inlineStr">
+      <c r="G46" s="41" t="inlineStr">
         <is>
           <t>What happens</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="42" t="inlineStr">
-        <is>
-          <t>AS FROZEN</t>
-        </is>
-      </c>
-      <c r="B45" s="47" t="n">
-        <v>1281</v>
-      </c>
-      <c r="C45" s="43" t="n">
-        <v>2308694</v>
-      </c>
-      <c r="D45" s="43" t="n">
-        <v>1328877</v>
-      </c>
-      <c r="E45" s="68" t="n">
-        <v>2049937</v>
-      </c>
-      <c r="F45" s="47" t="n">
-        <v>5687508</v>
-      </c>
-      <c r="G45" s="76" t="inlineStr">
-        <is>
-          <t>LD runs 121% of its 1,696,393 t line — surplus fleet piles onto LD</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="42" t="inlineStr">
-        <is>
-          <t>OPTION 1 · park 109 DT</t>
-        </is>
-      </c>
-      <c r="B46" s="52" t="n">
-        <v>1172</v>
-      </c>
-      <c r="C46" s="43" t="n">
-        <v>2308694</v>
-      </c>
-      <c r="D46" s="43" t="n">
-        <v>1328877</v>
-      </c>
-      <c r="E46" s="47" t="n">
-        <v>1697274</v>
-      </c>
-      <c r="F46" s="52" t="n">
-        <v>5334845</v>
-      </c>
-      <c r="G46" s="77" t="inlineStr">
-        <is>
-          <t>LD → 100.0% · 352,663 t NOT hauled · 109 trucks idle</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="42" t="inlineStr">
         <is>
-          <t>OPTION 2 · re-dispatch 109 DT</t>
-        </is>
-      </c>
-      <c r="B47" s="61" t="n">
+          <t>AS FROZEN</t>
+        </is>
+      </c>
+      <c r="B47" s="47" t="n">
         <v>1281</v>
       </c>
-      <c r="C47" s="61" t="n">
-        <v>2724032</v>
+      <c r="C47" s="43" t="n">
+        <v>2308694</v>
       </c>
       <c r="D47" s="43" t="n">
         <v>1328877</v>
       </c>
-      <c r="E47" s="47" t="n">
+      <c r="E47" s="68" t="n">
+        <v>2049937</v>
+      </c>
+      <c r="F47" s="47" t="n">
+        <v>5687508</v>
+      </c>
+      <c r="G47" s="76" t="inlineStr">
+        <is>
+          <t>LD runs 121% of its 1,696,393 t line — surplus fleet piles onto LD</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="42" t="inlineStr">
+        <is>
+          <t>OPTION 1 · park 109 DT</t>
+        </is>
+      </c>
+      <c r="B48" s="52" t="n">
+        <v>1172</v>
+      </c>
+      <c r="C48" s="43" t="n">
+        <v>2308694</v>
+      </c>
+      <c r="D48" s="43" t="n">
+        <v>1328877</v>
+      </c>
+      <c r="E48" s="47" t="n">
         <v>1697274</v>
       </c>
-      <c r="F47" s="61" t="n">
+      <c r="F48" s="52" t="n">
+        <v>5334845</v>
+      </c>
+      <c r="G48" s="77" t="inlineStr">
+        <is>
+          <t>LD → 100.0% · 352,663 t NOT hauled · 109 trucks idle</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="42" t="inlineStr">
+        <is>
+          <t>OPTION 2 · re-dispatch 109 DT</t>
+        </is>
+      </c>
+      <c r="B49" s="61" t="n">
+        <v>1281</v>
+      </c>
+      <c r="C49" s="61" t="n">
+        <v>2724032</v>
+      </c>
+      <c r="D49" s="43" t="n">
+        <v>1328877</v>
+      </c>
+      <c r="E49" s="47" t="n">
+        <v>1697274</v>
+      </c>
+      <c r="F49" s="61" t="n">
         <v>5750183</v>
       </c>
-      <c r="G47" s="78" t="inlineStr">
+      <c r="G49" s="78" t="inlineStr">
         <is>
           <t>LD → 100.0% · +415,338 t SAP stock at FeNi KM0 · no truck idle</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="41" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="87" t="inlineStr">
+        <is>
+          <t>RECLAIMING (IWIP own fleet)</t>
+        </is>
+      </c>
+      <c r="B50" s="88" t="n">
+        <v>28</v>
+      </c>
+      <c r="C50" s="89" t="n"/>
+      <c r="D50" s="89" t="n"/>
+      <c r="E50" s="89" t="n"/>
+      <c r="F50" s="88" t="n">
+        <v>188449</v>
+      </c>
+      <c r="G50" s="90" t="inlineStr">
+        <is>
+          <t>WMT hauled back out of the stockpiles: POS 12 125,116 t · POS 14 63,333 t. Same in all three options — it follows what the plan tips IN, not which option we pick.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51"/>
+    <row r="52">
+      <c r="A52" s="41" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="B49" s="41" t="inlineStr">
+      <c r="B52" s="41" t="inlineStr">
         <is>
           <t>December TARGET t</t>
         </is>
       </c>
-      <c r="C49" s="41" t="inlineStr">
+      <c r="C52" s="41" t="inlineStr">
         <is>
           <t>As frozen</t>
         </is>
       </c>
-      <c r="D49" s="41" t="inlineStr">
+      <c r="D52" s="41" t="inlineStr">
         <is>
           <t>Option 1 (park)</t>
         </is>
       </c>
-      <c r="E49" s="41" t="inlineStr">
+      <c r="E52" s="41" t="inlineStr">
         <is>
           <t>Option 2 (re-dispatch)</t>
         </is>
       </c>
-      <c r="F49" s="41" t="inlineStr"/>
-      <c r="G49" s="41" t="inlineStr">
+      <c r="F52" s="41" t="inlineStr"/>
+      <c r="G52" s="41" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="42" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="42" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="B50" s="43" t="n">
+      <c r="B53" s="43" t="n">
         <v>2311213</v>
       </c>
-      <c r="C50" s="84" t="n">
+      <c r="C53" s="84" t="n">
         <v>0.9989100961270121</v>
       </c>
-      <c r="D50" s="84" t="n">
+      <c r="D53" s="84" t="n">
         <v>0.9989100961270121</v>
       </c>
-      <c r="E50" s="45" t="n">
+      <c r="E53" s="45" t="n">
         <v>1.178615731219927</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="42" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="42" t="inlineStr">
         <is>
           <t>LIM-TOS</t>
         </is>
       </c>
-      <c r="B51" s="43" t="n">
+      <c r="B54" s="43" t="n">
         <v>1326082</v>
       </c>
-      <c r="C51" s="45" t="n">
+      <c r="C54" s="45" t="n">
         <v>1.002107712796041</v>
       </c>
-      <c r="D51" s="45" t="n">
+      <c r="D54" s="45" t="n">
         <v>1.002107712796041</v>
       </c>
-      <c r="E51" s="45" t="n">
+      <c r="E54" s="45" t="n">
         <v>1.002107712796041</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="42" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="42" t="inlineStr">
         <is>
           <t>LIM-LD</t>
         </is>
       </c>
-      <c r="B52" s="43" t="n">
+      <c r="B55" s="43" t="n">
         <v>1696393</v>
       </c>
-      <c r="C52" s="45" t="n">
+      <c r="C55" s="45" t="n">
         <v>1.20840925422352</v>
       </c>
-      <c r="D52" s="45" t="n">
+      <c r="D55" s="45" t="n">
         <v>1.000519511201352</v>
       </c>
-      <c r="E52" s="45" t="n">
+      <c r="E55" s="45" t="n">
         <v>1.000519511201352</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="60" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="60" t="inlineStr">
         <is>
           <t>TOTAL t/month</t>
         </is>
       </c>
-      <c r="B53" s="43" t="n">
+      <c r="B56" s="43" t="n">
         <v>5333688</v>
       </c>
-      <c r="C53" s="43" t="n">
+      <c r="C56" s="43" t="n">
         <v>5687508</v>
       </c>
-      <c r="D53" s="79" t="n">
+      <c r="D56" s="79" t="n">
         <v>5334845</v>
       </c>
-      <c r="E53" s="80" t="n">
+      <c r="E56" s="80" t="n">
         <v>5750183</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="81" t="inlineStr">
+    <row r="57"/>
+    <row r="58">
+      <c r="A58" s="81" t="inlineStr">
         <is>
           <t>Which trucks move (same 109 DT in both options)</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="41" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="41" t="inlineStr">
         <is>
           <t>Taken off (LIM-LD)</t>
         </is>
       </c>
-      <c r="B56" s="41" t="inlineStr">
+      <c r="B59" s="41" t="inlineStr">
         <is>
           <t>Contractor</t>
         </is>
       </c>
-      <c r="C56" s="41" t="inlineStr">
+      <c r="C59" s="41" t="inlineStr">
         <is>
           <t>DT</t>
         </is>
       </c>
-      <c r="D56" s="41" t="inlineStr"/>
-      <c r="E56" s="41" t="inlineStr">
+      <c r="D59" s="41" t="inlineStr"/>
+      <c r="E59" s="41" t="inlineStr">
         <is>
           <t>Option 2 sends them to</t>
         </is>
       </c>
-      <c r="F56" s="41" t="inlineStr">
+      <c r="F59" s="41" t="inlineStr">
         <is>
           <t>Contractor</t>
         </is>
       </c>
-      <c r="G56" s="41" t="inlineStr">
+      <c r="G59" s="41" t="inlineStr">
         <is>
           <t>DT</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="82" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="82" t="inlineStr">
         <is>
           <t>TF&gt;HUAFEI</t>
         </is>
       </c>
-      <c r="B57" s="82" t="inlineStr">
+      <c r="B60" s="82" t="inlineStr">
         <is>
           <t>RIM</t>
         </is>
       </c>
-      <c r="C57" s="68" t="n">
+      <c r="C60" s="68" t="n">
         <v>109</v>
       </c>
-      <c r="D57" s="66" t="n"/>
-      <c r="E57" s="54" t="inlineStr">
+      <c r="D60" s="66" t="n"/>
+      <c r="E60" s="54" t="inlineStr">
         <is>
           <t>KR&gt;FENI KM0</t>
         </is>
       </c>
-      <c r="F57" s="83" t="inlineStr">
+      <c r="F60" s="83" t="inlineStr">
         <is>
           <t>RIM</t>
         </is>
       </c>
-      <c r="G57" s="61" t="n">
+      <c r="G60" s="61" t="n">
         <v>55</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="66" t="n"/>
-      <c r="B58" s="66" t="n"/>
-      <c r="C58" s="66" t="n"/>
-      <c r="D58" s="66" t="n"/>
-      <c r="E58" s="54" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="66" t="n"/>
+      <c r="B61" s="66" t="n"/>
+      <c r="C61" s="66" t="n"/>
+      <c r="D61" s="66" t="n"/>
+      <c r="E61" s="54" t="inlineStr">
         <is>
           <t>TF&gt;FENI KM0</t>
         </is>
       </c>
-      <c r="F58" s="83" t="inlineStr">
+      <c r="F61" s="83" t="inlineStr">
         <is>
           <t>RIM</t>
         </is>
       </c>
-      <c r="G58" s="61" t="n">
+      <c r="G61" s="61" t="n">
         <v>54</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="40" t="inlineStr">
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64">
+      <c r="A64" s="40" t="inlineStr">
         <is>
           <t>Scenario 3.1.2 — December</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="41" t="inlineStr"/>
-      <c r="B62" s="41" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="41" t="inlineStr"/>
+      <c r="B65" s="41" t="inlineStr">
         <is>
           <t>Fleet DT</t>
         </is>
       </c>
-      <c r="C62" s="41" t="inlineStr">
+      <c r="C65" s="41" t="inlineStr">
         <is>
           <t>SAP t/mo</t>
         </is>
       </c>
-      <c r="D62" s="41" t="inlineStr">
+      <c r="D65" s="41" t="inlineStr">
         <is>
           <t>LIM-TOS t/mo</t>
         </is>
       </c>
-      <c r="E62" s="41" t="inlineStr">
+      <c r="E65" s="41" t="inlineStr">
         <is>
           <t>LIM-LD t/mo</t>
         </is>
       </c>
-      <c r="F62" s="41" t="inlineStr">
+      <c r="F65" s="41" t="inlineStr">
         <is>
           <t>TOTAL t/mo</t>
         </is>
       </c>
-      <c r="G62" s="41" t="inlineStr">
+      <c r="G65" s="41" t="inlineStr">
         <is>
           <t>What happens</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="42" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="42" t="inlineStr">
         <is>
           <t>AS FROZEN</t>
         </is>
       </c>
-      <c r="B63" s="47" t="n">
+      <c r="B66" s="47" t="n">
         <v>1281</v>
       </c>
-      <c r="C63" s="43" t="n">
+      <c r="C66" s="43" t="n">
         <v>2308694</v>
       </c>
-      <c r="D63" s="43" t="n">
+      <c r="D66" s="43" t="n">
         <v>1330830</v>
       </c>
-      <c r="E63" s="68" t="n">
+      <c r="E66" s="68" t="n">
         <v>2222731</v>
       </c>
-      <c r="F63" s="47" t="n">
+      <c r="F66" s="47" t="n">
         <v>5862255</v>
       </c>
-      <c r="G63" s="76" t="inlineStr">
+      <c r="G66" s="76" t="inlineStr">
         <is>
           <t>LD runs 131% of its 1,696,393 t line — surplus fleet piles onto LD</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="42" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="42" t="inlineStr">
         <is>
           <t>OPTION 1 · park 134 DT</t>
         </is>
       </c>
-      <c r="B64" s="52" t="n">
+      <c r="B67" s="52" t="n">
         <v>1147</v>
       </c>
-      <c r="C64" s="43" t="n">
+      <c r="C67" s="43" t="n">
         <v>2308694</v>
       </c>
-      <c r="D64" s="43" t="n">
+      <c r="D67" s="43" t="n">
         <v>1330830</v>
       </c>
-      <c r="E64" s="47" t="n">
+      <c r="E67" s="47" t="n">
         <v>1696615</v>
       </c>
-      <c r="F64" s="52" t="n">
+      <c r="F67" s="52" t="n">
         <v>5336139</v>
       </c>
-      <c r="G64" s="77" t="inlineStr">
+      <c r="G67" s="77" t="inlineStr">
         <is>
           <t>LD → 100.0% · 526,116 t NOT hauled · 134 trucks idle</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="42" t="inlineStr">
-        <is>
-          <t>OPTION 2 · re-dispatch 134 DT</t>
-        </is>
-      </c>
-      <c r="B65" s="61" t="n">
-        <v>1281</v>
-      </c>
-      <c r="C65" s="61" t="n">
-        <v>2819118</v>
-      </c>
-      <c r="D65" s="43" t="n">
-        <v>1330830</v>
-      </c>
-      <c r="E65" s="47" t="n">
-        <v>1696615</v>
-      </c>
-      <c r="F65" s="61" t="n">
-        <v>5846563</v>
-      </c>
-      <c r="G65" s="78" t="inlineStr">
-        <is>
-          <t>LD → 100.0% · +510,424 t SAP stock at FeNi KM0 · no truck idle</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="41" t="inlineStr">
-        <is>
-          <t>Material</t>
-        </is>
-      </c>
-      <c r="B67" s="41" t="inlineStr">
-        <is>
-          <t>December TARGET t</t>
-        </is>
-      </c>
-      <c r="C67" s="41" t="inlineStr">
-        <is>
-          <t>As frozen</t>
-        </is>
-      </c>
-      <c r="D67" s="41" t="inlineStr">
-        <is>
-          <t>Option 1 (park)</t>
-        </is>
-      </c>
-      <c r="E67" s="41" t="inlineStr">
-        <is>
-          <t>Option 2 (re-dispatch)</t>
-        </is>
-      </c>
-      <c r="F67" s="41" t="inlineStr"/>
-      <c r="G67" s="41" t="inlineStr">
-        <is>
-          <t> </t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="42" t="inlineStr">
         <is>
+          <t>OPTION 2 · re-dispatch 134 DT</t>
+        </is>
+      </c>
+      <c r="B68" s="61" t="n">
+        <v>1281</v>
+      </c>
+      <c r="C68" s="61" t="n">
+        <v>2819118</v>
+      </c>
+      <c r="D68" s="43" t="n">
+        <v>1330830</v>
+      </c>
+      <c r="E68" s="47" t="n">
+        <v>1696615</v>
+      </c>
+      <c r="F68" s="61" t="n">
+        <v>5846563</v>
+      </c>
+      <c r="G68" s="78" t="inlineStr">
+        <is>
+          <t>LD → 100.0% · +510,424 t SAP stock at FeNi KM0 · no truck idle</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="87" t="inlineStr">
+        <is>
+          <t>RECLAIMING (IWIP own fleet)</t>
+        </is>
+      </c>
+      <c r="B69" s="88" t="n">
+        <v>167</v>
+      </c>
+      <c r="C69" s="89" t="n"/>
+      <c r="D69" s="89" t="n"/>
+      <c r="E69" s="89" t="n"/>
+      <c r="F69" s="88" t="n">
+        <v>1389141</v>
+      </c>
+      <c r="G69" s="90" t="inlineStr">
+        <is>
+          <t>WMT hauled back out of the stockpiles: POS 12 125,116 t · POS 14 63,333 t · POS 6 1,200,692 t. Same in all three options — it follows what the plan tips IN, not which option we pick.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70"/>
+    <row r="71">
+      <c r="A71" s="41" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="B71" s="41" t="inlineStr">
+        <is>
+          <t>December TARGET t</t>
+        </is>
+      </c>
+      <c r="C71" s="41" t="inlineStr">
+        <is>
+          <t>As frozen</t>
+        </is>
+      </c>
+      <c r="D71" s="41" t="inlineStr">
+        <is>
+          <t>Option 1 (park)</t>
+        </is>
+      </c>
+      <c r="E71" s="41" t="inlineStr">
+        <is>
+          <t>Option 2 (re-dispatch)</t>
+        </is>
+      </c>
+      <c r="F71" s="41" t="inlineStr"/>
+      <c r="G71" s="41" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="42" t="inlineStr">
+        <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="B68" s="43" t="n">
+      <c r="B72" s="43" t="n">
         <v>2311213</v>
       </c>
-      <c r="C68" s="84" t="n">
+      <c r="C72" s="84" t="n">
         <v>0.9989100961270121</v>
       </c>
-      <c r="D68" s="84" t="n">
+      <c r="D72" s="84" t="n">
         <v>0.9989100961270121</v>
       </c>
-      <c r="E68" s="45" t="n">
+      <c r="E72" s="45" t="n">
         <v>1.219757028019486</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="42" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="42" t="inlineStr">
         <is>
           <t>LIM-TOS</t>
         </is>
       </c>
-      <c r="B69" s="43" t="n">
+      <c r="B73" s="43" t="n">
         <v>1326082</v>
       </c>
-      <c r="C69" s="45" t="n">
+      <c r="C73" s="45" t="n">
         <v>1.003580472399143</v>
       </c>
-      <c r="D69" s="45" t="n">
+      <c r="D73" s="45" t="n">
         <v>1.003580472399143</v>
       </c>
-      <c r="E69" s="45" t="n">
+      <c r="E73" s="45" t="n">
         <v>1.003580472399143</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="42" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="42" t="inlineStr">
         <is>
           <t>LIM-LD</t>
         </is>
       </c>
-      <c r="B70" s="43" t="n">
+      <c r="B74" s="43" t="n">
         <v>1696393</v>
       </c>
-      <c r="C70" s="45" t="n">
+      <c r="C74" s="45" t="n">
         <v>1.310268905849057</v>
       </c>
-      <c r="D70" s="45" t="n">
+      <c r="D74" s="45" t="n">
         <v>1.000130919236398</v>
       </c>
-      <c r="E70" s="45" t="n">
+      <c r="E74" s="45" t="n">
         <v>1.000130919236398</v>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="60" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="60" t="inlineStr">
         <is>
           <t>TOTAL t/month</t>
         </is>
       </c>
-      <c r="B71" s="43" t="n">
+      <c r="B75" s="43" t="n">
         <v>5333688</v>
       </c>
-      <c r="C71" s="43" t="n">
+      <c r="C75" s="43" t="n">
         <v>5862255</v>
       </c>
-      <c r="D71" s="79" t="n">
+      <c r="D75" s="79" t="n">
         <v>5336139</v>
       </c>
-      <c r="E71" s="80" t="n">
+      <c r="E75" s="80" t="n">
         <v>5846563</v>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="81" t="inlineStr">
+    <row r="76"/>
+    <row r="77">
+      <c r="A77" s="81" t="inlineStr">
         <is>
           <t>Which trucks move (same 134 DT in both options)</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="41" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="41" t="inlineStr">
         <is>
           <t>Taken off (LIM-LD)</t>
         </is>
       </c>
-      <c r="B74" s="41" t="inlineStr">
+      <c r="B78" s="41" t="inlineStr">
         <is>
           <t>Contractor</t>
         </is>
       </c>
-      <c r="C74" s="41" t="inlineStr">
+      <c r="C78" s="41" t="inlineStr">
         <is>
           <t>DT</t>
         </is>
       </c>
-      <c r="D74" s="41" t="inlineStr"/>
-      <c r="E74" s="41" t="inlineStr">
+      <c r="D78" s="41" t="inlineStr"/>
+      <c r="E78" s="41" t="inlineStr">
         <is>
           <t>Option 2 sends them to</t>
         </is>
       </c>
-      <c r="F74" s="41" t="inlineStr">
+      <c r="F78" s="41" t="inlineStr">
         <is>
           <t>Contractor</t>
         </is>
       </c>
-      <c r="G74" s="41" t="inlineStr">
+      <c r="G78" s="41" t="inlineStr">
         <is>
           <t>DT</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="82" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="82" t="inlineStr">
         <is>
           <t>TF&gt;POS 6</t>
         </is>
       </c>
-      <c r="B75" s="82" t="inlineStr">
+      <c r="B79" s="82" t="inlineStr">
         <is>
           <t>RIM</t>
         </is>
       </c>
-      <c r="C75" s="68" t="n">
+      <c r="C79" s="68" t="n">
         <v>133</v>
       </c>
-      <c r="D75" s="66" t="n"/>
-      <c r="E75" s="54" t="inlineStr">
+      <c r="D79" s="66" t="n"/>
+      <c r="E79" s="54" t="inlineStr">
         <is>
           <t>KR&gt;FENI KM0</t>
         </is>
       </c>
-      <c r="F75" s="83" t="inlineStr">
+      <c r="F79" s="83" t="inlineStr">
         <is>
           <t>RIM</t>
         </is>
       </c>
-      <c r="G75" s="61" t="n">
+      <c r="G79" s="61" t="n">
         <v>67</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="82" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="82" t="inlineStr">
         <is>
           <t>TF&gt;POS 6</t>
         </is>
       </c>
-      <c r="B76" s="82" t="inlineStr">
+      <c r="B80" s="82" t="inlineStr">
         <is>
           <t>SMA</t>
         </is>
       </c>
-      <c r="C76" s="68" t="n">
+      <c r="C80" s="68" t="n">
         <v>1</v>
       </c>
-      <c r="D76" s="66" t="n"/>
-      <c r="E76" s="54" t="inlineStr">
+      <c r="D80" s="66" t="n"/>
+      <c r="E80" s="54" t="inlineStr">
         <is>
           <t>TF&gt;FENI KM0</t>
         </is>
       </c>
-      <c r="F76" s="83" t="inlineStr">
+      <c r="F80" s="83" t="inlineStr">
         <is>
           <t>RIM</t>
         </is>
       </c>
-      <c r="G76" s="61" t="n">
+      <c r="G80" s="61" t="n">
         <v>66</v>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="66" t="n"/>
-      <c r="B77" s="66" t="n"/>
-      <c r="C77" s="66" t="n"/>
-      <c r="D77" s="66" t="n"/>
-      <c r="E77" s="54" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="66" t="n"/>
+      <c r="B81" s="66" t="n"/>
+      <c r="C81" s="66" t="n"/>
+      <c r="D81" s="66" t="n"/>
+      <c r="E81" s="54" t="inlineStr">
         <is>
           <t>KR&gt;FENI KM0</t>
         </is>
       </c>
-      <c r="F77" s="83" t="inlineStr">
+      <c r="F81" s="83" t="inlineStr">
         <is>
           <t>SMA</t>
         </is>
       </c>
-      <c r="G77" s="61" t="n">
+      <c r="G81" s="61" t="n">
         <v>1</v>
       </c>
     </row>

--- a/reports/scenario_comparison_dec_options.xlsx
+++ b/reports/scenario_comparison_dec_options.xlsx
@@ -8,7 +8,8 @@
   <sheets>
     <sheet name="Compare" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="December options" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Insights" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Adjustments" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Insights" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -24,7 +25,7 @@
     <numFmt numFmtId="167" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="168" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="60">
+  <fonts count="62">
     <font>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -418,8 +419,18 @@
       <color rgb="000F4C81"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00A52929"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="001B7A41"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="41">
+  <fills count="42">
     <fill>
       <patternFill/>
     </fill>
@@ -655,6 +666,11 @@
         <fgColor rgb="00EFF3FA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FBE9E9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="18">
     <border>
@@ -1016,7 +1032,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1254,6 +1270,24 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="40" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="55" fillId="40" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="47" fillId="41" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="44" fillId="37" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="37" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2574,7 +2608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H81"/>
+  <dimension ref="A1:H77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2621,7 +2655,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="40" t="inlineStr">
         <is>
@@ -2743,196 +2776,192 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="87" t="inlineStr">
-        <is>
-          <t>RECLAIMING (IWIP own fleet)</t>
-        </is>
-      </c>
-      <c r="B12" s="88" t="n">
-        <v>29</v>
-      </c>
-      <c r="C12" s="89" t="n"/>
-      <c r="D12" s="89" t="n"/>
-      <c r="E12" s="89" t="n"/>
-      <c r="F12" s="88" t="n">
-        <v>194308</v>
-      </c>
-      <c r="G12" s="90" t="inlineStr">
-        <is>
-          <t>WMT hauled back out of the stockpiles: POS 12 130,944 t · POS 14 63,364 t. Same in all three options — it follows what the plan tips IN, not which option we pick.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="13">
+      <c r="A13" s="41" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="B13" s="41" t="inlineStr">
+        <is>
+          <t>December TARGET t</t>
+        </is>
+      </c>
+      <c r="C13" s="41" t="inlineStr">
+        <is>
+          <t>As frozen</t>
+        </is>
+      </c>
+      <c r="D13" s="41" t="inlineStr">
+        <is>
+          <t>Option 1 (park)</t>
+        </is>
+      </c>
+      <c r="E13" s="41" t="inlineStr">
+        <is>
+          <t>Option 2 (re-dispatch)</t>
+        </is>
+      </c>
+      <c r="F13" s="41" t="inlineStr"/>
+      <c r="G13" s="41" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
     <row r="14">
-      <c r="A14" s="41" t="inlineStr">
-        <is>
-          <t>Material</t>
-        </is>
-      </c>
-      <c r="B14" s="41" t="inlineStr">
-        <is>
-          <t>December TARGET t</t>
-        </is>
-      </c>
-      <c r="C14" s="41" t="inlineStr">
-        <is>
-          <t>As frozen</t>
-        </is>
-      </c>
-      <c r="D14" s="41" t="inlineStr">
-        <is>
-          <t>Option 1 (park)</t>
-        </is>
-      </c>
-      <c r="E14" s="41" t="inlineStr">
-        <is>
-          <t>Option 2 (re-dispatch)</t>
-        </is>
-      </c>
-      <c r="F14" s="41" t="inlineStr"/>
-      <c r="G14" s="41" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
+      <c r="A14" s="42" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B14" s="43" t="n">
+        <v>2311213</v>
+      </c>
+      <c r="C14" s="45" t="n">
+        <v>1.002223075069238</v>
+      </c>
+      <c r="D14" s="45" t="n">
+        <v>1.002223075069238</v>
+      </c>
+      <c r="E14" s="45" t="n">
+        <v>1.109456289835684</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="42" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>LIM-TOS</t>
         </is>
       </c>
       <c r="B15" s="43" t="n">
-        <v>2311213</v>
+        <v>996084</v>
       </c>
       <c r="C15" s="45" t="n">
-        <v>1.002223075069238</v>
+        <v>1.003960509354633</v>
       </c>
       <c r="D15" s="45" t="n">
-        <v>1.002223075069238</v>
+        <v>1.003960509354633</v>
       </c>
       <c r="E15" s="45" t="n">
-        <v>1.109456289835684</v>
+        <v>1.003960509354633</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="42" t="inlineStr">
         <is>
-          <t>LIM-TOS</t>
+          <t>LIM-LD</t>
         </is>
       </c>
       <c r="B16" s="43" t="n">
-        <v>996084</v>
+        <v>1973655</v>
       </c>
       <c r="C16" s="45" t="n">
-        <v>1.003960509354633</v>
+        <v>1.106990836797718</v>
       </c>
       <c r="D16" s="45" t="n">
-        <v>1.003960509354633</v>
+        <v>1.000482029580521</v>
       </c>
       <c r="E16" s="45" t="n">
-        <v>1.003960509354633</v>
+        <v>1.000482029580521</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="42" t="inlineStr">
-        <is>
-          <t>LIM-LD</t>
+      <c r="A17" s="60" t="inlineStr">
+        <is>
+          <t>TOTAL t/month</t>
         </is>
       </c>
       <c r="B17" s="43" t="n">
-        <v>1973655</v>
-      </c>
-      <c r="C17" s="45" t="n">
-        <v>1.106990836797718</v>
-      </c>
-      <c r="D17" s="45" t="n">
-        <v>1.000482029580521</v>
-      </c>
-      <c r="E17" s="45" t="n">
-        <v>1.000482029580521</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="60" t="inlineStr">
-        <is>
-          <t>TOTAL t/month</t>
-        </is>
-      </c>
-      <c r="B18" s="43" t="n">
         <v>5280952</v>
       </c>
-      <c r="C18" s="43" t="n">
+      <c r="C17" s="43" t="n">
         <v>5501198</v>
       </c>
-      <c r="D18" s="79" t="n">
+      <c r="D17" s="79" t="n">
         <v>5290986</v>
       </c>
-      <c r="E18" s="80" t="n">
+      <c r="E17" s="80" t="n">
         <v>5538825</v>
       </c>
     </row>
-    <row r="19"/>
+    <row r="19">
+      <c r="A19" s="81" t="inlineStr">
+        <is>
+          <t>Which trucks move (same 65 DT in both options)</t>
+        </is>
+      </c>
+    </row>
     <row r="20">
-      <c r="A20" s="81" t="inlineStr">
-        <is>
-          <t>Which trucks move (same 65 DT in both options)</t>
+      <c r="A20" s="41" t="inlineStr">
+        <is>
+          <t>Taken off (LIM-LD)</t>
+        </is>
+      </c>
+      <c r="B20" s="41" t="inlineStr">
+        <is>
+          <t>Contractor</t>
+        </is>
+      </c>
+      <c r="C20" s="41" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="D20" s="41" t="inlineStr"/>
+      <c r="E20" s="41" t="inlineStr">
+        <is>
+          <t>Option 2 sends them to</t>
+        </is>
+      </c>
+      <c r="F20" s="41" t="inlineStr">
+        <is>
+          <t>Contractor</t>
+        </is>
+      </c>
+      <c r="G20" s="41" t="inlineStr">
+        <is>
+          <t>DT</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="41" t="inlineStr">
-        <is>
-          <t>Taken off (LIM-LD)</t>
-        </is>
-      </c>
-      <c r="B21" s="41" t="inlineStr">
-        <is>
-          <t>Contractor</t>
-        </is>
-      </c>
-      <c r="C21" s="41" t="inlineStr">
-        <is>
-          <t>DT</t>
-        </is>
-      </c>
-      <c r="D21" s="41" t="inlineStr"/>
-      <c r="E21" s="41" t="inlineStr">
-        <is>
-          <t>Option 2 sends them to</t>
-        </is>
-      </c>
-      <c r="F21" s="41" t="inlineStr">
-        <is>
-          <t>Contractor</t>
-        </is>
-      </c>
-      <c r="G21" s="41" t="inlineStr">
-        <is>
-          <t>DT</t>
-        </is>
+      <c r="A21" s="82" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B21" s="82" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C21" s="68" t="n">
+        <v>65</v>
+      </c>
+      <c r="D21" s="66" t="n"/>
+      <c r="E21" s="54" t="inlineStr">
+        <is>
+          <t>KR&gt;FENI KM0</t>
+        </is>
+      </c>
+      <c r="F21" s="83" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="G21" s="61" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="82" t="inlineStr">
-        <is>
-          <t>TF&gt;HUAFEI</t>
-        </is>
-      </c>
-      <c r="B22" s="82" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C22" s="68" t="n">
-        <v>65</v>
-      </c>
+      <c r="A22" s="66" t="n"/>
+      <c r="B22" s="66" t="n"/>
+      <c r="C22" s="66" t="n"/>
       <c r="D22" s="66" t="n"/>
       <c r="E22" s="54" t="inlineStr">
         <is>
-          <t>KR&gt;FENI KM0</t>
+          <t>TF&gt;FENI KM0</t>
         </is>
       </c>
       <c r="F22" s="83" t="inlineStr">
@@ -2941,78 +2970,84 @@
         </is>
       </c>
       <c r="G22" s="61" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="66" t="n"/>
-      <c r="B23" s="66" t="n"/>
-      <c r="C23" s="66" t="n"/>
-      <c r="D23" s="66" t="n"/>
-      <c r="E23" s="54" t="inlineStr">
-        <is>
-          <t>TF&gt;FENI KM0</t>
-        </is>
-      </c>
-      <c r="F23" s="83" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="G23" s="61" t="n">
         <v>32</v>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25"/>
+    <row r="25">
+      <c r="A25" s="40" t="inlineStr">
+        <is>
+          <t>Scenario 3.0.2 — December</t>
+        </is>
+      </c>
+    </row>
     <row r="26">
-      <c r="A26" s="40" t="inlineStr">
-        <is>
-          <t>Scenario 3.0.2 — December</t>
+      <c r="A26" s="41" t="inlineStr"/>
+      <c r="B26" s="41" t="inlineStr">
+        <is>
+          <t>Fleet DT</t>
+        </is>
+      </c>
+      <c r="C26" s="41" t="inlineStr">
+        <is>
+          <t>SAP t/mo</t>
+        </is>
+      </c>
+      <c r="D26" s="41" t="inlineStr">
+        <is>
+          <t>LIM-TOS t/mo</t>
+        </is>
+      </c>
+      <c r="E26" s="41" t="inlineStr">
+        <is>
+          <t>LIM-LD t/mo</t>
+        </is>
+      </c>
+      <c r="F26" s="41" t="inlineStr">
+        <is>
+          <t>TOTAL t/mo</t>
+        </is>
+      </c>
+      <c r="G26" s="41" t="inlineStr">
+        <is>
+          <t>What happens</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="41" t="inlineStr"/>
-      <c r="B27" s="41" t="inlineStr">
-        <is>
-          <t>Fleet DT</t>
-        </is>
-      </c>
-      <c r="C27" s="41" t="inlineStr">
-        <is>
-          <t>SAP t/mo</t>
-        </is>
-      </c>
-      <c r="D27" s="41" t="inlineStr">
-        <is>
-          <t>LIM-TOS t/mo</t>
-        </is>
-      </c>
-      <c r="E27" s="41" t="inlineStr">
-        <is>
-          <t>LIM-LD t/mo</t>
-        </is>
-      </c>
-      <c r="F27" s="41" t="inlineStr">
-        <is>
-          <t>TOTAL t/mo</t>
-        </is>
-      </c>
-      <c r="G27" s="41" t="inlineStr">
-        <is>
-          <t>What happens</t>
+      <c r="A27" s="42" t="inlineStr">
+        <is>
+          <t>AS FROZEN</t>
+        </is>
+      </c>
+      <c r="B27" s="47" t="n">
+        <v>1281</v>
+      </c>
+      <c r="C27" s="43" t="n">
+        <v>2316134</v>
+      </c>
+      <c r="D27" s="43" t="n">
+        <v>1001827</v>
+      </c>
+      <c r="E27" s="68" t="n">
+        <v>2370849</v>
+      </c>
+      <c r="F27" s="47" t="n">
+        <v>5688810</v>
+      </c>
+      <c r="G27" s="76" t="inlineStr">
+        <is>
+          <t>LD runs 120% of its 1,973,655 t line — surplus fleet piles onto LD</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="42" t="inlineStr">
         <is>
-          <t>AS FROZEN</t>
-        </is>
-      </c>
-      <c r="B28" s="47" t="n">
-        <v>1281</v>
+          <t>OPTION 1 · park 101 DT</t>
+        </is>
+      </c>
+      <c r="B28" s="52" t="n">
+        <v>1180</v>
       </c>
       <c r="C28" s="43" t="n">
         <v>2316134</v>
@@ -3020,29 +3055,29 @@
       <c r="D28" s="43" t="n">
         <v>1001827</v>
       </c>
-      <c r="E28" s="68" t="n">
-        <v>2370849</v>
-      </c>
-      <c r="F28" s="47" t="n">
-        <v>5688810</v>
-      </c>
-      <c r="G28" s="76" t="inlineStr">
-        <is>
-          <t>LD runs 120% of its 1,973,655 t line — surplus fleet piles onto LD</t>
+      <c r="E28" s="47" t="n">
+        <v>1974352</v>
+      </c>
+      <c r="F28" s="52" t="n">
+        <v>5292313</v>
+      </c>
+      <c r="G28" s="77" t="inlineStr">
+        <is>
+          <t>LD → 100.0% · 396,497 t NOT hauled · 101 trucks idle</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="42" t="inlineStr">
         <is>
-          <t>OPTION 1 · park 101 DT</t>
-        </is>
-      </c>
-      <c r="B29" s="52" t="n">
-        <v>1180</v>
-      </c>
-      <c r="C29" s="43" t="n">
-        <v>2316134</v>
+          <t>OPTION 2 · re-dispatch 101 DT</t>
+        </is>
+      </c>
+      <c r="B29" s="61" t="n">
+        <v>1281</v>
+      </c>
+      <c r="C29" s="61" t="n">
+        <v>2701018</v>
       </c>
       <c r="D29" s="43" t="n">
         <v>1001827</v>
@@ -3050,974 +3085,874 @@
       <c r="E29" s="47" t="n">
         <v>1974352</v>
       </c>
-      <c r="F29" s="52" t="n">
-        <v>5292313</v>
-      </c>
-      <c r="G29" s="77" t="inlineStr">
-        <is>
-          <t>LD → 100.0% · 396,497 t NOT hauled · 101 trucks idle</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="42" t="inlineStr">
-        <is>
-          <t>OPTION 2 · re-dispatch 101 DT</t>
-        </is>
-      </c>
-      <c r="B30" s="61" t="n">
-        <v>1281</v>
-      </c>
-      <c r="C30" s="61" t="n">
-        <v>2701018</v>
-      </c>
-      <c r="D30" s="43" t="n">
-        <v>1001827</v>
-      </c>
-      <c r="E30" s="47" t="n">
-        <v>1974352</v>
-      </c>
-      <c r="F30" s="61" t="n">
+      <c r="F29" s="61" t="n">
         <v>5677196</v>
       </c>
-      <c r="G30" s="78" t="inlineStr">
+      <c r="G29" s="78" t="inlineStr">
         <is>
           <t>LD → 100.0% · +384,884 t SAP stock at FeNi KM0 · no truck idle</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="87" t="inlineStr">
-        <is>
-          <t>RECLAIMING (IWIP own fleet)</t>
-        </is>
-      </c>
-      <c r="B31" s="88" t="n">
-        <v>178</v>
-      </c>
-      <c r="C31" s="89" t="n"/>
-      <c r="D31" s="89" t="n"/>
-      <c r="E31" s="89" t="n"/>
-      <c r="F31" s="88" t="n">
-        <v>1476499</v>
-      </c>
-      <c r="G31" s="90" t="inlineStr">
-        <is>
-          <t>WMT hauled back out of the stockpiles: POS 12 130,944 t · POS 14 63,364 t · POS 6 1,282,191 t. Same in all three options — it follows what the plan tips IN, not which option we pick.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32"/>
+      <c r="A31" s="41" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="B31" s="41" t="inlineStr">
+        <is>
+          <t>December TARGET t</t>
+        </is>
+      </c>
+      <c r="C31" s="41" t="inlineStr">
+        <is>
+          <t>As frozen</t>
+        </is>
+      </c>
+      <c r="D31" s="41" t="inlineStr">
+        <is>
+          <t>Option 1 (park)</t>
+        </is>
+      </c>
+      <c r="E31" s="41" t="inlineStr">
+        <is>
+          <t>Option 2 (re-dispatch)</t>
+        </is>
+      </c>
+      <c r="F31" s="41" t="inlineStr"/>
+      <c r="G31" s="41" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="42" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B32" s="43" t="n">
+        <v>2311213</v>
+      </c>
+      <c r="C32" s="45" t="n">
+        <v>1.002129184977758</v>
+      </c>
+      <c r="D32" s="45" t="n">
+        <v>1.002129184977758</v>
+      </c>
+      <c r="E32" s="45" t="n">
+        <v>1.168658016374951</v>
+      </c>
+    </row>
     <row r="33">
-      <c r="A33" s="41" t="inlineStr">
-        <is>
-          <t>Material</t>
-        </is>
-      </c>
-      <c r="B33" s="41" t="inlineStr">
-        <is>
-          <t>December TARGET t</t>
-        </is>
-      </c>
-      <c r="C33" s="41" t="inlineStr">
-        <is>
-          <t>As frozen</t>
-        </is>
-      </c>
-      <c r="D33" s="41" t="inlineStr">
-        <is>
-          <t>Option 1 (park)</t>
-        </is>
-      </c>
-      <c r="E33" s="41" t="inlineStr">
-        <is>
-          <t>Option 2 (re-dispatch)</t>
-        </is>
-      </c>
-      <c r="F33" s="41" t="inlineStr"/>
-      <c r="G33" s="41" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
+      <c r="A33" s="42" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="B33" s="43" t="n">
+        <v>996084</v>
+      </c>
+      <c r="C33" s="45" t="n">
+        <v>1.005765578003462</v>
+      </c>
+      <c r="D33" s="45" t="n">
+        <v>1.005765578003462</v>
+      </c>
+      <c r="E33" s="45" t="n">
+        <v>1.005765578003462</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="42" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>LIM-LD</t>
         </is>
       </c>
       <c r="B34" s="43" t="n">
-        <v>2311213</v>
+        <v>1973655</v>
       </c>
       <c r="C34" s="45" t="n">
-        <v>1.002129184977758</v>
+        <v>1.201247938469489</v>
       </c>
       <c r="D34" s="45" t="n">
-        <v>1.002129184977758</v>
+        <v>1.000353079511291</v>
       </c>
       <c r="E34" s="45" t="n">
-        <v>1.168658016374951</v>
+        <v>1.000353079511291</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="42" t="inlineStr">
-        <is>
-          <t>LIM-TOS</t>
+      <c r="A35" s="60" t="inlineStr">
+        <is>
+          <t>TOTAL t/month</t>
         </is>
       </c>
       <c r="B35" s="43" t="n">
-        <v>996084</v>
-      </c>
-      <c r="C35" s="45" t="n">
-        <v>1.005765578003462</v>
-      </c>
-      <c r="D35" s="45" t="n">
-        <v>1.005765578003462</v>
-      </c>
-      <c r="E35" s="45" t="n">
-        <v>1.005765578003462</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="42" t="inlineStr">
-        <is>
-          <t>LIM-LD</t>
-        </is>
-      </c>
-      <c r="B36" s="43" t="n">
-        <v>1973655</v>
-      </c>
-      <c r="C36" s="45" t="n">
-        <v>1.201247938469489</v>
-      </c>
-      <c r="D36" s="45" t="n">
-        <v>1.000353079511291</v>
-      </c>
-      <c r="E36" s="45" t="n">
-        <v>1.000353079511291</v>
+        <v>5280952</v>
+      </c>
+      <c r="C35" s="43" t="n">
+        <v>5688810</v>
+      </c>
+      <c r="D35" s="79" t="n">
+        <v>5292313</v>
+      </c>
+      <c r="E35" s="80" t="n">
+        <v>5677196</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="60" t="inlineStr">
-        <is>
-          <t>TOTAL t/month</t>
-        </is>
-      </c>
-      <c r="B37" s="43" t="n">
-        <v>5280952</v>
-      </c>
-      <c r="C37" s="43" t="n">
-        <v>5688810</v>
-      </c>
-      <c r="D37" s="79" t="n">
-        <v>5292313</v>
-      </c>
-      <c r="E37" s="80" t="n">
-        <v>5677196</v>
-      </c>
-    </row>
-    <row r="38"/>
+      <c r="A37" s="81" t="inlineStr">
+        <is>
+          <t>Which trucks move (same 101 DT in both options)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="41" t="inlineStr">
+        <is>
+          <t>Taken off (LIM-LD)</t>
+        </is>
+      </c>
+      <c r="B38" s="41" t="inlineStr">
+        <is>
+          <t>Contractor</t>
+        </is>
+      </c>
+      <c r="C38" s="41" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="D38" s="41" t="inlineStr"/>
+      <c r="E38" s="41" t="inlineStr">
+        <is>
+          <t>Option 2 sends them to</t>
+        </is>
+      </c>
+      <c r="F38" s="41" t="inlineStr">
+        <is>
+          <t>Contractor</t>
+        </is>
+      </c>
+      <c r="G38" s="41" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+    </row>
     <row r="39">
-      <c r="A39" s="81" t="inlineStr">
-        <is>
-          <t>Which trucks move (same 101 DT in both options)</t>
-        </is>
+      <c r="A39" s="82" t="inlineStr">
+        <is>
+          <t>TF&gt;POS 6</t>
+        </is>
+      </c>
+      <c r="B39" s="82" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C39" s="68" t="n">
+        <v>101</v>
+      </c>
+      <c r="D39" s="66" t="n"/>
+      <c r="E39" s="54" t="inlineStr">
+        <is>
+          <t>KR&gt;FENI KM0</t>
+        </is>
+      </c>
+      <c r="F39" s="83" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="G39" s="61" t="n">
+        <v>51</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="41" t="inlineStr">
-        <is>
-          <t>Taken off (LIM-LD)</t>
-        </is>
-      </c>
-      <c r="B40" s="41" t="inlineStr">
-        <is>
-          <t>Contractor</t>
-        </is>
-      </c>
-      <c r="C40" s="41" t="inlineStr">
-        <is>
-          <t>DT</t>
-        </is>
-      </c>
-      <c r="D40" s="41" t="inlineStr"/>
-      <c r="E40" s="41" t="inlineStr">
-        <is>
-          <t>Option 2 sends them to</t>
-        </is>
-      </c>
-      <c r="F40" s="41" t="inlineStr">
-        <is>
-          <t>Contractor</t>
-        </is>
-      </c>
-      <c r="G40" s="41" t="inlineStr">
-        <is>
-          <t>DT</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="82" t="inlineStr">
-        <is>
-          <t>TF&gt;POS 6</t>
-        </is>
-      </c>
-      <c r="B41" s="82" t="inlineStr">
+      <c r="A40" s="66" t="n"/>
+      <c r="B40" s="66" t="n"/>
+      <c r="C40" s="66" t="n"/>
+      <c r="D40" s="66" t="n"/>
+      <c r="E40" s="54" t="inlineStr">
+        <is>
+          <t>TF&gt;FENI KM0</t>
+        </is>
+      </c>
+      <c r="F40" s="83" t="inlineStr">
         <is>
           <t>RIM</t>
         </is>
       </c>
-      <c r="C41" s="68" t="n">
-        <v>101</v>
-      </c>
-      <c r="D41" s="66" t="n"/>
-      <c r="E41" s="54" t="inlineStr">
-        <is>
-          <t>KR&gt;FENI KM0</t>
-        </is>
-      </c>
-      <c r="F41" s="83" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="G41" s="61" t="n">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="66" t="n"/>
-      <c r="B42" s="66" t="n"/>
-      <c r="C42" s="66" t="n"/>
-      <c r="D42" s="66" t="n"/>
-      <c r="E42" s="54" t="inlineStr">
-        <is>
-          <t>TF&gt;FENI KM0</t>
-        </is>
-      </c>
-      <c r="F42" s="83" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="G42" s="61" t="n">
+      <c r="G40" s="61" t="n">
         <v>50</v>
       </c>
     </row>
-    <row r="43"/>
-    <row r="44"/>
+    <row r="43">
+      <c r="A43" s="40" t="inlineStr">
+        <is>
+          <t>Scenario 3.1.1 — December</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="41" t="inlineStr"/>
+      <c r="B44" s="41" t="inlineStr">
+        <is>
+          <t>Fleet DT</t>
+        </is>
+      </c>
+      <c r="C44" s="41" t="inlineStr">
+        <is>
+          <t>SAP t/mo</t>
+        </is>
+      </c>
+      <c r="D44" s="41" t="inlineStr">
+        <is>
+          <t>LIM-TOS t/mo</t>
+        </is>
+      </c>
+      <c r="E44" s="41" t="inlineStr">
+        <is>
+          <t>LIM-LD t/mo</t>
+        </is>
+      </c>
+      <c r="F44" s="41" t="inlineStr">
+        <is>
+          <t>TOTAL t/mo</t>
+        </is>
+      </c>
+      <c r="G44" s="41" t="inlineStr">
+        <is>
+          <t>What happens</t>
+        </is>
+      </c>
+    </row>
     <row r="45">
-      <c r="A45" s="40" t="inlineStr">
-        <is>
-          <t>Scenario 3.1.1 — December</t>
+      <c r="A45" s="42" t="inlineStr">
+        <is>
+          <t>AS FROZEN</t>
+        </is>
+      </c>
+      <c r="B45" s="47" t="n">
+        <v>1281</v>
+      </c>
+      <c r="C45" s="43" t="n">
+        <v>2308694</v>
+      </c>
+      <c r="D45" s="43" t="n">
+        <v>1328877</v>
+      </c>
+      <c r="E45" s="68" t="n">
+        <v>2049937</v>
+      </c>
+      <c r="F45" s="47" t="n">
+        <v>5687508</v>
+      </c>
+      <c r="G45" s="76" t="inlineStr">
+        <is>
+          <t>LD runs 121% of its 1,696,393 t line — surplus fleet piles onto LD</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="41" t="inlineStr"/>
-      <c r="B46" s="41" t="inlineStr">
-        <is>
-          <t>Fleet DT</t>
-        </is>
-      </c>
-      <c r="C46" s="41" t="inlineStr">
-        <is>
-          <t>SAP t/mo</t>
-        </is>
-      </c>
-      <c r="D46" s="41" t="inlineStr">
-        <is>
-          <t>LIM-TOS t/mo</t>
-        </is>
-      </c>
-      <c r="E46" s="41" t="inlineStr">
-        <is>
-          <t>LIM-LD t/mo</t>
-        </is>
-      </c>
-      <c r="F46" s="41" t="inlineStr">
-        <is>
-          <t>TOTAL t/mo</t>
-        </is>
-      </c>
-      <c r="G46" s="41" t="inlineStr">
-        <is>
-          <t>What happens</t>
+      <c r="A46" s="42" t="inlineStr">
+        <is>
+          <t>OPTION 1 · park 109 DT</t>
+        </is>
+      </c>
+      <c r="B46" s="52" t="n">
+        <v>1172</v>
+      </c>
+      <c r="C46" s="43" t="n">
+        <v>2308694</v>
+      </c>
+      <c r="D46" s="43" t="n">
+        <v>1328877</v>
+      </c>
+      <c r="E46" s="47" t="n">
+        <v>1697274</v>
+      </c>
+      <c r="F46" s="52" t="n">
+        <v>5334845</v>
+      </c>
+      <c r="G46" s="77" t="inlineStr">
+        <is>
+          <t>LD → 100.0% · 352,663 t NOT hauled · 109 trucks idle</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="42" t="inlineStr">
         <is>
-          <t>AS FROZEN</t>
-        </is>
-      </c>
-      <c r="B47" s="47" t="n">
+          <t>OPTION 2 · re-dispatch 109 DT</t>
+        </is>
+      </c>
+      <c r="B47" s="61" t="n">
         <v>1281</v>
       </c>
-      <c r="C47" s="43" t="n">
-        <v>2308694</v>
+      <c r="C47" s="61" t="n">
+        <v>2724032</v>
       </c>
       <c r="D47" s="43" t="n">
         <v>1328877</v>
       </c>
-      <c r="E47" s="68" t="n">
-        <v>2049937</v>
-      </c>
-      <c r="F47" s="47" t="n">
+      <c r="E47" s="47" t="n">
+        <v>1697274</v>
+      </c>
+      <c r="F47" s="61" t="n">
+        <v>5750183</v>
+      </c>
+      <c r="G47" s="78" t="inlineStr">
+        <is>
+          <t>LD → 100.0% · +415,338 t SAP stock at FeNi KM0 · no truck idle</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="41" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="B49" s="41" t="inlineStr">
+        <is>
+          <t>December TARGET t</t>
+        </is>
+      </c>
+      <c r="C49" s="41" t="inlineStr">
+        <is>
+          <t>As frozen</t>
+        </is>
+      </c>
+      <c r="D49" s="41" t="inlineStr">
+        <is>
+          <t>Option 1 (park)</t>
+        </is>
+      </c>
+      <c r="E49" s="41" t="inlineStr">
+        <is>
+          <t>Option 2 (re-dispatch)</t>
+        </is>
+      </c>
+      <c r="F49" s="41" t="inlineStr"/>
+      <c r="G49" s="41" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="42" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B50" s="43" t="n">
+        <v>2311213</v>
+      </c>
+      <c r="C50" s="84" t="n">
+        <v>0.9989100961270121</v>
+      </c>
+      <c r="D50" s="84" t="n">
+        <v>0.9989100961270121</v>
+      </c>
+      <c r="E50" s="45" t="n">
+        <v>1.178615731219927</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="42" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="B51" s="43" t="n">
+        <v>1326082</v>
+      </c>
+      <c r="C51" s="45" t="n">
+        <v>1.002107712796041</v>
+      </c>
+      <c r="D51" s="45" t="n">
+        <v>1.002107712796041</v>
+      </c>
+      <c r="E51" s="45" t="n">
+        <v>1.002107712796041</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="42" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="B52" s="43" t="n">
+        <v>1696393</v>
+      </c>
+      <c r="C52" s="45" t="n">
+        <v>1.20840925422352</v>
+      </c>
+      <c r="D52" s="45" t="n">
+        <v>1.000519511201352</v>
+      </c>
+      <c r="E52" s="45" t="n">
+        <v>1.000519511201352</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="60" t="inlineStr">
+        <is>
+          <t>TOTAL t/month</t>
+        </is>
+      </c>
+      <c r="B53" s="43" t="n">
+        <v>5333688</v>
+      </c>
+      <c r="C53" s="43" t="n">
         <v>5687508</v>
       </c>
-      <c r="G47" s="76" t="inlineStr">
-        <is>
-          <t>LD runs 121% of its 1,696,393 t line — surplus fleet piles onto LD</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="42" t="inlineStr">
-        <is>
-          <t>OPTION 1 · park 109 DT</t>
-        </is>
-      </c>
-      <c r="B48" s="52" t="n">
-        <v>1172</v>
-      </c>
-      <c r="C48" s="43" t="n">
+      <c r="D53" s="79" t="n">
+        <v>5334845</v>
+      </c>
+      <c r="E53" s="80" t="n">
+        <v>5750183</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="81" t="inlineStr">
+        <is>
+          <t>Which trucks move (same 109 DT in both options)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="41" t="inlineStr">
+        <is>
+          <t>Taken off (LIM-LD)</t>
+        </is>
+      </c>
+      <c r="B56" s="41" t="inlineStr">
+        <is>
+          <t>Contractor</t>
+        </is>
+      </c>
+      <c r="C56" s="41" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="D56" s="41" t="inlineStr"/>
+      <c r="E56" s="41" t="inlineStr">
+        <is>
+          <t>Option 2 sends them to</t>
+        </is>
+      </c>
+      <c r="F56" s="41" t="inlineStr">
+        <is>
+          <t>Contractor</t>
+        </is>
+      </c>
+      <c r="G56" s="41" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="82" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B57" s="82" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C57" s="68" t="n">
+        <v>109</v>
+      </c>
+      <c r="D57" s="66" t="n"/>
+      <c r="E57" s="54" t="inlineStr">
+        <is>
+          <t>KR&gt;FENI KM0</t>
+        </is>
+      </c>
+      <c r="F57" s="83" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="G57" s="61" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="66" t="n"/>
+      <c r="B58" s="66" t="n"/>
+      <c r="C58" s="66" t="n"/>
+      <c r="D58" s="66" t="n"/>
+      <c r="E58" s="54" t="inlineStr">
+        <is>
+          <t>TF&gt;FENI KM0</t>
+        </is>
+      </c>
+      <c r="F58" s="83" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="G58" s="61" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="40" t="inlineStr">
+        <is>
+          <t>Scenario 3.1.2 — December</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="41" t="inlineStr"/>
+      <c r="B62" s="41" t="inlineStr">
+        <is>
+          <t>Fleet DT</t>
+        </is>
+      </c>
+      <c r="C62" s="41" t="inlineStr">
+        <is>
+          <t>SAP t/mo</t>
+        </is>
+      </c>
+      <c r="D62" s="41" t="inlineStr">
+        <is>
+          <t>LIM-TOS t/mo</t>
+        </is>
+      </c>
+      <c r="E62" s="41" t="inlineStr">
+        <is>
+          <t>LIM-LD t/mo</t>
+        </is>
+      </c>
+      <c r="F62" s="41" t="inlineStr">
+        <is>
+          <t>TOTAL t/mo</t>
+        </is>
+      </c>
+      <c r="G62" s="41" t="inlineStr">
+        <is>
+          <t>What happens</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="42" t="inlineStr">
+        <is>
+          <t>AS FROZEN</t>
+        </is>
+      </c>
+      <c r="B63" s="47" t="n">
+        <v>1281</v>
+      </c>
+      <c r="C63" s="43" t="n">
         <v>2308694</v>
       </c>
-      <c r="D48" s="43" t="n">
-        <v>1328877</v>
-      </c>
-      <c r="E48" s="47" t="n">
-        <v>1697274</v>
-      </c>
-      <c r="F48" s="52" t="n">
-        <v>5334845</v>
-      </c>
-      <c r="G48" s="77" t="inlineStr">
-        <is>
-          <t>LD → 100.0% · 352,663 t NOT hauled · 109 trucks idle</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="42" t="inlineStr">
-        <is>
-          <t>OPTION 2 · re-dispatch 109 DT</t>
-        </is>
-      </c>
-      <c r="B49" s="61" t="n">
+      <c r="D63" s="43" t="n">
+        <v>1330830</v>
+      </c>
+      <c r="E63" s="68" t="n">
+        <v>2222731</v>
+      </c>
+      <c r="F63" s="47" t="n">
+        <v>5862255</v>
+      </c>
+      <c r="G63" s="76" t="inlineStr">
+        <is>
+          <t>LD runs 131% of its 1,696,393 t line — surplus fleet piles onto LD</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="42" t="inlineStr">
+        <is>
+          <t>OPTION 1 · park 134 DT</t>
+        </is>
+      </c>
+      <c r="B64" s="52" t="n">
+        <v>1147</v>
+      </c>
+      <c r="C64" s="43" t="n">
+        <v>2308694</v>
+      </c>
+      <c r="D64" s="43" t="n">
+        <v>1330830</v>
+      </c>
+      <c r="E64" s="47" t="n">
+        <v>1696615</v>
+      </c>
+      <c r="F64" s="52" t="n">
+        <v>5336139</v>
+      </c>
+      <c r="G64" s="77" t="inlineStr">
+        <is>
+          <t>LD → 100.0% · 526,116 t NOT hauled · 134 trucks idle</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="42" t="inlineStr">
+        <is>
+          <t>OPTION 2 · re-dispatch 134 DT</t>
+        </is>
+      </c>
+      <c r="B65" s="61" t="n">
         <v>1281</v>
       </c>
-      <c r="C49" s="61" t="n">
-        <v>2724032</v>
-      </c>
-      <c r="D49" s="43" t="n">
-        <v>1328877</v>
-      </c>
-      <c r="E49" s="47" t="n">
-        <v>1697274</v>
-      </c>
-      <c r="F49" s="61" t="n">
-        <v>5750183</v>
-      </c>
-      <c r="G49" s="78" t="inlineStr">
-        <is>
-          <t>LD → 100.0% · +415,338 t SAP stock at FeNi KM0 · no truck idle</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="87" t="inlineStr">
-        <is>
-          <t>RECLAIMING (IWIP own fleet)</t>
-        </is>
-      </c>
-      <c r="B50" s="88" t="n">
-        <v>28</v>
-      </c>
-      <c r="C50" s="89" t="n"/>
-      <c r="D50" s="89" t="n"/>
-      <c r="E50" s="89" t="n"/>
-      <c r="F50" s="88" t="n">
-        <v>188449</v>
-      </c>
-      <c r="G50" s="90" t="inlineStr">
-        <is>
-          <t>WMT hauled back out of the stockpiles: POS 12 125,116 t · POS 14 63,333 t. Same in all three options — it follows what the plan tips IN, not which option we pick.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51"/>
-    <row r="52">
-      <c r="A52" s="41" t="inlineStr">
+      <c r="C65" s="61" t="n">
+        <v>2819118</v>
+      </c>
+      <c r="D65" s="43" t="n">
+        <v>1330830</v>
+      </c>
+      <c r="E65" s="47" t="n">
+        <v>1696615</v>
+      </c>
+      <c r="F65" s="61" t="n">
+        <v>5846563</v>
+      </c>
+      <c r="G65" s="78" t="inlineStr">
+        <is>
+          <t>LD → 100.0% · +510,424 t SAP stock at FeNi KM0 · no truck idle</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="41" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="B52" s="41" t="inlineStr">
+      <c r="B67" s="41" t="inlineStr">
         <is>
           <t>December TARGET t</t>
         </is>
       </c>
-      <c r="C52" s="41" t="inlineStr">
+      <c r="C67" s="41" t="inlineStr">
         <is>
           <t>As frozen</t>
         </is>
       </c>
-      <c r="D52" s="41" t="inlineStr">
+      <c r="D67" s="41" t="inlineStr">
         <is>
           <t>Option 1 (park)</t>
         </is>
       </c>
-      <c r="E52" s="41" t="inlineStr">
+      <c r="E67" s="41" t="inlineStr">
         <is>
           <t>Option 2 (re-dispatch)</t>
         </is>
       </c>
-      <c r="F52" s="41" t="inlineStr"/>
-      <c r="G52" s="41" t="inlineStr">
+      <c r="F67" s="41" t="inlineStr"/>
+      <c r="G67" s="41" t="inlineStr">
         <is>
           <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="42" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="B53" s="43" t="n">
-        <v>2311213</v>
-      </c>
-      <c r="C53" s="84" t="n">
-        <v>0.9989100961270121</v>
-      </c>
-      <c r="D53" s="84" t="n">
-        <v>0.9989100961270121</v>
-      </c>
-      <c r="E53" s="45" t="n">
-        <v>1.178615731219927</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="42" t="inlineStr">
-        <is>
-          <t>LIM-TOS</t>
-        </is>
-      </c>
-      <c r="B54" s="43" t="n">
-        <v>1326082</v>
-      </c>
-      <c r="C54" s="45" t="n">
-        <v>1.002107712796041</v>
-      </c>
-      <c r="D54" s="45" t="n">
-        <v>1.002107712796041</v>
-      </c>
-      <c r="E54" s="45" t="n">
-        <v>1.002107712796041</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="42" t="inlineStr">
-        <is>
-          <t>LIM-LD</t>
-        </is>
-      </c>
-      <c r="B55" s="43" t="n">
-        <v>1696393</v>
-      </c>
-      <c r="C55" s="45" t="n">
-        <v>1.20840925422352</v>
-      </c>
-      <c r="D55" s="45" t="n">
-        <v>1.000519511201352</v>
-      </c>
-      <c r="E55" s="45" t="n">
-        <v>1.000519511201352</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="60" t="inlineStr">
-        <is>
-          <t>TOTAL t/month</t>
-        </is>
-      </c>
-      <c r="B56" s="43" t="n">
-        <v>5333688</v>
-      </c>
-      <c r="C56" s="43" t="n">
-        <v>5687508</v>
-      </c>
-      <c r="D56" s="79" t="n">
-        <v>5334845</v>
-      </c>
-      <c r="E56" s="80" t="n">
-        <v>5750183</v>
-      </c>
-    </row>
-    <row r="57"/>
-    <row r="58">
-      <c r="A58" s="81" t="inlineStr">
-        <is>
-          <t>Which trucks move (same 109 DT in both options)</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="41" t="inlineStr">
-        <is>
-          <t>Taken off (LIM-LD)</t>
-        </is>
-      </c>
-      <c r="B59" s="41" t="inlineStr">
-        <is>
-          <t>Contractor</t>
-        </is>
-      </c>
-      <c r="C59" s="41" t="inlineStr">
-        <is>
-          <t>DT</t>
-        </is>
-      </c>
-      <c r="D59" s="41" t="inlineStr"/>
-      <c r="E59" s="41" t="inlineStr">
-        <is>
-          <t>Option 2 sends them to</t>
-        </is>
-      </c>
-      <c r="F59" s="41" t="inlineStr">
-        <is>
-          <t>Contractor</t>
-        </is>
-      </c>
-      <c r="G59" s="41" t="inlineStr">
-        <is>
-          <t>DT</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="82" t="inlineStr">
-        <is>
-          <t>TF&gt;HUAFEI</t>
-        </is>
-      </c>
-      <c r="B60" s="82" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C60" s="68" t="n">
-        <v>109</v>
-      </c>
-      <c r="D60" s="66" t="n"/>
-      <c r="E60" s="54" t="inlineStr">
-        <is>
-          <t>KR&gt;FENI KM0</t>
-        </is>
-      </c>
-      <c r="F60" s="83" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="G60" s="61" t="n">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="66" t="n"/>
-      <c r="B61" s="66" t="n"/>
-      <c r="C61" s="66" t="n"/>
-      <c r="D61" s="66" t="n"/>
-      <c r="E61" s="54" t="inlineStr">
-        <is>
-          <t>TF&gt;FENI KM0</t>
-        </is>
-      </c>
-      <c r="F61" s="83" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="G61" s="61" t="n">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64">
-      <c r="A64" s="40" t="inlineStr">
-        <is>
-          <t>Scenario 3.1.2 — December</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="41" t="inlineStr"/>
-      <c r="B65" s="41" t="inlineStr">
-        <is>
-          <t>Fleet DT</t>
-        </is>
-      </c>
-      <c r="C65" s="41" t="inlineStr">
-        <is>
-          <t>SAP t/mo</t>
-        </is>
-      </c>
-      <c r="D65" s="41" t="inlineStr">
-        <is>
-          <t>LIM-TOS t/mo</t>
-        </is>
-      </c>
-      <c r="E65" s="41" t="inlineStr">
-        <is>
-          <t>LIM-LD t/mo</t>
-        </is>
-      </c>
-      <c r="F65" s="41" t="inlineStr">
-        <is>
-          <t>TOTAL t/mo</t>
-        </is>
-      </c>
-      <c r="G65" s="41" t="inlineStr">
-        <is>
-          <t>What happens</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="42" t="inlineStr">
-        <is>
-          <t>AS FROZEN</t>
-        </is>
-      </c>
-      <c r="B66" s="47" t="n">
-        <v>1281</v>
-      </c>
-      <c r="C66" s="43" t="n">
-        <v>2308694</v>
-      </c>
-      <c r="D66" s="43" t="n">
-        <v>1330830</v>
-      </c>
-      <c r="E66" s="68" t="n">
-        <v>2222731</v>
-      </c>
-      <c r="F66" s="47" t="n">
-        <v>5862255</v>
-      </c>
-      <c r="G66" s="76" t="inlineStr">
-        <is>
-          <t>LD runs 131% of its 1,696,393 t line — surplus fleet piles onto LD</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="42" t="inlineStr">
-        <is>
-          <t>OPTION 1 · park 134 DT</t>
-        </is>
-      </c>
-      <c r="B67" s="52" t="n">
-        <v>1147</v>
-      </c>
-      <c r="C67" s="43" t="n">
-        <v>2308694</v>
-      </c>
-      <c r="D67" s="43" t="n">
-        <v>1330830</v>
-      </c>
-      <c r="E67" s="47" t="n">
-        <v>1696615</v>
-      </c>
-      <c r="F67" s="52" t="n">
-        <v>5336139</v>
-      </c>
-      <c r="G67" s="77" t="inlineStr">
-        <is>
-          <t>LD → 100.0% · 526,116 t NOT hauled · 134 trucks idle</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="42" t="inlineStr">
         <is>
-          <t>OPTION 2 · re-dispatch 134 DT</t>
-        </is>
-      </c>
-      <c r="B68" s="61" t="n">
-        <v>1281</v>
-      </c>
-      <c r="C68" s="61" t="n">
-        <v>2819118</v>
-      </c>
-      <c r="D68" s="43" t="n">
-        <v>1330830</v>
-      </c>
-      <c r="E68" s="47" t="n">
-        <v>1696615</v>
-      </c>
-      <c r="F68" s="61" t="n">
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B68" s="43" t="n">
+        <v>2311213</v>
+      </c>
+      <c r="C68" s="84" t="n">
+        <v>0.9989100961270121</v>
+      </c>
+      <c r="D68" s="84" t="n">
+        <v>0.9989100961270121</v>
+      </c>
+      <c r="E68" s="45" t="n">
+        <v>1.219757028019486</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="42" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="B69" s="43" t="n">
+        <v>1326082</v>
+      </c>
+      <c r="C69" s="45" t="n">
+        <v>1.003580472399143</v>
+      </c>
+      <c r="D69" s="45" t="n">
+        <v>1.003580472399143</v>
+      </c>
+      <c r="E69" s="45" t="n">
+        <v>1.003580472399143</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="42" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="B70" s="43" t="n">
+        <v>1696393</v>
+      </c>
+      <c r="C70" s="45" t="n">
+        <v>1.310268905849057</v>
+      </c>
+      <c r="D70" s="45" t="n">
+        <v>1.000130919236398</v>
+      </c>
+      <c r="E70" s="45" t="n">
+        <v>1.000130919236398</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="60" t="inlineStr">
+        <is>
+          <t>TOTAL t/month</t>
+        </is>
+      </c>
+      <c r="B71" s="43" t="n">
+        <v>5333688</v>
+      </c>
+      <c r="C71" s="43" t="n">
+        <v>5862255</v>
+      </c>
+      <c r="D71" s="79" t="n">
+        <v>5336139</v>
+      </c>
+      <c r="E71" s="80" t="n">
         <v>5846563</v>
       </c>
-      <c r="G68" s="78" t="inlineStr">
-        <is>
-          <t>LD → 100.0% · +510,424 t SAP stock at FeNi KM0 · no truck idle</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="87" t="inlineStr">
-        <is>
-          <t>RECLAIMING (IWIP own fleet)</t>
-        </is>
-      </c>
-      <c r="B69" s="88" t="n">
-        <v>167</v>
-      </c>
-      <c r="C69" s="89" t="n"/>
-      <c r="D69" s="89" t="n"/>
-      <c r="E69" s="89" t="n"/>
-      <c r="F69" s="88" t="n">
-        <v>1389141</v>
-      </c>
-      <c r="G69" s="90" t="inlineStr">
-        <is>
-          <t>WMT hauled back out of the stockpiles: POS 12 125,116 t · POS 14 63,333 t · POS 6 1,200,692 t. Same in all three options — it follows what the plan tips IN, not which option we pick.</t>
-        </is>
-      </c>
-    </row>
-    <row r="70"/>
-    <row r="71">
-      <c r="A71" s="41" t="inlineStr">
-        <is>
-          <t>Material</t>
-        </is>
-      </c>
-      <c r="B71" s="41" t="inlineStr">
-        <is>
-          <t>December TARGET t</t>
-        </is>
-      </c>
-      <c r="C71" s="41" t="inlineStr">
-        <is>
-          <t>As frozen</t>
-        </is>
-      </c>
-      <c r="D71" s="41" t="inlineStr">
-        <is>
-          <t>Option 1 (park)</t>
-        </is>
-      </c>
-      <c r="E71" s="41" t="inlineStr">
-        <is>
-          <t>Option 2 (re-dispatch)</t>
-        </is>
-      </c>
-      <c r="F71" s="41" t="inlineStr"/>
-      <c r="G71" s="41" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="42" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="B72" s="43" t="n">
-        <v>2311213</v>
-      </c>
-      <c r="C72" s="84" t="n">
-        <v>0.9989100961270121</v>
-      </c>
-      <c r="D72" s="84" t="n">
-        <v>0.9989100961270121</v>
-      </c>
-      <c r="E72" s="45" t="n">
-        <v>1.219757028019486</v>
-      </c>
     </row>
     <row r="73">
-      <c r="A73" s="42" t="inlineStr">
-        <is>
-          <t>LIM-TOS</t>
-        </is>
-      </c>
-      <c r="B73" s="43" t="n">
-        <v>1326082</v>
-      </c>
-      <c r="C73" s="45" t="n">
-        <v>1.003580472399143</v>
-      </c>
-      <c r="D73" s="45" t="n">
-        <v>1.003580472399143</v>
-      </c>
-      <c r="E73" s="45" t="n">
-        <v>1.003580472399143</v>
+      <c r="A73" s="81" t="inlineStr">
+        <is>
+          <t>Which trucks move (same 134 DT in both options)</t>
+        </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="42" t="inlineStr">
-        <is>
-          <t>LIM-LD</t>
-        </is>
-      </c>
-      <c r="B74" s="43" t="n">
-        <v>1696393</v>
-      </c>
-      <c r="C74" s="45" t="n">
-        <v>1.310268905849057</v>
-      </c>
-      <c r="D74" s="45" t="n">
-        <v>1.000130919236398</v>
-      </c>
-      <c r="E74" s="45" t="n">
-        <v>1.000130919236398</v>
+      <c r="A74" s="41" t="inlineStr">
+        <is>
+          <t>Taken off (LIM-LD)</t>
+        </is>
+      </c>
+      <c r="B74" s="41" t="inlineStr">
+        <is>
+          <t>Contractor</t>
+        </is>
+      </c>
+      <c r="C74" s="41" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="D74" s="41" t="inlineStr"/>
+      <c r="E74" s="41" t="inlineStr">
+        <is>
+          <t>Option 2 sends them to</t>
+        </is>
+      </c>
+      <c r="F74" s="41" t="inlineStr">
+        <is>
+          <t>Contractor</t>
+        </is>
+      </c>
+      <c r="G74" s="41" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="60" t="inlineStr">
-        <is>
-          <t>TOTAL t/month</t>
-        </is>
-      </c>
-      <c r="B75" s="43" t="n">
-        <v>5333688</v>
-      </c>
-      <c r="C75" s="43" t="n">
-        <v>5862255</v>
-      </c>
-      <c r="D75" s="79" t="n">
-        <v>5336139</v>
-      </c>
-      <c r="E75" s="80" t="n">
-        <v>5846563</v>
-      </c>
-    </row>
-    <row r="76"/>
+      <c r="A75" s="82" t="inlineStr">
+        <is>
+          <t>TF&gt;POS 6</t>
+        </is>
+      </c>
+      <c r="B75" s="82" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C75" s="68" t="n">
+        <v>133</v>
+      </c>
+      <c r="D75" s="66" t="n"/>
+      <c r="E75" s="54" t="inlineStr">
+        <is>
+          <t>KR&gt;FENI KM0</t>
+        </is>
+      </c>
+      <c r="F75" s="83" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="G75" s="61" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="82" t="inlineStr">
+        <is>
+          <t>TF&gt;POS 6</t>
+        </is>
+      </c>
+      <c r="B76" s="82" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C76" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="D76" s="66" t="n"/>
+      <c r="E76" s="54" t="inlineStr">
+        <is>
+          <t>TF&gt;FENI KM0</t>
+        </is>
+      </c>
+      <c r="F76" s="83" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="G76" s="61" t="n">
+        <v>66</v>
+      </c>
+    </row>
     <row r="77">
-      <c r="A77" s="81" t="inlineStr">
-        <is>
-          <t>Which trucks move (same 134 DT in both options)</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="41" t="inlineStr">
-        <is>
-          <t>Taken off (LIM-LD)</t>
-        </is>
-      </c>
-      <c r="B78" s="41" t="inlineStr">
-        <is>
-          <t>Contractor</t>
-        </is>
-      </c>
-      <c r="C78" s="41" t="inlineStr">
-        <is>
-          <t>DT</t>
-        </is>
-      </c>
-      <c r="D78" s="41" t="inlineStr"/>
-      <c r="E78" s="41" t="inlineStr">
-        <is>
-          <t>Option 2 sends them to</t>
-        </is>
-      </c>
-      <c r="F78" s="41" t="inlineStr">
-        <is>
-          <t>Contractor</t>
-        </is>
-      </c>
-      <c r="G78" s="41" t="inlineStr">
-        <is>
-          <t>DT</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="82" t="inlineStr">
-        <is>
-          <t>TF&gt;POS 6</t>
-        </is>
-      </c>
-      <c r="B79" s="82" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C79" s="68" t="n">
-        <v>133</v>
-      </c>
-      <c r="D79" s="66" t="n"/>
-      <c r="E79" s="54" t="inlineStr">
+      <c r="A77" s="66" t="n"/>
+      <c r="B77" s="66" t="n"/>
+      <c r="C77" s="66" t="n"/>
+      <c r="D77" s="66" t="n"/>
+      <c r="E77" s="54" t="inlineStr">
         <is>
           <t>KR&gt;FENI KM0</t>
         </is>
       </c>
-      <c r="F79" s="83" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="G79" s="61" t="n">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="82" t="inlineStr">
-        <is>
-          <t>TF&gt;POS 6</t>
-        </is>
-      </c>
-      <c r="B80" s="82" t="inlineStr">
+      <c r="F77" s="83" t="inlineStr">
         <is>
           <t>SMA</t>
         </is>
       </c>
-      <c r="C80" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="D80" s="66" t="n"/>
-      <c r="E80" s="54" t="inlineStr">
-        <is>
-          <t>TF&gt;FENI KM0</t>
-        </is>
-      </c>
-      <c r="F80" s="83" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="G80" s="61" t="n">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="66" t="n"/>
-      <c r="B81" s="66" t="n"/>
-      <c r="C81" s="66" t="n"/>
-      <c r="D81" s="66" t="n"/>
-      <c r="E81" s="54" t="inlineStr">
-        <is>
-          <t>KR&gt;FENI KM0</t>
-        </is>
-      </c>
-      <c r="F81" s="83" t="inlineStr">
-        <is>
-          <t>SMA</t>
-        </is>
-      </c>
-      <c r="G81" s="61" t="n">
+      <c r="G77" s="61" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4038,6 +3973,874 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="73" t="inlineStr">
+        <is>
+          <t>Reaching 17 Mt — two kinds of adjustment</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="75" t="inlineStr">
+        <is>
+          <t>THE CONSTRAINTS: the fleet is fixed at 580 / 930 / 1,280 / 1,280 DT (Sep-Dec) and must NOT shrink. SAP cannot exceed its line — it is fixed per scenario. So only LIM-TOS and LIM-LD can move, and only by changing WHERE the trucks drive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="91" t="inlineStr">
+        <is>
+          <t>ADJUSTMENT A — fewer trucks in Nov/Dec: park the DT that push a month over its line. REJECTED by the owner: we do not want the DT number to go down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="92" t="inlineStr">
+        <is>
+          <t>ADJUSTMENT B — same trucks, different trip length: keep every DT working and move them between LD destinations. TF&gt;POS 6 yields 121.4 t/DT/day, TF&gt;HUAFEI 104.8 — so moving one truck from HUAFEI to POS 6 buys +16.6 t/day. This is the only lever left once the fleet and SAP are fixed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" s="50" t="inlineStr">
+        <is>
+          <t>Where each scenario stands against its lines</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="41" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B8" s="41" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="C8" s="41" t="inlineStr">
+        <is>
+          <t>Fleet DT</t>
+        </is>
+      </c>
+      <c r="D8" s="41" t="inlineStr">
+        <is>
+          <t>LIM-LD predicted</t>
+        </is>
+      </c>
+      <c r="E8" s="41" t="inlineStr">
+        <is>
+          <t>LIM-LD target</t>
+        </is>
+      </c>
+      <c r="F8" s="41" t="inlineStr">
+        <is>
+          <t>LD gap t</t>
+        </is>
+      </c>
+      <c r="G8" s="41" t="inlineStr">
+        <is>
+          <t>Month gap t</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="42" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="B9" s="42" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="C9" s="43" t="n">
+        <v>581</v>
+      </c>
+      <c r="D9" s="43" t="n">
+        <v>851940</v>
+      </c>
+      <c r="E9" s="43" t="n">
+        <v>890366</v>
+      </c>
+      <c r="F9" s="93" t="n">
+        <v>-38426</v>
+      </c>
+      <c r="G9" s="52" t="n">
+        <v>-50907</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="42" t="inlineStr"/>
+      <c r="B10" s="42" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="C10" s="43" t="n">
+        <v>931</v>
+      </c>
+      <c r="D10" s="43" t="n">
+        <v>1814864</v>
+      </c>
+      <c r="E10" s="43" t="n">
+        <v>2072629</v>
+      </c>
+      <c r="F10" s="93" t="n">
+        <v>-257765</v>
+      </c>
+      <c r="G10" s="52" t="n">
+        <v>-202025</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="42" t="inlineStr"/>
+      <c r="B11" s="42" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="C11" s="43" t="n">
+        <v>1280</v>
+      </c>
+      <c r="D11" s="43" t="n">
+        <v>2464530</v>
+      </c>
+      <c r="E11" s="43" t="n">
+        <v>2697656</v>
+      </c>
+      <c r="F11" s="93" t="n">
+        <v>-233126</v>
+      </c>
+      <c r="G11" s="52" t="n">
+        <v>-172448</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="42" t="inlineStr"/>
+      <c r="B12" s="42" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="C12" s="43" t="n">
+        <v>1281</v>
+      </c>
+      <c r="D12" s="43" t="n">
+        <v>2184849</v>
+      </c>
+      <c r="E12" s="43" t="n">
+        <v>1973655</v>
+      </c>
+      <c r="F12" s="94" t="n">
+        <v>211194</v>
+      </c>
+      <c r="G12" s="61" t="n">
+        <v>160195</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="60" t="inlineStr">
+        <is>
+          <t>3.0.1 YEAR</t>
+        </is>
+      </c>
+      <c r="B13" s="42" t="inlineStr">
+        <is>
+          <t>Sep–Dec</t>
+        </is>
+      </c>
+      <c r="D13" s="43" t="n">
+        <v>16738008</v>
+      </c>
+      <c r="E13" s="43" t="n">
+        <v>17003193</v>
+      </c>
+      <c r="G13" s="93" t="n">
+        <v>-265185</v>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="42" t="inlineStr">
+        <is>
+          <t>3.0.2</t>
+        </is>
+      </c>
+      <c r="B15" s="42" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="C15" s="43" t="n">
+        <v>581</v>
+      </c>
+      <c r="D15" s="43" t="n">
+        <v>851940</v>
+      </c>
+      <c r="E15" s="43" t="n">
+        <v>890366</v>
+      </c>
+      <c r="F15" s="93" t="n">
+        <v>-38426</v>
+      </c>
+      <c r="G15" s="52" t="n">
+        <v>-50907</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="42" t="inlineStr"/>
+      <c r="B16" s="42" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="C16" s="43" t="n">
+        <v>931</v>
+      </c>
+      <c r="D16" s="43" t="n">
+        <v>1965741</v>
+      </c>
+      <c r="E16" s="43" t="n">
+        <v>2072629</v>
+      </c>
+      <c r="F16" s="93" t="n">
+        <v>-106888</v>
+      </c>
+      <c r="G16" s="52" t="n">
+        <v>-48812</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="42" t="inlineStr"/>
+      <c r="B17" s="42" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="C17" s="43" t="n">
+        <v>1280</v>
+      </c>
+      <c r="D17" s="43" t="n">
+        <v>2672880</v>
+      </c>
+      <c r="E17" s="43" t="n">
+        <v>2697656</v>
+      </c>
+      <c r="F17" s="93" t="n">
+        <v>-24776</v>
+      </c>
+      <c r="G17" s="61" t="n">
+        <v>37007</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="42" t="inlineStr"/>
+      <c r="B18" s="42" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="C18" s="43" t="n">
+        <v>1281</v>
+      </c>
+      <c r="D18" s="43" t="n">
+        <v>2369919</v>
+      </c>
+      <c r="E18" s="43" t="n">
+        <v>1973655</v>
+      </c>
+      <c r="F18" s="94" t="n">
+        <v>396264</v>
+      </c>
+      <c r="G18" s="61" t="n">
+        <v>346837</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="60" t="inlineStr">
+        <is>
+          <t>3.0.2 YEAR</t>
+        </is>
+      </c>
+      <c r="B19" s="42" t="inlineStr">
+        <is>
+          <t>Sep–Dec</t>
+        </is>
+      </c>
+      <c r="D19" s="43" t="n">
+        <v>17287318</v>
+      </c>
+      <c r="E19" s="43" t="n">
+        <v>17003193</v>
+      </c>
+      <c r="G19" s="94" t="n">
+        <v>284125</v>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="42" t="inlineStr">
+        <is>
+          <t>3.1.1</t>
+        </is>
+      </c>
+      <c r="B21" s="42" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="C21" s="43" t="n">
+        <v>581</v>
+      </c>
+      <c r="D21" s="43" t="n">
+        <v>851940</v>
+      </c>
+      <c r="E21" s="43" t="n">
+        <v>840444</v>
+      </c>
+      <c r="F21" s="94" t="n">
+        <v>11496</v>
+      </c>
+      <c r="G21" s="61" t="n">
+        <v>20112</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="42" t="inlineStr"/>
+      <c r="B22" s="42" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="C22" s="43" t="n">
+        <v>931</v>
+      </c>
+      <c r="D22" s="43" t="n">
+        <v>1675736</v>
+      </c>
+      <c r="E22" s="43" t="n">
+        <v>1786681</v>
+      </c>
+      <c r="F22" s="93" t="n">
+        <v>-110945</v>
+      </c>
+      <c r="G22" s="52" t="n">
+        <v>-78928</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="42" t="inlineStr"/>
+      <c r="B23" s="42" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="C23" s="43" t="n">
+        <v>1280</v>
+      </c>
+      <c r="D23" s="43" t="n">
+        <v>2324910</v>
+      </c>
+      <c r="E23" s="43" t="n">
+        <v>2320788</v>
+      </c>
+      <c r="F23" s="94" t="n">
+        <v>4122</v>
+      </c>
+      <c r="G23" s="61" t="n">
+        <v>34487</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="42" t="inlineStr"/>
+      <c r="B24" s="42" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="C24" s="43" t="n">
+        <v>1281</v>
+      </c>
+      <c r="D24" s="43" t="n">
+        <v>2049937</v>
+      </c>
+      <c r="E24" s="43" t="n">
+        <v>1696393</v>
+      </c>
+      <c r="F24" s="94" t="n">
+        <v>353544</v>
+      </c>
+      <c r="G24" s="61" t="n">
+        <v>317465</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="60" t="inlineStr">
+        <is>
+          <t>3.1.1 YEAR</t>
+        </is>
+      </c>
+      <c r="B25" s="42" t="inlineStr">
+        <is>
+          <t>Sep–Dec</t>
+        </is>
+      </c>
+      <c r="D25" s="43" t="n">
+        <v>17296329</v>
+      </c>
+      <c r="E25" s="43" t="n">
+        <v>17003193</v>
+      </c>
+      <c r="G25" s="94" t="n">
+        <v>293136</v>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="42" t="inlineStr">
+        <is>
+          <t>3.1.2</t>
+        </is>
+      </c>
+      <c r="B27" s="42" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="C27" s="43" t="n">
+        <v>581</v>
+      </c>
+      <c r="D27" s="43" t="n">
+        <v>851940</v>
+      </c>
+      <c r="E27" s="43" t="n">
+        <v>840444</v>
+      </c>
+      <c r="F27" s="94" t="n">
+        <v>11496</v>
+      </c>
+      <c r="G27" s="61" t="n">
+        <v>20112</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="42" t="inlineStr"/>
+      <c r="B28" s="42" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="C28" s="43" t="n">
+        <v>931</v>
+      </c>
+      <c r="D28" s="43" t="n">
+        <v>1808447</v>
+      </c>
+      <c r="E28" s="43" t="n">
+        <v>1786681</v>
+      </c>
+      <c r="F28" s="94" t="n">
+        <v>21766</v>
+      </c>
+      <c r="G28" s="61" t="n">
+        <v>59284</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="42" t="inlineStr"/>
+      <c r="B29" s="42" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="C29" s="43" t="n">
+        <v>1280</v>
+      </c>
+      <c r="D29" s="43" t="n">
+        <v>2520240</v>
+      </c>
+      <c r="E29" s="43" t="n">
+        <v>2320788</v>
+      </c>
+      <c r="F29" s="94" t="n">
+        <v>199452</v>
+      </c>
+      <c r="G29" s="61" t="n">
+        <v>237094</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="42" t="inlineStr"/>
+      <c r="B30" s="42" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="C30" s="43" t="n">
+        <v>1281</v>
+      </c>
+      <c r="D30" s="43" t="n">
+        <v>2218732</v>
+      </c>
+      <c r="E30" s="43" t="n">
+        <v>1696393</v>
+      </c>
+      <c r="F30" s="94" t="n">
+        <v>522339</v>
+      </c>
+      <c r="G30" s="61" t="n">
+        <v>491883</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="60" t="inlineStr">
+        <is>
+          <t>3.1.2 YEAR</t>
+        </is>
+      </c>
+      <c r="B31" s="42" t="inlineStr">
+        <is>
+          <t>Sep–Dec</t>
+        </is>
+      </c>
+      <c r="D31" s="43" t="n">
+        <v>17811566</v>
+      </c>
+      <c r="E31" s="43" t="n">
+        <v>17003193</v>
+      </c>
+      <c r="G31" s="94" t="n">
+        <v>808373</v>
+      </c>
+    </row>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="50" t="inlineStr">
+        <is>
+          <t>ADJUSTMENT B — how far the trip-length lever actually reaches</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="28" customHeight="1">
+      <c r="A34" s="49" t="inlineStr">
+        <is>
+          <t>For each SHORT month: how many LD trucks would have to move from TF&gt;HUAFEI to TF&gt;POS 6 to close the gap, and how many LD trucks that month actually has. If the shift needed exceeds the fleet on the route, the gap cannot be closed by route mix alone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="41" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B35" s="41" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="C35" s="41" t="inlineStr">
+        <is>
+          <t>Gap to close t</t>
+        </is>
+      </c>
+      <c r="D35" s="41" t="inlineStr">
+        <is>
+          <t>DT to shift HUAFEI→POS 6</t>
+        </is>
+      </c>
+      <c r="E35" s="41" t="inlineStr">
+        <is>
+          <t>LD DT available</t>
+        </is>
+      </c>
+      <c r="F35" s="41" t="inlineStr">
+        <is>
+          <t>Feasible?</t>
+        </is>
+      </c>
+      <c r="G35" s="41" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="42" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="B36" s="42" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="C36" s="43" t="n">
+        <v>38426</v>
+      </c>
+      <c r="D36" s="59" t="n">
+        <v>77</v>
+      </c>
+      <c r="E36" s="43" t="n">
+        <v>268</v>
+      </c>
+      <c r="F36" s="95" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G36" s="76" t="inlineStr">
+        <is>
+          <t>shift 77 of 268 LD trucks to the longer POS 6 haul</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="42" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="B37" s="42" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="C37" s="43" t="n">
+        <v>257765</v>
+      </c>
+      <c r="D37" s="59" t="n">
+        <v>501</v>
+      </c>
+      <c r="E37" s="43" t="n">
+        <v>557</v>
+      </c>
+      <c r="F37" s="95" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G37" s="76" t="inlineStr">
+        <is>
+          <t>shift 501 of 557 LD trucks to the longer POS 6 haul</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="42" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="B38" s="42" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="C38" s="43" t="n">
+        <v>233126</v>
+      </c>
+      <c r="D38" s="59" t="n">
+        <v>468</v>
+      </c>
+      <c r="E38" s="43" t="n">
+        <v>788</v>
+      </c>
+      <c r="F38" s="95" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G38" s="76" t="inlineStr">
+        <is>
+          <t>shift 468 of 788 LD trucks to the longer POS 6 haul</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="42" t="inlineStr">
+        <is>
+          <t>3.0.2</t>
+        </is>
+      </c>
+      <c r="B39" s="42" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="C39" s="43" t="n">
+        <v>38426</v>
+      </c>
+      <c r="D39" s="59" t="n">
+        <v>77</v>
+      </c>
+      <c r="E39" s="43" t="n">
+        <v>268</v>
+      </c>
+      <c r="F39" s="95" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G39" s="76" t="inlineStr">
+        <is>
+          <t>shift 77 of 268 LD trucks to the longer POS 6 haul</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="42" t="inlineStr">
+        <is>
+          <t>3.0.2</t>
+        </is>
+      </c>
+      <c r="B40" s="42" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="C40" s="43" t="n">
+        <v>106888</v>
+      </c>
+      <c r="D40" s="59" t="n">
+        <v>208</v>
+      </c>
+      <c r="E40" s="43" t="n">
+        <v>278</v>
+      </c>
+      <c r="F40" s="95" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G40" s="76" t="inlineStr">
+        <is>
+          <t>shift 208 of 278 LD trucks to the longer POS 6 haul</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="42" t="inlineStr">
+        <is>
+          <t>3.0.2</t>
+        </is>
+      </c>
+      <c r="B41" s="42" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="C41" s="43" t="n">
+        <v>24776</v>
+      </c>
+      <c r="D41" s="59" t="n">
+        <v>50</v>
+      </c>
+      <c r="E41" s="43" t="n">
+        <v>394</v>
+      </c>
+      <c r="F41" s="95" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G41" s="76" t="inlineStr">
+        <is>
+          <t>shift 50 of 394 LD trucks to the longer POS 6 haul</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="42" t="inlineStr">
+        <is>
+          <t>3.1.1</t>
+        </is>
+      </c>
+      <c r="B42" s="42" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="C42" s="43" t="n">
+        <v>110945</v>
+      </c>
+      <c r="D42" s="59" t="n">
+        <v>216</v>
+      </c>
+      <c r="E42" s="43" t="n">
+        <v>514</v>
+      </c>
+      <c r="F42" s="95" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G42" s="76" t="inlineStr">
+        <is>
+          <t>shift 216 of 514 LD trucks to the longer POS 6 haul</t>
+        </is>
+      </c>
+    </row>
+    <row r="43"/>
+    <row r="44" ht="26" customHeight="1">
+      <c r="A44" s="96" t="inlineStr">
+        <is>
+          <t>READING: every short month CAN be closed by route mix — the shift needed is always smaller than the LD fleet on HUAFEI that month (3.0.1 Oct needs 501 of 557; Nov 468 of 788). But in 3.0.1 and 3.1.1 that means opening a POS 6 leg those scenarios do not have by definition, which turns them into .2 scenarios.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="26" customHeight="1">
+      <c r="A45" s="96" t="inlineStr">
+        <is>
+          <t>The .2 scenarios already run the split, which is why they clear the line (+284 kt and +808 kt) with only small October/November gaps left. 3.0.1 is the only scenario that stays short overall (-265 kt).</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="26" customHeight="1">
+      <c r="A46" s="96" t="inlineStr">
+        <is>
+          <t>CONCLUSION: adjustment B is feasible and needs no extra trucks — but it IS the POS 6 split. Choosing a .2 scenario applies the same lever as policy instead of month by month, and lands 17.29-17.81 Mt with the fleet untouched at 580/930/1,280/1,281 DT. December still finishes over its LD line, which is what Options 1 and 2 are for.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A44:G44"/>
+    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A46:G46"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:A19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/reports/scenario_comparison_dec_options.xlsx
+++ b/reports/scenario_comparison_dec_options.xlsx
@@ -8,7 +8,7 @@
   <sheets>
     <sheet name="Compare" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="December options" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Adjustments" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Adjustment paths" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Insights" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
@@ -25,7 +25,7 @@
     <numFmt numFmtId="167" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="168" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="62">
+  <fonts count="64">
     <font>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -427,6 +427,18 @@
     <font>
       <name val="Arial"/>
       <color rgb="001B7A41"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="005B6B7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00A52929"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -1032,7 +1044,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1290,6 +1302,20 @@
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="57" fillId="41" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="43" fillId="41" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="37" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3973,863 +3999,7976 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:H292"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="73" t="inlineStr">
         <is>
-          <t>Reaching 17 Mt — two kinds of adjustment</t>
+          <t>Adjustment B — same fleet, different trip length (path by path)</t>
         </is>
       </c>
     </row>
     <row r="2"/>
-    <row r="3" ht="30" customHeight="1">
+    <row r="3" ht="32" customHeight="1">
       <c r="A3" s="75" t="inlineStr">
         <is>
-          <t>THE CONSTRAINTS: the fleet is fixed at 580 / 930 / 1,280 / 1,280 DT (Sep-Dec) and must NOT shrink. SAP cannot exceed its line — it is fixed per scenario. So only LIM-TOS and LIM-LD can move, and only by changing WHERE the trucks drive.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="91" t="inlineStr">
-        <is>
-          <t>ADJUSTMENT A — fewer trucks in Nov/Dec: park the DT that push a month over its line. REJECTED by the owner: we do not want the DT number to go down.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="92" t="inlineStr">
-        <is>
-          <t>ADJUSTMENT B — same trucks, different trip length: keep every DT working and move them between LD destinations. TF&gt;POS 6 yields 121.4 t/DT/day, TF&gt;HUAFEI 104.8 — so moving one truck from HUAFEI to POS 6 buys +16.6 t/day. This is the only lever left once the fleet and SAP are fixed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6"/>
+          <t>The fleet stays at 580 / 930 / 1,280 / 1,281 DT and SAP stays on its line. The only change is WHERE the LIM-LD trucks drive: TF&gt;POS 6 is the longer haul and yields more per truck (RIM 126.8 vs 104.2 t/DT/day, SMA 115.9 vs 104.0), so moving a truck there buys +22.6 t/day (RIM) or +11.8 (SMA).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="75" t="inlineStr">
+        <is>
+          <t>RED rows = trucks TAKEN OUT of that path.   GREEN rows = trucks ADDED.   Every other path is untouched, which is why SAP and LIM-TOS finish unchanged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" s="40" t="inlineStr">
+        <is>
+          <t>Scenario 3.0.1</t>
+        </is>
+      </c>
+    </row>
     <row r="7">
-      <c r="A7" s="50" t="inlineStr">
-        <is>
-          <t>Where each scenario stands against its lines</t>
+      <c r="A7" s="81" t="inlineStr">
+        <is>
+          <t>September — move 83 DT from TF&gt;HUAFEI to TF&gt;POS 6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="41" t="inlineStr">
         <is>
-          <t>Scenario</t>
+          <t>Path</t>
         </is>
       </c>
       <c r="B8" s="41" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Contractor</t>
         </is>
       </c>
       <c r="C8" s="41" t="inlineStr">
         <is>
-          <t>Fleet DT</t>
+          <t>Material</t>
         </is>
       </c>
       <c r="D8" s="41" t="inlineStr">
         <is>
-          <t>LIM-LD predicted</t>
+          <t>DT before</t>
         </is>
       </c>
       <c r="E8" s="41" t="inlineStr">
         <is>
-          <t>LIM-LD target</t>
+          <t>DT after</t>
         </is>
       </c>
       <c r="F8" s="41" t="inlineStr">
         <is>
-          <t>LD gap t</t>
+          <t>Δ DT</t>
         </is>
       </c>
       <c r="G8" s="41" t="inlineStr">
         <is>
-          <t>Month gap t</t>
+          <t>t/month before</t>
+        </is>
+      </c>
+      <c r="H8" s="41" t="inlineStr">
+        <is>
+          <t>t/month AFTER</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="42" t="inlineStr">
-        <is>
-          <t>3.0.1</t>
-        </is>
-      </c>
-      <c r="B9" s="42" t="inlineStr">
-        <is>
-          <t>Sep</t>
-        </is>
-      </c>
-      <c r="C9" s="43" t="n">
-        <v>581</v>
-      </c>
-      <c r="D9" s="43" t="n">
-        <v>851940</v>
-      </c>
-      <c r="E9" s="43" t="n">
-        <v>890366</v>
+      <c r="A9" s="97" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B9" s="97" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C9" s="97" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D9" s="98" t="n">
+        <v>211</v>
+      </c>
+      <c r="E9" s="93" t="n">
+        <v>156</v>
       </c>
       <c r="F9" s="93" t="n">
-        <v>-38426</v>
-      </c>
-      <c r="G9" s="52" t="n">
-        <v>-50907</v>
+        <v>-55</v>
+      </c>
+      <c r="G9" s="98" t="n">
+        <v>670710</v>
+      </c>
+      <c r="H9" s="93" t="n">
+        <v>495880</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="42" t="inlineStr"/>
-      <c r="B10" s="42" t="inlineStr">
-        <is>
-          <t>Oct</t>
-        </is>
-      </c>
-      <c r="C10" s="43" t="n">
-        <v>931</v>
-      </c>
-      <c r="D10" s="43" t="n">
-        <v>1814864</v>
-      </c>
-      <c r="E10" s="43" t="n">
-        <v>2072629</v>
+      <c r="A10" s="97" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B10" s="97" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C10" s="97" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D10" s="98" t="n">
+        <v>57</v>
+      </c>
+      <c r="E10" s="93" t="n">
+        <v>29</v>
       </c>
       <c r="F10" s="93" t="n">
-        <v>-257765</v>
-      </c>
-      <c r="G10" s="52" t="n">
-        <v>-202025</v>
+        <v>-28</v>
+      </c>
+      <c r="G10" s="98" t="n">
+        <v>181230</v>
+      </c>
+      <c r="H10" s="93" t="n">
+        <v>92205</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="42" t="inlineStr"/>
-      <c r="B11" s="42" t="inlineStr">
-        <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="C11" s="43" t="n">
-        <v>1280</v>
+      <c r="A11" s="51" t="inlineStr">
+        <is>
+          <t>BLB&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B11" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C11" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
       </c>
       <c r="D11" s="43" t="n">
-        <v>2464530</v>
+        <v>83</v>
       </c>
       <c r="E11" s="43" t="n">
-        <v>2697656</v>
-      </c>
-      <c r="F11" s="93" t="n">
-        <v>-233126</v>
-      </c>
-      <c r="G11" s="52" t="n">
-        <v>-172448</v>
+        <v>83</v>
+      </c>
+      <c r="F11" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="43" t="n">
+        <v>610200</v>
+      </c>
+      <c r="H11" s="47" t="n">
+        <v>610200</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="42" t="inlineStr"/>
-      <c r="B12" s="42" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="C12" s="43" t="n">
-        <v>1281</v>
+      <c r="A12" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B12" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C12" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
       </c>
       <c r="D12" s="43" t="n">
-        <v>2184849</v>
+        <v>52</v>
       </c>
       <c r="E12" s="43" t="n">
-        <v>1973655</v>
-      </c>
-      <c r="F12" s="94" t="n">
-        <v>211194</v>
-      </c>
-      <c r="G12" s="61" t="n">
-        <v>160195</v>
+        <v>52</v>
+      </c>
+      <c r="F12" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="43" t="n">
+        <v>165300</v>
+      </c>
+      <c r="H12" s="47" t="n">
+        <v>165300</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="60" t="inlineStr">
-        <is>
-          <t>3.0.1 YEAR</t>
-        </is>
-      </c>
-      <c r="B13" s="42" t="inlineStr">
-        <is>
-          <t>Sep–Dec</t>
+      <c r="A13" s="51" t="inlineStr">
+        <is>
+          <t>KR&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B13" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C13" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
         </is>
       </c>
       <c r="D13" s="43" t="n">
-        <v>16738008</v>
+        <v>9</v>
       </c>
       <c r="E13" s="43" t="n">
+        <v>9</v>
+      </c>
+      <c r="F13" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="43" t="n">
+        <v>37800</v>
+      </c>
+      <c r="H13" s="47" t="n">
+        <v>37800</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B14" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C14" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D14" s="43" t="n">
+        <v>9</v>
+      </c>
+      <c r="E14" s="43" t="n">
+        <v>9</v>
+      </c>
+      <c r="F14" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="43" t="n">
+        <v>28620</v>
+      </c>
+      <c r="H14" s="47" t="n">
+        <v>28620</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;FENI KM15</t>
+        </is>
+      </c>
+      <c r="B15" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C15" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D15" s="43" t="n">
+        <v>77</v>
+      </c>
+      <c r="E15" s="43" t="n">
+        <v>77</v>
+      </c>
+      <c r="F15" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="43" t="n">
+        <v>246480</v>
+      </c>
+      <c r="H15" s="47" t="n">
+        <v>246480</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="51" t="inlineStr">
+        <is>
+          <t>KR&gt;FENI KM15</t>
+        </is>
+      </c>
+      <c r="B16" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C16" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D16" s="43" t="n">
+        <v>38</v>
+      </c>
+      <c r="E16" s="43" t="n">
+        <v>38</v>
+      </c>
+      <c r="F16" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="43" t="n">
+        <v>187800</v>
+      </c>
+      <c r="H16" s="47" t="n">
+        <v>187800</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="51" t="inlineStr">
+        <is>
+          <t>BLB&gt;FENI KM0</t>
+        </is>
+      </c>
+      <c r="B17" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C17" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D17" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="F17" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="43" t="n">
+        <v>68520</v>
+      </c>
+      <c r="H17" s="47" t="n">
+        <v>68520</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="51" t="inlineStr">
+        <is>
+          <t>KR&gt;POS 12</t>
+        </is>
+      </c>
+      <c r="B18" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C18" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D18" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="F18" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="43" t="n">
+        <v>62100</v>
+      </c>
+      <c r="H18" s="47" t="n">
+        <v>62100</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;POS 12</t>
+        </is>
+      </c>
+      <c r="B19" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C19" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D19" s="43" t="n">
+        <v>18</v>
+      </c>
+      <c r="E19" s="43" t="n">
+        <v>18</v>
+      </c>
+      <c r="F19" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="43" t="n">
+        <v>61470</v>
+      </c>
+      <c r="H19" s="47" t="n">
+        <v>61470</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="51" t="inlineStr">
+        <is>
+          <t>BLB&gt;POS 14</t>
+        </is>
+      </c>
+      <c r="B20" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C20" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D20" s="43" t="n">
+        <v>7</v>
+      </c>
+      <c r="E20" s="43" t="n">
+        <v>7</v>
+      </c>
+      <c r="F20" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="43" t="n">
+        <v>61320</v>
+      </c>
+      <c r="H20" s="47" t="n">
+        <v>61320</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="95" t="inlineStr">
+        <is>
+          <t>TF&gt;POS 6</t>
+        </is>
+      </c>
+      <c r="B21" s="95" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C21" s="95" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D21" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E21" s="94" t="n">
+        <v>28</v>
+      </c>
+      <c r="F21" s="94" t="n">
+        <v>28</v>
+      </c>
+      <c r="G21" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H21" s="94" t="n">
+        <v>106552</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="95" t="inlineStr">
+        <is>
+          <t>TF&gt;POS 6</t>
+        </is>
+      </c>
+      <c r="B22" s="95" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C22" s="95" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D22" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E22" s="94" t="n">
+        <v>55</v>
+      </c>
+      <c r="F22" s="94" t="n">
+        <v>55</v>
+      </c>
+      <c r="G22" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H22" s="94" t="n">
+        <v>191178</v>
+      </c>
+    </row>
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" s="102" t="inlineStr">
+        <is>
+          <t>October — move 278 DT from TF&gt;HUAFEI to TF&gt;POS 6  ·  still 98,200 t short: the §4 rule keeps the split at 50/50, so no more than half a row may move</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="41" t="inlineStr">
+        <is>
+          <t>Path</t>
+        </is>
+      </c>
+      <c r="B25" s="41" t="inlineStr">
+        <is>
+          <t>Contractor</t>
+        </is>
+      </c>
+      <c r="C25" s="41" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="D25" s="41" t="inlineStr">
+        <is>
+          <t>DT before</t>
+        </is>
+      </c>
+      <c r="E25" s="41" t="inlineStr">
+        <is>
+          <t>DT after</t>
+        </is>
+      </c>
+      <c r="F25" s="41" t="inlineStr">
+        <is>
+          <t>Δ DT</t>
+        </is>
+      </c>
+      <c r="G25" s="41" t="inlineStr">
+        <is>
+          <t>t/month before</t>
+        </is>
+      </c>
+      <c r="H25" s="41" t="inlineStr">
+        <is>
+          <t>t/month AFTER</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="97" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B26" s="97" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C26" s="97" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D26" s="98" t="n">
+        <v>345</v>
+      </c>
+      <c r="E26" s="93" t="n">
+        <v>173</v>
+      </c>
+      <c r="F26" s="93" t="n">
+        <v>-172</v>
+      </c>
+      <c r="G26" s="98" t="n">
+        <v>1124556</v>
+      </c>
+      <c r="H26" s="93" t="n">
+        <v>563908</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="97" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B27" s="97" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C27" s="97" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D27" s="98" t="n">
+        <v>212</v>
+      </c>
+      <c r="E27" s="93" t="n">
+        <v>106</v>
+      </c>
+      <c r="F27" s="93" t="n">
+        <v>-106</v>
+      </c>
+      <c r="G27" s="98" t="n">
+        <v>690308</v>
+      </c>
+      <c r="H27" s="93" t="n">
+        <v>345154</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="51" t="inlineStr">
+        <is>
+          <t>BLB&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B28" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C28" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D28" s="43" t="n">
+        <v>63</v>
+      </c>
+      <c r="E28" s="43" t="n">
+        <v>63</v>
+      </c>
+      <c r="F28" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="43" t="n">
+        <v>479632</v>
+      </c>
+      <c r="H28" s="47" t="n">
+        <v>479632</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B29" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C29" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D29" s="43" t="n">
+        <v>40</v>
+      </c>
+      <c r="E29" s="43" t="n">
+        <v>40</v>
+      </c>
+      <c r="F29" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="43" t="n">
+        <v>130231</v>
+      </c>
+      <c r="H29" s="47" t="n">
+        <v>130231</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B30" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C30" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D30" s="43" t="n">
+        <v>22</v>
+      </c>
+      <c r="E30" s="43" t="n">
+        <v>22</v>
+      </c>
+      <c r="F30" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="43" t="n">
+        <v>71703</v>
+      </c>
+      <c r="H30" s="47" t="n">
+        <v>71703</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="51" t="inlineStr">
+        <is>
+          <t>KR&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B31" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C31" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D31" s="43" t="n">
+        <v>13</v>
+      </c>
+      <c r="E31" s="43" t="n">
+        <v>13</v>
+      </c>
+      <c r="F31" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="43" t="n">
+        <v>55118</v>
+      </c>
+      <c r="H31" s="47" t="n">
+        <v>55118</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="51" t="inlineStr">
+        <is>
+          <t>BLB&gt;FENI KM0</t>
+        </is>
+      </c>
+      <c r="B32" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C32" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D32" s="43" t="n">
+        <v>65</v>
+      </c>
+      <c r="E32" s="43" t="n">
+        <v>65</v>
+      </c>
+      <c r="F32" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="43" t="n">
+        <v>458025</v>
+      </c>
+      <c r="H32" s="47" t="n">
+        <v>458025</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;FENI KM15</t>
+        </is>
+      </c>
+      <c r="B33" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C33" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D33" s="43" t="n">
+        <v>90</v>
+      </c>
+      <c r="E33" s="43" t="n">
+        <v>90</v>
+      </c>
+      <c r="F33" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="43" t="n">
+        <v>294159</v>
+      </c>
+      <c r="H33" s="47" t="n">
+        <v>294159</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="51" t="inlineStr">
+        <is>
+          <t>KR&gt;FENI KM15</t>
+        </is>
+      </c>
+      <c r="B34" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C34" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D34" s="43" t="n">
+        <v>46</v>
+      </c>
+      <c r="E34" s="43" t="n">
+        <v>46</v>
+      </c>
+      <c r="F34" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="43" t="n">
+        <v>228997</v>
+      </c>
+      <c r="H34" s="47" t="n">
+        <v>228997</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="51" t="inlineStr">
+        <is>
+          <t>BLB&gt;POS 14</t>
+        </is>
+      </c>
+      <c r="B35" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C35" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D35" s="43" t="n">
+        <v>7</v>
+      </c>
+      <c r="E35" s="43" t="n">
+        <v>7</v>
+      </c>
+      <c r="F35" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="43" t="n">
+        <v>63364</v>
+      </c>
+      <c r="H35" s="47" t="n">
+        <v>63364</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;POS 12</t>
+        </is>
+      </c>
+      <c r="B36" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C36" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D36" s="43" t="n">
+        <v>18</v>
+      </c>
+      <c r="E36" s="43" t="n">
+        <v>18</v>
+      </c>
+      <c r="F36" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="43" t="n">
+        <v>63302</v>
+      </c>
+      <c r="H36" s="47" t="n">
+        <v>63302</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="51" t="inlineStr">
+        <is>
+          <t>KR&gt;POS 12</t>
+        </is>
+      </c>
+      <c r="B37" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C37" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D37" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="F37" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="43" t="n">
+        <v>62806</v>
+      </c>
+      <c r="H37" s="47" t="n">
+        <v>62806</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="95" t="inlineStr">
+        <is>
+          <t>TF&gt;POS 6</t>
+        </is>
+      </c>
+      <c r="B38" s="95" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C38" s="95" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D38" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E38" s="94" t="n">
+        <v>172</v>
+      </c>
+      <c r="F38" s="94" t="n">
+        <v>172</v>
+      </c>
+      <c r="G38" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H38" s="94" t="n">
+        <v>676352</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="95" t="inlineStr">
+        <is>
+          <t>TF&gt;POS 6</t>
+        </is>
+      </c>
+      <c r="B39" s="95" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C39" s="95" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D39" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E39" s="94" t="n">
+        <v>106</v>
+      </c>
+      <c r="F39" s="94" t="n">
+        <v>106</v>
+      </c>
+      <c r="G39" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H39" s="94" t="n">
+        <v>380735</v>
+      </c>
+    </row>
+    <row r="40"/>
+    <row r="41">
+      <c r="A41" s="102" t="inlineStr">
+        <is>
+          <t>November — move 393 DT from TF&gt;HUAFEI to TF&gt;POS 6  ·  still 6,787 t short: the §4 rule keeps the split at 50/50, so no more than half a row may move</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="41" t="inlineStr">
+        <is>
+          <t>Path</t>
+        </is>
+      </c>
+      <c r="B42" s="41" t="inlineStr">
+        <is>
+          <t>Contractor</t>
+        </is>
+      </c>
+      <c r="C42" s="41" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="D42" s="41" t="inlineStr">
+        <is>
+          <t>DT before</t>
+        </is>
+      </c>
+      <c r="E42" s="41" t="inlineStr">
+        <is>
+          <t>DT after</t>
+        </is>
+      </c>
+      <c r="F42" s="41" t="inlineStr">
+        <is>
+          <t>Δ DT</t>
+        </is>
+      </c>
+      <c r="G42" s="41" t="inlineStr">
+        <is>
+          <t>t/month before</t>
+        </is>
+      </c>
+      <c r="H42" s="41" t="inlineStr">
+        <is>
+          <t>t/month AFTER</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="97" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B43" s="97" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C43" s="97" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D43" s="98" t="n">
+        <v>537</v>
+      </c>
+      <c r="E43" s="93" t="n">
+        <v>269</v>
+      </c>
+      <c r="F43" s="93" t="n">
+        <v>-268</v>
+      </c>
+      <c r="G43" s="98" t="n">
+        <v>1680450</v>
+      </c>
+      <c r="H43" s="93" t="n">
+        <v>841790</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="97" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B44" s="97" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C44" s="97" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D44" s="98" t="n">
+        <v>251</v>
+      </c>
+      <c r="E44" s="93" t="n">
+        <v>126</v>
+      </c>
+      <c r="F44" s="93" t="n">
+        <v>-125</v>
+      </c>
+      <c r="G44" s="98" t="n">
+        <v>784080</v>
+      </c>
+      <c r="H44" s="93" t="n">
+        <v>393602</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="51" t="inlineStr">
+        <is>
+          <t>BLB&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B45" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C45" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D45" s="43" t="n">
+        <v>103</v>
+      </c>
+      <c r="E45" s="43" t="n">
+        <v>103</v>
+      </c>
+      <c r="F45" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="43" t="n">
+        <v>755610</v>
+      </c>
+      <c r="H45" s="47" t="n">
+        <v>755610</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B46" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C46" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D46" s="43" t="n">
+        <v>67</v>
+      </c>
+      <c r="E46" s="43" t="n">
+        <v>67</v>
+      </c>
+      <c r="F46" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="43" t="n">
+        <v>209670</v>
+      </c>
+      <c r="H46" s="47" t="n">
+        <v>209670</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="51" t="inlineStr">
+        <is>
+          <t>KR&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B47" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C47" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D47" s="43" t="n">
+        <v>31</v>
+      </c>
+      <c r="E47" s="43" t="n">
+        <v>31</v>
+      </c>
+      <c r="F47" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="43" t="n">
+        <v>123360</v>
+      </c>
+      <c r="H47" s="47" t="n">
+        <v>123360</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="51" t="inlineStr">
+        <is>
+          <t>BLB&gt;FENI KM0</t>
+        </is>
+      </c>
+      <c r="B48" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C48" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D48" s="43" t="n">
+        <v>150</v>
+      </c>
+      <c r="E48" s="43" t="n">
+        <v>150</v>
+      </c>
+      <c r="F48" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="43" t="n">
+        <v>1020750</v>
+      </c>
+      <c r="H48" s="47" t="n">
+        <v>1020750</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;FENI KM15</t>
+        </is>
+      </c>
+      <c r="B49" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C49" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D49" s="43" t="n">
+        <v>78</v>
+      </c>
+      <c r="E49" s="43" t="n">
+        <v>78</v>
+      </c>
+      <c r="F49" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="43" t="n">
+        <v>244020</v>
+      </c>
+      <c r="H49" s="47" t="n">
+        <v>244020</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="51" t="inlineStr">
+        <is>
+          <t>KR&gt;FENI KM15</t>
+        </is>
+      </c>
+      <c r="B50" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C50" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D50" s="43" t="n">
+        <v>27</v>
+      </c>
+      <c r="E50" s="43" t="n">
+        <v>27</v>
+      </c>
+      <c r="F50" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="43" t="n">
+        <v>127500</v>
+      </c>
+      <c r="H50" s="47" t="n">
+        <v>127500</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="51" t="inlineStr">
+        <is>
+          <t>KR&gt;POS 12</t>
+        </is>
+      </c>
+      <c r="B51" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C51" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D51" s="43" t="n">
+        <v>11</v>
+      </c>
+      <c r="E51" s="43" t="n">
+        <v>11</v>
+      </c>
+      <c r="F51" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="43" t="n">
+        <v>65310</v>
+      </c>
+      <c r="H51" s="47" t="n">
+        <v>65310</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="51" t="inlineStr">
+        <is>
+          <t>BLB&gt;POS 14</t>
+        </is>
+      </c>
+      <c r="B52" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C52" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D52" s="43" t="n">
+        <v>7</v>
+      </c>
+      <c r="E52" s="43" t="n">
+        <v>7</v>
+      </c>
+      <c r="F52" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="43" t="n">
+        <v>61320</v>
+      </c>
+      <c r="H52" s="47" t="n">
+        <v>61320</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;POS 12</t>
+        </is>
+      </c>
+      <c r="B53" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C53" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D53" s="43" t="n">
+        <v>18</v>
+      </c>
+      <c r="E53" s="43" t="n">
+        <v>18</v>
+      </c>
+      <c r="F53" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="43" t="n">
+        <v>61020</v>
+      </c>
+      <c r="H53" s="47" t="n">
+        <v>61020</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="95" t="inlineStr">
+        <is>
+          <t>TF&gt;POS 6</t>
+        </is>
+      </c>
+      <c r="B54" s="95" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C54" s="95" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D54" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E54" s="94" t="n">
+        <v>268</v>
+      </c>
+      <c r="F54" s="94" t="n">
+        <v>268</v>
+      </c>
+      <c r="G54" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H54" s="94" t="n">
+        <v>1019855</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="95" t="inlineStr">
+        <is>
+          <t>TF&gt;POS 6</t>
+        </is>
+      </c>
+      <c r="B55" s="95" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C55" s="95" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D55" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E55" s="94" t="n">
+        <v>125</v>
+      </c>
+      <c r="F55" s="94" t="n">
+        <v>125</v>
+      </c>
+      <c r="G55" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H55" s="94" t="n">
+        <v>434497</v>
+      </c>
+    </row>
+    <row r="56"/>
+    <row r="57">
+      <c r="A57" s="100" t="inlineStr">
+        <is>
+          <t>December — no change needed (already at or above its line)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="41" t="inlineStr">
+        <is>
+          <t>Path</t>
+        </is>
+      </c>
+      <c r="B58" s="41" t="inlineStr">
+        <is>
+          <t>Contractor</t>
+        </is>
+      </c>
+      <c r="C58" s="41" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="D58" s="41" t="inlineStr">
+        <is>
+          <t>DT before</t>
+        </is>
+      </c>
+      <c r="E58" s="41" t="inlineStr">
+        <is>
+          <t>DT after</t>
+        </is>
+      </c>
+      <c r="F58" s="41" t="inlineStr">
+        <is>
+          <t>Δ DT</t>
+        </is>
+      </c>
+      <c r="G58" s="41" t="inlineStr">
+        <is>
+          <t>t/month before</t>
+        </is>
+      </c>
+      <c r="H58" s="41" t="inlineStr">
+        <is>
+          <t>t/month AFTER</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B59" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C59" s="51" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D59" s="43" t="n">
+        <v>436</v>
+      </c>
+      <c r="E59" s="43" t="n">
+        <v>436</v>
+      </c>
+      <c r="F59" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" s="43" t="n">
+        <v>1410035</v>
+      </c>
+      <c r="H59" s="47" t="n">
+        <v>1410035</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B60" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C60" s="51" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D60" s="43" t="n">
+        <v>240</v>
+      </c>
+      <c r="E60" s="43" t="n">
+        <v>240</v>
+      </c>
+      <c r="F60" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="43" t="n">
+        <v>774783</v>
+      </c>
+      <c r="H60" s="47" t="n">
+        <v>774783</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="51" t="inlineStr">
+        <is>
+          <t>BLB&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B61" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C61" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D61" s="43" t="n">
+        <v>95</v>
+      </c>
+      <c r="E61" s="43" t="n">
+        <v>95</v>
+      </c>
+      <c r="F61" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="43" t="n">
+        <v>720750</v>
+      </c>
+      <c r="H61" s="47" t="n">
+        <v>720750</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B62" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C62" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D62" s="43" t="n">
+        <v>62</v>
+      </c>
+      <c r="E62" s="43" t="n">
+        <v>62</v>
+      </c>
+      <c r="F62" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" s="43" t="n">
+        <v>200508</v>
+      </c>
+      <c r="H62" s="47" t="n">
+        <v>200508</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="51" t="inlineStr">
+        <is>
+          <t>KR&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B63" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C63" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D63" s="43" t="n">
+        <v>19</v>
+      </c>
+      <c r="E63" s="43" t="n">
+        <v>19</v>
+      </c>
+      <c r="F63" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="43" t="n">
+        <v>78771</v>
+      </c>
+      <c r="H63" s="47" t="n">
+        <v>78771</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="51" t="inlineStr">
+        <is>
+          <t>BLB&gt;FENI KM0</t>
+        </is>
+      </c>
+      <c r="B64" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C64" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D64" s="43" t="n">
+        <v>202</v>
+      </c>
+      <c r="E64" s="43" t="n">
+        <v>202</v>
+      </c>
+      <c r="F64" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="43" t="n">
+        <v>1419366</v>
+      </c>
+      <c r="H64" s="47" t="n">
+        <v>1419366</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;FENI KM15</t>
+        </is>
+      </c>
+      <c r="B65" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C65" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D65" s="43" t="n">
+        <v>141</v>
+      </c>
+      <c r="E65" s="43" t="n">
+        <v>141</v>
+      </c>
+      <c r="F65" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" s="43" t="n">
+        <v>458180</v>
+      </c>
+      <c r="H65" s="47" t="n">
+        <v>458180</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="51" t="inlineStr">
+        <is>
+          <t>KR&gt;FENI KM15</t>
+        </is>
+      </c>
+      <c r="B66" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C66" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D66" s="43" t="n">
+        <v>50</v>
+      </c>
+      <c r="E66" s="43" t="n">
+        <v>50</v>
+      </c>
+      <c r="F66" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="43" t="n">
+        <v>244497</v>
+      </c>
+      <c r="H66" s="47" t="n">
+        <v>244497</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="51" t="inlineStr">
+        <is>
+          <t>KR&gt;POS 12</t>
+        </is>
+      </c>
+      <c r="B67" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C67" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D67" s="43" t="n">
+        <v>11</v>
+      </c>
+      <c r="E67" s="43" t="n">
+        <v>11</v>
+      </c>
+      <c r="F67" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" s="43" t="n">
+        <v>67828</v>
+      </c>
+      <c r="H67" s="47" t="n">
+        <v>67828</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="51" t="inlineStr">
+        <is>
+          <t>BLB&gt;POS 14</t>
+        </is>
+      </c>
+      <c r="B68" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C68" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D68" s="43" t="n">
+        <v>7</v>
+      </c>
+      <c r="E68" s="43" t="n">
+        <v>7</v>
+      </c>
+      <c r="F68" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" s="43" t="n">
+        <v>63364</v>
+      </c>
+      <c r="H68" s="47" t="n">
+        <v>63364</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;POS 12</t>
+        </is>
+      </c>
+      <c r="B69" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C69" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D69" s="43" t="n">
+        <v>18</v>
+      </c>
+      <c r="E69" s="43" t="n">
+        <v>18</v>
+      </c>
+      <c r="F69" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" s="43" t="n">
+        <v>63116</v>
+      </c>
+      <c r="H69" s="47" t="n">
+        <v>63116</v>
+      </c>
+    </row>
+    <row r="70"/>
+    <row r="71">
+      <c r="A71" s="41" t="inlineStr">
+        <is>
+          <t>3.0.1 — year after adjustment</t>
+        </is>
+      </c>
+      <c r="B71" s="41" t="inlineStr"/>
+      <c r="C71" s="41" t="inlineStr"/>
+      <c r="D71" s="41" t="inlineStr"/>
+      <c r="E71" s="41" t="inlineStr"/>
+      <c r="F71" s="41" t="inlineStr"/>
+      <c r="G71" s="41" t="inlineStr">
+        <is>
+          <t>Sales line t</t>
+        </is>
+      </c>
+      <c r="H71" s="41" t="inlineStr">
+        <is>
+          <t>New tonnage t</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="42" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B72" s="101" t="inlineStr">
+        <is>
+          <t>unchanged</t>
+        </is>
+      </c>
+      <c r="G72" s="43" t="n">
+        <v>5718685</v>
+      </c>
+      <c r="H72" s="94" t="n">
+        <v>5754614</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="42" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="B73" s="101" t="inlineStr">
+        <is>
+          <t>unchanged</t>
+        </is>
+      </c>
+      <c r="G73" s="43" t="n">
+        <v>3650201</v>
+      </c>
+      <c r="H73" s="94" t="n">
+        <v>3667273</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="42" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="B74" s="70" t="inlineStr">
+        <is>
+          <t>more tonnage</t>
+        </is>
+      </c>
+      <c r="G74" s="43" t="n">
+        <v>7634306</v>
+      </c>
+      <c r="H74" s="94" t="n">
+        <v>7726525</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="60" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="G75" s="47" t="n">
         <v>17003193</v>
       </c>
-      <c r="G13" s="93" t="n">
-        <v>-265185</v>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" s="42" t="inlineStr">
-        <is>
-          <t>3.0.2</t>
-        </is>
-      </c>
-      <c r="B15" s="42" t="inlineStr">
-        <is>
-          <t>Sep</t>
-        </is>
-      </c>
-      <c r="C15" s="43" t="n">
-        <v>581</v>
-      </c>
-      <c r="D15" s="43" t="n">
-        <v>851940</v>
-      </c>
-      <c r="E15" s="43" t="n">
-        <v>890366</v>
-      </c>
-      <c r="F15" s="93" t="n">
-        <v>-38426</v>
-      </c>
-      <c r="G15" s="52" t="n">
-        <v>-50907</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="42" t="inlineStr"/>
-      <c r="B16" s="42" t="inlineStr">
-        <is>
-          <t>Oct</t>
-        </is>
-      </c>
-      <c r="C16" s="43" t="n">
-        <v>931</v>
-      </c>
-      <c r="D16" s="43" t="n">
-        <v>1965741</v>
-      </c>
-      <c r="E16" s="43" t="n">
-        <v>2072629</v>
-      </c>
-      <c r="F16" s="93" t="n">
-        <v>-106888</v>
-      </c>
-      <c r="G16" s="52" t="n">
-        <v>-48812</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="42" t="inlineStr"/>
-      <c r="B17" s="42" t="inlineStr">
-        <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="C17" s="43" t="n">
-        <v>1280</v>
-      </c>
-      <c r="D17" s="43" t="n">
-        <v>2672880</v>
-      </c>
-      <c r="E17" s="43" t="n">
-        <v>2697656</v>
-      </c>
-      <c r="F17" s="93" t="n">
-        <v>-24776</v>
-      </c>
-      <c r="G17" s="61" t="n">
-        <v>37007</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="42" t="inlineStr"/>
-      <c r="B18" s="42" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="C18" s="43" t="n">
-        <v>1281</v>
-      </c>
-      <c r="D18" s="43" t="n">
-        <v>2369919</v>
-      </c>
-      <c r="E18" s="43" t="n">
-        <v>1973655</v>
-      </c>
-      <c r="F18" s="94" t="n">
-        <v>396264</v>
-      </c>
-      <c r="G18" s="61" t="n">
-        <v>346837</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="60" t="inlineStr">
-        <is>
-          <t>3.0.2 YEAR</t>
-        </is>
-      </c>
-      <c r="B19" s="42" t="inlineStr">
-        <is>
-          <t>Sep–Dec</t>
-        </is>
-      </c>
-      <c r="D19" s="43" t="n">
-        <v>17287318</v>
-      </c>
-      <c r="E19" s="43" t="n">
+      <c r="H75" s="61" t="n">
+        <v>17148412</v>
+      </c>
+    </row>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78">
+      <c r="A78" s="40" t="inlineStr">
+        <is>
+          <t>Scenario 3.0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="81" t="inlineStr">
+        <is>
+          <t>September — move 83 DT from TF&gt;HUAFEI to TF&gt;POS 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="41" t="inlineStr">
+        <is>
+          <t>Path</t>
+        </is>
+      </c>
+      <c r="B80" s="41" t="inlineStr">
+        <is>
+          <t>Contractor</t>
+        </is>
+      </c>
+      <c r="C80" s="41" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="D80" s="41" t="inlineStr">
+        <is>
+          <t>DT before</t>
+        </is>
+      </c>
+      <c r="E80" s="41" t="inlineStr">
+        <is>
+          <t>DT after</t>
+        </is>
+      </c>
+      <c r="F80" s="41" t="inlineStr">
+        <is>
+          <t>Δ DT</t>
+        </is>
+      </c>
+      <c r="G80" s="41" t="inlineStr">
+        <is>
+          <t>t/month before</t>
+        </is>
+      </c>
+      <c r="H80" s="41" t="inlineStr">
+        <is>
+          <t>t/month AFTER</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="97" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B81" s="97" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C81" s="97" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D81" s="98" t="n">
+        <v>211</v>
+      </c>
+      <c r="E81" s="93" t="n">
+        <v>156</v>
+      </c>
+      <c r="F81" s="93" t="n">
+        <v>-55</v>
+      </c>
+      <c r="G81" s="98" t="n">
+        <v>670710</v>
+      </c>
+      <c r="H81" s="93" t="n">
+        <v>495880</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="97" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B82" s="97" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C82" s="97" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D82" s="98" t="n">
+        <v>57</v>
+      </c>
+      <c r="E82" s="93" t="n">
+        <v>29</v>
+      </c>
+      <c r="F82" s="93" t="n">
+        <v>-28</v>
+      </c>
+      <c r="G82" s="98" t="n">
+        <v>181230</v>
+      </c>
+      <c r="H82" s="93" t="n">
+        <v>92205</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="51" t="inlineStr">
+        <is>
+          <t>BLB&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B83" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C83" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D83" s="43" t="n">
+        <v>83</v>
+      </c>
+      <c r="E83" s="43" t="n">
+        <v>83</v>
+      </c>
+      <c r="F83" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" s="43" t="n">
+        <v>610200</v>
+      </c>
+      <c r="H83" s="47" t="n">
+        <v>610200</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B84" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C84" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D84" s="43" t="n">
+        <v>52</v>
+      </c>
+      <c r="E84" s="43" t="n">
+        <v>52</v>
+      </c>
+      <c r="F84" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" s="43" t="n">
+        <v>165300</v>
+      </c>
+      <c r="H84" s="47" t="n">
+        <v>165300</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="51" t="inlineStr">
+        <is>
+          <t>KR&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B85" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C85" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D85" s="43" t="n">
+        <v>9</v>
+      </c>
+      <c r="E85" s="43" t="n">
+        <v>9</v>
+      </c>
+      <c r="F85" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" s="43" t="n">
+        <v>37800</v>
+      </c>
+      <c r="H85" s="47" t="n">
+        <v>37800</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B86" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C86" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D86" s="43" t="n">
+        <v>9</v>
+      </c>
+      <c r="E86" s="43" t="n">
+        <v>9</v>
+      </c>
+      <c r="F86" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="43" t="n">
+        <v>28620</v>
+      </c>
+      <c r="H86" s="47" t="n">
+        <v>28620</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;FENI KM15</t>
+        </is>
+      </c>
+      <c r="B87" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C87" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D87" s="43" t="n">
+        <v>77</v>
+      </c>
+      <c r="E87" s="43" t="n">
+        <v>77</v>
+      </c>
+      <c r="F87" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="43" t="n">
+        <v>246480</v>
+      </c>
+      <c r="H87" s="47" t="n">
+        <v>246480</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="51" t="inlineStr">
+        <is>
+          <t>KR&gt;FENI KM15</t>
+        </is>
+      </c>
+      <c r="B88" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C88" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D88" s="43" t="n">
+        <v>38</v>
+      </c>
+      <c r="E88" s="43" t="n">
+        <v>38</v>
+      </c>
+      <c r="F88" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="43" t="n">
+        <v>187800</v>
+      </c>
+      <c r="H88" s="47" t="n">
+        <v>187800</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="51" t="inlineStr">
+        <is>
+          <t>BLB&gt;FENI KM0</t>
+        </is>
+      </c>
+      <c r="B89" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C89" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D89" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E89" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="F89" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" s="43" t="n">
+        <v>68520</v>
+      </c>
+      <c r="H89" s="47" t="n">
+        <v>68520</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="51" t="inlineStr">
+        <is>
+          <t>KR&gt;POS 12</t>
+        </is>
+      </c>
+      <c r="B90" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C90" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D90" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E90" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="F90" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" s="43" t="n">
+        <v>62100</v>
+      </c>
+      <c r="H90" s="47" t="n">
+        <v>62100</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;POS 12</t>
+        </is>
+      </c>
+      <c r="B91" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C91" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D91" s="43" t="n">
+        <v>18</v>
+      </c>
+      <c r="E91" s="43" t="n">
+        <v>18</v>
+      </c>
+      <c r="F91" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" s="43" t="n">
+        <v>61470</v>
+      </c>
+      <c r="H91" s="47" t="n">
+        <v>61470</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="51" t="inlineStr">
+        <is>
+          <t>BLB&gt;POS 14</t>
+        </is>
+      </c>
+      <c r="B92" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C92" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D92" s="43" t="n">
+        <v>7</v>
+      </c>
+      <c r="E92" s="43" t="n">
+        <v>7</v>
+      </c>
+      <c r="F92" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" s="43" t="n">
+        <v>61320</v>
+      </c>
+      <c r="H92" s="47" t="n">
+        <v>61320</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="95" t="inlineStr">
+        <is>
+          <t>TF&gt;POS 6</t>
+        </is>
+      </c>
+      <c r="B93" s="95" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C93" s="95" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D93" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E93" s="94" t="n">
+        <v>28</v>
+      </c>
+      <c r="F93" s="94" t="n">
+        <v>28</v>
+      </c>
+      <c r="G93" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H93" s="94" t="n">
+        <v>106552</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="95" t="inlineStr">
+        <is>
+          <t>TF&gt;POS 6</t>
+        </is>
+      </c>
+      <c r="B94" s="95" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C94" s="95" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D94" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E94" s="94" t="n">
+        <v>55</v>
+      </c>
+      <c r="F94" s="94" t="n">
+        <v>55</v>
+      </c>
+      <c r="G94" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H94" s="94" t="n">
+        <v>191178</v>
+      </c>
+    </row>
+    <row r="95"/>
+    <row r="96">
+      <c r="A96" s="102" t="inlineStr">
+        <is>
+          <t>October — move 139 DT from TF&gt;HUAFEI to TF&gt;POS 6  ·  still 27,106 t short: the §4 rule keeps the split at 50/50, so no more than half a row may move</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="41" t="inlineStr">
+        <is>
+          <t>Path</t>
+        </is>
+      </c>
+      <c r="B97" s="41" t="inlineStr">
+        <is>
+          <t>Contractor</t>
+        </is>
+      </c>
+      <c r="C97" s="41" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="D97" s="41" t="inlineStr">
+        <is>
+          <t>DT before</t>
+        </is>
+      </c>
+      <c r="E97" s="41" t="inlineStr">
+        <is>
+          <t>DT after</t>
+        </is>
+      </c>
+      <c r="F97" s="41" t="inlineStr">
+        <is>
+          <t>Δ DT</t>
+        </is>
+      </c>
+      <c r="G97" s="41" t="inlineStr">
+        <is>
+          <t>t/month before</t>
+        </is>
+      </c>
+      <c r="H97" s="41" t="inlineStr">
+        <is>
+          <t>t/month AFTER</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;POS 6</t>
+        </is>
+      </c>
+      <c r="B98" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C98" s="51" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D98" s="43" t="n">
+        <v>172</v>
+      </c>
+      <c r="E98" s="43" t="n">
+        <v>172</v>
+      </c>
+      <c r="F98" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" s="43" t="n">
+        <v>679365</v>
+      </c>
+      <c r="H98" s="47" t="n">
+        <v>679365</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="97" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B99" s="97" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C99" s="97" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D99" s="98" t="n">
+        <v>172</v>
+      </c>
+      <c r="E99" s="93" t="n">
+        <v>86</v>
+      </c>
+      <c r="F99" s="93" t="n">
+        <v>-86</v>
+      </c>
+      <c r="G99" s="98" t="n">
+        <v>559519</v>
+      </c>
+      <c r="H99" s="93" t="n">
+        <v>279760</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;POS 6</t>
+        </is>
+      </c>
+      <c r="B100" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C100" s="51" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D100" s="43" t="n">
+        <v>106</v>
+      </c>
+      <c r="E100" s="43" t="n">
+        <v>106</v>
+      </c>
+      <c r="F100" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" s="43" t="n">
+        <v>382447</v>
+      </c>
+      <c r="H100" s="47" t="n">
+        <v>382447</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="97" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B101" s="97" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C101" s="97" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D101" s="98" t="n">
+        <v>106</v>
+      </c>
+      <c r="E101" s="93" t="n">
+        <v>53</v>
+      </c>
+      <c r="F101" s="93" t="n">
+        <v>-53</v>
+      </c>
+      <c r="G101" s="98" t="n">
+        <v>344410</v>
+      </c>
+      <c r="H101" s="93" t="n">
+        <v>172205</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="51" t="inlineStr">
+        <is>
+          <t>BLB&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B102" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C102" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D102" s="43" t="n">
+        <v>63</v>
+      </c>
+      <c r="E102" s="43" t="n">
+        <v>63</v>
+      </c>
+      <c r="F102" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" s="43" t="n">
+        <v>479632</v>
+      </c>
+      <c r="H102" s="47" t="n">
+        <v>479632</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B103" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C103" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D103" s="43" t="n">
+        <v>40</v>
+      </c>
+      <c r="E103" s="43" t="n">
+        <v>40</v>
+      </c>
+      <c r="F103" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" s="43" t="n">
+        <v>129952</v>
+      </c>
+      <c r="H103" s="47" t="n">
+        <v>129952</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B104" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C104" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D104" s="43" t="n">
+        <v>23</v>
+      </c>
+      <c r="E104" s="43" t="n">
+        <v>23</v>
+      </c>
+      <c r="F104" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" s="43" t="n">
+        <v>74834</v>
+      </c>
+      <c r="H104" s="47" t="n">
+        <v>74834</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="51" t="inlineStr">
+        <is>
+          <t>KR&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B105" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C105" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D105" s="43" t="n">
+        <v>13</v>
+      </c>
+      <c r="E105" s="43" t="n">
+        <v>13</v>
+      </c>
+      <c r="F105" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" s="43" t="n">
+        <v>54777</v>
+      </c>
+      <c r="H105" s="47" t="n">
+        <v>54777</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="51" t="inlineStr">
+        <is>
+          <t>BLB&gt;FENI KM0</t>
+        </is>
+      </c>
+      <c r="B106" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C106" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D106" s="43" t="n">
+        <v>65</v>
+      </c>
+      <c r="E106" s="43" t="n">
+        <v>65</v>
+      </c>
+      <c r="F106" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" s="43" t="n">
+        <v>458025</v>
+      </c>
+      <c r="H106" s="47" t="n">
+        <v>458025</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;FENI KM15</t>
+        </is>
+      </c>
+      <c r="B107" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C107" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D107" s="43" t="n">
+        <v>90</v>
+      </c>
+      <c r="E107" s="43" t="n">
+        <v>90</v>
+      </c>
+      <c r="F107" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" s="43" t="n">
+        <v>294066</v>
+      </c>
+      <c r="H107" s="47" t="n">
+        <v>294066</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="51" t="inlineStr">
+        <is>
+          <t>KR&gt;FENI KM15</t>
+        </is>
+      </c>
+      <c r="B108" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C108" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D108" s="43" t="n">
+        <v>46</v>
+      </c>
+      <c r="E108" s="43" t="n">
+        <v>46</v>
+      </c>
+      <c r="F108" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G108" s="43" t="n">
+        <v>228966</v>
+      </c>
+      <c r="H108" s="47" t="n">
+        <v>228966</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="51" t="inlineStr">
+        <is>
+          <t>BLB&gt;POS 14</t>
+        </is>
+      </c>
+      <c r="B109" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C109" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D109" s="43" t="n">
+        <v>7</v>
+      </c>
+      <c r="E109" s="43" t="n">
+        <v>7</v>
+      </c>
+      <c r="F109" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" s="43" t="n">
+        <v>63364</v>
+      </c>
+      <c r="H109" s="47" t="n">
+        <v>63364</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;POS 12</t>
+        </is>
+      </c>
+      <c r="B110" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C110" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D110" s="43" t="n">
+        <v>18</v>
+      </c>
+      <c r="E110" s="43" t="n">
+        <v>18</v>
+      </c>
+      <c r="F110" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" s="43" t="n">
+        <v>63302</v>
+      </c>
+      <c r="H110" s="47" t="n">
+        <v>63302</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="51" t="inlineStr">
+        <is>
+          <t>KR&gt;POS 12</t>
+        </is>
+      </c>
+      <c r="B111" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C111" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D111" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E111" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="F111" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G111" s="43" t="n">
+        <v>62775</v>
+      </c>
+      <c r="H111" s="47" t="n">
+        <v>62775</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="95" t="inlineStr">
+        <is>
+          <t>TF&gt;POS 6</t>
+        </is>
+      </c>
+      <c r="B112" s="95" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C112" s="95" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D112" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E112" s="94" t="n">
+        <v>86</v>
+      </c>
+      <c r="F112" s="94" t="n">
+        <v>86</v>
+      </c>
+      <c r="G112" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H112" s="94" t="n">
+        <v>338176</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="95" t="inlineStr">
+        <is>
+          <t>TF&gt;POS 6</t>
+        </is>
+      </c>
+      <c r="B113" s="95" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C113" s="95" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D113" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E113" s="94" t="n">
+        <v>53</v>
+      </c>
+      <c r="F113" s="94" t="n">
+        <v>53</v>
+      </c>
+      <c r="G113" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H113" s="94" t="n">
+        <v>190367</v>
+      </c>
+    </row>
+    <row r="114"/>
+    <row r="115">
+      <c r="A115" s="81" t="inlineStr">
+        <is>
+          <t>November — move 37 DT from TF&gt;HUAFEI to TF&gt;POS 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="41" t="inlineStr">
+        <is>
+          <t>Path</t>
+        </is>
+      </c>
+      <c r="B116" s="41" t="inlineStr">
+        <is>
+          <t>Contractor</t>
+        </is>
+      </c>
+      <c r="C116" s="41" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="D116" s="41" t="inlineStr">
+        <is>
+          <t>DT before</t>
+        </is>
+      </c>
+      <c r="E116" s="41" t="inlineStr">
+        <is>
+          <t>DT after</t>
+        </is>
+      </c>
+      <c r="F116" s="41" t="inlineStr">
+        <is>
+          <t>Δ DT</t>
+        </is>
+      </c>
+      <c r="G116" s="41" t="inlineStr">
+        <is>
+          <t>t/month before</t>
+        </is>
+      </c>
+      <c r="H116" s="41" t="inlineStr">
+        <is>
+          <t>t/month AFTER</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;POS 6</t>
+        </is>
+      </c>
+      <c r="B117" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C117" s="51" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D117" s="43" t="n">
+        <v>268</v>
+      </c>
+      <c r="E117" s="43" t="n">
+        <v>268</v>
+      </c>
+      <c r="F117" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G117" s="43" t="n">
+        <v>1015920</v>
+      </c>
+      <c r="H117" s="47" t="n">
+        <v>1015920</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="97" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B118" s="97" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C118" s="97" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D118" s="98" t="n">
+        <v>269</v>
+      </c>
+      <c r="E118" s="93" t="n">
+        <v>232</v>
+      </c>
+      <c r="F118" s="93" t="n">
+        <v>-37</v>
+      </c>
+      <c r="G118" s="98" t="n">
+        <v>836400</v>
+      </c>
+      <c r="H118" s="93" t="n">
+        <v>721356</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;POS 6</t>
+        </is>
+      </c>
+      <c r="B119" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C119" s="51" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D119" s="43" t="n">
+        <v>125</v>
+      </c>
+      <c r="E119" s="43" t="n">
+        <v>125</v>
+      </c>
+      <c r="F119" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G119" s="43" t="n">
+        <v>432810</v>
+      </c>
+      <c r="H119" s="47" t="n">
+        <v>432810</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B120" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C120" s="51" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D120" s="43" t="n">
+        <v>125</v>
+      </c>
+      <c r="E120" s="43" t="n">
+        <v>125</v>
+      </c>
+      <c r="F120" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G120" s="43" t="n">
+        <v>387750</v>
+      </c>
+      <c r="H120" s="47" t="n">
+        <v>387750</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="51" t="inlineStr">
+        <is>
+          <t>BLB&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B121" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C121" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D121" s="43" t="n">
+        <v>103</v>
+      </c>
+      <c r="E121" s="43" t="n">
+        <v>103</v>
+      </c>
+      <c r="F121" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G121" s="43" t="n">
+        <v>755610</v>
+      </c>
+      <c r="H121" s="47" t="n">
+        <v>755610</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B122" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C122" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D122" s="43" t="n">
+        <v>67</v>
+      </c>
+      <c r="E122" s="43" t="n">
+        <v>67</v>
+      </c>
+      <c r="F122" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G122" s="43" t="n">
+        <v>208320</v>
+      </c>
+      <c r="H122" s="47" t="n">
+        <v>208320</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="51" t="inlineStr">
+        <is>
+          <t>KR&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B123" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C123" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D123" s="43" t="n">
+        <v>32</v>
+      </c>
+      <c r="E123" s="43" t="n">
+        <v>32</v>
+      </c>
+      <c r="F123" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G123" s="43" t="n">
+        <v>125790</v>
+      </c>
+      <c r="H123" s="47" t="n">
+        <v>125790</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="51" t="inlineStr">
+        <is>
+          <t>BLB&gt;FENI KM0</t>
+        </is>
+      </c>
+      <c r="B124" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C124" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D124" s="43" t="n">
+        <v>150</v>
+      </c>
+      <c r="E124" s="43" t="n">
+        <v>150</v>
+      </c>
+      <c r="F124" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G124" s="43" t="n">
+        <v>1020750</v>
+      </c>
+      <c r="H124" s="47" t="n">
+        <v>1020750</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;FENI KM15</t>
+        </is>
+      </c>
+      <c r="B125" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C125" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D125" s="43" t="n">
+        <v>78</v>
+      </c>
+      <c r="E125" s="43" t="n">
+        <v>78</v>
+      </c>
+      <c r="F125" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G125" s="43" t="n">
+        <v>244020</v>
+      </c>
+      <c r="H125" s="47" t="n">
+        <v>244020</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="51" t="inlineStr">
+        <is>
+          <t>KR&gt;FENI KM15</t>
+        </is>
+      </c>
+      <c r="B126" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C126" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D126" s="43" t="n">
+        <v>27</v>
+      </c>
+      <c r="E126" s="43" t="n">
+        <v>27</v>
+      </c>
+      <c r="F126" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G126" s="43" t="n">
+        <v>127530</v>
+      </c>
+      <c r="H126" s="47" t="n">
+        <v>127530</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="51" t="inlineStr">
+        <is>
+          <t>KR&gt;POS 12</t>
+        </is>
+      </c>
+      <c r="B127" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C127" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D127" s="43" t="n">
+        <v>11</v>
+      </c>
+      <c r="E127" s="43" t="n">
+        <v>11</v>
+      </c>
+      <c r="F127" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G127" s="43" t="n">
+        <v>65310</v>
+      </c>
+      <c r="H127" s="47" t="n">
+        <v>65310</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="51" t="inlineStr">
+        <is>
+          <t>BLB&gt;POS 14</t>
+        </is>
+      </c>
+      <c r="B128" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C128" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D128" s="43" t="n">
+        <v>7</v>
+      </c>
+      <c r="E128" s="43" t="n">
+        <v>7</v>
+      </c>
+      <c r="F128" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G128" s="43" t="n">
+        <v>61320</v>
+      </c>
+      <c r="H128" s="47" t="n">
+        <v>61320</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;POS 12</t>
+        </is>
+      </c>
+      <c r="B129" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C129" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D129" s="43" t="n">
+        <v>18</v>
+      </c>
+      <c r="E129" s="43" t="n">
+        <v>18</v>
+      </c>
+      <c r="F129" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G129" s="43" t="n">
+        <v>61020</v>
+      </c>
+      <c r="H129" s="47" t="n">
+        <v>61020</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="95" t="inlineStr">
+        <is>
+          <t>TF&gt;POS 6</t>
+        </is>
+      </c>
+      <c r="B130" s="95" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C130" s="95" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D130" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E130" s="94" t="n">
+        <v>37</v>
+      </c>
+      <c r="F130" s="94" t="n">
+        <v>37</v>
+      </c>
+      <c r="G130" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H130" s="94" t="n">
+        <v>140801</v>
+      </c>
+    </row>
+    <row r="131"/>
+    <row r="132">
+      <c r="A132" s="100" t="inlineStr">
+        <is>
+          <t>December — no change needed (already at or above its line)</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="41" t="inlineStr">
+        <is>
+          <t>Path</t>
+        </is>
+      </c>
+      <c r="B133" s="41" t="inlineStr">
+        <is>
+          <t>Contractor</t>
+        </is>
+      </c>
+      <c r="C133" s="41" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="D133" s="41" t="inlineStr">
+        <is>
+          <t>DT before</t>
+        </is>
+      </c>
+      <c r="E133" s="41" t="inlineStr">
+        <is>
+          <t>DT after</t>
+        </is>
+      </c>
+      <c r="F133" s="41" t="inlineStr">
+        <is>
+          <t>Δ DT</t>
+        </is>
+      </c>
+      <c r="G133" s="41" t="inlineStr">
+        <is>
+          <t>t/month before</t>
+        </is>
+      </c>
+      <c r="H133" s="41" t="inlineStr">
+        <is>
+          <t>t/month AFTER</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;POS 6</t>
+        </is>
+      </c>
+      <c r="B134" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C134" s="51" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D134" s="43" t="n">
+        <v>217</v>
+      </c>
+      <c r="E134" s="43" t="n">
+        <v>217</v>
+      </c>
+      <c r="F134" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G134" s="43" t="n">
+        <v>851539</v>
+      </c>
+      <c r="H134" s="47" t="n">
+        <v>851539</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B135" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C135" s="51" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D135" s="43" t="n">
+        <v>218</v>
+      </c>
+      <c r="E135" s="43" t="n">
+        <v>218</v>
+      </c>
+      <c r="F135" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G135" s="43" t="n">
+        <v>702398</v>
+      </c>
+      <c r="H135" s="47" t="n">
+        <v>702398</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;POS 6</t>
+        </is>
+      </c>
+      <c r="B136" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C136" s="51" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D136" s="43" t="n">
+        <v>120</v>
+      </c>
+      <c r="E136" s="43" t="n">
+        <v>120</v>
+      </c>
+      <c r="F136" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G136" s="43" t="n">
+        <v>430125</v>
+      </c>
+      <c r="H136" s="47" t="n">
+        <v>430125</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B137" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C137" s="51" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D137" s="43" t="n">
+        <v>120</v>
+      </c>
+      <c r="E137" s="43" t="n">
+        <v>120</v>
+      </c>
+      <c r="F137" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G137" s="43" t="n">
+        <v>385826</v>
+      </c>
+      <c r="H137" s="47" t="n">
+        <v>385826</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="51" t="inlineStr">
+        <is>
+          <t>BLB&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B138" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C138" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D138" s="43" t="n">
+        <v>95</v>
+      </c>
+      <c r="E138" s="43" t="n">
+        <v>95</v>
+      </c>
+      <c r="F138" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G138" s="43" t="n">
+        <v>720750</v>
+      </c>
+      <c r="H138" s="47" t="n">
+        <v>720750</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B139" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C139" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D139" s="43" t="n">
+        <v>63</v>
+      </c>
+      <c r="E139" s="43" t="n">
+        <v>63</v>
+      </c>
+      <c r="F139" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G139" s="43" t="n">
+        <v>202988</v>
+      </c>
+      <c r="H139" s="47" t="n">
+        <v>202988</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="51" t="inlineStr">
+        <is>
+          <t>KR&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B140" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C140" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D140" s="43" t="n">
+        <v>19</v>
+      </c>
+      <c r="E140" s="43" t="n">
+        <v>19</v>
+      </c>
+      <c r="F140" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G140" s="43" t="n">
+        <v>77965</v>
+      </c>
+      <c r="H140" s="47" t="n">
+        <v>77965</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="51" t="inlineStr">
+        <is>
+          <t>BLB&gt;FENI KM0</t>
+        </is>
+      </c>
+      <c r="B141" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C141" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D141" s="43" t="n">
+        <v>202</v>
+      </c>
+      <c r="E141" s="43" t="n">
+        <v>202</v>
+      </c>
+      <c r="F141" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G141" s="43" t="n">
+        <v>1419366</v>
+      </c>
+      <c r="H141" s="47" t="n">
+        <v>1419366</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;FENI KM15</t>
+        </is>
+      </c>
+      <c r="B142" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C142" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D142" s="43" t="n">
+        <v>141</v>
+      </c>
+      <c r="E142" s="43" t="n">
+        <v>141</v>
+      </c>
+      <c r="F142" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G142" s="43" t="n">
+        <v>458180</v>
+      </c>
+      <c r="H142" s="47" t="n">
+        <v>458180</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="51" t="inlineStr">
+        <is>
+          <t>KR&gt;FENI KM15</t>
+        </is>
+      </c>
+      <c r="B143" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C143" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D143" s="43" t="n">
+        <v>50</v>
+      </c>
+      <c r="E143" s="43" t="n">
+        <v>50</v>
+      </c>
+      <c r="F143" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G143" s="43" t="n">
+        <v>244435</v>
+      </c>
+      <c r="H143" s="47" t="n">
+        <v>244435</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="51" t="inlineStr">
+        <is>
+          <t>KR&gt;POS 12</t>
+        </is>
+      </c>
+      <c r="B144" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C144" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D144" s="43" t="n">
+        <v>11</v>
+      </c>
+      <c r="E144" s="43" t="n">
+        <v>11</v>
+      </c>
+      <c r="F144" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G144" s="43" t="n">
+        <v>67797</v>
+      </c>
+      <c r="H144" s="47" t="n">
+        <v>67797</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="51" t="inlineStr">
+        <is>
+          <t>BLB&gt;POS 14</t>
+        </is>
+      </c>
+      <c r="B145" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C145" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D145" s="43" t="n">
+        <v>7</v>
+      </c>
+      <c r="E145" s="43" t="n">
+        <v>7</v>
+      </c>
+      <c r="F145" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G145" s="43" t="n">
+        <v>63364</v>
+      </c>
+      <c r="H145" s="47" t="n">
+        <v>63364</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;POS 12</t>
+        </is>
+      </c>
+      <c r="B146" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C146" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D146" s="43" t="n">
+        <v>18</v>
+      </c>
+      <c r="E146" s="43" t="n">
+        <v>18</v>
+      </c>
+      <c r="F146" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G146" s="43" t="n">
+        <v>63116</v>
+      </c>
+      <c r="H146" s="47" t="n">
+        <v>63116</v>
+      </c>
+    </row>
+    <row r="147"/>
+    <row r="148">
+      <c r="A148" s="41" t="inlineStr">
+        <is>
+          <t>3.0.2 — year after adjustment</t>
+        </is>
+      </c>
+      <c r="B148" s="41" t="inlineStr"/>
+      <c r="C148" s="41" t="inlineStr"/>
+      <c r="D148" s="41" t="inlineStr"/>
+      <c r="E148" s="41" t="inlineStr"/>
+      <c r="F148" s="41" t="inlineStr"/>
+      <c r="G148" s="41" t="inlineStr">
+        <is>
+          <t>Sales line t</t>
+        </is>
+      </c>
+      <c r="H148" s="41" t="inlineStr">
+        <is>
+          <t>New tonnage t</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="42" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B149" s="101" t="inlineStr">
+        <is>
+          <t>unchanged</t>
+        </is>
+      </c>
+      <c r="G149" s="43" t="n">
+        <v>5718685</v>
+      </c>
+      <c r="H149" s="94" t="n">
+        <v>5754396</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="42" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="B150" s="101" t="inlineStr">
+        <is>
+          <t>unchanged</t>
+        </is>
+      </c>
+      <c r="G150" s="43" t="n">
+        <v>3650201</v>
+      </c>
+      <c r="H150" s="94" t="n">
+        <v>3672538</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="42" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="B151" s="70" t="inlineStr">
+        <is>
+          <t>more tonnage</t>
+        </is>
+      </c>
+      <c r="G151" s="43" t="n">
+        <v>7634306</v>
+      </c>
+      <c r="H151" s="94" t="n">
+        <v>7996660</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="60" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="G152" s="47" t="n">
         <v>17003193</v>
       </c>
-      <c r="G19" s="94" t="n">
-        <v>284125</v>
-      </c>
-    </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" s="42" t="inlineStr">
-        <is>
-          <t>3.1.1</t>
-        </is>
-      </c>
-      <c r="B21" s="42" t="inlineStr">
-        <is>
-          <t>Sep</t>
-        </is>
-      </c>
-      <c r="C21" s="43" t="n">
-        <v>581</v>
-      </c>
-      <c r="D21" s="43" t="n">
-        <v>851940</v>
-      </c>
-      <c r="E21" s="43" t="n">
-        <v>840444</v>
-      </c>
-      <c r="F21" s="94" t="n">
-        <v>11496</v>
-      </c>
-      <c r="G21" s="61" t="n">
-        <v>20112</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="42" t="inlineStr"/>
-      <c r="B22" s="42" t="inlineStr">
-        <is>
-          <t>Oct</t>
-        </is>
-      </c>
-      <c r="C22" s="43" t="n">
-        <v>931</v>
-      </c>
-      <c r="D22" s="43" t="n">
-        <v>1675736</v>
-      </c>
-      <c r="E22" s="43" t="n">
-        <v>1786681</v>
-      </c>
-      <c r="F22" s="93" t="n">
-        <v>-110945</v>
-      </c>
-      <c r="G22" s="52" t="n">
-        <v>-78928</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="42" t="inlineStr"/>
-      <c r="B23" s="42" t="inlineStr">
-        <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="C23" s="43" t="n">
-        <v>1280</v>
-      </c>
-      <c r="D23" s="43" t="n">
-        <v>2324910</v>
-      </c>
-      <c r="E23" s="43" t="n">
-        <v>2320788</v>
-      </c>
-      <c r="F23" s="94" t="n">
-        <v>4122</v>
-      </c>
-      <c r="G23" s="61" t="n">
-        <v>34487</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="42" t="inlineStr"/>
-      <c r="B24" s="42" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="C24" s="43" t="n">
-        <v>1281</v>
-      </c>
-      <c r="D24" s="43" t="n">
-        <v>2049937</v>
-      </c>
-      <c r="E24" s="43" t="n">
-        <v>1696393</v>
-      </c>
-      <c r="F24" s="94" t="n">
-        <v>353544</v>
-      </c>
-      <c r="G24" s="61" t="n">
-        <v>317465</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="60" t="inlineStr">
-        <is>
-          <t>3.1.1 YEAR</t>
-        </is>
-      </c>
-      <c r="B25" s="42" t="inlineStr">
-        <is>
-          <t>Sep–Dec</t>
-        </is>
-      </c>
-      <c r="D25" s="43" t="n">
-        <v>17296329</v>
-      </c>
-      <c r="E25" s="43" t="n">
+      <c r="H152" s="61" t="n">
+        <v>17423594</v>
+      </c>
+    </row>
+    <row r="153"/>
+    <row r="154"/>
+    <row r="155">
+      <c r="A155" s="40" t="inlineStr">
+        <is>
+          <t>Scenario 3.1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="100" t="inlineStr">
+        <is>
+          <t>September — no change needed (already at or above its line)</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="41" t="inlineStr">
+        <is>
+          <t>Path</t>
+        </is>
+      </c>
+      <c r="B157" s="41" t="inlineStr">
+        <is>
+          <t>Contractor</t>
+        </is>
+      </c>
+      <c r="C157" s="41" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="D157" s="41" t="inlineStr">
+        <is>
+          <t>DT before</t>
+        </is>
+      </c>
+      <c r="E157" s="41" t="inlineStr">
+        <is>
+          <t>DT after</t>
+        </is>
+      </c>
+      <c r="F157" s="41" t="inlineStr">
+        <is>
+          <t>Δ DT</t>
+        </is>
+      </c>
+      <c r="G157" s="41" t="inlineStr">
+        <is>
+          <t>t/month before</t>
+        </is>
+      </c>
+      <c r="H157" s="41" t="inlineStr">
+        <is>
+          <t>t/month AFTER</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B158" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C158" s="51" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D158" s="43" t="n">
+        <v>211</v>
+      </c>
+      <c r="E158" s="43" t="n">
+        <v>211</v>
+      </c>
+      <c r="F158" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G158" s="43" t="n">
+        <v>670710</v>
+      </c>
+      <c r="H158" s="47" t="n">
+        <v>670710</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B159" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C159" s="51" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D159" s="43" t="n">
+        <v>57</v>
+      </c>
+      <c r="E159" s="43" t="n">
+        <v>57</v>
+      </c>
+      <c r="F159" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G159" s="43" t="n">
+        <v>181230</v>
+      </c>
+      <c r="H159" s="47" t="n">
+        <v>181230</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="51" t="inlineStr">
+        <is>
+          <t>BLB&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B160" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C160" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D160" s="43" t="n">
+        <v>83</v>
+      </c>
+      <c r="E160" s="43" t="n">
+        <v>83</v>
+      </c>
+      <c r="F160" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G160" s="43" t="n">
+        <v>610200</v>
+      </c>
+      <c r="H160" s="47" t="n">
+        <v>610200</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B161" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C161" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D161" s="43" t="n">
+        <v>52</v>
+      </c>
+      <c r="E161" s="43" t="n">
+        <v>52</v>
+      </c>
+      <c r="F161" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G161" s="43" t="n">
+        <v>165300</v>
+      </c>
+      <c r="H161" s="47" t="n">
+        <v>165300</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="51" t="inlineStr">
+        <is>
+          <t>KR&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B162" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C162" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D162" s="43" t="n">
+        <v>9</v>
+      </c>
+      <c r="E162" s="43" t="n">
+        <v>9</v>
+      </c>
+      <c r="F162" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G162" s="43" t="n">
+        <v>37800</v>
+      </c>
+      <c r="H162" s="47" t="n">
+        <v>37800</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B163" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C163" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D163" s="43" t="n">
+        <v>9</v>
+      </c>
+      <c r="E163" s="43" t="n">
+        <v>9</v>
+      </c>
+      <c r="F163" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G163" s="43" t="n">
+        <v>28620</v>
+      </c>
+      <c r="H163" s="47" t="n">
+        <v>28620</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;FENI KM15</t>
+        </is>
+      </c>
+      <c r="B164" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C164" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D164" s="43" t="n">
+        <v>77</v>
+      </c>
+      <c r="E164" s="43" t="n">
+        <v>77</v>
+      </c>
+      <c r="F164" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G164" s="43" t="n">
+        <v>246480</v>
+      </c>
+      <c r="H164" s="47" t="n">
+        <v>246480</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="51" t="inlineStr">
+        <is>
+          <t>KR&gt;FENI KM15</t>
+        </is>
+      </c>
+      <c r="B165" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C165" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D165" s="43" t="n">
+        <v>38</v>
+      </c>
+      <c r="E165" s="43" t="n">
+        <v>38</v>
+      </c>
+      <c r="F165" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G165" s="43" t="n">
+        <v>187800</v>
+      </c>
+      <c r="H165" s="47" t="n">
+        <v>187800</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="51" t="inlineStr">
+        <is>
+          <t>BLB&gt;FENI KM0</t>
+        </is>
+      </c>
+      <c r="B166" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C166" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D166" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E166" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="F166" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G166" s="43" t="n">
+        <v>68520</v>
+      </c>
+      <c r="H166" s="47" t="n">
+        <v>68520</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="51" t="inlineStr">
+        <is>
+          <t>KR&gt;POS 12</t>
+        </is>
+      </c>
+      <c r="B167" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C167" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D167" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E167" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="F167" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G167" s="43" t="n">
+        <v>62100</v>
+      </c>
+      <c r="H167" s="47" t="n">
+        <v>62100</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;POS 12</t>
+        </is>
+      </c>
+      <c r="B168" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C168" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D168" s="43" t="n">
+        <v>18</v>
+      </c>
+      <c r="E168" s="43" t="n">
+        <v>18</v>
+      </c>
+      <c r="F168" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G168" s="43" t="n">
+        <v>61470</v>
+      </c>
+      <c r="H168" s="47" t="n">
+        <v>61470</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="51" t="inlineStr">
+        <is>
+          <t>BLB&gt;POS 14</t>
+        </is>
+      </c>
+      <c r="B169" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C169" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D169" s="43" t="n">
+        <v>7</v>
+      </c>
+      <c r="E169" s="43" t="n">
+        <v>7</v>
+      </c>
+      <c r="F169" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G169" s="43" t="n">
+        <v>61320</v>
+      </c>
+      <c r="H169" s="47" t="n">
+        <v>61320</v>
+      </c>
+    </row>
+    <row r="170"/>
+    <row r="171">
+      <c r="A171" s="81" t="inlineStr">
+        <is>
+          <t>October — move 165 DT from TF&gt;HUAFEI to TF&gt;POS 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="41" t="inlineStr">
+        <is>
+          <t>Path</t>
+        </is>
+      </c>
+      <c r="B172" s="41" t="inlineStr">
+        <is>
+          <t>Contractor</t>
+        </is>
+      </c>
+      <c r="C172" s="41" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="D172" s="41" t="inlineStr">
+        <is>
+          <t>DT before</t>
+        </is>
+      </c>
+      <c r="E172" s="41" t="inlineStr">
+        <is>
+          <t>DT after</t>
+        </is>
+      </c>
+      <c r="F172" s="41" t="inlineStr">
+        <is>
+          <t>Δ DT</t>
+        </is>
+      </c>
+      <c r="G172" s="41" t="inlineStr">
+        <is>
+          <t>t/month before</t>
+        </is>
+      </c>
+      <c r="H172" s="41" t="inlineStr">
+        <is>
+          <t>t/month AFTER</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="97" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B173" s="97" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C173" s="97" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D173" s="98" t="n">
+        <v>302</v>
+      </c>
+      <c r="E173" s="93" t="n">
+        <v>151</v>
+      </c>
+      <c r="F173" s="93" t="n">
+        <v>-151</v>
+      </c>
+      <c r="G173" s="98" t="n">
+        <v>984963</v>
+      </c>
+      <c r="H173" s="93" t="n">
+        <v>492482</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="97" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B174" s="97" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C174" s="97" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D174" s="98" t="n">
+        <v>212</v>
+      </c>
+      <c r="E174" s="93" t="n">
+        <v>198</v>
+      </c>
+      <c r="F174" s="93" t="n">
+        <v>-14</v>
+      </c>
+      <c r="G174" s="98" t="n">
+        <v>690742</v>
+      </c>
+      <c r="H174" s="93" t="n">
+        <v>645127</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="51" t="inlineStr">
+        <is>
+          <t>BLB&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B175" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C175" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D175" s="43" t="n">
+        <v>107</v>
+      </c>
+      <c r="E175" s="43" t="n">
+        <v>107</v>
+      </c>
+      <c r="F175" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G175" s="43" t="n">
+        <v>810743</v>
+      </c>
+      <c r="H175" s="47" t="n">
+        <v>810743</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B176" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C176" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D176" s="43" t="n">
+        <v>40</v>
+      </c>
+      <c r="E176" s="43" t="n">
+        <v>40</v>
+      </c>
+      <c r="F176" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G176" s="43" t="n">
+        <v>130324</v>
+      </c>
+      <c r="H176" s="47" t="n">
+        <v>130324</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B177" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C177" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D177" s="43" t="n">
+        <v>22</v>
+      </c>
+      <c r="E177" s="43" t="n">
+        <v>22</v>
+      </c>
+      <c r="F177" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G177" s="43" t="n">
+        <v>71765</v>
+      </c>
+      <c r="H177" s="47" t="n">
+        <v>71765</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="51" t="inlineStr">
+        <is>
+          <t>KR&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B178" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C178" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D178" s="43" t="n">
+        <v>13</v>
+      </c>
+      <c r="E178" s="43" t="n">
+        <v>13</v>
+      </c>
+      <c r="F178" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G178" s="43" t="n">
+        <v>55180</v>
+      </c>
+      <c r="H178" s="47" t="n">
+        <v>55180</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="51" t="inlineStr">
+        <is>
+          <t>BLB&gt;FENI KM0</t>
+        </is>
+      </c>
+      <c r="B179" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C179" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D179" s="43" t="n">
+        <v>65</v>
+      </c>
+      <c r="E179" s="43" t="n">
+        <v>65</v>
+      </c>
+      <c r="F179" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G179" s="43" t="n">
+        <v>458025</v>
+      </c>
+      <c r="H179" s="47" t="n">
+        <v>458025</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;FENI KM15</t>
+        </is>
+      </c>
+      <c r="B180" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C180" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D180" s="43" t="n">
+        <v>89</v>
+      </c>
+      <c r="E180" s="43" t="n">
+        <v>89</v>
+      </c>
+      <c r="F180" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G180" s="43" t="n">
+        <v>291400</v>
+      </c>
+      <c r="H180" s="47" t="n">
+        <v>291400</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="51" t="inlineStr">
+        <is>
+          <t>KR&gt;FENI KM15</t>
+        </is>
+      </c>
+      <c r="B181" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C181" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D181" s="43" t="n">
+        <v>46</v>
+      </c>
+      <c r="E181" s="43" t="n">
+        <v>46</v>
+      </c>
+      <c r="F181" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G181" s="43" t="n">
+        <v>229865</v>
+      </c>
+      <c r="H181" s="47" t="n">
+        <v>229865</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="51" t="inlineStr">
+        <is>
+          <t>BLB&gt;POS 14</t>
+        </is>
+      </c>
+      <c r="B182" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C182" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D182" s="43" t="n">
+        <v>7</v>
+      </c>
+      <c r="E182" s="43" t="n">
+        <v>7</v>
+      </c>
+      <c r="F182" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G182" s="43" t="n">
+        <v>63364</v>
+      </c>
+      <c r="H182" s="47" t="n">
+        <v>63364</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;POS 12</t>
+        </is>
+      </c>
+      <c r="B183" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C183" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D183" s="43" t="n">
+        <v>18</v>
+      </c>
+      <c r="E183" s="43" t="n">
+        <v>18</v>
+      </c>
+      <c r="F183" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G183" s="43" t="n">
+        <v>63333</v>
+      </c>
+      <c r="H183" s="47" t="n">
+        <v>63333</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="51" t="inlineStr">
+        <is>
+          <t>KR&gt;POS 12</t>
+        </is>
+      </c>
+      <c r="B184" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C184" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D184" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E184" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="F184" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G184" s="43" t="n">
+        <v>63054</v>
+      </c>
+      <c r="H184" s="47" t="n">
+        <v>63054</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="95" t="inlineStr">
+        <is>
+          <t>TF&gt;POS 6</t>
+        </is>
+      </c>
+      <c r="B185" s="95" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C185" s="95" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D185" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E185" s="94" t="n">
+        <v>151</v>
+      </c>
+      <c r="F185" s="94" t="n">
+        <v>151</v>
+      </c>
+      <c r="G185" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H185" s="94" t="n">
+        <v>593774</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="95" t="inlineStr">
+        <is>
+          <t>TF&gt;POS 6</t>
+        </is>
+      </c>
+      <c r="B186" s="95" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C186" s="95" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D186" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E186" s="94" t="n">
+        <v>14</v>
+      </c>
+      <c r="F186" s="94" t="n">
+        <v>14</v>
+      </c>
+      <c r="G186" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H186" s="94" t="n">
+        <v>50286</v>
+      </c>
+    </row>
+    <row r="187"/>
+    <row r="188">
+      <c r="A188" s="100" t="inlineStr">
+        <is>
+          <t>November — no change needed (already at or above its line)</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="41" t="inlineStr">
+        <is>
+          <t>Path</t>
+        </is>
+      </c>
+      <c r="B189" s="41" t="inlineStr">
+        <is>
+          <t>Contractor</t>
+        </is>
+      </c>
+      <c r="C189" s="41" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="D189" s="41" t="inlineStr">
+        <is>
+          <t>DT before</t>
+        </is>
+      </c>
+      <c r="E189" s="41" t="inlineStr">
+        <is>
+          <t>DT after</t>
+        </is>
+      </c>
+      <c r="F189" s="41" t="inlineStr">
+        <is>
+          <t>Δ DT</t>
+        </is>
+      </c>
+      <c r="G189" s="41" t="inlineStr">
+        <is>
+          <t>t/month before</t>
+        </is>
+      </c>
+      <c r="H189" s="41" t="inlineStr">
+        <is>
+          <t>t/month AFTER</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B190" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C190" s="51" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D190" s="43" t="n">
+        <v>492</v>
+      </c>
+      <c r="E190" s="43" t="n">
+        <v>492</v>
+      </c>
+      <c r="F190" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G190" s="43" t="n">
+        <v>1538400</v>
+      </c>
+      <c r="H190" s="47" t="n">
+        <v>1538400</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B191" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C191" s="51" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D191" s="43" t="n">
+        <v>252</v>
+      </c>
+      <c r="E191" s="43" t="n">
+        <v>252</v>
+      </c>
+      <c r="F191" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G191" s="43" t="n">
+        <v>786510</v>
+      </c>
+      <c r="H191" s="47" t="n">
+        <v>786510</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="51" t="inlineStr">
+        <is>
+          <t>BLB&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B192" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C192" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D192" s="43" t="n">
+        <v>148</v>
+      </c>
+      <c r="E192" s="43" t="n">
+        <v>148</v>
+      </c>
+      <c r="F192" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G192" s="43" t="n">
+        <v>1081050</v>
+      </c>
+      <c r="H192" s="47" t="n">
+        <v>1081050</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B193" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C193" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D193" s="43" t="n">
+        <v>67</v>
+      </c>
+      <c r="E193" s="43" t="n">
+        <v>67</v>
+      </c>
+      <c r="F193" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G193" s="43" t="n">
+        <v>209490</v>
+      </c>
+      <c r="H193" s="47" t="n">
+        <v>209490</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="51" t="inlineStr">
+        <is>
+          <t>KR&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B194" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C194" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D194" s="43" t="n">
+        <v>31</v>
+      </c>
+      <c r="E194" s="43" t="n">
+        <v>31</v>
+      </c>
+      <c r="F194" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G194" s="43" t="n">
+        <v>123570</v>
+      </c>
+      <c r="H194" s="47" t="n">
+        <v>123570</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="51" t="inlineStr">
+        <is>
+          <t>BLB&gt;FENI KM0</t>
+        </is>
+      </c>
+      <c r="B195" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C195" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D195" s="43" t="n">
+        <v>150</v>
+      </c>
+      <c r="E195" s="43" t="n">
+        <v>150</v>
+      </c>
+      <c r="F195" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G195" s="43" t="n">
+        <v>1020750</v>
+      </c>
+      <c r="H195" s="47" t="n">
+        <v>1020750</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;FENI KM15</t>
+        </is>
+      </c>
+      <c r="B196" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C196" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D196" s="43" t="n">
+        <v>78</v>
+      </c>
+      <c r="E196" s="43" t="n">
+        <v>78</v>
+      </c>
+      <c r="F196" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G196" s="43" t="n">
+        <v>244530</v>
+      </c>
+      <c r="H196" s="47" t="n">
+        <v>244530</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="51" t="inlineStr">
+        <is>
+          <t>KR&gt;FENI KM15</t>
+        </is>
+      </c>
+      <c r="B197" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C197" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D197" s="43" t="n">
+        <v>27</v>
+      </c>
+      <c r="E197" s="43" t="n">
+        <v>27</v>
+      </c>
+      <c r="F197" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G197" s="43" t="n">
+        <v>128070</v>
+      </c>
+      <c r="H197" s="47" t="n">
+        <v>128070</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="51" t="inlineStr">
+        <is>
+          <t>BLB&gt;POS 14</t>
+        </is>
+      </c>
+      <c r="B198" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C198" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D198" s="43" t="n">
+        <v>7</v>
+      </c>
+      <c r="E198" s="43" t="n">
+        <v>7</v>
+      </c>
+      <c r="F198" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G198" s="43" t="n">
+        <v>61320</v>
+      </c>
+      <c r="H198" s="47" t="n">
+        <v>61320</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;POS 12</t>
+        </is>
+      </c>
+      <c r="B199" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C199" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D199" s="43" t="n">
+        <v>18</v>
+      </c>
+      <c r="E199" s="43" t="n">
+        <v>18</v>
+      </c>
+      <c r="F199" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G199" s="43" t="n">
+        <v>61080</v>
+      </c>
+      <c r="H199" s="47" t="n">
+        <v>61080</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="51" t="inlineStr">
+        <is>
+          <t>KR&gt;POS 12</t>
+        </is>
+      </c>
+      <c r="B200" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C200" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D200" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E200" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="F200" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G200" s="43" t="n">
+        <v>59730</v>
+      </c>
+      <c r="H200" s="47" t="n">
+        <v>59730</v>
+      </c>
+    </row>
+    <row r="201"/>
+    <row r="202">
+      <c r="A202" s="100" t="inlineStr">
+        <is>
+          <t>December — no change needed (already at or above its line)</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="41" t="inlineStr">
+        <is>
+          <t>Path</t>
+        </is>
+      </c>
+      <c r="B203" s="41" t="inlineStr">
+        <is>
+          <t>Contractor</t>
+        </is>
+      </c>
+      <c r="C203" s="41" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="D203" s="41" t="inlineStr">
+        <is>
+          <t>DT before</t>
+        </is>
+      </c>
+      <c r="E203" s="41" t="inlineStr">
+        <is>
+          <t>DT after</t>
+        </is>
+      </c>
+      <c r="F203" s="41" t="inlineStr">
+        <is>
+          <t>Δ DT</t>
+        </is>
+      </c>
+      <c r="G203" s="41" t="inlineStr">
+        <is>
+          <t>t/month before</t>
+        </is>
+      </c>
+      <c r="H203" s="41" t="inlineStr">
+        <is>
+          <t>t/month AFTER</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B204" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C204" s="51" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D204" s="43" t="n">
+        <v>393</v>
+      </c>
+      <c r="E204" s="43" t="n">
+        <v>393</v>
+      </c>
+      <c r="F204" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G204" s="43" t="n">
+        <v>1271527</v>
+      </c>
+      <c r="H204" s="47" t="n">
+        <v>1271527</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B205" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C205" s="51" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D205" s="43" t="n">
+        <v>241</v>
+      </c>
+      <c r="E205" s="43" t="n">
+        <v>241</v>
+      </c>
+      <c r="F205" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G205" s="43" t="n">
+        <v>778410</v>
+      </c>
+      <c r="H205" s="47" t="n">
+        <v>778410</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="51" t="inlineStr">
+        <is>
+          <t>BLB&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B206" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C206" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D206" s="43" t="n">
+        <v>139</v>
+      </c>
+      <c r="E206" s="43" t="n">
+        <v>139</v>
+      </c>
+      <c r="F206" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G206" s="43" t="n">
+        <v>1049381</v>
+      </c>
+      <c r="H206" s="47" t="n">
+        <v>1049381</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B207" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C207" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D207" s="43" t="n">
+        <v>62</v>
+      </c>
+      <c r="E207" s="43" t="n">
+        <v>62</v>
+      </c>
+      <c r="F207" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G207" s="43" t="n">
+        <v>200601</v>
+      </c>
+      <c r="H207" s="47" t="n">
+        <v>200601</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="51" t="inlineStr">
+        <is>
+          <t>KR&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B208" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C208" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D208" s="43" t="n">
+        <v>19</v>
+      </c>
+      <c r="E208" s="43" t="n">
+        <v>19</v>
+      </c>
+      <c r="F208" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G208" s="43" t="n">
+        <v>78895</v>
+      </c>
+      <c r="H208" s="47" t="n">
+        <v>78895</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="51" t="inlineStr">
+        <is>
+          <t>BLB&gt;FENI KM0</t>
+        </is>
+      </c>
+      <c r="B209" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C209" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D209" s="43" t="n">
+        <v>202</v>
+      </c>
+      <c r="E209" s="43" t="n">
+        <v>202</v>
+      </c>
+      <c r="F209" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G209" s="43" t="n">
+        <v>1418994</v>
+      </c>
+      <c r="H209" s="47" t="n">
+        <v>1418994</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;FENI KM15</t>
+        </is>
+      </c>
+      <c r="B210" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C210" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D210" s="43" t="n">
+        <v>140</v>
+      </c>
+      <c r="E210" s="43" t="n">
+        <v>140</v>
+      </c>
+      <c r="F210" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G210" s="43" t="n">
+        <v>455762</v>
+      </c>
+      <c r="H210" s="47" t="n">
+        <v>455762</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="51" t="inlineStr">
+        <is>
+          <t>KR&gt;FENI KM15</t>
+        </is>
+      </c>
+      <c r="B211" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C211" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D211" s="43" t="n">
+        <v>50</v>
+      </c>
+      <c r="E211" s="43" t="n">
+        <v>50</v>
+      </c>
+      <c r="F211" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G211" s="43" t="n">
+        <v>245489</v>
+      </c>
+      <c r="H211" s="47" t="n">
+        <v>245489</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="51" t="inlineStr">
+        <is>
+          <t>BLB&gt;POS 14</t>
+        </is>
+      </c>
+      <c r="B212" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C212" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D212" s="43" t="n">
+        <v>7</v>
+      </c>
+      <c r="E212" s="43" t="n">
+        <v>7</v>
+      </c>
+      <c r="F212" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G212" s="43" t="n">
+        <v>63333</v>
+      </c>
+      <c r="H212" s="47" t="n">
+        <v>63333</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;POS 12</t>
+        </is>
+      </c>
+      <c r="B213" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C213" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D213" s="43" t="n">
+        <v>18</v>
+      </c>
+      <c r="E213" s="43" t="n">
+        <v>18</v>
+      </c>
+      <c r="F213" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G213" s="43" t="n">
+        <v>63147</v>
+      </c>
+      <c r="H213" s="47" t="n">
+        <v>63147</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="51" t="inlineStr">
+        <is>
+          <t>KR&gt;POS 12</t>
+        </is>
+      </c>
+      <c r="B214" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C214" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D214" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E214" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="F214" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G214" s="43" t="n">
+        <v>61969</v>
+      </c>
+      <c r="H214" s="47" t="n">
+        <v>61969</v>
+      </c>
+    </row>
+    <row r="215"/>
+    <row r="216">
+      <c r="A216" s="41" t="inlineStr">
+        <is>
+          <t>3.1.1 — year after adjustment</t>
+        </is>
+      </c>
+      <c r="B216" s="41" t="inlineStr"/>
+      <c r="C216" s="41" t="inlineStr"/>
+      <c r="D216" s="41" t="inlineStr"/>
+      <c r="E216" s="41" t="inlineStr"/>
+      <c r="F216" s="41" t="inlineStr"/>
+      <c r="G216" s="41" t="inlineStr">
+        <is>
+          <t>Sales line t</t>
+        </is>
+      </c>
+      <c r="H216" s="41" t="inlineStr">
+        <is>
+          <t>New tonnage t</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="42" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B217" s="101" t="inlineStr">
+        <is>
+          <t>unchanged</t>
+        </is>
+      </c>
+      <c r="G217" s="43" t="n">
+        <v>5718685</v>
+      </c>
+      <c r="H217" s="94" t="n">
+        <v>5740905</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="42" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="B218" s="101" t="inlineStr">
+        <is>
+          <t>unchanged</t>
+        </is>
+      </c>
+      <c r="G218" s="43" t="n">
+        <v>4640202</v>
+      </c>
+      <c r="H218" s="94" t="n">
+        <v>4652919</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="42" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="B219" s="70" t="inlineStr">
+        <is>
+          <t>more tonnage</t>
+        </is>
+      </c>
+      <c r="G219" s="43" t="n">
+        <v>6644306</v>
+      </c>
+      <c r="H219" s="94" t="n">
+        <v>7008455</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="60" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="G220" s="47" t="n">
         <v>17003193</v>
       </c>
-      <c r="G25" s="94" t="n">
-        <v>293136</v>
-      </c>
-    </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" s="42" t="inlineStr">
-        <is>
-          <t>3.1.2</t>
-        </is>
-      </c>
-      <c r="B27" s="42" t="inlineStr">
-        <is>
-          <t>Sep</t>
-        </is>
-      </c>
-      <c r="C27" s="43" t="n">
-        <v>581</v>
-      </c>
-      <c r="D27" s="43" t="n">
-        <v>851940</v>
-      </c>
-      <c r="E27" s="43" t="n">
-        <v>840444</v>
-      </c>
-      <c r="F27" s="94" t="n">
-        <v>11496</v>
-      </c>
-      <c r="G27" s="61" t="n">
-        <v>20112</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="42" t="inlineStr"/>
-      <c r="B28" s="42" t="inlineStr">
-        <is>
-          <t>Oct</t>
-        </is>
-      </c>
-      <c r="C28" s="43" t="n">
-        <v>931</v>
-      </c>
-      <c r="D28" s="43" t="n">
-        <v>1808447</v>
-      </c>
-      <c r="E28" s="43" t="n">
-        <v>1786681</v>
-      </c>
-      <c r="F28" s="94" t="n">
-        <v>21766</v>
-      </c>
-      <c r="G28" s="61" t="n">
-        <v>59284</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="42" t="inlineStr"/>
-      <c r="B29" s="42" t="inlineStr">
-        <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="C29" s="43" t="n">
-        <v>1280</v>
-      </c>
-      <c r="D29" s="43" t="n">
-        <v>2520240</v>
-      </c>
-      <c r="E29" s="43" t="n">
-        <v>2320788</v>
-      </c>
-      <c r="F29" s="94" t="n">
-        <v>199452</v>
-      </c>
-      <c r="G29" s="61" t="n">
-        <v>237094</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="42" t="inlineStr"/>
-      <c r="B30" s="42" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="C30" s="43" t="n">
-        <v>1281</v>
-      </c>
-      <c r="D30" s="43" t="n">
-        <v>2218732</v>
-      </c>
-      <c r="E30" s="43" t="n">
-        <v>1696393</v>
-      </c>
-      <c r="F30" s="94" t="n">
-        <v>522339</v>
-      </c>
-      <c r="G30" s="61" t="n">
-        <v>491883</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="60" t="inlineStr">
-        <is>
-          <t>3.1.2 YEAR</t>
-        </is>
-      </c>
-      <c r="B31" s="42" t="inlineStr">
-        <is>
-          <t>Sep–Dec</t>
-        </is>
-      </c>
-      <c r="D31" s="43" t="n">
-        <v>17811566</v>
-      </c>
-      <c r="E31" s="43" t="n">
+      <c r="H220" s="61" t="n">
+        <v>17402279</v>
+      </c>
+    </row>
+    <row r="221"/>
+    <row r="222"/>
+    <row r="223">
+      <c r="A223" s="40" t="inlineStr">
+        <is>
+          <t>Scenario 3.1.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="100" t="inlineStr">
+        <is>
+          <t>September — no change needed (already at or above its line)</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="41" t="inlineStr">
+        <is>
+          <t>Path</t>
+        </is>
+      </c>
+      <c r="B225" s="41" t="inlineStr">
+        <is>
+          <t>Contractor</t>
+        </is>
+      </c>
+      <c r="C225" s="41" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="D225" s="41" t="inlineStr">
+        <is>
+          <t>DT before</t>
+        </is>
+      </c>
+      <c r="E225" s="41" t="inlineStr">
+        <is>
+          <t>DT after</t>
+        </is>
+      </c>
+      <c r="F225" s="41" t="inlineStr">
+        <is>
+          <t>Δ DT</t>
+        </is>
+      </c>
+      <c r="G225" s="41" t="inlineStr">
+        <is>
+          <t>t/month before</t>
+        </is>
+      </c>
+      <c r="H225" s="41" t="inlineStr">
+        <is>
+          <t>t/month AFTER</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B226" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C226" s="51" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D226" s="43" t="n">
+        <v>211</v>
+      </c>
+      <c r="E226" s="43" t="n">
+        <v>211</v>
+      </c>
+      <c r="F226" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G226" s="43" t="n">
+        <v>670710</v>
+      </c>
+      <c r="H226" s="47" t="n">
+        <v>670710</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B227" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C227" s="51" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D227" s="43" t="n">
+        <v>57</v>
+      </c>
+      <c r="E227" s="43" t="n">
+        <v>57</v>
+      </c>
+      <c r="F227" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G227" s="43" t="n">
+        <v>181230</v>
+      </c>
+      <c r="H227" s="47" t="n">
+        <v>181230</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="51" t="inlineStr">
+        <is>
+          <t>BLB&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B228" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C228" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D228" s="43" t="n">
+        <v>83</v>
+      </c>
+      <c r="E228" s="43" t="n">
+        <v>83</v>
+      </c>
+      <c r="F228" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G228" s="43" t="n">
+        <v>610200</v>
+      </c>
+      <c r="H228" s="47" t="n">
+        <v>610200</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B229" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C229" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D229" s="43" t="n">
+        <v>52</v>
+      </c>
+      <c r="E229" s="43" t="n">
+        <v>52</v>
+      </c>
+      <c r="F229" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G229" s="43" t="n">
+        <v>165300</v>
+      </c>
+      <c r="H229" s="47" t="n">
+        <v>165300</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="51" t="inlineStr">
+        <is>
+          <t>KR&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B230" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C230" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D230" s="43" t="n">
+        <v>9</v>
+      </c>
+      <c r="E230" s="43" t="n">
+        <v>9</v>
+      </c>
+      <c r="F230" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G230" s="43" t="n">
+        <v>37800</v>
+      </c>
+      <c r="H230" s="47" t="n">
+        <v>37800</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B231" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C231" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D231" s="43" t="n">
+        <v>9</v>
+      </c>
+      <c r="E231" s="43" t="n">
+        <v>9</v>
+      </c>
+      <c r="F231" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G231" s="43" t="n">
+        <v>28620</v>
+      </c>
+      <c r="H231" s="47" t="n">
+        <v>28620</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;FENI KM15</t>
+        </is>
+      </c>
+      <c r="B232" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C232" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D232" s="43" t="n">
+        <v>77</v>
+      </c>
+      <c r="E232" s="43" t="n">
+        <v>77</v>
+      </c>
+      <c r="F232" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G232" s="43" t="n">
+        <v>246480</v>
+      </c>
+      <c r="H232" s="47" t="n">
+        <v>246480</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="51" t="inlineStr">
+        <is>
+          <t>KR&gt;FENI KM15</t>
+        </is>
+      </c>
+      <c r="B233" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C233" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D233" s="43" t="n">
+        <v>38</v>
+      </c>
+      <c r="E233" s="43" t="n">
+        <v>38</v>
+      </c>
+      <c r="F233" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G233" s="43" t="n">
+        <v>187800</v>
+      </c>
+      <c r="H233" s="47" t="n">
+        <v>187800</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="51" t="inlineStr">
+        <is>
+          <t>BLB&gt;FENI KM0</t>
+        </is>
+      </c>
+      <c r="B234" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C234" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D234" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E234" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="F234" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G234" s="43" t="n">
+        <v>68520</v>
+      </c>
+      <c r="H234" s="47" t="n">
+        <v>68520</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="51" t="inlineStr">
+        <is>
+          <t>KR&gt;POS 12</t>
+        </is>
+      </c>
+      <c r="B235" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C235" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D235" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E235" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="F235" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G235" s="43" t="n">
+        <v>62100</v>
+      </c>
+      <c r="H235" s="47" t="n">
+        <v>62100</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;POS 12</t>
+        </is>
+      </c>
+      <c r="B236" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C236" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D236" s="43" t="n">
+        <v>18</v>
+      </c>
+      <c r="E236" s="43" t="n">
+        <v>18</v>
+      </c>
+      <c r="F236" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G236" s="43" t="n">
+        <v>61470</v>
+      </c>
+      <c r="H236" s="47" t="n">
+        <v>61470</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="51" t="inlineStr">
+        <is>
+          <t>BLB&gt;POS 14</t>
+        </is>
+      </c>
+      <c r="B237" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C237" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D237" s="43" t="n">
+        <v>7</v>
+      </c>
+      <c r="E237" s="43" t="n">
+        <v>7</v>
+      </c>
+      <c r="F237" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G237" s="43" t="n">
+        <v>61320</v>
+      </c>
+      <c r="H237" s="47" t="n">
+        <v>61320</v>
+      </c>
+    </row>
+    <row r="238"/>
+    <row r="239">
+      <c r="A239" s="100" t="inlineStr">
+        <is>
+          <t>October — no change needed (already at or above its line)</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="41" t="inlineStr">
+        <is>
+          <t>Path</t>
+        </is>
+      </c>
+      <c r="B240" s="41" t="inlineStr">
+        <is>
+          <t>Contractor</t>
+        </is>
+      </c>
+      <c r="C240" s="41" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="D240" s="41" t="inlineStr">
+        <is>
+          <t>DT before</t>
+        </is>
+      </c>
+      <c r="E240" s="41" t="inlineStr">
+        <is>
+          <t>DT after</t>
+        </is>
+      </c>
+      <c r="F240" s="41" t="inlineStr">
+        <is>
+          <t>Δ DT</t>
+        </is>
+      </c>
+      <c r="G240" s="41" t="inlineStr">
+        <is>
+          <t>t/month before</t>
+        </is>
+      </c>
+      <c r="H240" s="41" t="inlineStr">
+        <is>
+          <t>t/month AFTER</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;POS 6</t>
+        </is>
+      </c>
+      <c r="B241" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C241" s="51" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D241" s="43" t="n">
+        <v>150</v>
+      </c>
+      <c r="E241" s="43" t="n">
+        <v>150</v>
+      </c>
+      <c r="F241" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G241" s="43" t="n">
+        <v>592937</v>
+      </c>
+      <c r="H241" s="47" t="n">
+        <v>592937</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B242" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C242" s="51" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D242" s="43" t="n">
+        <v>150</v>
+      </c>
+      <c r="E242" s="43" t="n">
+        <v>150</v>
+      </c>
+      <c r="F242" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G242" s="43" t="n">
+        <v>488188</v>
+      </c>
+      <c r="H242" s="47" t="n">
+        <v>488188</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;POS 6</t>
+        </is>
+      </c>
+      <c r="B243" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C243" s="51" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D243" s="43" t="n">
+        <v>106</v>
+      </c>
+      <c r="E243" s="43" t="n">
+        <v>106</v>
+      </c>
+      <c r="F243" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G243" s="43" t="n">
+        <v>382726</v>
+      </c>
+      <c r="H243" s="47" t="n">
+        <v>382726</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B244" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C244" s="51" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D244" s="43" t="n">
+        <v>106</v>
+      </c>
+      <c r="E244" s="43" t="n">
+        <v>106</v>
+      </c>
+      <c r="F244" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G244" s="43" t="n">
+        <v>344596</v>
+      </c>
+      <c r="H244" s="47" t="n">
+        <v>344596</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="51" t="inlineStr">
+        <is>
+          <t>BLB&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B245" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C245" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D245" s="43" t="n">
+        <v>107</v>
+      </c>
+      <c r="E245" s="43" t="n">
+        <v>107</v>
+      </c>
+      <c r="F245" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G245" s="43" t="n">
+        <v>810743</v>
+      </c>
+      <c r="H245" s="47" t="n">
+        <v>810743</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B246" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C246" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D246" s="43" t="n">
+        <v>40</v>
+      </c>
+      <c r="E246" s="43" t="n">
+        <v>40</v>
+      </c>
+      <c r="F246" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G246" s="43" t="n">
+        <v>130045</v>
+      </c>
+      <c r="H246" s="47" t="n">
+        <v>130045</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B247" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C247" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D247" s="43" t="n">
+        <v>23</v>
+      </c>
+      <c r="E247" s="43" t="n">
+        <v>23</v>
+      </c>
+      <c r="F247" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G247" s="43" t="n">
+        <v>74865</v>
+      </c>
+      <c r="H247" s="47" t="n">
+        <v>74865</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="51" t="inlineStr">
+        <is>
+          <t>KR&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B248" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C248" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D248" s="43" t="n">
+        <v>13</v>
+      </c>
+      <c r="E248" s="43" t="n">
+        <v>13</v>
+      </c>
+      <c r="F248" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G248" s="43" t="n">
+        <v>54839</v>
+      </c>
+      <c r="H248" s="47" t="n">
+        <v>54839</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="51" t="inlineStr">
+        <is>
+          <t>BLB&gt;FENI KM0</t>
+        </is>
+      </c>
+      <c r="B249" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C249" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D249" s="43" t="n">
+        <v>65</v>
+      </c>
+      <c r="E249" s="43" t="n">
+        <v>65</v>
+      </c>
+      <c r="F249" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G249" s="43" t="n">
+        <v>458025</v>
+      </c>
+      <c r="H249" s="47" t="n">
+        <v>458025</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;FENI KM15</t>
+        </is>
+      </c>
+      <c r="B250" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C250" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D250" s="43" t="n">
+        <v>90</v>
+      </c>
+      <c r="E250" s="43" t="n">
+        <v>90</v>
+      </c>
+      <c r="F250" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G250" s="43" t="n">
+        <v>294562</v>
+      </c>
+      <c r="H250" s="47" t="n">
+        <v>294562</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="51" t="inlineStr">
+        <is>
+          <t>KR&gt;FENI KM15</t>
+        </is>
+      </c>
+      <c r="B251" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C251" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D251" s="43" t="n">
+        <v>46</v>
+      </c>
+      <c r="E251" s="43" t="n">
+        <v>46</v>
+      </c>
+      <c r="F251" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G251" s="43" t="n">
+        <v>229772</v>
+      </c>
+      <c r="H251" s="47" t="n">
+        <v>229772</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="51" t="inlineStr">
+        <is>
+          <t>BLB&gt;POS 14</t>
+        </is>
+      </c>
+      <c r="B252" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C252" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D252" s="43" t="n">
+        <v>7</v>
+      </c>
+      <c r="E252" s="43" t="n">
+        <v>7</v>
+      </c>
+      <c r="F252" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G252" s="43" t="n">
+        <v>63364</v>
+      </c>
+      <c r="H252" s="47" t="n">
+        <v>63364</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;POS 12</t>
+        </is>
+      </c>
+      <c r="B253" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C253" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D253" s="43" t="n">
+        <v>18</v>
+      </c>
+      <c r="E253" s="43" t="n">
+        <v>18</v>
+      </c>
+      <c r="F253" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G253" s="43" t="n">
+        <v>63333</v>
+      </c>
+      <c r="H253" s="47" t="n">
+        <v>63333</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="51" t="inlineStr">
+        <is>
+          <t>KR&gt;POS 12</t>
+        </is>
+      </c>
+      <c r="B254" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C254" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D254" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E254" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="F254" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G254" s="43" t="n">
+        <v>62992</v>
+      </c>
+      <c r="H254" s="47" t="n">
+        <v>62992</v>
+      </c>
+    </row>
+    <row r="255"/>
+    <row r="256">
+      <c r="A256" s="100" t="inlineStr">
+        <is>
+          <t>November — no change needed (already at or above its line)</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="41" t="inlineStr">
+        <is>
+          <t>Path</t>
+        </is>
+      </c>
+      <c r="B257" s="41" t="inlineStr">
+        <is>
+          <t>Contractor</t>
+        </is>
+      </c>
+      <c r="C257" s="41" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="D257" s="41" t="inlineStr">
+        <is>
+          <t>DT before</t>
+        </is>
+      </c>
+      <c r="E257" s="41" t="inlineStr">
+        <is>
+          <t>DT after</t>
+        </is>
+      </c>
+      <c r="F257" s="41" t="inlineStr">
+        <is>
+          <t>Δ DT</t>
+        </is>
+      </c>
+      <c r="G257" s="41" t="inlineStr">
+        <is>
+          <t>t/month before</t>
+        </is>
+      </c>
+      <c r="H257" s="41" t="inlineStr">
+        <is>
+          <t>t/month AFTER</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;POS 6</t>
+        </is>
+      </c>
+      <c r="B258" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C258" s="51" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D258" s="43" t="n">
+        <v>246</v>
+      </c>
+      <c r="E258" s="43" t="n">
+        <v>246</v>
+      </c>
+      <c r="F258" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G258" s="43" t="n">
+        <v>933330</v>
+      </c>
+      <c r="H258" s="47" t="n">
+        <v>933330</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B259" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C259" s="51" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D259" s="43" t="n">
+        <v>246</v>
+      </c>
+      <c r="E259" s="43" t="n">
+        <v>246</v>
+      </c>
+      <c r="F259" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G259" s="43" t="n">
+        <v>765600</v>
+      </c>
+      <c r="H259" s="47" t="n">
+        <v>765600</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;POS 6</t>
+        </is>
+      </c>
+      <c r="B260" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C260" s="51" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D260" s="43" t="n">
+        <v>125</v>
+      </c>
+      <c r="E260" s="43" t="n">
+        <v>125</v>
+      </c>
+      <c r="F260" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G260" s="43" t="n">
+        <v>433200</v>
+      </c>
+      <c r="H260" s="47" t="n">
+        <v>433200</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B261" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C261" s="51" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D261" s="43" t="n">
+        <v>125</v>
+      </c>
+      <c r="E261" s="43" t="n">
+        <v>125</v>
+      </c>
+      <c r="F261" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G261" s="43" t="n">
+        <v>388140</v>
+      </c>
+      <c r="H261" s="47" t="n">
+        <v>388140</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="51" t="inlineStr">
+        <is>
+          <t>BLB&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B262" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C262" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D262" s="43" t="n">
+        <v>148</v>
+      </c>
+      <c r="E262" s="43" t="n">
+        <v>148</v>
+      </c>
+      <c r="F262" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G262" s="43" t="n">
+        <v>1081050</v>
+      </c>
+      <c r="H262" s="47" t="n">
+        <v>1081050</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B263" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C263" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D263" s="43" t="n">
+        <v>67</v>
+      </c>
+      <c r="E263" s="43" t="n">
+        <v>67</v>
+      </c>
+      <c r="F263" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G263" s="43" t="n">
+        <v>208530</v>
+      </c>
+      <c r="H263" s="47" t="n">
+        <v>208530</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="51" t="inlineStr">
+        <is>
+          <t>KR&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B264" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C264" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D264" s="43" t="n">
+        <v>32</v>
+      </c>
+      <c r="E264" s="43" t="n">
+        <v>32</v>
+      </c>
+      <c r="F264" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G264" s="43" t="n">
+        <v>125970</v>
+      </c>
+      <c r="H264" s="47" t="n">
+        <v>125970</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="51" t="inlineStr">
+        <is>
+          <t>BLB&gt;FENI KM0</t>
+        </is>
+      </c>
+      <c r="B265" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C265" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D265" s="43" t="n">
+        <v>150</v>
+      </c>
+      <c r="E265" s="43" t="n">
+        <v>150</v>
+      </c>
+      <c r="F265" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G265" s="43" t="n">
+        <v>1020750</v>
+      </c>
+      <c r="H265" s="47" t="n">
+        <v>1020750</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;FENI KM15</t>
+        </is>
+      </c>
+      <c r="B266" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C266" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D266" s="43" t="n">
+        <v>78</v>
+      </c>
+      <c r="E266" s="43" t="n">
+        <v>78</v>
+      </c>
+      <c r="F266" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G266" s="43" t="n">
+        <v>244530</v>
+      </c>
+      <c r="H266" s="47" t="n">
+        <v>244530</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="51" t="inlineStr">
+        <is>
+          <t>KR&gt;FENI KM15</t>
+        </is>
+      </c>
+      <c r="B267" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C267" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D267" s="43" t="n">
+        <v>27</v>
+      </c>
+      <c r="E267" s="43" t="n">
+        <v>27</v>
+      </c>
+      <c r="F267" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G267" s="43" t="n">
+        <v>128040</v>
+      </c>
+      <c r="H267" s="47" t="n">
+        <v>128040</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="51" t="inlineStr">
+        <is>
+          <t>KR&gt;POS 12</t>
+        </is>
+      </c>
+      <c r="B268" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C268" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D268" s="43" t="n">
+        <v>11</v>
+      </c>
+      <c r="E268" s="43" t="n">
+        <v>11</v>
+      </c>
+      <c r="F268" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G268" s="43" t="n">
+        <v>65610</v>
+      </c>
+      <c r="H268" s="47" t="n">
+        <v>65610</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="51" t="inlineStr">
+        <is>
+          <t>BLB&gt;POS 14</t>
+        </is>
+      </c>
+      <c r="B269" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C269" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D269" s="43" t="n">
+        <v>7</v>
+      </c>
+      <c r="E269" s="43" t="n">
+        <v>7</v>
+      </c>
+      <c r="F269" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G269" s="43" t="n">
+        <v>61320</v>
+      </c>
+      <c r="H269" s="47" t="n">
+        <v>61320</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;POS 12</t>
+        </is>
+      </c>
+      <c r="B270" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C270" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D270" s="43" t="n">
+        <v>18</v>
+      </c>
+      <c r="E270" s="43" t="n">
+        <v>18</v>
+      </c>
+      <c r="F270" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G270" s="43" t="n">
+        <v>61080</v>
+      </c>
+      <c r="H270" s="47" t="n">
+        <v>61080</v>
+      </c>
+    </row>
+    <row r="271"/>
+    <row r="272">
+      <c r="A272" s="100" t="inlineStr">
+        <is>
+          <t>December — no change needed (already at or above its line)</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="41" t="inlineStr">
+        <is>
+          <t>Path</t>
+        </is>
+      </c>
+      <c r="B273" s="41" t="inlineStr">
+        <is>
+          <t>Contractor</t>
+        </is>
+      </c>
+      <c r="C273" s="41" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="D273" s="41" t="inlineStr">
+        <is>
+          <t>DT before</t>
+        </is>
+      </c>
+      <c r="E273" s="41" t="inlineStr">
+        <is>
+          <t>DT after</t>
+        </is>
+      </c>
+      <c r="F273" s="41" t="inlineStr">
+        <is>
+          <t>Δ DT</t>
+        </is>
+      </c>
+      <c r="G273" s="41" t="inlineStr">
+        <is>
+          <t>t/month before</t>
+        </is>
+      </c>
+      <c r="H273" s="41" t="inlineStr">
+        <is>
+          <t>t/month AFTER</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;POS 6</t>
+        </is>
+      </c>
+      <c r="B274" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C274" s="51" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D274" s="43" t="n">
+        <v>195</v>
+      </c>
+      <c r="E274" s="43" t="n">
+        <v>195</v>
+      </c>
+      <c r="F274" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G274" s="43" t="n">
+        <v>766196</v>
+      </c>
+      <c r="H274" s="47" t="n">
+        <v>766196</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B275" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C275" s="51" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D275" s="43" t="n">
+        <v>196</v>
+      </c>
+      <c r="E275" s="43" t="n">
+        <v>196</v>
+      </c>
+      <c r="F275" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G275" s="43" t="n">
+        <v>632307</v>
+      </c>
+      <c r="H275" s="47" t="n">
+        <v>632307</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;POS 6</t>
+        </is>
+      </c>
+      <c r="B276" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C276" s="51" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D276" s="43" t="n">
+        <v>120</v>
+      </c>
+      <c r="E276" s="43" t="n">
+        <v>120</v>
+      </c>
+      <c r="F276" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G276" s="43" t="n">
+        <v>430683</v>
+      </c>
+      <c r="H276" s="47" t="n">
+        <v>430683</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B277" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C277" s="51" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D277" s="43" t="n">
+        <v>121</v>
+      </c>
+      <c r="E277" s="43" t="n">
+        <v>121</v>
+      </c>
+      <c r="F277" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G277" s="43" t="n">
+        <v>389577</v>
+      </c>
+      <c r="H277" s="47" t="n">
+        <v>389577</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="51" t="inlineStr">
+        <is>
+          <t>BLB&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B278" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C278" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D278" s="43" t="n">
+        <v>139</v>
+      </c>
+      <c r="E278" s="43" t="n">
+        <v>139</v>
+      </c>
+      <c r="F278" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G278" s="43" t="n">
+        <v>1049629</v>
+      </c>
+      <c r="H278" s="47" t="n">
+        <v>1049629</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B279" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C279" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D279" s="43" t="n">
+        <v>63</v>
+      </c>
+      <c r="E279" s="43" t="n">
+        <v>63</v>
+      </c>
+      <c r="F279" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G279" s="43" t="n">
+        <v>203236</v>
+      </c>
+      <c r="H279" s="47" t="n">
+        <v>203236</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="51" t="inlineStr">
+        <is>
+          <t>KR&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B280" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C280" s="51" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D280" s="43" t="n">
+        <v>19</v>
+      </c>
+      <c r="E280" s="43" t="n">
+        <v>19</v>
+      </c>
+      <c r="F280" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G280" s="43" t="n">
+        <v>78120</v>
+      </c>
+      <c r="H280" s="47" t="n">
+        <v>78120</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="51" t="inlineStr">
+        <is>
+          <t>BLB&gt;FENI KM0</t>
+        </is>
+      </c>
+      <c r="B281" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C281" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D281" s="43" t="n">
+        <v>202</v>
+      </c>
+      <c r="E281" s="43" t="n">
+        <v>202</v>
+      </c>
+      <c r="F281" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G281" s="43" t="n">
+        <v>1419366</v>
+      </c>
+      <c r="H281" s="47" t="n">
+        <v>1419366</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;FENI KM15</t>
+        </is>
+      </c>
+      <c r="B282" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C282" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D282" s="43" t="n">
+        <v>141</v>
+      </c>
+      <c r="E282" s="43" t="n">
+        <v>141</v>
+      </c>
+      <c r="F282" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G282" s="43" t="n">
+        <v>458955</v>
+      </c>
+      <c r="H282" s="47" t="n">
+        <v>458955</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="51" t="inlineStr">
+        <is>
+          <t>KR&gt;FENI KM15</t>
+        </is>
+      </c>
+      <c r="B283" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C283" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D283" s="43" t="n">
+        <v>50</v>
+      </c>
+      <c r="E283" s="43" t="n">
+        <v>50</v>
+      </c>
+      <c r="F283" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G283" s="43" t="n">
+        <v>245427</v>
+      </c>
+      <c r="H283" s="47" t="n">
+        <v>245427</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="51" t="inlineStr">
+        <is>
+          <t>BLB&gt;POS 14</t>
+        </is>
+      </c>
+      <c r="B284" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C284" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D284" s="43" t="n">
+        <v>7</v>
+      </c>
+      <c r="E284" s="43" t="n">
+        <v>7</v>
+      </c>
+      <c r="F284" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G284" s="43" t="n">
+        <v>63364</v>
+      </c>
+      <c r="H284" s="47" t="n">
+        <v>63364</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;POS 12</t>
+        </is>
+      </c>
+      <c r="B285" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C285" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D285" s="43" t="n">
+        <v>18</v>
+      </c>
+      <c r="E285" s="43" t="n">
+        <v>18</v>
+      </c>
+      <c r="F285" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G285" s="43" t="n">
+        <v>63178</v>
+      </c>
+      <c r="H285" s="47" t="n">
+        <v>63178</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="51" t="inlineStr">
+        <is>
+          <t>KR&gt;POS 12</t>
+        </is>
+      </c>
+      <c r="B286" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C286" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D286" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E286" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="F286" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G286" s="43" t="n">
+        <v>61938</v>
+      </c>
+      <c r="H286" s="47" t="n">
+        <v>61938</v>
+      </c>
+    </row>
+    <row r="287"/>
+    <row r="288">
+      <c r="A288" s="41" t="inlineStr">
+        <is>
+          <t>3.1.2 — year after adjustment</t>
+        </is>
+      </c>
+      <c r="B288" s="41" t="inlineStr"/>
+      <c r="C288" s="41" t="inlineStr"/>
+      <c r="D288" s="41" t="inlineStr"/>
+      <c r="E288" s="41" t="inlineStr"/>
+      <c r="F288" s="41" t="inlineStr"/>
+      <c r="G288" s="41" t="inlineStr">
+        <is>
+          <t>Sales line t</t>
+        </is>
+      </c>
+      <c r="H288" s="41" t="inlineStr">
+        <is>
+          <t>New tonnage t</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="42" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B289" s="101" t="inlineStr">
+        <is>
+          <t>unchanged</t>
+        </is>
+      </c>
+      <c r="G289" s="43" t="n">
+        <v>5718685</v>
+      </c>
+      <c r="H289" s="94" t="n">
+        <v>5753296</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="42" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="B290" s="101" t="inlineStr">
+        <is>
+          <t>unchanged</t>
+        </is>
+      </c>
+      <c r="G290" s="43" t="n">
+        <v>4640202</v>
+      </c>
+      <c r="H290" s="94" t="n">
+        <v>4658947</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="42" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="B291" s="101" t="inlineStr">
+        <is>
+          <t>unchanged</t>
+        </is>
+      </c>
+      <c r="G291" s="43" t="n">
+        <v>6644306</v>
+      </c>
+      <c r="H291" s="94" t="n">
+        <v>7399420</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="60" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="G292" s="47" t="n">
         <v>17003193</v>
       </c>
-      <c r="G31" s="94" t="n">
-        <v>808373</v>
-      </c>
-    </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" s="50" t="inlineStr">
-        <is>
-          <t>ADJUSTMENT B — how far the trip-length lever actually reaches</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="28" customHeight="1">
-      <c r="A34" s="49" t="inlineStr">
-        <is>
-          <t>For each SHORT month: how many LD trucks would have to move from TF&gt;HUAFEI to TF&gt;POS 6 to close the gap, and how many LD trucks that month actually has. If the shift needed exceeds the fleet on the route, the gap cannot be closed by route mix alone.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="41" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="B35" s="41" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="C35" s="41" t="inlineStr">
-        <is>
-          <t>Gap to close t</t>
-        </is>
-      </c>
-      <c r="D35" s="41" t="inlineStr">
-        <is>
-          <t>DT to shift HUAFEI→POS 6</t>
-        </is>
-      </c>
-      <c r="E35" s="41" t="inlineStr">
-        <is>
-          <t>LD DT available</t>
-        </is>
-      </c>
-      <c r="F35" s="41" t="inlineStr">
-        <is>
-          <t>Feasible?</t>
-        </is>
-      </c>
-      <c r="G35" s="41" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="42" t="inlineStr">
-        <is>
-          <t>3.0.1</t>
-        </is>
-      </c>
-      <c r="B36" s="42" t="inlineStr">
-        <is>
-          <t>Sep</t>
-        </is>
-      </c>
-      <c r="C36" s="43" t="n">
-        <v>38426</v>
-      </c>
-      <c r="D36" s="59" t="n">
-        <v>77</v>
-      </c>
-      <c r="E36" s="43" t="n">
-        <v>268</v>
-      </c>
-      <c r="F36" s="95" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G36" s="76" t="inlineStr">
-        <is>
-          <t>shift 77 of 268 LD trucks to the longer POS 6 haul</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="42" t="inlineStr">
-        <is>
-          <t>3.0.1</t>
-        </is>
-      </c>
-      <c r="B37" s="42" t="inlineStr">
-        <is>
-          <t>Oct</t>
-        </is>
-      </c>
-      <c r="C37" s="43" t="n">
-        <v>257765</v>
-      </c>
-      <c r="D37" s="59" t="n">
-        <v>501</v>
-      </c>
-      <c r="E37" s="43" t="n">
-        <v>557</v>
-      </c>
-      <c r="F37" s="95" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G37" s="76" t="inlineStr">
-        <is>
-          <t>shift 501 of 557 LD trucks to the longer POS 6 haul</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="42" t="inlineStr">
-        <is>
-          <t>3.0.1</t>
-        </is>
-      </c>
-      <c r="B38" s="42" t="inlineStr">
-        <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="C38" s="43" t="n">
-        <v>233126</v>
-      </c>
-      <c r="D38" s="59" t="n">
-        <v>468</v>
-      </c>
-      <c r="E38" s="43" t="n">
-        <v>788</v>
-      </c>
-      <c r="F38" s="95" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G38" s="76" t="inlineStr">
-        <is>
-          <t>shift 468 of 788 LD trucks to the longer POS 6 haul</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="42" t="inlineStr">
-        <is>
-          <t>3.0.2</t>
-        </is>
-      </c>
-      <c r="B39" s="42" t="inlineStr">
-        <is>
-          <t>Sep</t>
-        </is>
-      </c>
-      <c r="C39" s="43" t="n">
-        <v>38426</v>
-      </c>
-      <c r="D39" s="59" t="n">
-        <v>77</v>
-      </c>
-      <c r="E39" s="43" t="n">
-        <v>268</v>
-      </c>
-      <c r="F39" s="95" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G39" s="76" t="inlineStr">
-        <is>
-          <t>shift 77 of 268 LD trucks to the longer POS 6 haul</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="42" t="inlineStr">
-        <is>
-          <t>3.0.2</t>
-        </is>
-      </c>
-      <c r="B40" s="42" t="inlineStr">
-        <is>
-          <t>Oct</t>
-        </is>
-      </c>
-      <c r="C40" s="43" t="n">
-        <v>106888</v>
-      </c>
-      <c r="D40" s="59" t="n">
-        <v>208</v>
-      </c>
-      <c r="E40" s="43" t="n">
-        <v>278</v>
-      </c>
-      <c r="F40" s="95" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G40" s="76" t="inlineStr">
-        <is>
-          <t>shift 208 of 278 LD trucks to the longer POS 6 haul</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="42" t="inlineStr">
-        <is>
-          <t>3.0.2</t>
-        </is>
-      </c>
-      <c r="B41" s="42" t="inlineStr">
-        <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="C41" s="43" t="n">
-        <v>24776</v>
-      </c>
-      <c r="D41" s="59" t="n">
-        <v>50</v>
-      </c>
-      <c r="E41" s="43" t="n">
-        <v>394</v>
-      </c>
-      <c r="F41" s="95" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G41" s="76" t="inlineStr">
-        <is>
-          <t>shift 50 of 394 LD trucks to the longer POS 6 haul</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="42" t="inlineStr">
-        <is>
-          <t>3.1.1</t>
-        </is>
-      </c>
-      <c r="B42" s="42" t="inlineStr">
-        <is>
-          <t>Oct</t>
-        </is>
-      </c>
-      <c r="C42" s="43" t="n">
-        <v>110945</v>
-      </c>
-      <c r="D42" s="59" t="n">
-        <v>216</v>
-      </c>
-      <c r="E42" s="43" t="n">
-        <v>514</v>
-      </c>
-      <c r="F42" s="95" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G42" s="76" t="inlineStr">
-        <is>
-          <t>shift 216 of 514 LD trucks to the longer POS 6 haul</t>
-        </is>
-      </c>
-    </row>
-    <row r="43"/>
-    <row r="44" ht="26" customHeight="1">
-      <c r="A44" s="96" t="inlineStr">
-        <is>
-          <t>READING: every short month CAN be closed by route mix — the shift needed is always smaller than the LD fleet on HUAFEI that month (3.0.1 Oct needs 501 of 557; Nov 468 of 788). But in 3.0.1 and 3.1.1 that means opening a POS 6 leg those scenarios do not have by definition, which turns them into .2 scenarios.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="26" customHeight="1">
-      <c r="A45" s="96" t="inlineStr">
-        <is>
-          <t>The .2 scenarios already run the split, which is why they clear the line (+284 kt and +808 kt) with only small October/November gaps left. 3.0.1 is the only scenario that stays short overall (-265 kt).</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="26" customHeight="1">
-      <c r="A46" s="96" t="inlineStr">
-        <is>
-          <t>CONCLUSION: adjustment B is feasible and needs no extra trucks — but it IS the POS 6 split. Choosing a .2 scenario applies the same lever as policy instead of month by month, and lands 17.29-17.81 Mt with the fleet untouched at 580/930/1,280/1,281 DT. December still finishes over its LD line, which is what Options 1 and 2 are for.</t>
-        </is>
+      <c r="H292" s="61" t="n">
+        <v>17811663</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A44:G44"/>
-    <mergeCell ref="A45:G45"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A34:G34"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A46:G46"/>
+  <mergeCells count="2">
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A3:H3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/scenario_comparison_dec_options.xlsx
+++ b/reports/scenario_comparison_dec_options.xlsx
@@ -22,7 +22,7 @@
     <numFmt numFmtId="165" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="166" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="53">
+  <fonts count="54">
     <font>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -376,6 +376,12 @@
     <font>
       <name val="Arial"/>
       <color rgb="005B6B7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001B7A41"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -911,7 +917,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1082,6 +1088,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="51" fillId="41" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="41" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2401,7 +2410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K114"/>
+  <dimension ref="A1:K117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2441,14 +2450,14 @@
     <row r="5" ht="34" customHeight="1">
       <c r="A5" s="40" t="inlineStr">
         <is>
-          <t>OPTION 2 — LONGER HAUL: keep them working by moving SAP from the KM15 legs to the LONGER KM0 legs. TF&gt;FENI KM0 is 67.8 km against KM15's 52.8 (78.4 vs 105.4 t/DT/day) and KR&gt;FENI KM0 is 39.0 km against 24.0 (102.6 vs 160.4), so the SAME tonnage needs 1.34x and 1.56x the trucks. SAP tonnage does not rise — the tonnes simply travel further, which is what absorbs the trucks.</t>
+          <t>OPTION 2 — LONGER HAUL: keep them working by moving SAP onto LONGER legs — KM15 to KM0 first, then POS 12 to KM0. TF&gt;FENI KM0 is 67.8 km against KM15's 52.8 (78.4 vs 105.4 t/DT/day) and KR&gt;FENI KM0 is 39.0 km against 24.0 (102.6 vs 160.4), so the SAME tonnage needs 1.34x and 1.56x the trucks. SAP tonnage does not rise — the tonnes simply travel further, which is what absorbs the trucks.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>RULES KEPT: a truck never changes contractor. RIM works BLB and TF only, SMA works KR and TF only, so RIM trucks go to TF&gt;FENI KM0 and SMA trucks to KR&gt;FENI KM0. Whatever the KM0 legs cannot absorb is reported as trucks to park — that is the honest ceiling.</t>
+          <t>RULES KEPT: a truck never changes contractor. RIM works BLB and TF only, SMA works KR and TF only, so RIM trucks go to TF&gt;FENI KM0 and SMA trucks to KR&gt;FENI KM0. The surplus is taken from BOTH contractors LIM-LD rows in whatever mix absorbs the most trucks — RIM first, since its TF leg is the bigger sink. Parking is the LAST resort: it appears only for trucks no longer haul can take.</t>
         </is>
       </c>
     </row>
@@ -2526,35 +2535,35 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="45" t="inlineStr">
+      <c r="A12" s="51" t="inlineStr">
         <is>
           <t>TF&gt;HUAFEI</t>
         </is>
       </c>
-      <c r="B12" s="45" t="inlineStr">
+      <c r="B12" s="51" t="inlineStr">
         <is>
           <t>RIM</t>
         </is>
       </c>
-      <c r="C12" s="45" t="inlineStr">
+      <c r="C12" s="51" t="inlineStr">
         <is>
           <t>LIM-LD</t>
         </is>
       </c>
-      <c r="D12" s="46" t="n">
+      <c r="D12" s="52" t="n">
         <v>436</v>
       </c>
-      <c r="E12" s="46" t="n">
-        <v>436</v>
-      </c>
-      <c r="F12" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="46" t="n">
+      <c r="E12" s="53" t="n">
+        <v>389</v>
+      </c>
+      <c r="F12" s="53" t="n">
+        <v>-47</v>
+      </c>
+      <c r="G12" s="52" t="n">
         <v>1410035</v>
       </c>
-      <c r="H12" s="48" t="n">
-        <v>1410035</v>
+      <c r="H12" s="53" t="n">
+        <v>1258036</v>
       </c>
       <c r="J12" s="49" t="inlineStr">
         <is>
@@ -2585,16 +2594,16 @@
         <v>240</v>
       </c>
       <c r="E13" s="53" t="n">
-        <v>175</v>
+        <v>222</v>
       </c>
       <c r="F13" s="53" t="n">
-        <v>-65</v>
+        <v>-18</v>
       </c>
       <c r="G13" s="52" t="n">
         <v>774783</v>
       </c>
       <c r="H13" s="53" t="n">
-        <v>564946</v>
+        <v>716674</v>
       </c>
       <c r="J13" s="49" t="inlineStr">
         <is>
@@ -2642,7 +2651,7 @@
         </is>
       </c>
       <c r="K14" s="50" t="n">
-        <v>1.000671818276244</v>
+        <v>1.000534586450106</v>
       </c>
     </row>
     <row r="15">
@@ -2750,35 +2759,35 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="45" t="inlineStr">
+      <c r="A18" s="51" t="inlineStr">
         <is>
           <t>TF&gt;FENI KM15</t>
         </is>
       </c>
-      <c r="B18" s="45" t="inlineStr">
+      <c r="B18" s="51" t="inlineStr">
         <is>
           <t>RIM</t>
         </is>
       </c>
-      <c r="C18" s="45" t="inlineStr">
+      <c r="C18" s="51" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="D18" s="46" t="n">
+      <c r="D18" s="52" t="n">
         <v>141</v>
       </c>
-      <c r="E18" s="46" t="n">
-        <v>141</v>
-      </c>
-      <c r="F18" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="46" t="n">
+      <c r="E18" s="53" t="n">
+        <v>5</v>
+      </c>
+      <c r="F18" s="53" t="n">
+        <v>-136</v>
+      </c>
+      <c r="G18" s="52" t="n">
         <v>458180</v>
       </c>
-      <c r="H18" s="48" t="n">
-        <v>458180</v>
+      <c r="H18" s="53" t="n">
+        <v>12265</v>
       </c>
     </row>
     <row r="19">
@@ -2801,16 +2810,16 @@
         <v>50</v>
       </c>
       <c r="E19" s="53" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F19" s="53" t="n">
-        <v>-46</v>
+        <v>-32</v>
       </c>
       <c r="G19" s="52" t="n">
         <v>244497</v>
       </c>
       <c r="H19" s="53" t="n">
-        <v>15279</v>
+        <v>85621</v>
       </c>
     </row>
     <row r="20">
@@ -2931,10 +2940,10 @@
         </is>
       </c>
       <c r="E23" s="58" t="n">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="F23" s="58" t="n">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="G23" s="57" t="inlineStr">
         <is>
@@ -2942,326 +2951,330 @@
         </is>
       </c>
       <c r="H23" s="58" t="n">
-        <v>229218</v>
+        <v>158876</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="59" t="inlineStr">
+      <c r="A24" s="56" t="inlineStr">
+        <is>
+          <t>TF&gt;FENI KM0</t>
+        </is>
+      </c>
+      <c r="B24" s="56" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C24" s="56" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D24" s="57" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E24" s="58" t="n">
+        <v>183</v>
+      </c>
+      <c r="F24" s="58" t="n">
+        <v>183</v>
+      </c>
+      <c r="G24" s="57" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H24" s="58" t="n">
+        <v>445915</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="59" t="inlineStr">
         <is>
           <t>OPTION 1 — PARK all 65 DT</t>
-        </is>
-      </c>
-      <c r="B24" s="60" t="inlineStr"/>
-      <c r="C24" s="60" t="inlineStr"/>
-      <c r="D24" s="61" t="n">
-        <v>65</v>
-      </c>
-      <c r="E24" s="61" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="61" t="n">
-        <v>-65</v>
-      </c>
-      <c r="G24" s="60" t="inlineStr"/>
-      <c r="H24" s="62" t="inlineStr">
-        <is>
-          <t>65 trucks stand idle</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="63" t="inlineStr">
-        <is>
-          <t>OPTION 2 — work 26 DT on longer KM0 hauls</t>
         </is>
       </c>
       <c r="B25" s="60" t="inlineStr"/>
       <c r="C25" s="60" t="inlineStr"/>
-      <c r="D25" s="64" t="n">
+      <c r="D25" s="61" t="n">
         <v>65</v>
       </c>
-      <c r="E25" s="64" t="n">
-        <v>26</v>
+      <c r="E25" s="61" t="n">
+        <v>0</v>
       </c>
       <c r="F25" s="61" t="n">
-        <v>-39</v>
+        <v>-65</v>
       </c>
       <c r="G25" s="60" t="inlineStr"/>
-      <c r="H25" s="65" t="inlineStr">
-        <is>
-          <t>26 keep working · 39 still park</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="41" t="inlineStr">
+      <c r="H25" s="62" t="inlineStr">
+        <is>
+          <t>65 trucks stand idle</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="63" t="inlineStr">
+        <is>
+          <t>OPTION 2 — work 65 DT on longer KM0 hauls</t>
+        </is>
+      </c>
+      <c r="B26" s="60" t="inlineStr"/>
+      <c r="C26" s="60" t="inlineStr"/>
+      <c r="D26" s="64" t="n">
+        <v>65</v>
+      </c>
+      <c r="E26" s="64" t="n">
+        <v>65</v>
+      </c>
+      <c r="F26" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="60" t="inlineStr"/>
+      <c r="H26" s="66" t="inlineStr">
+        <is>
+          <t>65 keep working · none parked</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="41" t="inlineStr">
         <is>
           <t>Scenario 3.0.2</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="42" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="42" t="inlineStr">
         <is>
           <t>Within the 103% band, untouched: September 95.7%, October 94.8%, November 99.1%</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="43" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="43" t="inlineStr">
         <is>
           <t>December — LIM-LD 120.1% of its line · surplus 396,264 t · 123 DT come out</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="44" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="44" t="inlineStr">
         <is>
           <t>Path / option</t>
         </is>
       </c>
-      <c r="B32" s="44" t="inlineStr">
+      <c r="B33" s="44" t="inlineStr">
         <is>
           <t>Contractor</t>
         </is>
       </c>
-      <c r="C32" s="44" t="inlineStr">
+      <c r="C33" s="44" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="D32" s="44" t="inlineStr">
+      <c r="D33" s="44" t="inlineStr">
         <is>
           <t>DT before</t>
         </is>
       </c>
-      <c r="E32" s="44" t="inlineStr">
+      <c r="E33" s="44" t="inlineStr">
         <is>
           <t>DT after</t>
         </is>
       </c>
-      <c r="F32" s="44" t="inlineStr">
+      <c r="F33" s="44" t="inlineStr">
         <is>
           <t>Δ DT</t>
         </is>
       </c>
-      <c r="G32" s="44" t="inlineStr">
+      <c r="G33" s="44" t="inlineStr">
         <is>
           <t>t/month before</t>
         </is>
       </c>
-      <c r="H32" s="44" t="inlineStr">
+      <c r="H33" s="44" t="inlineStr">
         <is>
           <t>t/month AFTER</t>
         </is>
       </c>
-      <c r="J32" s="44" t="inlineStr">
+      <c r="J33" s="44" t="inlineStr">
         <is>
           <t>Coverage after</t>
         </is>
       </c>
-      <c r="K32" s="44" t="inlineStr">
+      <c r="K33" s="44" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="45" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="45" t="inlineStr">
         <is>
           <t>TF&gt;POS 6</t>
         </is>
       </c>
-      <c r="B33" s="45" t="inlineStr">
+      <c r="B34" s="45" t="inlineStr">
         <is>
           <t>RIM</t>
         </is>
       </c>
-      <c r="C33" s="45" t="inlineStr">
+      <c r="C34" s="45" t="inlineStr">
         <is>
           <t>LIM-LD</t>
         </is>
       </c>
-      <c r="D33" s="46" t="n">
+      <c r="D34" s="46" t="n">
         <v>217</v>
       </c>
-      <c r="E33" s="46" t="n">
+      <c r="E34" s="46" t="n">
         <v>217</v>
       </c>
-      <c r="F33" s="47" t="n">
+      <c r="F34" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="G33" s="46" t="n">
+      <c r="G34" s="46" t="n">
         <v>851539</v>
       </c>
-      <c r="H33" s="48" t="n">
+      <c r="H34" s="48" t="n">
         <v>851539</v>
       </c>
-      <c r="J33" s="49" t="inlineStr">
+      <c r="J34" s="49" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="K33" s="50" t="n">
+      <c r="K34" s="50" t="n">
         <v>1.002182836458604</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="51" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="51" t="inlineStr">
         <is>
           <t>TF&gt;HUAFEI</t>
         </is>
       </c>
-      <c r="B34" s="51" t="inlineStr">
+      <c r="B35" s="51" t="inlineStr">
         <is>
           <t>RIM</t>
         </is>
       </c>
-      <c r="C34" s="51" t="inlineStr">
+      <c r="C35" s="51" t="inlineStr">
         <is>
           <t>LIM-LD</t>
         </is>
       </c>
-      <c r="D34" s="52" t="n">
+      <c r="D35" s="52" t="n">
         <v>218</v>
       </c>
-      <c r="E34" s="53" t="n">
-        <v>215</v>
-      </c>
-      <c r="F34" s="53" t="n">
-        <v>-3</v>
-      </c>
-      <c r="G34" s="52" t="n">
+      <c r="E35" s="53" t="n">
+        <v>121</v>
+      </c>
+      <c r="F35" s="53" t="n">
+        <v>-97</v>
+      </c>
+      <c r="G35" s="52" t="n">
         <v>702398</v>
       </c>
-      <c r="H34" s="53" t="n">
-        <v>692732</v>
-      </c>
-      <c r="J34" s="49" t="inlineStr">
+      <c r="H35" s="53" t="n">
+        <v>389863</v>
+      </c>
+      <c r="J35" s="49" t="inlineStr">
         <is>
           <t>LIM-TOS</t>
         </is>
       </c>
-      <c r="K34" s="50" t="n">
+      <c r="K35" s="50" t="n">
         <v>1.005641090510439</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="45" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="45" t="inlineStr">
         <is>
           <t>TF&gt;POS 6</t>
         </is>
       </c>
-      <c r="B35" s="45" t="inlineStr">
+      <c r="B36" s="45" t="inlineStr">
         <is>
           <t>SMA</t>
         </is>
       </c>
-      <c r="C35" s="45" t="inlineStr">
+      <c r="C36" s="45" t="inlineStr">
         <is>
           <t>LIM-LD</t>
         </is>
       </c>
-      <c r="D35" s="46" t="n">
+      <c r="D36" s="46" t="n">
         <v>120</v>
       </c>
-      <c r="E35" s="46" t="n">
+      <c r="E36" s="46" t="n">
         <v>120</v>
       </c>
-      <c r="F35" s="47" t="n">
+      <c r="F36" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="G35" s="46" t="n">
+      <c r="G36" s="46" t="n">
         <v>430125</v>
       </c>
-      <c r="H35" s="48" t="n">
+      <c r="H36" s="48" t="n">
         <v>430125</v>
       </c>
-      <c r="J35" s="49" t="inlineStr">
+      <c r="J36" s="49" t="inlineStr">
         <is>
           <t>LIM-LD</t>
         </is>
       </c>
-      <c r="K35" s="50" t="n">
-        <v>1.000375431611434</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="51" t="inlineStr">
+      <c r="K36" s="50" t="n">
+        <v>1.000051922326045</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="51" t="inlineStr">
         <is>
           <t>TF&gt;HUAFEI</t>
         </is>
       </c>
-      <c r="B36" s="51" t="inlineStr">
+      <c r="B37" s="51" t="inlineStr">
         <is>
           <t>SMA</t>
         </is>
       </c>
-      <c r="C36" s="51" t="inlineStr">
+      <c r="C37" s="51" t="inlineStr">
         <is>
           <t>LIM-LD</t>
         </is>
       </c>
-      <c r="D36" s="52" t="n">
+      <c r="D37" s="52" t="n">
         <v>120</v>
       </c>
-      <c r="E36" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" s="53" t="n">
-        <v>-120</v>
-      </c>
-      <c r="G36" s="52" t="n">
+      <c r="E37" s="53" t="n">
+        <v>94</v>
+      </c>
+      <c r="F37" s="53" t="n">
+        <v>-26</v>
+      </c>
+      <c r="G37" s="52" t="n">
         <v>385826</v>
       </c>
-      <c r="H36" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="54" t="inlineStr">
+      <c r="H37" s="53" t="n">
+        <v>302230</v>
+      </c>
+      <c r="J37" s="54" t="inlineStr">
         <is>
           <t>was LD</t>
         </is>
       </c>
-      <c r="K36" s="55" t="n">
+      <c r="K37" s="55" t="n">
         <v>1.200776731495626</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="45" t="inlineStr">
-        <is>
-          <t>BLB&gt;HUAFEI</t>
-        </is>
-      </c>
-      <c r="B37" s="45" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C37" s="45" t="inlineStr">
-        <is>
-          <t>LIM-TOS</t>
-        </is>
-      </c>
-      <c r="D37" s="46" t="n">
-        <v>95</v>
-      </c>
-      <c r="E37" s="46" t="n">
-        <v>95</v>
-      </c>
-      <c r="F37" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" s="46" t="n">
-        <v>720750</v>
-      </c>
-      <c r="H37" s="48" t="n">
-        <v>720750</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="45" t="inlineStr">
         <is>
-          <t>TF&gt;HUAFEI</t>
+          <t>BLB&gt;HUAFEI</t>
         </is>
       </c>
       <c r="B38" s="45" t="inlineStr">
@@ -3275,30 +3288,30 @@
         </is>
       </c>
       <c r="D38" s="46" t="n">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="E38" s="46" t="n">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="F38" s="47" t="n">
         <v>0</v>
       </c>
       <c r="G38" s="46" t="n">
-        <v>202988</v>
+        <v>720750</v>
       </c>
       <c r="H38" s="48" t="n">
-        <v>202988</v>
+        <v>720750</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="45" t="inlineStr">
         <is>
-          <t>KR&gt;HUAFEI</t>
+          <t>TF&gt;HUAFEI</t>
         </is>
       </c>
       <c r="B39" s="45" t="inlineStr">
         <is>
-          <t>SMA</t>
+          <t>RIM</t>
         </is>
       </c>
       <c r="C39" s="45" t="inlineStr">
@@ -3307,158 +3320,158 @@
         </is>
       </c>
       <c r="D39" s="46" t="n">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="E39" s="46" t="n">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="F39" s="47" t="n">
         <v>0</v>
       </c>
       <c r="G39" s="46" t="n">
-        <v>77965</v>
+        <v>202988</v>
       </c>
       <c r="H39" s="48" t="n">
-        <v>77965</v>
+        <v>202988</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="45" t="inlineStr">
         <is>
-          <t>BLB&gt;FENI KM0</t>
+          <t>KR&gt;HUAFEI</t>
         </is>
       </c>
       <c r="B40" s="45" t="inlineStr">
         <is>
-          <t>RIM</t>
+          <t>SMA</t>
         </is>
       </c>
       <c r="C40" s="45" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>LIM-TOS</t>
         </is>
       </c>
       <c r="D40" s="46" t="n">
-        <v>202</v>
+        <v>19</v>
       </c>
       <c r="E40" s="46" t="n">
-        <v>202</v>
+        <v>19</v>
       </c>
       <c r="F40" s="47" t="n">
         <v>0</v>
       </c>
       <c r="G40" s="46" t="n">
+        <v>77965</v>
+      </c>
+      <c r="H40" s="48" t="n">
+        <v>77965</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="45" t="inlineStr">
+        <is>
+          <t>BLB&gt;FENI KM0</t>
+        </is>
+      </c>
+      <c r="B41" s="45" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C41" s="45" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D41" s="46" t="n">
+        <v>202</v>
+      </c>
+      <c r="E41" s="46" t="n">
+        <v>202</v>
+      </c>
+      <c r="F41" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="46" t="n">
         <v>1419366</v>
       </c>
-      <c r="H40" s="48" t="n">
+      <c r="H41" s="48" t="n">
         <v>1419366</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="51" t="inlineStr">
-        <is>
-          <t>TF&gt;FENI KM15</t>
-        </is>
-      </c>
-      <c r="B41" s="51" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C41" s="51" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="D41" s="52" t="n">
-        <v>141</v>
-      </c>
-      <c r="E41" s="53" t="n">
-        <v>132</v>
-      </c>
-      <c r="F41" s="53" t="n">
-        <v>-9</v>
-      </c>
-      <c r="G41" s="52" t="n">
-        <v>458180</v>
-      </c>
-      <c r="H41" s="53" t="n">
-        <v>429742</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="51" t="inlineStr">
         <is>
+          <t>TF&gt;FENI KM15</t>
+        </is>
+      </c>
+      <c r="B42" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C42" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D42" s="52" t="n">
+        <v>141</v>
+      </c>
+      <c r="E42" s="53" t="n">
+        <v>5</v>
+      </c>
+      <c r="F42" s="53" t="n">
+        <v>-136</v>
+      </c>
+      <c r="G42" s="52" t="n">
+        <v>458180</v>
+      </c>
+      <c r="H42" s="53" t="n">
+        <v>12265</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="51" t="inlineStr">
+        <is>
           <t>KR&gt;FENI KM15</t>
         </is>
       </c>
-      <c r="B42" s="51" t="inlineStr">
+      <c r="B43" s="51" t="inlineStr">
         <is>
           <t>SMA</t>
         </is>
       </c>
-      <c r="C42" s="51" t="inlineStr">
+      <c r="C43" s="51" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="D42" s="52" t="n">
+      <c r="D43" s="52" t="n">
         <v>50</v>
       </c>
-      <c r="E42" s="53" t="n">
+      <c r="E43" s="53" t="n">
         <v>4</v>
       </c>
-      <c r="F42" s="53" t="n">
+      <c r="F43" s="53" t="n">
         <v>-46</v>
       </c>
-      <c r="G42" s="52" t="n">
+      <c r="G43" s="52" t="n">
         <v>244435</v>
       </c>
-      <c r="H42" s="53" t="n">
-        <v>15217</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="45" t="inlineStr">
-        <is>
-          <t>KR&gt;POS 12</t>
-        </is>
-      </c>
-      <c r="B43" s="45" t="inlineStr">
-        <is>
-          <t>SMA</t>
-        </is>
-      </c>
-      <c r="C43" s="45" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="D43" s="46" t="n">
-        <v>11</v>
-      </c>
-      <c r="E43" s="46" t="n">
-        <v>11</v>
-      </c>
-      <c r="F43" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" s="46" t="n">
-        <v>67797</v>
-      </c>
-      <c r="H43" s="48" t="n">
-        <v>67797</v>
+      <c r="H43" s="53" t="n">
+        <v>14948</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="45" t="inlineStr">
         <is>
-          <t>BLB&gt;POS 14</t>
+          <t>KR&gt;POS 12</t>
         </is>
       </c>
       <c r="B44" s="45" t="inlineStr">
         <is>
-          <t>RIM</t>
+          <t>SMA</t>
         </is>
       </c>
       <c r="C44" s="45" t="inlineStr">
@@ -3467,25 +3480,25 @@
         </is>
       </c>
       <c r="D44" s="46" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E44" s="46" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F44" s="47" t="n">
         <v>0</v>
       </c>
       <c r="G44" s="46" t="n">
-        <v>63364</v>
+        <v>67797</v>
       </c>
       <c r="H44" s="48" t="n">
-        <v>63364</v>
+        <v>67797</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="45" t="inlineStr">
         <is>
-          <t>TF&gt;POS 12</t>
+          <t>BLB&gt;POS 14</t>
         </is>
       </c>
       <c r="B45" s="45" t="inlineStr">
@@ -3499,252 +3512,244 @@
         </is>
       </c>
       <c r="D45" s="46" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E45" s="46" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="F45" s="47" t="n">
         <v>0</v>
       </c>
       <c r="G45" s="46" t="n">
+        <v>63364</v>
+      </c>
+      <c r="H45" s="48" t="n">
+        <v>63364</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;POS 12</t>
+        </is>
+      </c>
+      <c r="B46" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C46" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D46" s="52" t="n">
+        <v>18</v>
+      </c>
+      <c r="E46" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="53" t="n">
+        <v>-18</v>
+      </c>
+      <c r="G46" s="52" t="n">
         <v>63116</v>
       </c>
-      <c r="H45" s="48" t="n">
-        <v>63116</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="56" t="inlineStr">
-        <is>
-          <t>KR&gt;FENI KM0</t>
-        </is>
-      </c>
-      <c r="B46" s="56" t="inlineStr">
-        <is>
-          <t>SMA</t>
-        </is>
-      </c>
-      <c r="C46" s="56" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="D46" s="57" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E46" s="58" t="n">
-        <v>72</v>
-      </c>
-      <c r="F46" s="58" t="n">
-        <v>72</v>
-      </c>
-      <c r="G46" s="57" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H46" s="58" t="n">
-        <v>229218</v>
+      <c r="H46" s="53" t="n">
+        <v>1341</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="56" t="inlineStr">
         <is>
+          <t>KR&gt;FENI KM0</t>
+        </is>
+      </c>
+      <c r="B47" s="56" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C47" s="56" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D47" s="57" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E47" s="58" t="n">
+        <v>72</v>
+      </c>
+      <c r="F47" s="58" t="n">
+        <v>72</v>
+      </c>
+      <c r="G47" s="57" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H47" s="58" t="n">
+        <v>229487</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="56" t="inlineStr">
+        <is>
           <t>TF&gt;FENI KM0</t>
         </is>
       </c>
-      <c r="B47" s="56" t="inlineStr">
+      <c r="B48" s="56" t="inlineStr">
         <is>
           <t>RIM</t>
         </is>
       </c>
-      <c r="C47" s="56" t="inlineStr">
+      <c r="C48" s="56" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="D47" s="57" t="inlineStr">
+      <c r="D48" s="57" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E47" s="58" t="n">
-        <v>12</v>
-      </c>
-      <c r="F47" s="58" t="n">
-        <v>12</v>
-      </c>
-      <c r="G47" s="57" t="inlineStr">
+      <c r="E48" s="58" t="n">
+        <v>215</v>
+      </c>
+      <c r="F48" s="58" t="n">
+        <v>215</v>
+      </c>
+      <c r="G48" s="57" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H47" s="58" t="n">
-        <v>28438</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="59" t="inlineStr">
+      <c r="H48" s="58" t="n">
+        <v>507690</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="59" t="inlineStr">
         <is>
           <t>OPTION 1 — PARK all 123 DT</t>
-        </is>
-      </c>
-      <c r="B48" s="60" t="inlineStr"/>
-      <c r="C48" s="60" t="inlineStr"/>
-      <c r="D48" s="61" t="n">
-        <v>123</v>
-      </c>
-      <c r="E48" s="61" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" s="61" t="n">
-        <v>-123</v>
-      </c>
-      <c r="G48" s="60" t="inlineStr"/>
-      <c r="H48" s="62" t="inlineStr">
-        <is>
-          <t>123 trucks stand idle</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="63" t="inlineStr">
-        <is>
-          <t>OPTION 2 — work 29 DT on longer KM0 hauls</t>
         </is>
       </c>
       <c r="B49" s="60" t="inlineStr"/>
       <c r="C49" s="60" t="inlineStr"/>
-      <c r="D49" s="64" t="n">
+      <c r="D49" s="61" t="n">
         <v>123</v>
       </c>
-      <c r="E49" s="64" t="n">
-        <v>29</v>
+      <c r="E49" s="61" t="n">
+        <v>0</v>
       </c>
       <c r="F49" s="61" t="n">
-        <v>-94</v>
+        <v>-123</v>
       </c>
       <c r="G49" s="60" t="inlineStr"/>
-      <c r="H49" s="65" t="inlineStr">
-        <is>
-          <t>29 keep working · 94 still park</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="41" t="inlineStr">
+      <c r="H49" s="62" t="inlineStr">
+        <is>
+          <t>123 trucks stand idle</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="63" t="inlineStr">
+        <is>
+          <t>OPTION 2 — work 87 DT on longer KM0 hauls</t>
+        </is>
+      </c>
+      <c r="B50" s="60" t="inlineStr"/>
+      <c r="C50" s="60" t="inlineStr"/>
+      <c r="D50" s="64" t="n">
+        <v>123</v>
+      </c>
+      <c r="E50" s="64" t="n">
+        <v>87</v>
+      </c>
+      <c r="F50" s="61" t="n">
+        <v>-36</v>
+      </c>
+      <c r="G50" s="60" t="inlineStr"/>
+      <c r="H50" s="65" t="inlineStr">
+        <is>
+          <t>87 keep working · 36 still park</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="41" t="inlineStr">
         <is>
           <t>Scenario 3.1.1</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="42" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="42" t="inlineStr">
         <is>
           <t>Within the 103% band, untouched: September 101.4%, October 93.8%, November 100.2%</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="43" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="43" t="inlineStr">
         <is>
           <t>December — LIM-LD 120.8% of its line · surplus 353,544 t · 109 DT come out</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="44" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="44" t="inlineStr">
         <is>
           <t>Path / option</t>
         </is>
       </c>
-      <c r="B56" s="44" t="inlineStr">
+      <c r="B57" s="44" t="inlineStr">
         <is>
           <t>Contractor</t>
         </is>
       </c>
-      <c r="C56" s="44" t="inlineStr">
+      <c r="C57" s="44" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="D56" s="44" t="inlineStr">
+      <c r="D57" s="44" t="inlineStr">
         <is>
           <t>DT before</t>
         </is>
       </c>
-      <c r="E56" s="44" t="inlineStr">
+      <c r="E57" s="44" t="inlineStr">
         <is>
           <t>DT after</t>
         </is>
       </c>
-      <c r="F56" s="44" t="inlineStr">
+      <c r="F57" s="44" t="inlineStr">
         <is>
           <t>Δ DT</t>
         </is>
       </c>
-      <c r="G56" s="44" t="inlineStr">
+      <c r="G57" s="44" t="inlineStr">
         <is>
           <t>t/month before</t>
         </is>
       </c>
-      <c r="H56" s="44" t="inlineStr">
+      <c r="H57" s="44" t="inlineStr">
         <is>
           <t>t/month AFTER</t>
         </is>
       </c>
-      <c r="J56" s="44" t="inlineStr">
+      <c r="J57" s="44" t="inlineStr">
         <is>
           <t>Coverage after</t>
         </is>
       </c>
-      <c r="K56" s="44" t="inlineStr">
+      <c r="K57" s="44" t="inlineStr">
         <is>
           <t>%</t>
         </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="45" t="inlineStr">
-        <is>
-          <t>TF&gt;HUAFEI</t>
-        </is>
-      </c>
-      <c r="B57" s="45" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C57" s="45" t="inlineStr">
-        <is>
-          <t>LIM-LD</t>
-        </is>
-      </c>
-      <c r="D57" s="46" t="n">
-        <v>393</v>
-      </c>
-      <c r="E57" s="46" t="n">
-        <v>393</v>
-      </c>
-      <c r="F57" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="G57" s="46" t="n">
-        <v>1271527</v>
-      </c>
-      <c r="H57" s="48" t="n">
-        <v>1271527</v>
-      </c>
-      <c r="J57" s="49" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="K57" s="50" t="n">
-        <v>0.9989100961270121</v>
       </c>
     </row>
     <row r="58">
@@ -3755,82 +3760,82 @@
       </c>
       <c r="B58" s="51" t="inlineStr">
         <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C58" s="51" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D58" s="52" t="n">
+        <v>393</v>
+      </c>
+      <c r="E58" s="53" t="n">
+        <v>311</v>
+      </c>
+      <c r="F58" s="53" t="n">
+        <v>-82</v>
+      </c>
+      <c r="G58" s="52" t="n">
+        <v>1271527</v>
+      </c>
+      <c r="H58" s="53" t="n">
+        <v>1006221</v>
+      </c>
+      <c r="J58" s="49" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="K58" s="50" t="n">
+        <v>0.9989100961270121</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B59" s="51" t="inlineStr">
+        <is>
           <t>SMA</t>
         </is>
       </c>
-      <c r="C58" s="51" t="inlineStr">
+      <c r="C59" s="51" t="inlineStr">
         <is>
           <t>LIM-LD</t>
         </is>
       </c>
-      <c r="D58" s="52" t="n">
+      <c r="D59" s="52" t="n">
         <v>241</v>
       </c>
-      <c r="E58" s="53" t="n">
-        <v>132</v>
-      </c>
-      <c r="F58" s="53" t="n">
-        <v>-109</v>
-      </c>
-      <c r="G58" s="52" t="n">
+      <c r="E59" s="53" t="n">
+        <v>214</v>
+      </c>
+      <c r="F59" s="53" t="n">
+        <v>-27</v>
+      </c>
+      <c r="G59" s="52" t="n">
         <v>778410</v>
       </c>
-      <c r="H58" s="53" t="n">
-        <v>426349</v>
-      </c>
-      <c r="J58" s="49" t="inlineStr">
+      <c r="H59" s="53" t="n">
+        <v>691202</v>
+      </c>
+      <c r="J59" s="49" t="inlineStr">
         <is>
           <t>LIM-TOS</t>
         </is>
       </c>
-      <c r="K58" s="50" t="n">
+      <c r="K59" s="50" t="n">
         <v>1.002107712796041</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="45" t="inlineStr">
-        <is>
-          <t>BLB&gt;HUAFEI</t>
-        </is>
-      </c>
-      <c r="B59" s="45" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C59" s="45" t="inlineStr">
-        <is>
-          <t>LIM-TOS</t>
-        </is>
-      </c>
-      <c r="D59" s="46" t="n">
-        <v>139</v>
-      </c>
-      <c r="E59" s="46" t="n">
-        <v>139</v>
-      </c>
-      <c r="F59" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="G59" s="46" t="n">
-        <v>1049381</v>
-      </c>
-      <c r="H59" s="48" t="n">
-        <v>1049381</v>
-      </c>
-      <c r="J59" s="49" t="inlineStr">
-        <is>
-          <t>LIM-LD</t>
-        </is>
-      </c>
-      <c r="K59" s="50" t="n">
-        <v>1.000874234710444</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="45" t="inlineStr">
         <is>
-          <t>TF&gt;HUAFEI</t>
+          <t>BLB&gt;HUAFEI</t>
         </is>
       </c>
       <c r="B60" s="45" t="inlineStr">
@@ -3844,38 +3849,38 @@
         </is>
       </c>
       <c r="D60" s="46" t="n">
-        <v>62</v>
+        <v>139</v>
       </c>
       <c r="E60" s="46" t="n">
-        <v>62</v>
+        <v>139</v>
       </c>
       <c r="F60" s="47" t="n">
         <v>0</v>
       </c>
       <c r="G60" s="46" t="n">
-        <v>200601</v>
+        <v>1049381</v>
       </c>
       <c r="H60" s="48" t="n">
-        <v>200601</v>
-      </c>
-      <c r="J60" s="54" t="inlineStr">
-        <is>
-          <t>was LD</t>
-        </is>
-      </c>
-      <c r="K60" s="55" t="n">
-        <v>1.20840925422352</v>
+        <v>1049381</v>
+      </c>
+      <c r="J60" s="49" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="K60" s="50" t="n">
+        <v>1.000607378492595</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="45" t="inlineStr">
         <is>
-          <t>KR&gt;HUAFEI</t>
+          <t>TF&gt;HUAFEI</t>
         </is>
       </c>
       <c r="B61" s="45" t="inlineStr">
         <is>
-          <t>SMA</t>
+          <t>RIM</t>
         </is>
       </c>
       <c r="C61" s="45" t="inlineStr">
@@ -3884,57 +3889,65 @@
         </is>
       </c>
       <c r="D61" s="46" t="n">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="E61" s="46" t="n">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="F61" s="47" t="n">
         <v>0</v>
       </c>
       <c r="G61" s="46" t="n">
-        <v>78895</v>
+        <v>200601</v>
       </c>
       <c r="H61" s="48" t="n">
-        <v>78895</v>
+        <v>200601</v>
+      </c>
+      <c r="J61" s="54" t="inlineStr">
+        <is>
+          <t>was LD</t>
+        </is>
+      </c>
+      <c r="K61" s="55" t="n">
+        <v>1.20840925422352</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="45" t="inlineStr">
         <is>
-          <t>BLB&gt;FENI KM0</t>
+          <t>KR&gt;HUAFEI</t>
         </is>
       </c>
       <c r="B62" s="45" t="inlineStr">
         <is>
-          <t>RIM</t>
+          <t>SMA</t>
         </is>
       </c>
       <c r="C62" s="45" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>LIM-TOS</t>
         </is>
       </c>
       <c r="D62" s="46" t="n">
-        <v>202</v>
+        <v>19</v>
       </c>
       <c r="E62" s="46" t="n">
-        <v>202</v>
+        <v>19</v>
       </c>
       <c r="F62" s="47" t="n">
         <v>0</v>
       </c>
       <c r="G62" s="46" t="n">
-        <v>1418994</v>
+        <v>78895</v>
       </c>
       <c r="H62" s="48" t="n">
-        <v>1418994</v>
+        <v>78895</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="45" t="inlineStr">
         <is>
-          <t>TF&gt;FENI KM15</t>
+          <t>BLB&gt;FENI KM0</t>
         </is>
       </c>
       <c r="B63" s="45" t="inlineStr">
@@ -3948,89 +3961,89 @@
         </is>
       </c>
       <c r="D63" s="46" t="n">
-        <v>140</v>
+        <v>202</v>
       </c>
       <c r="E63" s="46" t="n">
-        <v>140</v>
+        <v>202</v>
       </c>
       <c r="F63" s="47" t="n">
         <v>0</v>
       </c>
       <c r="G63" s="46" t="n">
-        <v>455762</v>
+        <v>1418994</v>
       </c>
       <c r="H63" s="48" t="n">
-        <v>455762</v>
+        <v>1418994</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="51" t="inlineStr">
         <is>
+          <t>TF&gt;FENI KM15</t>
+        </is>
+      </c>
+      <c r="B64" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C64" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D64" s="52" t="n">
+        <v>140</v>
+      </c>
+      <c r="E64" s="53" t="n">
+        <v>4</v>
+      </c>
+      <c r="F64" s="53" t="n">
+        <v>-136</v>
+      </c>
+      <c r="G64" s="52" t="n">
+        <v>455762</v>
+      </c>
+      <c r="H64" s="53" t="n">
+        <v>9847</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="51" t="inlineStr">
+        <is>
           <t>KR&gt;FENI KM15</t>
         </is>
       </c>
-      <c r="B64" s="51" t="inlineStr">
+      <c r="B65" s="51" t="inlineStr">
         <is>
           <t>SMA</t>
         </is>
       </c>
-      <c r="C64" s="51" t="inlineStr">
+      <c r="C65" s="51" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="D64" s="52" t="n">
+      <c r="D65" s="52" t="n">
         <v>50</v>
       </c>
-      <c r="E64" s="53" t="n">
+      <c r="E65" s="53" t="n">
         <v>2</v>
       </c>
-      <c r="F64" s="53" t="n">
+      <c r="F65" s="53" t="n">
         <v>-48</v>
       </c>
-      <c r="G64" s="52" t="n">
+      <c r="G65" s="52" t="n">
         <v>245489</v>
       </c>
-      <c r="H64" s="53" t="n">
-        <v>7454</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="45" t="inlineStr">
-        <is>
-          <t>BLB&gt;POS 14</t>
-        </is>
-      </c>
-      <c r="B65" s="45" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C65" s="45" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="D65" s="46" t="n">
-        <v>7</v>
-      </c>
-      <c r="E65" s="46" t="n">
-        <v>7</v>
-      </c>
-      <c r="F65" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="G65" s="46" t="n">
-        <v>63333</v>
-      </c>
-      <c r="H65" s="48" t="n">
-        <v>63333</v>
+      <c r="H65" s="53" t="n">
+        <v>7175</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="45" t="inlineStr">
         <is>
-          <t>TF&gt;POS 12</t>
+          <t>BLB&gt;POS 14</t>
         </is>
       </c>
       <c r="B66" s="45" t="inlineStr">
@@ -4044,288 +4057,276 @@
         </is>
       </c>
       <c r="D66" s="46" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E66" s="46" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="F66" s="47" t="n">
         <v>0</v>
       </c>
       <c r="G66" s="46" t="n">
+        <v>63333</v>
+      </c>
+      <c r="H66" s="48" t="n">
+        <v>63333</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;POS 12</t>
+        </is>
+      </c>
+      <c r="B67" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C67" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D67" s="52" t="n">
+        <v>18</v>
+      </c>
+      <c r="E67" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" s="53" t="n">
+        <v>-18</v>
+      </c>
+      <c r="G67" s="52" t="n">
         <v>63147</v>
       </c>
-      <c r="H66" s="48" t="n">
-        <v>63147</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="45" t="inlineStr">
+      <c r="H67" s="53" t="n">
+        <v>1372</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="45" t="inlineStr">
         <is>
           <t>KR&gt;POS 12</t>
         </is>
       </c>
-      <c r="B67" s="45" t="inlineStr">
+      <c r="B68" s="45" t="inlineStr">
         <is>
           <t>SMA</t>
         </is>
       </c>
-      <c r="C67" s="45" t="inlineStr">
+      <c r="C68" s="45" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="D67" s="46" t="n">
+      <c r="D68" s="46" t="n">
         <v>10</v>
       </c>
-      <c r="E67" s="46" t="n">
+      <c r="E68" s="46" t="n">
         <v>10</v>
       </c>
-      <c r="F67" s="47" t="n">
+      <c r="F68" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="G67" s="46" t="n">
+      <c r="G68" s="46" t="n">
         <v>61969</v>
       </c>
-      <c r="H67" s="48" t="n">
+      <c r="H68" s="48" t="n">
         <v>61969</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="56" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="56" t="inlineStr">
         <is>
           <t>KR&gt;FENI KM0</t>
         </is>
       </c>
-      <c r="B68" s="56" t="inlineStr">
+      <c r="B69" s="56" t="inlineStr">
         <is>
           <t>SMA</t>
         </is>
       </c>
-      <c r="C68" s="56" t="inlineStr">
+      <c r="C69" s="56" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="D68" s="57" t="inlineStr">
+      <c r="D69" s="57" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E68" s="58" t="n">
+      <c r="E69" s="58" t="n">
         <v>75</v>
       </c>
-      <c r="F68" s="58" t="n">
+      <c r="F69" s="58" t="n">
         <v>75</v>
       </c>
-      <c r="G68" s="57" t="inlineStr">
+      <c r="G69" s="57" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H68" s="58" t="n">
-        <v>238035</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="59" t="inlineStr">
+      <c r="H69" s="58" t="n">
+        <v>238314</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="56" t="inlineStr">
+        <is>
+          <t>TF&gt;FENI KM0</t>
+        </is>
+      </c>
+      <c r="B70" s="56" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C70" s="56" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D70" s="57" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E70" s="58" t="n">
+        <v>215</v>
+      </c>
+      <c r="F70" s="58" t="n">
+        <v>215</v>
+      </c>
+      <c r="G70" s="57" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H70" s="58" t="n">
+        <v>507690</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="59" t="inlineStr">
         <is>
           <t>OPTION 1 — PARK all 109 DT</t>
         </is>
       </c>
-      <c r="B69" s="60" t="inlineStr"/>
-      <c r="C69" s="60" t="inlineStr"/>
-      <c r="D69" s="61" t="n">
+      <c r="B71" s="60" t="inlineStr"/>
+      <c r="C71" s="60" t="inlineStr"/>
+      <c r="D71" s="61" t="n">
         <v>109</v>
       </c>
-      <c r="E69" s="61" t="n">
+      <c r="E71" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="F69" s="61" t="n">
+      <c r="F71" s="61" t="n">
         <v>-109</v>
       </c>
-      <c r="G69" s="60" t="inlineStr"/>
-      <c r="H69" s="62" t="inlineStr">
+      <c r="G71" s="60" t="inlineStr"/>
+      <c r="H71" s="62" t="inlineStr">
         <is>
           <t>109 trucks stand idle</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="63" t="inlineStr">
-        <is>
-          <t>OPTION 2 — work 27 DT on longer KM0 hauls</t>
-        </is>
-      </c>
-      <c r="B70" s="60" t="inlineStr"/>
-      <c r="C70" s="60" t="inlineStr"/>
-      <c r="D70" s="64" t="n">
+    <row r="72">
+      <c r="A72" s="63" t="inlineStr">
+        <is>
+          <t>OPTION 2 — work 88 DT on longer KM0 hauls</t>
+        </is>
+      </c>
+      <c r="B72" s="60" t="inlineStr"/>
+      <c r="C72" s="60" t="inlineStr"/>
+      <c r="D72" s="64" t="n">
         <v>109</v>
       </c>
-      <c r="E70" s="64" t="n">
-        <v>27</v>
-      </c>
-      <c r="F70" s="61" t="n">
-        <v>-82</v>
-      </c>
-      <c r="G70" s="60" t="inlineStr"/>
-      <c r="H70" s="65" t="inlineStr">
-        <is>
-          <t>27 keep working · 82 still park</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="41" t="inlineStr">
+      <c r="E72" s="64" t="n">
+        <v>88</v>
+      </c>
+      <c r="F72" s="61" t="n">
+        <v>-21</v>
+      </c>
+      <c r="G72" s="60" t="inlineStr"/>
+      <c r="H72" s="65" t="inlineStr">
+        <is>
+          <t>88 keep working · 21 still park</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="41" t="inlineStr">
         <is>
           <t>Scenario 3.1.2</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="42" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="42" t="inlineStr">
         <is>
           <t>Within the 103% band, untouched: September 101.4%, October 101.2%</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="43" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="43" t="inlineStr">
         <is>
           <t>November — LIM-LD 108.6% of its line · surplus 199,452 t · 64 DT come out</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="44" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="44" t="inlineStr">
         <is>
           <t>Path / option</t>
         </is>
       </c>
-      <c r="B77" s="44" t="inlineStr">
+      <c r="B79" s="44" t="inlineStr">
         <is>
           <t>Contractor</t>
         </is>
       </c>
-      <c r="C77" s="44" t="inlineStr">
+      <c r="C79" s="44" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="D77" s="44" t="inlineStr">
+      <c r="D79" s="44" t="inlineStr">
         <is>
           <t>DT before</t>
         </is>
       </c>
-      <c r="E77" s="44" t="inlineStr">
+      <c r="E79" s="44" t="inlineStr">
         <is>
           <t>DT after</t>
         </is>
       </c>
-      <c r="F77" s="44" t="inlineStr">
+      <c r="F79" s="44" t="inlineStr">
         <is>
           <t>Δ DT</t>
         </is>
       </c>
-      <c r="G77" s="44" t="inlineStr">
+      <c r="G79" s="44" t="inlineStr">
         <is>
           <t>t/month before</t>
         </is>
       </c>
-      <c r="H77" s="44" t="inlineStr">
+      <c r="H79" s="44" t="inlineStr">
         <is>
           <t>t/month AFTER</t>
         </is>
       </c>
-      <c r="J77" s="44" t="inlineStr">
+      <c r="J79" s="44" t="inlineStr">
         <is>
           <t>Coverage after</t>
         </is>
       </c>
-      <c r="K77" s="44" t="inlineStr">
+      <c r="K79" s="44" t="inlineStr">
         <is>
           <t>%</t>
         </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="45" t="inlineStr">
-        <is>
-          <t>TF&gt;POS 6</t>
-        </is>
-      </c>
-      <c r="B78" s="45" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C78" s="45" t="inlineStr">
-        <is>
-          <t>LIM-LD</t>
-        </is>
-      </c>
-      <c r="D78" s="46" t="n">
-        <v>246</v>
-      </c>
-      <c r="E78" s="46" t="n">
-        <v>246</v>
-      </c>
-      <c r="F78" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="G78" s="46" t="n">
-        <v>933330</v>
-      </c>
-      <c r="H78" s="48" t="n">
-        <v>933330</v>
-      </c>
-      <c r="J78" s="49" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="K78" s="50" t="n">
-        <v>1.008568170337829</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="45" t="inlineStr">
-        <is>
-          <t>TF&gt;HUAFEI</t>
-        </is>
-      </c>
-      <c r="B79" s="45" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C79" s="45" t="inlineStr">
-        <is>
-          <t>LIM-LD</t>
-        </is>
-      </c>
-      <c r="D79" s="46" t="n">
-        <v>246</v>
-      </c>
-      <c r="E79" s="46" t="n">
-        <v>246</v>
-      </c>
-      <c r="F79" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="G79" s="46" t="n">
-        <v>765600</v>
-      </c>
-      <c r="H79" s="48" t="n">
-        <v>765600</v>
-      </c>
-      <c r="J79" s="49" t="inlineStr">
-        <is>
-          <t>LIM-TOS</t>
-        </is>
-      </c>
-      <c r="K79" s="50" t="n">
-        <v>1.000660957221576</v>
       </c>
     </row>
     <row r="80">
@@ -4336,7 +4337,7 @@
       </c>
       <c r="B80" s="45" t="inlineStr">
         <is>
-          <t>SMA</t>
+          <t>RIM</t>
         </is>
       </c>
       <c r="C80" s="45" t="inlineStr">
@@ -4345,27 +4346,27 @@
         </is>
       </c>
       <c r="D80" s="46" t="n">
-        <v>125</v>
+        <v>246</v>
       </c>
       <c r="E80" s="46" t="n">
-        <v>125</v>
+        <v>246</v>
       </c>
       <c r="F80" s="47" t="n">
         <v>0</v>
       </c>
       <c r="G80" s="46" t="n">
-        <v>433200</v>
+        <v>933330</v>
       </c>
       <c r="H80" s="48" t="n">
-        <v>433200</v>
+        <v>933330</v>
       </c>
       <c r="J80" s="49" t="inlineStr">
         <is>
-          <t>LIM-LD</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="K80" s="50" t="n">
-        <v>1.000325027533751</v>
+        <v>1.008568170337828</v>
       </c>
     </row>
     <row r="81">
@@ -4376,7 +4377,7 @@
       </c>
       <c r="B81" s="51" t="inlineStr">
         <is>
-          <t>SMA</t>
+          <t>RIM</t>
         </is>
       </c>
       <c r="C81" s="51" t="inlineStr">
@@ -4385,102 +4386,118 @@
         </is>
       </c>
       <c r="D81" s="52" t="n">
-        <v>125</v>
+        <v>246</v>
       </c>
       <c r="E81" s="53" t="n">
-        <v>61</v>
+        <v>196</v>
       </c>
       <c r="F81" s="53" t="n">
-        <v>-64</v>
+        <v>-50</v>
       </c>
       <c r="G81" s="52" t="n">
-        <v>388140</v>
+        <v>765600</v>
       </c>
       <c r="H81" s="53" t="n">
-        <v>189412</v>
-      </c>
-      <c r="J81" s="54" t="inlineStr">
-        <is>
-          <t>was LD</t>
-        </is>
-      </c>
-      <c r="K81" s="55" t="n">
-        <v>1.085941499180451</v>
+        <v>609990</v>
+      </c>
+      <c r="J81" s="49" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="K81" s="50" t="n">
+        <v>1.000660957221576</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="45" t="inlineStr">
         <is>
-          <t>BLB&gt;HUAFEI</t>
+          <t>TF&gt;POS 6</t>
         </is>
       </c>
       <c r="B82" s="45" t="inlineStr">
         <is>
-          <t>RIM</t>
+          <t>SMA</t>
         </is>
       </c>
       <c r="C82" s="45" t="inlineStr">
         <is>
-          <t>LIM-TOS</t>
+          <t>LIM-LD</t>
         </is>
       </c>
       <c r="D82" s="46" t="n">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="E82" s="46" t="n">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="F82" s="47" t="n">
         <v>0</v>
       </c>
       <c r="G82" s="46" t="n">
-        <v>1081050</v>
+        <v>433200</v>
       </c>
       <c r="H82" s="48" t="n">
-        <v>1081050</v>
+        <v>433200</v>
+      </c>
+      <c r="J82" s="49" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="K82" s="50" t="n">
+        <v>1.000172598230618</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="45" t="inlineStr">
+      <c r="A83" s="51" t="inlineStr">
         <is>
           <t>TF&gt;HUAFEI</t>
         </is>
       </c>
-      <c r="B83" s="45" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C83" s="45" t="inlineStr">
-        <is>
-          <t>LIM-TOS</t>
-        </is>
-      </c>
-      <c r="D83" s="46" t="n">
-        <v>67</v>
-      </c>
-      <c r="E83" s="46" t="n">
-        <v>67</v>
-      </c>
-      <c r="F83" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="G83" s="46" t="n">
-        <v>208530</v>
-      </c>
-      <c r="H83" s="48" t="n">
-        <v>208530</v>
+      <c r="B83" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C83" s="51" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D83" s="52" t="n">
+        <v>125</v>
+      </c>
+      <c r="E83" s="53" t="n">
+        <v>111</v>
+      </c>
+      <c r="F83" s="53" t="n">
+        <v>-14</v>
+      </c>
+      <c r="G83" s="52" t="n">
+        <v>388140</v>
+      </c>
+      <c r="H83" s="53" t="n">
+        <v>344668</v>
+      </c>
+      <c r="J83" s="54" t="inlineStr">
+        <is>
+          <t>was LD</t>
+        </is>
+      </c>
+      <c r="K83" s="55" t="n">
+        <v>1.085941499180451</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="45" t="inlineStr">
         <is>
-          <t>KR&gt;HUAFEI</t>
+          <t>BLB&gt;HUAFEI</t>
         </is>
       </c>
       <c r="B84" s="45" t="inlineStr">
         <is>
-          <t>SMA</t>
+          <t>RIM</t>
         </is>
       </c>
       <c r="C84" s="45" t="inlineStr">
@@ -4489,25 +4506,25 @@
         </is>
       </c>
       <c r="D84" s="46" t="n">
-        <v>32</v>
+        <v>148</v>
       </c>
       <c r="E84" s="46" t="n">
-        <v>32</v>
+        <v>148</v>
       </c>
       <c r="F84" s="47" t="n">
         <v>0</v>
       </c>
       <c r="G84" s="46" t="n">
-        <v>125970</v>
+        <v>1081050</v>
       </c>
       <c r="H84" s="48" t="n">
-        <v>125970</v>
+        <v>1081050</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="45" t="inlineStr">
         <is>
-          <t>BLB&gt;FENI KM0</t>
+          <t>TF&gt;HUAFEI</t>
         </is>
       </c>
       <c r="B85" s="45" t="inlineStr">
@@ -4517,162 +4534,162 @@
       </c>
       <c r="C85" s="45" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>LIM-TOS</t>
         </is>
       </c>
       <c r="D85" s="46" t="n">
-        <v>150</v>
+        <v>67</v>
       </c>
       <c r="E85" s="46" t="n">
-        <v>150</v>
+        <v>67</v>
       </c>
       <c r="F85" s="47" t="n">
         <v>0</v>
       </c>
       <c r="G85" s="46" t="n">
-        <v>1020750</v>
+        <v>208530</v>
       </c>
       <c r="H85" s="48" t="n">
-        <v>1020750</v>
+        <v>208530</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="45" t="inlineStr">
         <is>
-          <t>TF&gt;FENI KM15</t>
+          <t>KR&gt;HUAFEI</t>
         </is>
       </c>
       <c r="B86" s="45" t="inlineStr">
         <is>
-          <t>RIM</t>
+          <t>SMA</t>
         </is>
       </c>
       <c r="C86" s="45" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>LIM-TOS</t>
         </is>
       </c>
       <c r="D86" s="46" t="n">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="E86" s="46" t="n">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="F86" s="47" t="n">
         <v>0</v>
       </c>
       <c r="G86" s="46" t="n">
+        <v>125970</v>
+      </c>
+      <c r="H86" s="48" t="n">
+        <v>125970</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="45" t="inlineStr">
+        <is>
+          <t>BLB&gt;FENI KM0</t>
+        </is>
+      </c>
+      <c r="B87" s="45" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C87" s="45" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D87" s="46" t="n">
+        <v>150</v>
+      </c>
+      <c r="E87" s="46" t="n">
+        <v>150</v>
+      </c>
+      <c r="F87" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="46" t="n">
+        <v>1020750</v>
+      </c>
+      <c r="H87" s="48" t="n">
+        <v>1020750</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;FENI KM15</t>
+        </is>
+      </c>
+      <c r="B88" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C88" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D88" s="52" t="n">
+        <v>78</v>
+      </c>
+      <c r="E88" s="53" t="n">
+        <v>5</v>
+      </c>
+      <c r="F88" s="53" t="n">
+        <v>-73</v>
+      </c>
+      <c r="G88" s="52" t="n">
         <v>244530</v>
       </c>
-      <c r="H86" s="48" t="n">
-        <v>244530</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="51" t="inlineStr">
+      <c r="H88" s="53" t="n">
+        <v>14992</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="51" t="inlineStr">
         <is>
           <t>KR&gt;FENI KM15</t>
         </is>
       </c>
-      <c r="B87" s="51" t="inlineStr">
+      <c r="B89" s="51" t="inlineStr">
         <is>
           <t>SMA</t>
         </is>
       </c>
-      <c r="C87" s="51" t="inlineStr">
+      <c r="C89" s="51" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="D87" s="52" t="n">
+      <c r="D89" s="52" t="n">
         <v>27</v>
       </c>
-      <c r="E87" s="53" t="n">
+      <c r="E89" s="53" t="n">
         <v>2</v>
       </c>
-      <c r="F87" s="53" t="n">
+      <c r="F89" s="53" t="n">
         <v>-25</v>
       </c>
-      <c r="G87" s="52" t="n">
+      <c r="G89" s="52" t="n">
         <v>128040</v>
       </c>
-      <c r="H87" s="53" t="n">
-        <v>8596</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="45" t="inlineStr">
-        <is>
-          <t>KR&gt;POS 12</t>
-        </is>
-      </c>
-      <c r="B88" s="45" t="inlineStr">
-        <is>
-          <t>SMA</t>
-        </is>
-      </c>
-      <c r="C88" s="45" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="D88" s="46" t="n">
-        <v>11</v>
-      </c>
-      <c r="E88" s="46" t="n">
-        <v>11</v>
-      </c>
-      <c r="F88" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="G88" s="46" t="n">
-        <v>65610</v>
-      </c>
-      <c r="H88" s="48" t="n">
-        <v>65610</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="45" t="inlineStr">
-        <is>
-          <t>BLB&gt;POS 14</t>
-        </is>
-      </c>
-      <c r="B89" s="45" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C89" s="45" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="D89" s="46" t="n">
-        <v>7</v>
-      </c>
-      <c r="E89" s="46" t="n">
-        <v>7</v>
-      </c>
-      <c r="F89" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="G89" s="46" t="n">
-        <v>61320</v>
-      </c>
-      <c r="H89" s="48" t="n">
-        <v>61320</v>
+      <c r="H89" s="53" t="n">
+        <v>8456</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="45" t="inlineStr">
         <is>
-          <t>TF&gt;POS 12</t>
+          <t>KR&gt;POS 12</t>
         </is>
       </c>
       <c r="B90" s="45" t="inlineStr">
         <is>
-          <t>RIM</t>
+          <t>SMA</t>
         </is>
       </c>
       <c r="C90" s="45" t="inlineStr">
@@ -4681,424 +4698,428 @@
         </is>
       </c>
       <c r="D90" s="46" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E90" s="46" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F90" s="47" t="n">
         <v>0</v>
       </c>
       <c r="G90" s="46" t="n">
+        <v>65610</v>
+      </c>
+      <c r="H90" s="48" t="n">
+        <v>65610</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="45" t="inlineStr">
+        <is>
+          <t>BLB&gt;POS 14</t>
+        </is>
+      </c>
+      <c r="B91" s="45" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C91" s="45" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D91" s="46" t="n">
+        <v>7</v>
+      </c>
+      <c r="E91" s="46" t="n">
+        <v>7</v>
+      </c>
+      <c r="F91" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" s="46" t="n">
+        <v>61320</v>
+      </c>
+      <c r="H91" s="48" t="n">
+        <v>61320</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;POS 12</t>
+        </is>
+      </c>
+      <c r="B92" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C92" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D92" s="52" t="n">
+        <v>18</v>
+      </c>
+      <c r="E92" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" s="53" t="n">
+        <v>-18</v>
+      </c>
+      <c r="G92" s="52" t="n">
         <v>61080</v>
       </c>
-      <c r="H90" s="48" t="n">
-        <v>61080</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="56" t="inlineStr">
+      <c r="H92" s="53" t="n">
+        <v>1298</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="56" t="inlineStr">
         <is>
           <t>KR&gt;FENI KM0</t>
         </is>
       </c>
-      <c r="B91" s="56" t="inlineStr">
+      <c r="B93" s="56" t="inlineStr">
         <is>
           <t>SMA</t>
         </is>
       </c>
-      <c r="C91" s="56" t="inlineStr">
+      <c r="C93" s="56" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="D91" s="57" t="inlineStr">
+      <c r="D93" s="57" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E91" s="58" t="n">
+      <c r="E93" s="58" t="n">
         <v>39</v>
       </c>
-      <c r="F91" s="58" t="n">
+      <c r="F93" s="58" t="n">
         <v>39</v>
       </c>
-      <c r="G91" s="57" t="inlineStr">
+      <c r="G93" s="57" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H91" s="58" t="n">
-        <v>119444</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="59" t="inlineStr">
+      <c r="H93" s="58" t="n">
+        <v>119584</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="56" t="inlineStr">
+        <is>
+          <t>TF&gt;FENI KM0</t>
+        </is>
+      </c>
+      <c r="B94" s="56" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C94" s="56" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D94" s="57" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E94" s="58" t="n">
+        <v>129</v>
+      </c>
+      <c r="F94" s="58" t="n">
+        <v>129</v>
+      </c>
+      <c r="G94" s="57" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H94" s="58" t="n">
+        <v>289320</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="59" t="inlineStr">
         <is>
           <t>OPTION 1 — PARK all 64 DT</t>
         </is>
       </c>
-      <c r="B92" s="60" t="inlineStr"/>
-      <c r="C92" s="60" t="inlineStr"/>
-      <c r="D92" s="61" t="n">
+      <c r="B95" s="60" t="inlineStr"/>
+      <c r="C95" s="60" t="inlineStr"/>
+      <c r="D95" s="61" t="n">
         <v>64</v>
       </c>
-      <c r="E92" s="61" t="n">
+      <c r="E95" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="F92" s="61" t="n">
+      <c r="F95" s="61" t="n">
         <v>-64</v>
       </c>
-      <c r="G92" s="60" t="inlineStr"/>
-      <c r="H92" s="62" t="inlineStr">
+      <c r="G95" s="60" t="inlineStr"/>
+      <c r="H95" s="62" t="inlineStr">
         <is>
           <t>64 trucks stand idle</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="63" t="inlineStr">
-        <is>
-          <t>OPTION 2 — work 14 DT on longer KM0 hauls</t>
-        </is>
-      </c>
-      <c r="B93" s="60" t="inlineStr"/>
-      <c r="C93" s="60" t="inlineStr"/>
-      <c r="D93" s="64" t="n">
+    <row r="96">
+      <c r="A96" s="63" t="inlineStr">
+        <is>
+          <t>OPTION 2 — work 53 DT on longer KM0 hauls</t>
+        </is>
+      </c>
+      <c r="B96" s="60" t="inlineStr"/>
+      <c r="C96" s="60" t="inlineStr"/>
+      <c r="D96" s="64" t="n">
         <v>64</v>
       </c>
-      <c r="E93" s="64" t="n">
-        <v>14</v>
-      </c>
-      <c r="F93" s="61" t="n">
-        <v>-50</v>
-      </c>
-      <c r="G93" s="60" t="inlineStr"/>
-      <c r="H93" s="65" t="inlineStr">
-        <is>
-          <t>14 keep working · 50 still park</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="43" t="inlineStr">
-        <is>
-          <t>December — LIM-LD 130.8% of its line · surplus 522,339 t · 162 DT come out</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="44" t="inlineStr">
+      <c r="E96" s="64" t="n">
+        <v>53</v>
+      </c>
+      <c r="F96" s="61" t="n">
+        <v>-11</v>
+      </c>
+      <c r="G96" s="60" t="inlineStr"/>
+      <c r="H96" s="65" t="inlineStr">
+        <is>
+          <t>53 keep working · 11 still park</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="43" t="inlineStr">
+        <is>
+          <t>December — LIM-LD 130.8% of its line · surplus 522,339 t · 161 DT come out</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="44" t="inlineStr">
         <is>
           <t>Path / option</t>
         </is>
       </c>
-      <c r="B97" s="44" t="inlineStr">
+      <c r="B100" s="44" t="inlineStr">
         <is>
           <t>Contractor</t>
         </is>
       </c>
-      <c r="C97" s="44" t="inlineStr">
+      <c r="C100" s="44" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="D97" s="44" t="inlineStr">
+      <c r="D100" s="44" t="inlineStr">
         <is>
           <t>DT before</t>
         </is>
       </c>
-      <c r="E97" s="44" t="inlineStr">
+      <c r="E100" s="44" t="inlineStr">
         <is>
           <t>DT after</t>
         </is>
       </c>
-      <c r="F97" s="44" t="inlineStr">
+      <c r="F100" s="44" t="inlineStr">
         <is>
           <t>Δ DT</t>
         </is>
       </c>
-      <c r="G97" s="44" t="inlineStr">
+      <c r="G100" s="44" t="inlineStr">
         <is>
           <t>t/month before</t>
         </is>
       </c>
-      <c r="H97" s="44" t="inlineStr">
+      <c r="H100" s="44" t="inlineStr">
         <is>
           <t>t/month AFTER</t>
         </is>
       </c>
-      <c r="J97" s="44" t="inlineStr">
+      <c r="J100" s="44" t="inlineStr">
         <is>
           <t>Coverage after</t>
         </is>
       </c>
-      <c r="K97" s="44" t="inlineStr">
+      <c r="K100" s="44" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="45" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="45" t="inlineStr">
         <is>
           <t>TF&gt;POS 6</t>
         </is>
       </c>
-      <c r="B98" s="45" t="inlineStr">
+      <c r="B101" s="45" t="inlineStr">
         <is>
           <t>RIM</t>
         </is>
       </c>
-      <c r="C98" s="45" t="inlineStr">
+      <c r="C101" s="45" t="inlineStr">
         <is>
           <t>LIM-LD</t>
         </is>
       </c>
-      <c r="D98" s="46" t="n">
+      <c r="D101" s="46" t="n">
         <v>195</v>
       </c>
-      <c r="E98" s="46" t="n">
+      <c r="E101" s="46" t="n">
         <v>195</v>
       </c>
-      <c r="F98" s="47" t="n">
+      <c r="F101" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="G98" s="46" t="n">
+      <c r="G101" s="46" t="n">
         <v>766196</v>
       </c>
-      <c r="H98" s="48" t="n">
+      <c r="H101" s="48" t="n">
         <v>766196</v>
       </c>
-      <c r="J98" s="49" t="inlineStr">
+      <c r="J101" s="49" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="K98" s="50" t="n">
+      <c r="K101" s="50" t="n">
         <v>1.000439163331117</v>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="51" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="51" t="inlineStr">
         <is>
           <t>TF&gt;HUAFEI</t>
         </is>
       </c>
-      <c r="B99" s="51" t="inlineStr">
+      <c r="B102" s="51" t="inlineStr">
         <is>
           <t>RIM</t>
         </is>
       </c>
-      <c r="C99" s="51" t="inlineStr">
+      <c r="C102" s="51" t="inlineStr">
         <is>
           <t>LIM-LD</t>
         </is>
       </c>
-      <c r="D99" s="52" t="n">
+      <c r="D102" s="52" t="n">
         <v>196</v>
       </c>
-      <c r="E99" s="53" t="n">
-        <v>155</v>
-      </c>
-      <c r="F99" s="53" t="n">
-        <v>-41</v>
-      </c>
-      <c r="G99" s="52" t="n">
+      <c r="E102" s="53" t="n">
+        <v>62</v>
+      </c>
+      <c r="F102" s="53" t="n">
+        <v>-134</v>
+      </c>
+      <c r="G102" s="52" t="n">
         <v>632307</v>
       </c>
-      <c r="H99" s="53" t="n">
-        <v>500039</v>
-      </c>
-      <c r="J99" s="49" t="inlineStr">
+      <c r="H102" s="53" t="n">
+        <v>200015</v>
+      </c>
+      <c r="J102" s="49" t="inlineStr">
         <is>
           <t>LIM-TOS</t>
         </is>
       </c>
-      <c r="K99" s="50" t="n">
+      <c r="K102" s="50" t="n">
         <v>1.003697358081929</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="45" t="inlineStr">
-        <is>
-          <t>TF&gt;POS 6</t>
-        </is>
-      </c>
-      <c r="B100" s="45" t="inlineStr">
-        <is>
-          <t>SMA</t>
-        </is>
-      </c>
-      <c r="C100" s="45" t="inlineStr">
-        <is>
-          <t>LIM-LD</t>
-        </is>
-      </c>
-      <c r="D100" s="46" t="n">
-        <v>120</v>
-      </c>
-      <c r="E100" s="46" t="n">
-        <v>120</v>
-      </c>
-      <c r="F100" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="G100" s="46" t="n">
-        <v>430683</v>
-      </c>
-      <c r="H100" s="48" t="n">
-        <v>430683</v>
-      </c>
-      <c r="J100" s="49" t="inlineStr">
-        <is>
-          <t>LIM-LD</t>
-        </is>
-      </c>
-      <c r="K100" s="50" t="n">
-        <v>1.000309302726191</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="51" t="inlineStr">
-        <is>
-          <t>TF&gt;HUAFEI</t>
-        </is>
-      </c>
-      <c r="B101" s="51" t="inlineStr">
-        <is>
-          <t>SMA</t>
-        </is>
-      </c>
-      <c r="C101" s="51" t="inlineStr">
-        <is>
-          <t>LIM-LD</t>
-        </is>
-      </c>
-      <c r="D101" s="52" t="n">
-        <v>121</v>
-      </c>
-      <c r="E101" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="F101" s="53" t="n">
-        <v>-121</v>
-      </c>
-      <c r="G101" s="52" t="n">
-        <v>389577</v>
-      </c>
-      <c r="H101" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="J101" s="54" t="inlineStr">
-        <is>
-          <t>was LD</t>
-        </is>
-      </c>
-      <c r="K101" s="55" t="n">
-        <v>1.307911551155894</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="45" t="inlineStr">
-        <is>
-          <t>BLB&gt;HUAFEI</t>
-        </is>
-      </c>
-      <c r="B102" s="45" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C102" s="45" t="inlineStr">
-        <is>
-          <t>LIM-TOS</t>
-        </is>
-      </c>
-      <c r="D102" s="46" t="n">
-        <v>139</v>
-      </c>
-      <c r="E102" s="46" t="n">
-        <v>139</v>
-      </c>
-      <c r="F102" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="G102" s="46" t="n">
-        <v>1049629</v>
-      </c>
-      <c r="H102" s="48" t="n">
-        <v>1049629</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="45" t="inlineStr">
         <is>
-          <t>TF&gt;HUAFEI</t>
+          <t>TF&gt;POS 6</t>
         </is>
       </c>
       <c r="B103" s="45" t="inlineStr">
         <is>
-          <t>RIM</t>
+          <t>SMA</t>
         </is>
       </c>
       <c r="C103" s="45" t="inlineStr">
         <is>
-          <t>LIM-TOS</t>
+          <t>LIM-LD</t>
         </is>
       </c>
       <c r="D103" s="46" t="n">
-        <v>63</v>
+        <v>120</v>
       </c>
       <c r="E103" s="46" t="n">
-        <v>63</v>
+        <v>120</v>
       </c>
       <c r="F103" s="47" t="n">
         <v>0</v>
       </c>
       <c r="G103" s="46" t="n">
-        <v>203236</v>
+        <v>430683</v>
       </c>
       <c r="H103" s="48" t="n">
-        <v>203236</v>
+        <v>430683</v>
+      </c>
+      <c r="J103" s="49" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="K103" s="50" t="n">
+        <v>1.001855746064243</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="45" t="inlineStr">
-        <is>
-          <t>KR&gt;HUAFEI</t>
-        </is>
-      </c>
-      <c r="B104" s="45" t="inlineStr">
+      <c r="A104" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B104" s="51" t="inlineStr">
         <is>
           <t>SMA</t>
         </is>
       </c>
-      <c r="C104" s="45" t="inlineStr">
-        <is>
-          <t>LIM-TOS</t>
-        </is>
-      </c>
-      <c r="D104" s="46" t="n">
-        <v>19</v>
-      </c>
-      <c r="E104" s="46" t="n">
-        <v>19</v>
-      </c>
-      <c r="F104" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="G104" s="46" t="n">
-        <v>78120</v>
-      </c>
-      <c r="H104" s="48" t="n">
-        <v>78120</v>
+      <c r="C104" s="51" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="D104" s="52" t="n">
+        <v>121</v>
+      </c>
+      <c r="E104" s="53" t="n">
+        <v>94</v>
+      </c>
+      <c r="F104" s="53" t="n">
+        <v>-27</v>
+      </c>
+      <c r="G104" s="52" t="n">
+        <v>389577</v>
+      </c>
+      <c r="H104" s="53" t="n">
+        <v>302647</v>
+      </c>
+      <c r="J104" s="54" t="inlineStr">
+        <is>
+          <t>was LD</t>
+        </is>
+      </c>
+      <c r="K104" s="55" t="n">
+        <v>1.307911551155894</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="45" t="inlineStr">
         <is>
-          <t>BLB&gt;FENI KM0</t>
+          <t>BLB&gt;HUAFEI</t>
         </is>
       </c>
       <c r="B105" s="45" t="inlineStr">
@@ -5108,93 +5129,93 @@
       </c>
       <c r="C105" s="45" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>LIM-TOS</t>
         </is>
       </c>
       <c r="D105" s="46" t="n">
-        <v>202</v>
+        <v>139</v>
       </c>
       <c r="E105" s="46" t="n">
-        <v>202</v>
+        <v>139</v>
       </c>
       <c r="F105" s="47" t="n">
         <v>0</v>
       </c>
       <c r="G105" s="46" t="n">
-        <v>1419366</v>
+        <v>1049629</v>
       </c>
       <c r="H105" s="48" t="n">
-        <v>1419366</v>
+        <v>1049629</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="51" t="inlineStr">
-        <is>
-          <t>TF&gt;FENI KM15</t>
-        </is>
-      </c>
-      <c r="B106" s="51" t="inlineStr">
+      <c r="A106" s="45" t="inlineStr">
+        <is>
+          <t>TF&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B106" s="45" t="inlineStr">
         <is>
           <t>RIM</t>
         </is>
       </c>
-      <c r="C106" s="51" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="D106" s="52" t="n">
-        <v>141</v>
-      </c>
-      <c r="E106" s="53" t="n">
-        <v>22</v>
-      </c>
-      <c r="F106" s="53" t="n">
-        <v>-119</v>
-      </c>
-      <c r="G106" s="52" t="n">
-        <v>458955</v>
-      </c>
-      <c r="H106" s="53" t="n">
-        <v>70301</v>
+      <c r="C106" s="45" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D106" s="46" t="n">
+        <v>63</v>
+      </c>
+      <c r="E106" s="46" t="n">
+        <v>63</v>
+      </c>
+      <c r="F106" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" s="46" t="n">
+        <v>203236</v>
+      </c>
+      <c r="H106" s="48" t="n">
+        <v>203236</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="51" t="inlineStr">
-        <is>
-          <t>KR&gt;FENI KM15</t>
-        </is>
-      </c>
-      <c r="B107" s="51" t="inlineStr">
+      <c r="A107" s="45" t="inlineStr">
+        <is>
+          <t>KR&gt;HUAFEI</t>
+        </is>
+      </c>
+      <c r="B107" s="45" t="inlineStr">
         <is>
           <t>SMA</t>
         </is>
       </c>
-      <c r="C107" s="51" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="D107" s="52" t="n">
-        <v>50</v>
-      </c>
-      <c r="E107" s="53" t="n">
-        <v>2</v>
-      </c>
-      <c r="F107" s="53" t="n">
-        <v>-48</v>
-      </c>
-      <c r="G107" s="52" t="n">
-        <v>245427</v>
-      </c>
-      <c r="H107" s="53" t="n">
-        <v>7392</v>
+      <c r="C107" s="45" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D107" s="46" t="n">
+        <v>19</v>
+      </c>
+      <c r="E107" s="46" t="n">
+        <v>19</v>
+      </c>
+      <c r="F107" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" s="46" t="n">
+        <v>78120</v>
+      </c>
+      <c r="H107" s="48" t="n">
+        <v>78120</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="45" t="inlineStr">
         <is>
-          <t>BLB&gt;POS 14</t>
+          <t>BLB&gt;FENI KM0</t>
         </is>
       </c>
       <c r="B108" s="45" t="inlineStr">
@@ -5208,202 +5229,298 @@
         </is>
       </c>
       <c r="D108" s="46" t="n">
-        <v>7</v>
+        <v>202</v>
       </c>
       <c r="E108" s="46" t="n">
-        <v>7</v>
+        <v>202</v>
       </c>
       <c r="F108" s="47" t="n">
         <v>0</v>
       </c>
       <c r="G108" s="46" t="n">
+        <v>1419366</v>
+      </c>
+      <c r="H108" s="48" t="n">
+        <v>1419366</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="51" t="inlineStr">
+        <is>
+          <t>TF&gt;FENI KM15</t>
+        </is>
+      </c>
+      <c r="B109" s="51" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C109" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D109" s="52" t="n">
+        <v>141</v>
+      </c>
+      <c r="E109" s="53" t="n">
+        <v>5</v>
+      </c>
+      <c r="F109" s="53" t="n">
+        <v>-136</v>
+      </c>
+      <c r="G109" s="52" t="n">
+        <v>458955</v>
+      </c>
+      <c r="H109" s="53" t="n">
+        <v>13040</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="51" t="inlineStr">
+        <is>
+          <t>KR&gt;FENI KM15</t>
+        </is>
+      </c>
+      <c r="B110" s="51" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C110" s="51" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D110" s="52" t="n">
+        <v>50</v>
+      </c>
+      <c r="E110" s="53" t="n">
+        <v>2</v>
+      </c>
+      <c r="F110" s="53" t="n">
+        <v>-48</v>
+      </c>
+      <c r="G110" s="52" t="n">
+        <v>245427</v>
+      </c>
+      <c r="H110" s="53" t="n">
+        <v>7113</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="45" t="inlineStr">
+        <is>
+          <t>BLB&gt;POS 14</t>
+        </is>
+      </c>
+      <c r="B111" s="45" t="inlineStr">
+        <is>
+          <t>RIM</t>
+        </is>
+      </c>
+      <c r="C111" s="45" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D111" s="46" t="n">
+        <v>7</v>
+      </c>
+      <c r="E111" s="46" t="n">
+        <v>7</v>
+      </c>
+      <c r="F111" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G111" s="46" t="n">
         <v>63364</v>
       </c>
-      <c r="H108" s="48" t="n">
+      <c r="H111" s="48" t="n">
         <v>63364</v>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="45" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="51" t="inlineStr">
         <is>
           <t>TF&gt;POS 12</t>
         </is>
       </c>
-      <c r="B109" s="45" t="inlineStr">
+      <c r="B112" s="51" t="inlineStr">
         <is>
           <t>RIM</t>
         </is>
       </c>
-      <c r="C109" s="45" t="inlineStr">
+      <c r="C112" s="51" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="D109" s="46" t="n">
+      <c r="D112" s="52" t="n">
         <v>18</v>
       </c>
-      <c r="E109" s="46" t="n">
-        <v>18</v>
-      </c>
-      <c r="F109" s="47" t="n">
+      <c r="E112" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="G109" s="46" t="n">
+      <c r="F112" s="53" t="n">
+        <v>-18</v>
+      </c>
+      <c r="G112" s="52" t="n">
         <v>63178</v>
       </c>
-      <c r="H109" s="48" t="n">
-        <v>63178</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="45" t="inlineStr">
+      <c r="H112" s="53" t="n">
+        <v>1403</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="45" t="inlineStr">
         <is>
           <t>KR&gt;POS 12</t>
         </is>
       </c>
-      <c r="B110" s="45" t="inlineStr">
+      <c r="B113" s="45" t="inlineStr">
         <is>
           <t>SMA</t>
         </is>
       </c>
-      <c r="C110" s="45" t="inlineStr">
+      <c r="C113" s="45" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="D110" s="46" t="n">
+      <c r="D113" s="46" t="n">
         <v>10</v>
       </c>
-      <c r="E110" s="46" t="n">
+      <c r="E113" s="46" t="n">
         <v>10</v>
       </c>
-      <c r="F110" s="47" t="n">
+      <c r="F113" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="G110" s="46" t="n">
+      <c r="G113" s="46" t="n">
         <v>61938</v>
       </c>
-      <c r="H110" s="48" t="n">
+      <c r="H113" s="48" t="n">
         <v>61938</v>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="56" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="56" t="inlineStr">
         <is>
           <t>KR&gt;FENI KM0</t>
         </is>
       </c>
-      <c r="B111" s="56" t="inlineStr">
+      <c r="B114" s="56" t="inlineStr">
         <is>
           <t>SMA</t>
         </is>
       </c>
-      <c r="C111" s="56" t="inlineStr">
+      <c r="C114" s="56" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="D111" s="57" t="inlineStr">
+      <c r="D114" s="57" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E111" s="58" t="n">
+      <c r="E114" s="58" t="n">
         <v>75</v>
       </c>
-      <c r="F111" s="58" t="n">
+      <c r="F114" s="58" t="n">
         <v>75</v>
       </c>
-      <c r="G111" s="57" t="inlineStr">
+      <c r="G114" s="57" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H111" s="58" t="n">
-        <v>238035</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="56" t="inlineStr">
+      <c r="H114" s="58" t="n">
+        <v>238314</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="56" t="inlineStr">
         <is>
           <t>TF&gt;FENI KM0</t>
         </is>
       </c>
-      <c r="B112" s="56" t="inlineStr">
+      <c r="B115" s="56" t="inlineStr">
         <is>
           <t>RIM</t>
         </is>
       </c>
-      <c r="C112" s="56" t="inlineStr">
+      <c r="C115" s="56" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="D112" s="57" t="inlineStr">
+      <c r="D115" s="57" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E112" s="58" t="n">
-        <v>160</v>
-      </c>
-      <c r="F112" s="58" t="n">
-        <v>160</v>
-      </c>
-      <c r="G112" s="57" t="inlineStr">
+      <c r="E115" s="58" t="n">
+        <v>215</v>
+      </c>
+      <c r="F115" s="58" t="n">
+        <v>215</v>
+      </c>
+      <c r="G115" s="57" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H112" s="58" t="n">
-        <v>388654</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="59" t="inlineStr">
-        <is>
-          <t>OPTION 1 — PARK all 162 DT</t>
-        </is>
-      </c>
-      <c r="B113" s="60" t="inlineStr"/>
-      <c r="C113" s="60" t="inlineStr"/>
-      <c r="D113" s="61" t="n">
-        <v>162</v>
-      </c>
-      <c r="E113" s="61" t="n">
+      <c r="H115" s="58" t="n">
+        <v>507690</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="59" t="inlineStr">
+        <is>
+          <t>OPTION 1 — PARK all 161 DT</t>
+        </is>
+      </c>
+      <c r="B116" s="60" t="inlineStr"/>
+      <c r="C116" s="60" t="inlineStr"/>
+      <c r="D116" s="61" t="n">
+        <v>161</v>
+      </c>
+      <c r="E116" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="F113" s="61" t="n">
-        <v>-162</v>
-      </c>
-      <c r="G113" s="60" t="inlineStr"/>
-      <c r="H113" s="62" t="inlineStr">
-        <is>
-          <t>162 trucks stand idle</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="63" t="inlineStr">
-        <is>
-          <t>OPTION 2 — work 68 DT on longer KM0 hauls</t>
-        </is>
-      </c>
-      <c r="B114" s="60" t="inlineStr"/>
-      <c r="C114" s="60" t="inlineStr"/>
-      <c r="D114" s="64" t="n">
-        <v>162</v>
-      </c>
-      <c r="E114" s="64" t="n">
-        <v>68</v>
-      </c>
-      <c r="F114" s="61" t="n">
-        <v>-94</v>
-      </c>
-      <c r="G114" s="60" t="inlineStr"/>
-      <c r="H114" s="65" t="inlineStr">
-        <is>
-          <t>68 keep working · 94 still park</t>
+      <c r="F116" s="61" t="n">
+        <v>-161</v>
+      </c>
+      <c r="G116" s="60" t="inlineStr"/>
+      <c r="H116" s="62" t="inlineStr">
+        <is>
+          <t>161 trucks stand idle</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="63" t="inlineStr">
+        <is>
+          <t>OPTION 2 — work 88 DT on longer KM0 hauls</t>
+        </is>
+      </c>
+      <c r="B117" s="60" t="inlineStr"/>
+      <c r="C117" s="60" t="inlineStr"/>
+      <c r="D117" s="64" t="n">
+        <v>161</v>
+      </c>
+      <c r="E117" s="64" t="n">
+        <v>88</v>
+      </c>
+      <c r="F117" s="61" t="n">
+        <v>-73</v>
+      </c>
+      <c r="G117" s="60" t="inlineStr"/>
+      <c r="H117" s="65" t="inlineStr">
+        <is>
+          <t>88 keep working · 73 still park</t>
         </is>
       </c>
     </row>

--- a/reports/scenario_comparison_dec_options.xlsx
+++ b/reports/scenario_comparison_dec_options.xlsx
@@ -7,7 +7,7 @@
   </bookViews>
   <sheets>
     <sheet name="Compare" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Year adjustment" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Fleet levelling" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Insights" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
@@ -22,7 +22,7 @@
     <numFmt numFmtId="165" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="166" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="58">
+  <fonts count="59">
     <font>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -406,6 +406,12 @@
       <b val="1"/>
       <color rgb="000F4C81"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001B7A41"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="43">
@@ -940,7 +946,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1151,6 +1157,13 @@
     <xf numFmtId="3" fontId="47" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="45" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="49" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2468,276 +2481,296 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H63"/>
+  <dimension ref="A1:H58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="52" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="39" t="inlineStr">
         <is>
-          <t>Bringing the YEAR to 100% — how many trucks we do not need</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="40" customHeight="1">
+          <t>Fleet levelling — one running level all year</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
       <c r="A3" s="40" t="inlineStr">
         <is>
-          <t>THE TARGET IS THE YEAR, not each month. SAP and LIM-TOS already land on their year lines; LIM-LD is the one running over (3.0.2 103.0%, 3.1.1 103.9%, 3.1.2 111.4%). We remove only enough LIM-LD to bring the YEAR to 100%, so a single month may still sit above its own line — that is fine, and it is why far fewer trucks are freed than a month-by-month fix would demand.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="40" customHeight="1">
+          <t>The fleet grows through the year (581 · 931 · 1,280 · 1,281 DT). Running every truck flat out overshoots the LIM-LD year line, so some must stand down. Parking a different number each month would force them to BUY for the peak and leave those trucks idle a month later.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
       <c r="A4" s="40" t="inlineStr">
         <is>
-          <t>RULES STILL HOLD IN EVERY MONTH: no month is pushed BELOW its own line, a truck never changes contractor, RIM works BLB and TF only and SMA works KR and TF only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="40" customHeight="1">
-      <c r="A5" s="40" t="inlineStr">
-        <is>
-          <t>THE FREED TRUCKS ARE OPTIONAL CAPACITY. First we try to keep them working by moving SAP onto LONGER hauls (KM15 to KM0, POS 12 to KM0) — the same tonnage over a longer distance needs more trucks. Only what no haul can take is reported as trucks we simply do not need.</t>
+          <t>Instead we hold ONE running level all year: the highest level every month can keep while the YEAR still lands on its line. That level is the fleet they actually need to own.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="44" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B6" s="44" t="inlineStr">
+        <is>
+          <t>FLEET TO OWN</t>
+        </is>
+      </c>
+      <c r="C6" s="44" t="inlineStr">
+        <is>
+          <t>Nov run</t>
+        </is>
+      </c>
+      <c r="D6" s="44" t="inlineStr">
+        <is>
+          <t>Dec run</t>
+        </is>
+      </c>
+      <c r="E6" s="44" t="inlineStr">
+        <is>
+          <t>DT parked</t>
+        </is>
+      </c>
+      <c r="F6" s="44" t="inlineStr">
+        <is>
+          <t>LIM-LD year was</t>
+        </is>
+      </c>
+      <c r="G6" s="44" t="inlineStr">
+        <is>
+          <t>LIM-LD year now</t>
+        </is>
+      </c>
+      <c r="H6" s="44" t="inlineStr">
+        <is>
+          <t>Together year</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="41" t="inlineStr">
-        <is>
-          <t>THE ANSWER — trucks not needed, per scenario</t>
-        </is>
+      <c r="A7" s="67" t="inlineStr">
+        <is>
+          <t>3.0.1</t>
+        </is>
+      </c>
+      <c r="B7" s="56" t="inlineStr">
+        <is>
+          <t>no change</t>
+        </is>
+      </c>
+      <c r="C7" s="46" t="n">
+        <v>1280</v>
+      </c>
+      <c r="D7" s="46" t="n">
+        <v>1281</v>
+      </c>
+      <c r="E7" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="80" t="n">
+        <v>0.9583298075817238</v>
+      </c>
+      <c r="G7" s="50" t="n">
+        <v>0.9583298075817238</v>
+      </c>
+      <c r="H7" s="50" t="n">
+        <v>0.9844039283917985</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="44" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="B8" s="44" t="inlineStr">
-        <is>
-          <t>LIM-LD year now</t>
-        </is>
-      </c>
-      <c r="C8" s="44" t="inlineStr">
-        <is>
-          <t>Year line</t>
-        </is>
-      </c>
-      <c r="D8" s="44" t="inlineStr">
-        <is>
-          <t>Now %</t>
-        </is>
-      </c>
-      <c r="E8" s="44" t="inlineStr">
-        <is>
-          <t>Trucks freed</t>
-        </is>
-      </c>
-      <c r="F8" s="44" t="inlineStr">
-        <is>
-          <t>Kept working (longer hauls)</t>
-        </is>
-      </c>
-      <c r="G8" s="44" t="inlineStr">
-        <is>
-          <t>NOT NEEDED</t>
-        </is>
-      </c>
-      <c r="H8" s="44" t="inlineStr">
-        <is>
-          <t>Year LD after</t>
-        </is>
+      <c r="A8" s="67" t="inlineStr">
+        <is>
+          <t>3.0.2</t>
+        </is>
+      </c>
+      <c r="B8" s="58" t="n">
+        <v>1244</v>
+      </c>
+      <c r="C8" s="46" t="n">
+        <v>1244</v>
+      </c>
+      <c r="D8" s="46" t="n">
+        <v>1244</v>
+      </c>
+      <c r="E8" s="79" t="n">
+        <v>73</v>
+      </c>
+      <c r="F8" s="81" t="n">
+        <v>1.029626006607542</v>
+      </c>
+      <c r="G8" s="50" t="n">
+        <v>0.9994156617947111</v>
+      </c>
+      <c r="H8" s="50" t="n">
+        <v>1.00314440861065</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="67" t="inlineStr">
         <is>
-          <t>3.0.1</t>
-        </is>
-      </c>
-      <c r="B9" s="46" t="n">
-        <v>7316183</v>
+          <t>3.1.1</t>
+        </is>
+      </c>
+      <c r="B9" s="58" t="n">
+        <v>1239</v>
       </c>
       <c r="C9" s="46" t="n">
-        <v>7634306</v>
-      </c>
-      <c r="D9" s="68" t="n">
-        <v>0.9583298075817238</v>
-      </c>
-      <c r="E9" s="69" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="69" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="58" t="n">
-        <v>0</v>
+        <v>1239</v>
+      </c>
+      <c r="D9" s="46" t="n">
+        <v>1239</v>
+      </c>
+      <c r="E9" s="79" t="n">
+        <v>83</v>
+      </c>
+      <c r="F9" s="81" t="n">
+        <v>1.038862900053068</v>
+      </c>
+      <c r="G9" s="50" t="n">
+        <v>0.9991867558336038</v>
       </c>
       <c r="H9" s="50" t="n">
-        <v>0.9583298075817238</v>
+        <v>1.001733413065755</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="67" t="inlineStr">
         <is>
-          <t>3.0.2</t>
-        </is>
-      </c>
-      <c r="B10" s="46" t="n">
-        <v>7860480</v>
+          <t>3.1.2</t>
+        </is>
+      </c>
+      <c r="B10" s="58" t="n">
+        <v>1161</v>
       </c>
       <c r="C10" s="46" t="n">
-        <v>7634306</v>
-      </c>
-      <c r="D10" s="70" t="n">
-        <v>1.029626006607542</v>
-      </c>
-      <c r="E10" s="71" t="n">
-        <v>70</v>
-      </c>
-      <c r="F10" s="58" t="n">
-        <v>70</v>
-      </c>
-      <c r="G10" s="58" t="n">
+        <v>1161</v>
+      </c>
+      <c r="D10" s="46" t="n">
+        <v>1161</v>
+      </c>
+      <c r="E10" s="79" t="n">
+        <v>239</v>
+      </c>
+      <c r="F10" s="81" t="n">
+        <v>1.113639106928549</v>
+      </c>
+      <c r="G10" s="50" t="n">
+        <v>0.999877543964426</v>
+      </c>
+      <c r="H10" s="50" t="n">
+        <v>1.003088441366754</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="41" t="inlineStr">
+        <is>
+          <t>Scenario 3.0.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="72" t="inlineStr">
+        <is>
+          <t>LIM-LD year is 95.8% — under its line. No parking, no levelling needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="41" t="inlineStr">
+        <is>
+          <t>Scenario 3.0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="82" t="inlineStr">
+        <is>
+          <t>Fleet to own: 1244 DT, held every month.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="44" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B18" s="44" t="inlineStr">
+        <is>
+          <t>Fleet available</t>
+        </is>
+      </c>
+      <c r="C18" s="44" t="inlineStr">
+        <is>
+          <t>PARKED</t>
+        </is>
+      </c>
+      <c r="D18" s="44" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
+      <c r="E18" s="44" t="inlineStr"/>
+      <c r="F18" s="44" t="inlineStr"/>
+      <c r="G18" s="44" t="inlineStr"/>
+      <c r="H18" s="44" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="67" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="B19" s="46" t="n">
+        <v>581</v>
+      </c>
+      <c r="C19" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="H10" s="50" t="n">
-        <v>1.0000909696791</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="67" t="inlineStr">
-        <is>
-          <t>3.1.1</t>
-        </is>
-      </c>
-      <c r="B11" s="46" t="n">
-        <v>6902523</v>
-      </c>
-      <c r="C11" s="46" t="n">
-        <v>6644306</v>
-      </c>
-      <c r="D11" s="70" t="n">
-        <v>1.038862900053068</v>
-      </c>
-      <c r="E11" s="71" t="n">
-        <v>79</v>
-      </c>
-      <c r="F11" s="58" t="n">
-        <v>79</v>
-      </c>
-      <c r="G11" s="58" t="n">
+      <c r="D19" s="58" t="n">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="67" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="B20" s="46" t="n">
+        <v>931</v>
+      </c>
+      <c r="C20" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="H11" s="50" t="n">
-        <v>1.000408890947364</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="67" t="inlineStr">
-        <is>
-          <t>3.1.2</t>
-        </is>
-      </c>
-      <c r="B12" s="46" t="n">
-        <v>7399359</v>
-      </c>
-      <c r="C12" s="46" t="n">
-        <v>6644306</v>
-      </c>
-      <c r="D12" s="70" t="n">
-        <v>1.113639106928549</v>
-      </c>
-      <c r="E12" s="71" t="n">
-        <v>234</v>
-      </c>
-      <c r="F12" s="58" t="n">
-        <v>163</v>
-      </c>
-      <c r="G12" s="53" t="n">
-        <v>71</v>
-      </c>
-      <c r="H12" s="50" t="n">
-        <v>1.001169677059233</v>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="42" t="inlineStr">
-        <is>
-          <t>Reading: 3.0.1 needs no change — its year LIM-LD is already 95.8%, under the line. The other three each free trucks, and in 3.0.2 and 3.1.1 EVERY freed truck stays working on a longer haul, so nothing is wasted. Only 3.1.2, which runs 11.4% over, ends with trucks it genuinely does not need.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="41" t="inlineStr">
-        <is>
-          <t>Scenario 3.0.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="72" t="inlineStr">
-        <is>
-          <t>Year LIM-LD is 95.8% — already at or under the line. No adjustment needed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="41" t="inlineStr">
-        <is>
-          <t>Scenario 3.0.2</t>
-        </is>
+      <c r="D20" s="58" t="n">
+        <v>931</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="44" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="B21" s="44" t="inlineStr">
-        <is>
-          <t>LIM-LD before</t>
-        </is>
-      </c>
-      <c r="C21" s="44" t="inlineStr">
-        <is>
-          <t>LIM-LD after</t>
-        </is>
-      </c>
-      <c r="D21" s="44" t="inlineStr">
-        <is>
-          <t>Tonnes removed</t>
-        </is>
-      </c>
-      <c r="E21" s="44" t="inlineStr">
-        <is>
-          <t>DT freed</t>
-        </is>
-      </c>
-      <c r="F21" s="44" t="inlineStr">
-        <is>
-          <t>Kept working</t>
-        </is>
-      </c>
-      <c r="G21" s="44" t="inlineStr">
-        <is>
-          <t>Not needed</t>
-        </is>
-      </c>
-      <c r="H21" s="44" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
+      <c r="A21" s="67" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="B21" s="46" t="n">
+        <v>1280</v>
+      </c>
+      <c r="C21" s="53" t="n">
+        <v>36</v>
+      </c>
+      <c r="D21" s="58" t="n">
+        <v>1244</v>
       </c>
     </row>
     <row r="22">
@@ -2746,209 +2779,124 @@
           <t>Dec</t>
         </is>
       </c>
-      <c r="B22" s="70" t="n">
-        <v>1.200776731495626</v>
-      </c>
-      <c r="C22" s="50" t="n">
-        <v>1.086532089127519</v>
-      </c>
-      <c r="D22" s="46" t="n">
-        <v>225480</v>
-      </c>
-      <c r="E22" s="71" t="n">
-        <v>70</v>
-      </c>
-      <c r="F22" s="73" t="n">
-        <v>70</v>
-      </c>
-      <c r="G22" s="73" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="74" t="inlineStr">
-        <is>
-          <t>from RIM 61 DT + SMA 9 DT · stays above its own line, the YEAR is what lands on 100%</t>
-        </is>
+      <c r="B22" s="46" t="n">
+        <v>1281</v>
+      </c>
+      <c r="C22" s="53" t="n">
+        <v>37</v>
+      </c>
+      <c r="D22" s="58" t="n">
+        <v>1244</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="75" t="inlineStr">
         <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="D23" s="48" t="n">
-        <v>225480</v>
-      </c>
-      <c r="E23" s="71" t="n">
-        <v>70</v>
-      </c>
-      <c r="F23" s="73" t="n">
-        <v>70</v>
-      </c>
-      <c r="G23" s="73" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="76" t="inlineStr">
-        <is>
-          <t>year LIM-LD 103.0% -&gt; 100.0%</t>
-        </is>
+          <t>TOTAL parked</t>
+        </is>
+      </c>
+      <c r="C23" s="79" t="n">
+        <v>73</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="77" t="inlineStr">
-        <is>
-          <t>Where the kept trucks work — same SAP tonnage, longer haul</t>
-        </is>
-      </c>
+      <c r="A25" s="44" t="inlineStr">
+        <is>
+          <t>Sep–Dec year</t>
+        </is>
+      </c>
+      <c r="B25" s="44" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="C25" s="44" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D25" s="44" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="E25" s="44" t="inlineStr">
+        <is>
+          <t>Together</t>
+        </is>
+      </c>
+      <c r="F25" s="44" t="inlineStr"/>
+      <c r="G25" s="44" t="inlineStr"/>
+      <c r="H25" s="44" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="44" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="B26" s="44" t="inlineStr">
-        <is>
-          <t>Contractor</t>
-        </is>
-      </c>
-      <c r="C26" s="44" t="inlineStr">
-        <is>
-          <t>Moved from</t>
-        </is>
-      </c>
-      <c r="D26" s="44" t="inlineStr">
-        <is>
-          <t>Moved to</t>
-        </is>
-      </c>
-      <c r="E26" s="44" t="inlineStr">
-        <is>
-          <t>SAP t/day shifted</t>
-        </is>
-      </c>
-      <c r="F26" s="44" t="inlineStr">
-        <is>
-          <t>DT off</t>
-        </is>
-      </c>
-      <c r="G26" s="44" t="inlineStr">
-        <is>
-          <t>DT on</t>
-        </is>
-      </c>
-      <c r="H26" s="44" t="inlineStr">
-        <is>
-          <t>Extra DT used</t>
-        </is>
+      <c r="A26" s="67" t="inlineStr">
+        <is>
+          <t>Sales line t</t>
+        </is>
+      </c>
+      <c r="B26" s="46" t="n">
+        <v>5718685</v>
+      </c>
+      <c r="C26" s="46" t="n">
+        <v>3650201</v>
+      </c>
+      <c r="D26" s="46" t="n">
+        <v>7634306</v>
+      </c>
+      <c r="E26" s="48" t="n">
+        <v>17003192</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="45" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="B27" s="67" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C27" s="51" t="inlineStr">
-        <is>
-          <t>TF&gt;FENI KM15</t>
-        </is>
-      </c>
-      <c r="D27" s="56" t="inlineStr">
-        <is>
-          <t>TF&gt;FENI KM0</t>
-        </is>
-      </c>
-      <c r="E27" s="46" t="n">
-        <v>14384</v>
-      </c>
-      <c r="F27" s="78" t="n">
-        <v>136</v>
-      </c>
-      <c r="G27" s="73" t="n">
-        <v>183</v>
-      </c>
-      <c r="H27" s="58" t="n">
-        <v>47</v>
+      <c r="A27" s="67" t="inlineStr">
+        <is>
+          <t>Year predicted</t>
+        </is>
+      </c>
+      <c r="B27" s="48" t="n">
+        <v>5754365</v>
+      </c>
+      <c r="C27" s="48" t="n">
+        <v>3672447</v>
+      </c>
+      <c r="D27" s="48" t="n">
+        <v>7629845</v>
+      </c>
+      <c r="E27" s="48" t="n">
+        <v>17056657</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="45" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="B28" s="67" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C28" s="51" t="inlineStr">
-        <is>
-          <t>TF&gt;POS 12</t>
-        </is>
-      </c>
-      <c r="D28" s="56" t="inlineStr">
-        <is>
-          <t>TF&gt;FENI KM0</t>
-        </is>
-      </c>
-      <c r="E28" s="46" t="n">
-        <v>1992</v>
-      </c>
-      <c r="F28" s="78" t="n">
-        <v>18</v>
-      </c>
-      <c r="G28" s="73" t="n">
-        <v>32</v>
-      </c>
-      <c r="H28" s="58" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="45" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="B29" s="67" t="inlineStr">
-        <is>
-          <t>SMA</t>
-        </is>
-      </c>
-      <c r="C29" s="51" t="inlineStr">
-        <is>
-          <t>KR&gt;FENI KM15</t>
-        </is>
-      </c>
-      <c r="D29" s="56" t="inlineStr">
-        <is>
-          <t>KR&gt;FENI KM0</t>
-        </is>
-      </c>
-      <c r="E29" s="46" t="n">
-        <v>2563</v>
-      </c>
-      <c r="F29" s="78" t="n">
-        <v>16</v>
-      </c>
-      <c r="G29" s="73" t="n">
-        <v>25</v>
-      </c>
-      <c r="H29" s="58" t="n">
-        <v>9</v>
+      <c r="A28" s="67" t="inlineStr">
+        <is>
+          <t>YEAR % of target</t>
+        </is>
+      </c>
+      <c r="B28" s="50" t="n">
+        <v>1.006239196598519</v>
+      </c>
+      <c r="C28" s="50" t="n">
+        <v>1.006094458907879</v>
+      </c>
+      <c r="D28" s="50" t="n">
+        <v>0.9994156617947111</v>
+      </c>
+      <c r="E28" s="50" t="n">
+        <v>1.00314440861065</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="41" t="inlineStr">
+        <is>
+          <t>Scenario 3.1.1</t>
+        </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="41" t="inlineStr">
-        <is>
-          <t>Scenario 3.1.1</t>
+      <c r="A32" s="82" t="inlineStr">
+        <is>
+          <t>Fleet to own: 1239 DT, held every month.</t>
         </is>
       </c>
     </row>
@@ -2960,833 +2908,390 @@
       </c>
       <c r="B33" s="44" t="inlineStr">
         <is>
-          <t>LIM-LD before</t>
+          <t>Fleet available</t>
         </is>
       </c>
       <c r="C33" s="44" t="inlineStr">
         <is>
-          <t>LIM-LD after</t>
+          <t>PARKED</t>
         </is>
       </c>
       <c r="D33" s="44" t="inlineStr">
         <is>
-          <t>Tonnes removed</t>
-        </is>
-      </c>
-      <c r="E33" s="44" t="inlineStr">
-        <is>
-          <t>DT freed</t>
-        </is>
-      </c>
-      <c r="F33" s="44" t="inlineStr">
-        <is>
-          <t>Kept working</t>
-        </is>
-      </c>
-      <c r="G33" s="44" t="inlineStr">
-        <is>
-          <t>Not needed</t>
-        </is>
-      </c>
-      <c r="H33" s="44" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
+          <t>RUNNING</t>
+        </is>
+      </c>
+      <c r="E33" s="44" t="inlineStr"/>
+      <c r="F33" s="44" t="inlineStr"/>
+      <c r="G33" s="44" t="inlineStr"/>
+      <c r="H33" s="44" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="67" t="inlineStr">
         <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="B34" s="46" t="n">
+        <v>581</v>
+      </c>
+      <c r="C34" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="58" t="n">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="67" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="B35" s="46" t="n">
+        <v>931</v>
+      </c>
+      <c r="C35" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="58" t="n">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="67" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="B36" s="46" t="n">
+        <v>1280</v>
+      </c>
+      <c r="C36" s="53" t="n">
+        <v>41</v>
+      </c>
+      <c r="D36" s="58" t="n">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="67" t="inlineStr">
+        <is>
           <t>Dec</t>
         </is>
       </c>
-      <c r="B34" s="70" t="n">
-        <v>1.20840925422352</v>
-      </c>
-      <c r="C34" s="50" t="n">
-        <v>1.057795449860331</v>
-      </c>
-      <c r="D34" s="46" t="n">
-        <v>255500</v>
-      </c>
-      <c r="E34" s="71" t="n">
-        <v>79</v>
-      </c>
-      <c r="F34" s="73" t="n">
-        <v>79</v>
-      </c>
-      <c r="G34" s="73" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="74" t="inlineStr">
-        <is>
-          <t>from RIM 61 DT + SMA 18 DT · stays above its own line, the YEAR is what lands on 100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="75" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="D35" s="48" t="n">
-        <v>255500</v>
-      </c>
-      <c r="E35" s="71" t="n">
-        <v>79</v>
-      </c>
-      <c r="F35" s="73" t="n">
-        <v>79</v>
-      </c>
-      <c r="G35" s="73" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" s="76" t="inlineStr">
-        <is>
-          <t>year LIM-LD 103.9% -&gt; 100.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="77" t="inlineStr">
-        <is>
-          <t>Where the kept trucks work — same SAP tonnage, longer haul</t>
-        </is>
+      <c r="B37" s="46" t="n">
+        <v>1281</v>
+      </c>
+      <c r="C37" s="53" t="n">
+        <v>42</v>
+      </c>
+      <c r="D37" s="58" t="n">
+        <v>1239</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="44" t="inlineStr">
+      <c r="A38" s="75" t="inlineStr">
+        <is>
+          <t>TOTAL parked</t>
+        </is>
+      </c>
+      <c r="C38" s="79" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="44" t="inlineStr">
+        <is>
+          <t>Sep–Dec year</t>
+        </is>
+      </c>
+      <c r="B40" s="44" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="C40" s="44" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D40" s="44" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="E40" s="44" t="inlineStr">
+        <is>
+          <t>Together</t>
+        </is>
+      </c>
+      <c r="F40" s="44" t="inlineStr"/>
+      <c r="G40" s="44" t="inlineStr"/>
+      <c r="H40" s="44" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="67" t="inlineStr">
+        <is>
+          <t>Sales line t</t>
+        </is>
+      </c>
+      <c r="B41" s="46" t="n">
+        <v>5718685</v>
+      </c>
+      <c r="C41" s="46" t="n">
+        <v>4640202</v>
+      </c>
+      <c r="D41" s="46" t="n">
+        <v>6644306</v>
+      </c>
+      <c r="E41" s="48" t="n">
+        <v>17003193</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="67" t="inlineStr">
+        <is>
+          <t>Year predicted</t>
+        </is>
+      </c>
+      <c r="B42" s="48" t="n">
+        <v>5740906</v>
+      </c>
+      <c r="C42" s="48" t="n">
+        <v>4652858</v>
+      </c>
+      <c r="D42" s="48" t="n">
+        <v>6638903</v>
+      </c>
+      <c r="E42" s="48" t="n">
+        <v>17032667</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="67" t="inlineStr">
+        <is>
+          <t>YEAR % of target</t>
+        </is>
+      </c>
+      <c r="B43" s="50" t="n">
+        <v>1.003885683509408</v>
+      </c>
+      <c r="C43" s="50" t="n">
+        <v>1.002727467468011</v>
+      </c>
+      <c r="D43" s="50" t="n">
+        <v>0.9991867558336038</v>
+      </c>
+      <c r="E43" s="50" t="n">
+        <v>1.001733413065755</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="41" t="inlineStr">
+        <is>
+          <t>Scenario 3.1.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="82" t="inlineStr">
+        <is>
+          <t>Fleet to own: 1161 DT, held every month.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="44" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="B38" s="44" t="inlineStr">
-        <is>
-          <t>Contractor</t>
-        </is>
-      </c>
-      <c r="C38" s="44" t="inlineStr">
-        <is>
-          <t>Moved from</t>
-        </is>
-      </c>
-      <c r="D38" s="44" t="inlineStr">
-        <is>
-          <t>Moved to</t>
-        </is>
-      </c>
-      <c r="E38" s="44" t="inlineStr">
-        <is>
-          <t>SAP t/day shifted</t>
-        </is>
-      </c>
-      <c r="F38" s="44" t="inlineStr">
-        <is>
-          <t>DT off</t>
-        </is>
-      </c>
-      <c r="G38" s="44" t="inlineStr">
-        <is>
-          <t>DT on</t>
-        </is>
-      </c>
-      <c r="H38" s="44" t="inlineStr">
-        <is>
-          <t>Extra DT used</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="45" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="B39" s="67" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C39" s="51" t="inlineStr">
-        <is>
-          <t>TF&gt;FENI KM15</t>
-        </is>
-      </c>
-      <c r="D39" s="56" t="inlineStr">
-        <is>
-          <t>TF&gt;FENI KM0</t>
-        </is>
-      </c>
-      <c r="E39" s="46" t="n">
-        <v>14384</v>
-      </c>
-      <c r="F39" s="78" t="n">
-        <v>136</v>
-      </c>
-      <c r="G39" s="73" t="n">
-        <v>183</v>
-      </c>
-      <c r="H39" s="58" t="n">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="45" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="B40" s="67" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C40" s="51" t="inlineStr">
-        <is>
-          <t>TF&gt;POS 12</t>
-        </is>
-      </c>
-      <c r="D40" s="56" t="inlineStr">
-        <is>
-          <t>TF&gt;FENI KM0</t>
-        </is>
-      </c>
-      <c r="E40" s="46" t="n">
-        <v>1992</v>
-      </c>
-      <c r="F40" s="78" t="n">
-        <v>18</v>
-      </c>
-      <c r="G40" s="73" t="n">
-        <v>32</v>
-      </c>
-      <c r="H40" s="58" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="45" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="B41" s="67" t="inlineStr">
-        <is>
-          <t>SMA</t>
-        </is>
-      </c>
-      <c r="C41" s="51" t="inlineStr">
-        <is>
-          <t>KR&gt;FENI KM15</t>
-        </is>
-      </c>
-      <c r="D41" s="56" t="inlineStr">
-        <is>
-          <t>KR&gt;FENI KM0</t>
-        </is>
-      </c>
-      <c r="E41" s="46" t="n">
-        <v>5125</v>
-      </c>
-      <c r="F41" s="78" t="n">
-        <v>32</v>
-      </c>
-      <c r="G41" s="73" t="n">
-        <v>50</v>
-      </c>
-      <c r="H41" s="58" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="41" t="inlineStr">
-        <is>
-          <t>Scenario 3.1.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="44" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="B45" s="44" t="inlineStr">
-        <is>
-          <t>LIM-LD before</t>
-        </is>
-      </c>
-      <c r="C45" s="44" t="inlineStr">
-        <is>
-          <t>LIM-LD after</t>
-        </is>
-      </c>
-      <c r="D45" s="44" t="inlineStr">
-        <is>
-          <t>Tonnes removed</t>
-        </is>
-      </c>
-      <c r="E45" s="44" t="inlineStr">
-        <is>
-          <t>DT freed</t>
-        </is>
-      </c>
-      <c r="F45" s="44" t="inlineStr">
-        <is>
-          <t>Kept working</t>
-        </is>
-      </c>
-      <c r="G45" s="44" t="inlineStr">
-        <is>
-          <t>Not needed</t>
-        </is>
-      </c>
-      <c r="H45" s="44" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="67" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="B46" s="70" t="n">
-        <v>1.307911551155894</v>
-      </c>
-      <c r="C46" s="50" t="n">
-        <v>1.001860148915527</v>
-      </c>
-      <c r="D46" s="46" t="n">
-        <v>519183</v>
-      </c>
-      <c r="E46" s="71" t="n">
-        <v>161</v>
-      </c>
-      <c r="F46" s="73" t="n">
-        <v>94</v>
-      </c>
-      <c r="G46" s="79" t="n">
-        <v>67</v>
-      </c>
-      <c r="H46" s="74" t="inlineStr">
-        <is>
-          <t>from RIM 128 DT + SMA 33 DT · stays above its own line, the YEAR is what lands on 100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="67" t="inlineStr">
-        <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="B47" s="70" t="n">
-        <v>1.085941499180451</v>
-      </c>
-      <c r="C47" s="50" t="n">
-        <v>1.000181011689175</v>
-      </c>
-      <c r="D47" s="46" t="n">
-        <v>199032</v>
-      </c>
-      <c r="E47" s="71" t="n">
-        <v>64</v>
-      </c>
-      <c r="F47" s="73" t="n">
-        <v>60</v>
-      </c>
-      <c r="G47" s="79" t="n">
-        <v>4</v>
-      </c>
-      <c r="H47" s="74" t="inlineStr">
-        <is>
-          <t>from RIM 43 DT + SMA 21 DT · stays above its own line, the YEAR is what lands on 100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="67" t="inlineStr">
-        <is>
-          <t>Sep</t>
-        </is>
-      </c>
-      <c r="B48" s="70" t="n">
-        <v>1.013678484229764</v>
-      </c>
-      <c r="C48" s="50" t="n">
-        <v>1.002329219968693</v>
-      </c>
-      <c r="D48" s="46" t="n">
-        <v>9538</v>
-      </c>
-      <c r="E48" s="71" t="n">
-        <v>3</v>
-      </c>
-      <c r="F48" s="73" t="n">
-        <v>3</v>
-      </c>
-      <c r="G48" s="73" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" s="74" t="inlineStr">
-        <is>
-          <t>from RIM 3 DT · stays above its own line, the YEAR is what lands on 100%</t>
-        </is>
-      </c>
+      <c r="B48" s="44" t="inlineStr">
+        <is>
+          <t>Fleet available</t>
+        </is>
+      </c>
+      <c r="C48" s="44" t="inlineStr">
+        <is>
+          <t>PARKED</t>
+        </is>
+      </c>
+      <c r="D48" s="44" t="inlineStr">
+        <is>
+          <t>RUNNING</t>
+        </is>
+      </c>
+      <c r="E48" s="44" t="inlineStr"/>
+      <c r="F48" s="44" t="inlineStr"/>
+      <c r="G48" s="44" t="inlineStr"/>
+      <c r="H48" s="44" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="67" t="inlineStr">
         <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="B49" s="46" t="n">
+        <v>581</v>
+      </c>
+      <c r="C49" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" s="58" t="n">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="67" t="inlineStr">
+        <is>
           <t>Oct</t>
         </is>
       </c>
-      <c r="B49" s="70" t="n">
-        <v>1.012182364954908</v>
-      </c>
-      <c r="C49" s="50" t="n">
-        <v>1.001252870546001</v>
-      </c>
-      <c r="D49" s="46" t="n">
-        <v>19528</v>
-      </c>
-      <c r="E49" s="71" t="n">
-        <v>6</v>
-      </c>
-      <c r="F49" s="73" t="n">
-        <v>6</v>
-      </c>
-      <c r="G49" s="73" t="n">
+      <c r="B50" s="46" t="n">
+        <v>931</v>
+      </c>
+      <c r="C50" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="H49" s="74" t="inlineStr">
-        <is>
-          <t>from RIM 6 DT · stays above its own line, the YEAR is what lands on 100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="75" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="D50" s="48" t="n">
-        <v>747281</v>
-      </c>
-      <c r="E50" s="71" t="n">
-        <v>234</v>
-      </c>
-      <c r="F50" s="73" t="n">
-        <v>163</v>
-      </c>
-      <c r="G50" s="79" t="n">
-        <v>71</v>
-      </c>
-      <c r="H50" s="76" t="inlineStr">
-        <is>
-          <t>year LIM-LD 111.4% -&gt; 100.1%</t>
-        </is>
+      <c r="D50" s="58" t="n">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="67" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="B51" s="46" t="n">
+        <v>1280</v>
+      </c>
+      <c r="C51" s="53" t="n">
+        <v>119</v>
+      </c>
+      <c r="D51" s="58" t="n">
+        <v>1161</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="77" t="inlineStr">
-        <is>
-          <t>Where the kept trucks work — same SAP tonnage, longer haul</t>
-        </is>
+      <c r="A52" s="67" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="B52" s="46" t="n">
+        <v>1281</v>
+      </c>
+      <c r="C52" s="53" t="n">
+        <v>120</v>
+      </c>
+      <c r="D52" s="58" t="n">
+        <v>1161</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="44" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="B53" s="44" t="inlineStr">
-        <is>
-          <t>Contractor</t>
-        </is>
-      </c>
-      <c r="C53" s="44" t="inlineStr">
-        <is>
-          <t>Moved from</t>
-        </is>
-      </c>
-      <c r="D53" s="44" t="inlineStr">
-        <is>
-          <t>Moved to</t>
-        </is>
-      </c>
-      <c r="E53" s="44" t="inlineStr">
-        <is>
-          <t>SAP t/day shifted</t>
-        </is>
-      </c>
-      <c r="F53" s="44" t="inlineStr">
-        <is>
-          <t>DT off</t>
-        </is>
-      </c>
-      <c r="G53" s="44" t="inlineStr">
-        <is>
-          <t>DT on</t>
-        </is>
-      </c>
-      <c r="H53" s="44" t="inlineStr">
-        <is>
-          <t>Extra DT used</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="45" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="B54" s="67" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C54" s="51" t="inlineStr">
-        <is>
-          <t>TF&gt;FENI KM15</t>
-        </is>
-      </c>
-      <c r="D54" s="56" t="inlineStr">
-        <is>
-          <t>TF&gt;FENI KM0</t>
-        </is>
-      </c>
-      <c r="E54" s="46" t="n">
-        <v>14384</v>
-      </c>
-      <c r="F54" s="78" t="n">
-        <v>136</v>
-      </c>
-      <c r="G54" s="73" t="n">
-        <v>183</v>
-      </c>
-      <c r="H54" s="58" t="n">
-        <v>47</v>
+      <c r="A53" s="75" t="inlineStr">
+        <is>
+          <t>TOTAL parked</t>
+        </is>
+      </c>
+      <c r="C53" s="79" t="n">
+        <v>239</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="45" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="B55" s="67" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C55" s="51" t="inlineStr">
-        <is>
-          <t>TF&gt;POS 12</t>
-        </is>
-      </c>
-      <c r="D55" s="56" t="inlineStr">
-        <is>
-          <t>TF&gt;FENI KM0</t>
-        </is>
-      </c>
-      <c r="E55" s="46" t="n">
-        <v>1992</v>
-      </c>
-      <c r="F55" s="78" t="n">
-        <v>18</v>
-      </c>
-      <c r="G55" s="73" t="n">
-        <v>32</v>
-      </c>
-      <c r="H55" s="58" t="n">
-        <v>14</v>
-      </c>
+      <c r="A55" s="44" t="inlineStr">
+        <is>
+          <t>Sep–Dec year</t>
+        </is>
+      </c>
+      <c r="B55" s="44" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="C55" s="44" t="inlineStr">
+        <is>
+          <t>LIM-TOS</t>
+        </is>
+      </c>
+      <c r="D55" s="44" t="inlineStr">
+        <is>
+          <t>LIM-LD</t>
+        </is>
+      </c>
+      <c r="E55" s="44" t="inlineStr">
+        <is>
+          <t>Together</t>
+        </is>
+      </c>
+      <c r="F55" s="44" t="inlineStr"/>
+      <c r="G55" s="44" t="inlineStr"/>
+      <c r="H55" s="44" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="45" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="B56" s="67" t="inlineStr">
-        <is>
-          <t>SMA</t>
-        </is>
-      </c>
-      <c r="C56" s="51" t="inlineStr">
-        <is>
-          <t>KR&gt;FENI KM15</t>
-        </is>
-      </c>
-      <c r="D56" s="56" t="inlineStr">
-        <is>
-          <t>KR&gt;FENI KM0</t>
-        </is>
-      </c>
-      <c r="E56" s="46" t="n">
-        <v>7688</v>
-      </c>
-      <c r="F56" s="78" t="n">
-        <v>48</v>
-      </c>
-      <c r="G56" s="73" t="n">
-        <v>75</v>
-      </c>
-      <c r="H56" s="58" t="n">
-        <v>27</v>
+      <c r="A56" s="67" t="inlineStr">
+        <is>
+          <t>Sales line t</t>
+        </is>
+      </c>
+      <c r="B56" s="46" t="n">
+        <v>5718685</v>
+      </c>
+      <c r="C56" s="46" t="n">
+        <v>4640202</v>
+      </c>
+      <c r="D56" s="46" t="n">
+        <v>6644306</v>
+      </c>
+      <c r="E56" s="48" t="n">
+        <v>17003193</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="45" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="B57" s="67" t="inlineStr">
-        <is>
-          <t>SMA</t>
-        </is>
-      </c>
-      <c r="C57" s="51" t="inlineStr">
-        <is>
-          <t>KR&gt;POS 12</t>
-        </is>
-      </c>
-      <c r="D57" s="56" t="inlineStr">
-        <is>
-          <t>KR&gt;FENI KM0</t>
-        </is>
-      </c>
-      <c r="E57" s="46" t="n">
-        <v>1779</v>
-      </c>
-      <c r="F57" s="78" t="n">
-        <v>9</v>
-      </c>
-      <c r="G57" s="73" t="n">
-        <v>15</v>
-      </c>
-      <c r="H57" s="58" t="n">
-        <v>6</v>
+      <c r="A57" s="67" t="inlineStr">
+        <is>
+          <t>Year predicted</t>
+        </is>
+      </c>
+      <c r="B57" s="48" t="n">
+        <v>5753327</v>
+      </c>
+      <c r="C57" s="48" t="n">
+        <v>4658887</v>
+      </c>
+      <c r="D57" s="48" t="n">
+        <v>6643492</v>
+      </c>
+      <c r="E57" s="48" t="n">
+        <v>17055706</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="45" t="inlineStr">
-        <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="B58" s="67" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C58" s="51" t="inlineStr">
-        <is>
-          <t>TF&gt;FENI KM15</t>
-        </is>
-      </c>
-      <c r="D58" s="56" t="inlineStr">
-        <is>
-          <t>TF&gt;FENI KM0</t>
-        </is>
-      </c>
-      <c r="E58" s="46" t="n">
-        <v>7651</v>
-      </c>
-      <c r="F58" s="78" t="n">
-        <v>73</v>
-      </c>
-      <c r="G58" s="73" t="n">
-        <v>98</v>
-      </c>
-      <c r="H58" s="58" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="45" t="inlineStr">
-        <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="B59" s="67" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C59" s="51" t="inlineStr">
-        <is>
-          <t>TF&gt;POS 12</t>
-        </is>
-      </c>
-      <c r="D59" s="56" t="inlineStr">
-        <is>
-          <t>TF&gt;FENI KM0</t>
-        </is>
-      </c>
-      <c r="E59" s="46" t="n">
-        <v>1992</v>
-      </c>
-      <c r="F59" s="78" t="n">
-        <v>18</v>
-      </c>
-      <c r="G59" s="73" t="n">
-        <v>32</v>
-      </c>
-      <c r="H59" s="58" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="45" t="inlineStr">
-        <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="B60" s="67" t="inlineStr">
-        <is>
-          <t>SMA</t>
-        </is>
-      </c>
-      <c r="C60" s="51" t="inlineStr">
-        <is>
-          <t>KR&gt;FENI KM15</t>
-        </is>
-      </c>
-      <c r="D60" s="56" t="inlineStr">
-        <is>
-          <t>KR&gt;FENI KM0</t>
-        </is>
-      </c>
-      <c r="E60" s="46" t="n">
-        <v>3986</v>
-      </c>
-      <c r="F60" s="78" t="n">
-        <v>25</v>
-      </c>
-      <c r="G60" s="73" t="n">
-        <v>39</v>
-      </c>
-      <c r="H60" s="58" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="45" t="inlineStr">
-        <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="B61" s="67" t="inlineStr">
-        <is>
-          <t>SMA</t>
-        </is>
-      </c>
-      <c r="C61" s="51" t="inlineStr">
-        <is>
-          <t>KR&gt;POS 12</t>
-        </is>
-      </c>
-      <c r="D61" s="56" t="inlineStr">
-        <is>
-          <t>KR&gt;FENI KM0</t>
-        </is>
-      </c>
-      <c r="E61" s="46" t="n">
-        <v>2075</v>
-      </c>
-      <c r="F61" s="78" t="n">
-        <v>10</v>
-      </c>
-      <c r="G61" s="73" t="n">
-        <v>17</v>
-      </c>
-      <c r="H61" s="58" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="45" t="inlineStr">
-        <is>
-          <t>Sep</t>
-        </is>
-      </c>
-      <c r="B62" s="67" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C62" s="51" t="inlineStr">
-        <is>
-          <t>TF&gt;FENI KM15</t>
-        </is>
-      </c>
-      <c r="D62" s="56" t="inlineStr">
-        <is>
-          <t>TF&gt;FENI KM0</t>
-        </is>
-      </c>
-      <c r="E62" s="46" t="n">
-        <v>918</v>
-      </c>
-      <c r="F62" s="78" t="n">
-        <v>9</v>
-      </c>
-      <c r="G62" s="73" t="n">
-        <v>12</v>
-      </c>
-      <c r="H62" s="58" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="45" t="inlineStr">
-        <is>
-          <t>Oct</t>
-        </is>
-      </c>
-      <c r="B63" s="67" t="inlineStr">
-        <is>
-          <t>RIM</t>
-        </is>
-      </c>
-      <c r="C63" s="51" t="inlineStr">
-        <is>
-          <t>TF&gt;FENI KM15</t>
-        </is>
-      </c>
-      <c r="D63" s="56" t="inlineStr">
-        <is>
-          <t>TF&gt;FENI KM0</t>
-        </is>
-      </c>
-      <c r="E63" s="46" t="n">
-        <v>1836</v>
-      </c>
-      <c r="F63" s="78" t="n">
-        <v>17</v>
-      </c>
-      <c r="G63" s="73" t="n">
-        <v>23</v>
-      </c>
-      <c r="H63" s="58" t="n">
-        <v>6</v>
+      <c r="A58" s="67" t="inlineStr">
+        <is>
+          <t>YEAR % of target</t>
+        </is>
+      </c>
+      <c r="B58" s="50" t="n">
+        <v>1.00605768633873</v>
+      </c>
+      <c r="C58" s="50" t="n">
+        <v>1.004026764352069</v>
+      </c>
+      <c r="D58" s="50" t="n">
+        <v>0.999877543964426</v>
+      </c>
+      <c r="E58" s="50" t="n">
+        <v>1.003088441366754</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="2">
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A5:H5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
